--- a/artfynd/A 28940-2026 artfynd.xlsx
+++ b/artfynd/A 28940-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY34"/>
+  <dimension ref="A1:AY96"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -966,10 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128346578</v>
+        <v>135192063</v>
       </c>
       <c r="B5" t="n">
-        <v>91909</v>
+        <v>89354</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -977,34 +977,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>510</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Höbrännflon sö, Jmt</t>
+          <t>Höbrännflon, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>469082</v>
+        <v>469031</v>
       </c>
       <c r="R5" t="n">
-        <v>7078001</v>
+        <v>7078166</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1031,12 +1031,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-09-09</t>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-09-09</t>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1063,10 +1073,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128346633</v>
+        <v>135192175</v>
       </c>
       <c r="B6" t="n">
-        <v>91923</v>
+        <v>92546</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1074,34 +1084,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1204</v>
+        <v>760</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Höbrännflon sö, Jmt</t>
+          <t>Höbrännflon, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>469137</v>
+        <v>469206</v>
       </c>
       <c r="R6" t="n">
-        <v>7078055</v>
+        <v>7078077</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1128,12 +1138,22 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-09-09</t>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-09-09</t>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1160,10 +1180,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128346632</v>
+        <v>135192051</v>
       </c>
       <c r="B7" t="n">
-        <v>80432</v>
+        <v>91970</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1171,34 +1191,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>1108</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Höbrännflon sö, Jmt</t>
+          <t>Höbrännflon, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>468909</v>
+        <v>468905</v>
       </c>
       <c r="R7" t="n">
-        <v>7077971</v>
+        <v>7078357</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1225,12 +1245,22 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-09-09</t>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-09-09</t>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1257,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128346579</v>
+        <v>128346578</v>
       </c>
       <c r="B8" t="n">
-        <v>57953</v>
+        <v>91909</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1268,21 +1298,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1292,10 +1322,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>469196</v>
+        <v>469082</v>
       </c>
       <c r="R8" t="n">
-        <v>7077970</v>
+        <v>7078001</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1328,11 +1358,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-09-09</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1359,32 +1384,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128346580</v>
+        <v>128346633</v>
       </c>
       <c r="B9" t="n">
-        <v>57953</v>
+        <v>91923</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>1204</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1394,10 +1419,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>469066</v>
+        <v>469137</v>
       </c>
       <c r="R9" t="n">
-        <v>7077948</v>
+        <v>7078055</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1430,11 +1455,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-09-09</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1461,45 +1481,45 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128346581</v>
+        <v>135192023</v>
       </c>
       <c r="B10" t="n">
-        <v>57953</v>
+        <v>79373</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Höbrännflon sö, Jmt</t>
+          <t>Höbrännflon, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>468873</v>
+        <v>469151</v>
       </c>
       <c r="R10" t="n">
-        <v>7077929</v>
+        <v>7078176</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1526,17 +1546,27 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-09-09</t>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>09:31</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2025-09-09</t>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>09:31</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1563,45 +1593,45 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128346582</v>
+        <v>135192025</v>
       </c>
       <c r="B11" t="n">
-        <v>57953</v>
+        <v>79373</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Höbrännflon sö, Jmt</t>
+          <t>Höbrännflon, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>468940</v>
+        <v>469160</v>
       </c>
       <c r="R11" t="n">
-        <v>7077734</v>
+        <v>7078154</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1628,17 +1658,27 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-09-09</t>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>09:36</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2025-09-09</t>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>09:36</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1665,45 +1705,45 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128346583</v>
+        <v>135192028</v>
       </c>
       <c r="B12" t="n">
-        <v>57953</v>
+        <v>79373</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Höbrännflon sö, Jmt</t>
+          <t>Höbrännflon, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>468969</v>
+        <v>469195</v>
       </c>
       <c r="R12" t="n">
-        <v>7077711</v>
+        <v>7078100</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1730,17 +1770,27 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-09-09</t>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2025-09-09</t>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1767,45 +1817,45 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128346585</v>
+        <v>135192031</v>
       </c>
       <c r="B13" t="n">
-        <v>57953</v>
+        <v>79373</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Höbrännflon sö, Jmt</t>
+          <t>Höbrännflon, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>468968</v>
+        <v>469158</v>
       </c>
       <c r="R13" t="n">
-        <v>7077679</v>
+        <v>7078106</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1832,17 +1882,27 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-09-09</t>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2025-09-09</t>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1869,45 +1929,45 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128346586</v>
+        <v>135192033</v>
       </c>
       <c r="B14" t="n">
-        <v>57953</v>
+        <v>79373</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Höbrännflon sö, Jmt</t>
+          <t>Höbrännflon, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>468984</v>
+        <v>469111</v>
       </c>
       <c r="R14" t="n">
-        <v>7077636</v>
+        <v>7078095</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1934,17 +1994,27 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-09-09</t>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>09:53</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2025-09-09</t>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>09:53</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -1971,45 +2041,45 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128346607</v>
+        <v>135192036</v>
       </c>
       <c r="B15" t="n">
-        <v>57953</v>
+        <v>79373</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Höbrännflon sö, Jmt</t>
+          <t>Höbrännflon, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>468839</v>
+        <v>469089</v>
       </c>
       <c r="R15" t="n">
-        <v>7077932</v>
+        <v>7078197</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2036,17 +2106,27 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-09-09</t>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2025-09-09</t>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2073,45 +2153,45 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128346608</v>
+        <v>135192038</v>
       </c>
       <c r="B16" t="n">
-        <v>57953</v>
+        <v>79373</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Höbrännflon sö, Jmt</t>
+          <t>Höbrännflon, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>468870</v>
+        <v>469078</v>
       </c>
       <c r="R16" t="n">
-        <v>7077959</v>
+        <v>7078215</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2138,17 +2218,27 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-09-09</t>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2025-09-09</t>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2175,45 +2265,45 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128346609</v>
+        <v>135192040</v>
       </c>
       <c r="B17" t="n">
-        <v>57953</v>
+        <v>79373</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Höbrännflon sö, Jmt</t>
+          <t>Höbrännflon, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>468906</v>
+        <v>469055</v>
       </c>
       <c r="R17" t="n">
-        <v>7077980</v>
+        <v>7078251</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2240,17 +2330,27 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-09-09</t>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2025-09-09</t>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2277,45 +2377,45 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128346610</v>
+        <v>135192041</v>
       </c>
       <c r="B18" t="n">
-        <v>57953</v>
+        <v>79373</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Höbrännflon sö, Jmt</t>
+          <t>Höbrännflon, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>468891</v>
+        <v>469057</v>
       </c>
       <c r="R18" t="n">
-        <v>7077967</v>
+        <v>7078295</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2342,17 +2442,27 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-09-09</t>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2025-09-09</t>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Ringhack färska 2 träd</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2379,45 +2489,45 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128346611</v>
+        <v>135192043</v>
       </c>
       <c r="B19" t="n">
-        <v>57953</v>
+        <v>79373</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Höbrännflon sö, Jmt</t>
+          <t>Höbrännflon, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>468913</v>
+        <v>469004</v>
       </c>
       <c r="R19" t="n">
-        <v>7077967</v>
+        <v>7078286</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2444,17 +2554,27 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-09-09</t>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2025-09-09</t>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2481,45 +2601,45 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128346612</v>
+        <v>135192053</v>
       </c>
       <c r="B20" t="n">
-        <v>57953</v>
+        <v>79373</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Höbrännflon sö, Jmt</t>
+          <t>Höbrännflon, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>468917</v>
+        <v>468898</v>
       </c>
       <c r="R20" t="n">
-        <v>7077967</v>
+        <v>7078332</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2546,17 +2666,27 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-09-09</t>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2025-09-09</t>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2583,45 +2713,45 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128346613</v>
+        <v>135192055</v>
       </c>
       <c r="B21" t="n">
-        <v>57953</v>
+        <v>79373</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Höbrännflon sö, Jmt</t>
+          <t>Höbrännflon, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>468925</v>
+        <v>468928</v>
       </c>
       <c r="R21" t="n">
-        <v>7077966</v>
+        <v>7078320</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2648,17 +2778,27 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-09-09</t>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2025-09-09</t>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2685,45 +2825,45 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128346614</v>
+        <v>135192059</v>
       </c>
       <c r="B22" t="n">
-        <v>57953</v>
+        <v>79373</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Höbrännflon sö, Jmt</t>
+          <t>Höbrännflon, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>468931</v>
+        <v>468977</v>
       </c>
       <c r="R22" t="n">
-        <v>7077965</v>
+        <v>7078269</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2750,17 +2890,27 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-09-09</t>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2025-09-09</t>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2787,45 +2937,45 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128346615</v>
+        <v>135192065</v>
       </c>
       <c r="B23" t="n">
-        <v>57953</v>
+        <v>79373</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Höbrännflon sö, Jmt</t>
+          <t>Höbrännflon, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>468940</v>
+        <v>469039</v>
       </c>
       <c r="R23" t="n">
-        <v>7077960</v>
+        <v>7078146</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2852,17 +3002,27 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-09-09</t>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2025-09-09</t>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2889,45 +3049,45 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128346616</v>
+        <v>135192069</v>
       </c>
       <c r="B24" t="n">
-        <v>57953</v>
+        <v>79373</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Höbrännflon sö, Jmt</t>
+          <t>Höbrännflon, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>468979</v>
+        <v>469072</v>
       </c>
       <c r="R24" t="n">
-        <v>7077962</v>
+        <v>7078093</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2954,17 +3114,27 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2025-09-09</t>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2025-09-09</t>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -2991,45 +3161,45 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128346617</v>
+        <v>135192110</v>
       </c>
       <c r="B25" t="n">
-        <v>57953</v>
+        <v>79373</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Höbrännflon sö, Jmt</t>
+          <t>Höbrännflon, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>468994</v>
+        <v>469052</v>
       </c>
       <c r="R25" t="n">
-        <v>7077960</v>
+        <v>7077724</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3056,17 +3226,27 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2025-09-09</t>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2025-09-09</t>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3093,45 +3273,45 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128346618</v>
+        <v>135192141</v>
       </c>
       <c r="B26" t="n">
-        <v>57953</v>
+        <v>79373</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Höbrännflon sö, Jmt</t>
+          <t>Höbrännflon, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>469012</v>
+        <v>469190</v>
       </c>
       <c r="R26" t="n">
-        <v>7077965</v>
+        <v>7077923</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3158,17 +3338,27 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2025-09-09</t>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2025-09-09</t>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3195,45 +3385,45 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128346619</v>
+        <v>135192145</v>
       </c>
       <c r="B27" t="n">
-        <v>57953</v>
+        <v>79373</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Höbrännflon sö, Jmt</t>
+          <t>Höbrännflon, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>469014</v>
+        <v>469302</v>
       </c>
       <c r="R27" t="n">
-        <v>7077963</v>
+        <v>7077879</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3260,17 +3450,27 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2025-09-09</t>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2025-09-09</t>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3297,45 +3497,45 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128346620</v>
+        <v>135192148</v>
       </c>
       <c r="B28" t="n">
-        <v>57953</v>
+        <v>79373</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Höbrännflon sö, Jmt</t>
+          <t>Höbrännflon, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>469031</v>
+        <v>469354</v>
       </c>
       <c r="R28" t="n">
-        <v>7077964</v>
+        <v>7077833</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3362,17 +3562,27 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2025-09-09</t>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2025-09-09</t>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3399,45 +3609,45 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128346621</v>
+        <v>135192171</v>
       </c>
       <c r="B29" t="n">
-        <v>57953</v>
+        <v>79373</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Höbrännflon sö, Jmt</t>
+          <t>Höbrännflon, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>469043</v>
+        <v>469197</v>
       </c>
       <c r="R29" t="n">
-        <v>7077965</v>
+        <v>7078034</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3464,17 +3674,27 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2025-09-09</t>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2025-09-09</t>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3501,10 +3721,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128346622</v>
+        <v>128346632</v>
       </c>
       <c r="B30" t="n">
-        <v>57953</v>
+        <v>80432</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3512,21 +3732,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3536,10 +3756,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>469052</v>
+        <v>468909</v>
       </c>
       <c r="R30" t="n">
-        <v>7077969</v>
+        <v>7077971</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3572,11 +3792,6 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-09-09</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3603,27 +3818,27 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128346623</v>
+        <v>135192073</v>
       </c>
       <c r="B31" t="n">
-        <v>57953</v>
+        <v>57972</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -3631,17 +3846,33 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I31" t="inlineStr"/>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Höbrännflon sö, Jmt</t>
+          <t>Höbrännflon, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>469057</v>
+        <v>469093</v>
       </c>
       <c r="R31" t="n">
-        <v>7077970</v>
+        <v>7078018</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3668,17 +3899,22 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2025-09-09</t>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2025-09-09</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Ringhack färska</t>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3705,7 +3941,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128346624</v>
+        <v>128346579</v>
       </c>
       <c r="B32" t="n">
         <v>57953</v>
@@ -3740,10 +3976,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>469057</v>
+        <v>469196</v>
       </c>
       <c r="R32" t="n">
-        <v>7077968</v>
+        <v>7077970</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3780,7 +4016,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3807,7 +4043,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128346625</v>
+        <v>128346580</v>
       </c>
       <c r="B33" t="n">
         <v>57953</v>
@@ -3842,10 +4078,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>469169</v>
+        <v>469066</v>
       </c>
       <c r="R33" t="n">
-        <v>7078067</v>
+        <v>7077948</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3909,32 +4145,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128346628</v>
+        <v>128346581</v>
       </c>
       <c r="B34" t="n">
-        <v>97989</v>
+        <v>57953</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>221941</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3944,10 +4180,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>468931</v>
+        <v>468873</v>
       </c>
       <c r="R34" t="n">
-        <v>7077743</v>
+        <v>7077929</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3982,6 +4218,11 @@
           <t>2025-09-09</t>
         </is>
       </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
+        </is>
+      </c>
       <c r="AD34" t="b">
         <v>0</v>
       </c>
@@ -4003,6 +4244,6885 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>128346582</v>
+      </c>
+      <c r="B35" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Höbrännflon sö, Jmt</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>468940</v>
+      </c>
+      <c r="R35" t="n">
+        <v>7077734</v>
+      </c>
+      <c r="S35" t="n">
+        <v>10</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>128346583</v>
+      </c>
+      <c r="B36" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Höbrännflon sö, Jmt</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>468969</v>
+      </c>
+      <c r="R36" t="n">
+        <v>7077711</v>
+      </c>
+      <c r="S36" t="n">
+        <v>10</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>128346585</v>
+      </c>
+      <c r="B37" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Höbrännflon sö, Jmt</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>468968</v>
+      </c>
+      <c r="R37" t="n">
+        <v>7077679</v>
+      </c>
+      <c r="S37" t="n">
+        <v>10</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>128346586</v>
+      </c>
+      <c r="B38" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Höbrännflon sö, Jmt</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>468984</v>
+      </c>
+      <c r="R38" t="n">
+        <v>7077636</v>
+      </c>
+      <c r="S38" t="n">
+        <v>10</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>128346607</v>
+      </c>
+      <c r="B39" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Höbrännflon sö, Jmt</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>468839</v>
+      </c>
+      <c r="R39" t="n">
+        <v>7077932</v>
+      </c>
+      <c r="S39" t="n">
+        <v>10</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>128346608</v>
+      </c>
+      <c r="B40" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Höbrännflon sö, Jmt</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>468870</v>
+      </c>
+      <c r="R40" t="n">
+        <v>7077959</v>
+      </c>
+      <c r="S40" t="n">
+        <v>10</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>128346609</v>
+      </c>
+      <c r="B41" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Höbrännflon sö, Jmt</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>468906</v>
+      </c>
+      <c r="R41" t="n">
+        <v>7077980</v>
+      </c>
+      <c r="S41" t="n">
+        <v>10</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>128346610</v>
+      </c>
+      <c r="B42" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Höbrännflon sö, Jmt</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>468891</v>
+      </c>
+      <c r="R42" t="n">
+        <v>7077967</v>
+      </c>
+      <c r="S42" t="n">
+        <v>10</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Ringhack färska 2 träd</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>128346611</v>
+      </c>
+      <c r="B43" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Höbrännflon sö, Jmt</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>468913</v>
+      </c>
+      <c r="R43" t="n">
+        <v>7077967</v>
+      </c>
+      <c r="S43" t="n">
+        <v>10</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>128346612</v>
+      </c>
+      <c r="B44" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Höbrännflon sö, Jmt</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>468917</v>
+      </c>
+      <c r="R44" t="n">
+        <v>7077967</v>
+      </c>
+      <c r="S44" t="n">
+        <v>10</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>128346613</v>
+      </c>
+      <c r="B45" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Höbrännflon sö, Jmt</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>468925</v>
+      </c>
+      <c r="R45" t="n">
+        <v>7077966</v>
+      </c>
+      <c r="S45" t="n">
+        <v>10</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>128346614</v>
+      </c>
+      <c r="B46" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Höbrännflon sö, Jmt</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>468931</v>
+      </c>
+      <c r="R46" t="n">
+        <v>7077965</v>
+      </c>
+      <c r="S46" t="n">
+        <v>10</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>128346615</v>
+      </c>
+      <c r="B47" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Höbrännflon sö, Jmt</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>468940</v>
+      </c>
+      <c r="R47" t="n">
+        <v>7077960</v>
+      </c>
+      <c r="S47" t="n">
+        <v>10</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>128346616</v>
+      </c>
+      <c r="B48" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Höbrännflon sö, Jmt</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>468979</v>
+      </c>
+      <c r="R48" t="n">
+        <v>7077962</v>
+      </c>
+      <c r="S48" t="n">
+        <v>10</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>128346617</v>
+      </c>
+      <c r="B49" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Höbrännflon sö, Jmt</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>468994</v>
+      </c>
+      <c r="R49" t="n">
+        <v>7077960</v>
+      </c>
+      <c r="S49" t="n">
+        <v>10</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>128346618</v>
+      </c>
+      <c r="B50" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Höbrännflon sö, Jmt</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>469012</v>
+      </c>
+      <c r="R50" t="n">
+        <v>7077965</v>
+      </c>
+      <c r="S50" t="n">
+        <v>10</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>128346619</v>
+      </c>
+      <c r="B51" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Höbrännflon sö, Jmt</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>469014</v>
+      </c>
+      <c r="R51" t="n">
+        <v>7077963</v>
+      </c>
+      <c r="S51" t="n">
+        <v>10</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
+        </is>
+      </c>
+      <c r="AD51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>128346620</v>
+      </c>
+      <c r="B52" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Höbrännflon sö, Jmt</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>469031</v>
+      </c>
+      <c r="R52" t="n">
+        <v>7077964</v>
+      </c>
+      <c r="S52" t="n">
+        <v>10</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
+        </is>
+      </c>
+      <c r="AD52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>128346621</v>
+      </c>
+      <c r="B53" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>Höbrännflon sö, Jmt</t>
+        </is>
+      </c>
+      <c r="Q53" t="n">
+        <v>469043</v>
+      </c>
+      <c r="R53" t="n">
+        <v>7077965</v>
+      </c>
+      <c r="S53" t="n">
+        <v>10</v>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
+        </is>
+      </c>
+      <c r="AD53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT53" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>128346622</v>
+      </c>
+      <c r="B54" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>Höbrännflon sö, Jmt</t>
+        </is>
+      </c>
+      <c r="Q54" t="n">
+        <v>469052</v>
+      </c>
+      <c r="R54" t="n">
+        <v>7077969</v>
+      </c>
+      <c r="S54" t="n">
+        <v>10</v>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
+        </is>
+      </c>
+      <c r="AD54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT54" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>128346623</v>
+      </c>
+      <c r="B55" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>Höbrännflon sö, Jmt</t>
+        </is>
+      </c>
+      <c r="Q55" t="n">
+        <v>469057</v>
+      </c>
+      <c r="R55" t="n">
+        <v>7077970</v>
+      </c>
+      <c r="S55" t="n">
+        <v>10</v>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
+        </is>
+      </c>
+      <c r="AD55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT55" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX55" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>128346624</v>
+      </c>
+      <c r="B56" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>Höbrännflon sö, Jmt</t>
+        </is>
+      </c>
+      <c r="Q56" t="n">
+        <v>469057</v>
+      </c>
+      <c r="R56" t="n">
+        <v>7077968</v>
+      </c>
+      <c r="S56" t="n">
+        <v>10</v>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
+        </is>
+      </c>
+      <c r="AD56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT56" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>128346625</v>
+      </c>
+      <c r="B57" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>Höbrännflon sö, Jmt</t>
+        </is>
+      </c>
+      <c r="Q57" t="n">
+        <v>469169</v>
+      </c>
+      <c r="R57" t="n">
+        <v>7078067</v>
+      </c>
+      <c r="S57" t="n">
+        <v>10</v>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
+      <c r="AD57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT57" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX57" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>135192022</v>
+      </c>
+      <c r="B58" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>Höbrännflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q58" t="n">
+        <v>469168</v>
+      </c>
+      <c r="R58" t="n">
+        <v>7078178</v>
+      </c>
+      <c r="S58" t="n">
+        <v>10</v>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="Z58" t="inlineStr">
+        <is>
+          <t>09:29</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="AB58" t="inlineStr">
+        <is>
+          <t>09:29</t>
+        </is>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>äldre ringhack</t>
+        </is>
+      </c>
+      <c r="AD58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT58" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX58" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>135192026</v>
+      </c>
+      <c r="B59" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>Höbrännflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q59" t="n">
+        <v>469186</v>
+      </c>
+      <c r="R59" t="n">
+        <v>7078140</v>
+      </c>
+      <c r="S59" t="n">
+        <v>10</v>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="Z59" t="inlineStr">
+        <is>
+          <t>09:38</t>
+        </is>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="AB59" t="inlineStr">
+        <is>
+          <t>09:38</t>
+        </is>
+      </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>äldre ringhack</t>
+        </is>
+      </c>
+      <c r="AD59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT59" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX59" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>135192030</v>
+      </c>
+      <c r="B60" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>Höbrännflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q60" t="n">
+        <v>469177</v>
+      </c>
+      <c r="R60" t="n">
+        <v>7078094</v>
+      </c>
+      <c r="S60" t="n">
+        <v>10</v>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="Z60" t="inlineStr">
+        <is>
+          <t>09:48</t>
+        </is>
+      </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="AB60" t="inlineStr">
+        <is>
+          <t>09:48</t>
+        </is>
+      </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>äldre ringhack</t>
+        </is>
+      </c>
+      <c r="AD60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT60" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX60" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>135192045</v>
+      </c>
+      <c r="B61" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>Höbrännflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q61" t="n">
+        <v>468993</v>
+      </c>
+      <c r="R61" t="n">
+        <v>7078287</v>
+      </c>
+      <c r="S61" t="n">
+        <v>10</v>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y61" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="Z61" t="inlineStr">
+        <is>
+          <t>10:18</t>
+        </is>
+      </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="AB61" t="inlineStr">
+        <is>
+          <t>10:18</t>
+        </is>
+      </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>ringhack</t>
+        </is>
+      </c>
+      <c r="AD61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT61" t="inlineStr"/>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX61" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>135192047</v>
+      </c>
+      <c r="B62" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>Höbrännflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q62" t="n">
+        <v>468901</v>
+      </c>
+      <c r="R62" t="n">
+        <v>7078371</v>
+      </c>
+      <c r="S62" t="n">
+        <v>10</v>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="Z62" t="inlineStr">
+        <is>
+          <t>10:25</t>
+        </is>
+      </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="AB62" t="inlineStr">
+        <is>
+          <t>10:25</t>
+        </is>
+      </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>äldre ringhack</t>
+        </is>
+      </c>
+      <c r="AD62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT62" t="inlineStr"/>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX62" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>135192048</v>
+      </c>
+      <c r="B63" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>Höbrännflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q63" t="n">
+        <v>468891</v>
+      </c>
+      <c r="R63" t="n">
+        <v>7078390</v>
+      </c>
+      <c r="S63" t="n">
+        <v>10</v>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="Z63" t="inlineStr">
+        <is>
+          <t>10:28</t>
+        </is>
+      </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="AB63" t="inlineStr">
+        <is>
+          <t>10:28</t>
+        </is>
+      </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>färska o och äldre ringhack</t>
+        </is>
+      </c>
+      <c r="AD63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT63" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX63" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>135192050</v>
+      </c>
+      <c r="B64" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>Höbrännflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q64" t="n">
+        <v>468864</v>
+      </c>
+      <c r="R64" t="n">
+        <v>7078369</v>
+      </c>
+      <c r="S64" t="n">
+        <v>10</v>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="Z64" t="inlineStr">
+        <is>
+          <t>10:31</t>
+        </is>
+      </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="AB64" t="inlineStr">
+        <is>
+          <t>10:31</t>
+        </is>
+      </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>färska och äldre ringhack</t>
+        </is>
+      </c>
+      <c r="AD64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT64" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX64" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY64" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>135192056</v>
+      </c>
+      <c r="B65" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>Höbrännflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q65" t="n">
+        <v>468923</v>
+      </c>
+      <c r="R65" t="n">
+        <v>7078311</v>
+      </c>
+      <c r="S65" t="n">
+        <v>10</v>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y65" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="Z65" t="inlineStr">
+        <is>
+          <t>10:37</t>
+        </is>
+      </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="AB65" t="inlineStr">
+        <is>
+          <t>10:37</t>
+        </is>
+      </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>äldre ringhack</t>
+        </is>
+      </c>
+      <c r="AD65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT65" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX65" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY65" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>135192074</v>
+      </c>
+      <c r="B66" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>Höbrännflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q66" t="n">
+        <v>469051</v>
+      </c>
+      <c r="R66" t="n">
+        <v>7077912</v>
+      </c>
+      <c r="S66" t="n">
+        <v>10</v>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W66" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y66" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="Z66" t="inlineStr">
+        <is>
+          <t>11:05</t>
+        </is>
+      </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="AB66" t="inlineStr">
+        <is>
+          <t>11:05</t>
+        </is>
+      </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>äldre ringhack</t>
+        </is>
+      </c>
+      <c r="AD66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT66" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX66" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY66" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>135192077</v>
+      </c>
+      <c r="B67" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>Höbrännflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q67" t="n">
+        <v>469002</v>
+      </c>
+      <c r="R67" t="n">
+        <v>7077895</v>
+      </c>
+      <c r="S67" t="n">
+        <v>10</v>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W67" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y67" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="Z67" t="inlineStr">
+        <is>
+          <t>11:09</t>
+        </is>
+      </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="AB67" t="inlineStr">
+        <is>
+          <t>11:09</t>
+        </is>
+      </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>äldre ringhack</t>
+        </is>
+      </c>
+      <c r="AD67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT67" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX67" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY67" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>135192079</v>
+      </c>
+      <c r="B68" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr"/>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>Höbrännflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q68" t="n">
+        <v>469028</v>
+      </c>
+      <c r="R68" t="n">
+        <v>7077856</v>
+      </c>
+      <c r="S68" t="n">
+        <v>10</v>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W68" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y68" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="Z68" t="inlineStr">
+        <is>
+          <t>11:12</t>
+        </is>
+      </c>
+      <c r="AA68" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="AB68" t="inlineStr">
+        <is>
+          <t>11:12</t>
+        </is>
+      </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>äldre ringhack</t>
+        </is>
+      </c>
+      <c r="AD68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT68" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX68" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY68" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>135192085</v>
+      </c>
+      <c r="B69" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>Höbrännflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q69" t="n">
+        <v>468941</v>
+      </c>
+      <c r="R69" t="n">
+        <v>7077921</v>
+      </c>
+      <c r="S69" t="n">
+        <v>10</v>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W69" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y69" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="Z69" t="inlineStr">
+        <is>
+          <t>11:18</t>
+        </is>
+      </c>
+      <c r="AA69" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="AB69" t="inlineStr">
+        <is>
+          <t>11:18</t>
+        </is>
+      </c>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>äldre ringhack</t>
+        </is>
+      </c>
+      <c r="AD69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT69" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX69" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY69" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>135192088</v>
+      </c>
+      <c r="B70" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>Höbrännflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q70" t="n">
+        <v>468900</v>
+      </c>
+      <c r="R70" t="n">
+        <v>7077908</v>
+      </c>
+      <c r="S70" t="n">
+        <v>10</v>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W70" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y70" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="Z70" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="AA70" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="AB70" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="AC70" t="inlineStr">
+        <is>
+          <t>färska och äldre ringhack</t>
+        </is>
+      </c>
+      <c r="AD70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT70" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX70" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY70" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>135192093</v>
+      </c>
+      <c r="B71" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr"/>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>Höbrännflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q71" t="n">
+        <v>468841</v>
+      </c>
+      <c r="R71" t="n">
+        <v>7077895</v>
+      </c>
+      <c r="S71" t="n">
+        <v>10</v>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W71" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y71" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="Z71" t="inlineStr">
+        <is>
+          <t>11:28</t>
+        </is>
+      </c>
+      <c r="AA71" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="AB71" t="inlineStr">
+        <is>
+          <t>11:28</t>
+        </is>
+      </c>
+      <c r="AC71" t="inlineStr">
+        <is>
+          <t>äldre ringhack</t>
+        </is>
+      </c>
+      <c r="AD71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT71" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX71" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY71" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>135192095</v>
+      </c>
+      <c r="B72" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr"/>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>Höbrännflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q72" t="n">
+        <v>468832</v>
+      </c>
+      <c r="R72" t="n">
+        <v>7077861</v>
+      </c>
+      <c r="S72" t="n">
+        <v>10</v>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V72" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W72" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y72" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="Z72" t="inlineStr">
+        <is>
+          <t>11:32</t>
+        </is>
+      </c>
+      <c r="AA72" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="AB72" t="inlineStr">
+        <is>
+          <t>11:32</t>
+        </is>
+      </c>
+      <c r="AC72" t="inlineStr">
+        <is>
+          <t>äldre ringhack</t>
+        </is>
+      </c>
+      <c r="AD72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT72" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX72" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY72" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>135192112</v>
+      </c>
+      <c r="B73" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E73" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr"/>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>Höbrännflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q73" t="n">
+        <v>469029</v>
+      </c>
+      <c r="R73" t="n">
+        <v>7077764</v>
+      </c>
+      <c r="S73" t="n">
+        <v>10</v>
+      </c>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V73" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W73" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y73" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="Z73" t="inlineStr">
+        <is>
+          <t>11:55</t>
+        </is>
+      </c>
+      <c r="AA73" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="AB73" t="inlineStr">
+        <is>
+          <t>11:55</t>
+        </is>
+      </c>
+      <c r="AC73" t="inlineStr">
+        <is>
+          <t>äldre ringhack</t>
+        </is>
+      </c>
+      <c r="AD73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT73" t="inlineStr"/>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX73" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY73" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>135192116</v>
+      </c>
+      <c r="B74" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E74" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr"/>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>Höbrännflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q74" t="n">
+        <v>469092</v>
+      </c>
+      <c r="R74" t="n">
+        <v>7077868</v>
+      </c>
+      <c r="S74" t="n">
+        <v>10</v>
+      </c>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V74" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W74" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y74" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="Z74" t="inlineStr">
+        <is>
+          <t>12:02</t>
+        </is>
+      </c>
+      <c r="AA74" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="AB74" t="inlineStr">
+        <is>
+          <t>12:02</t>
+        </is>
+      </c>
+      <c r="AC74" t="inlineStr">
+        <is>
+          <t>äldre ringhack</t>
+        </is>
+      </c>
+      <c r="AD74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT74" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX74" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY74" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>135192118</v>
+      </c>
+      <c r="B75" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E75" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr"/>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t>Höbrännflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q75" t="n">
+        <v>469121</v>
+      </c>
+      <c r="R75" t="n">
+        <v>7077852</v>
+      </c>
+      <c r="S75" t="n">
+        <v>10</v>
+      </c>
+      <c r="T75" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U75" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V75" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W75" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y75" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="Z75" t="inlineStr">
+        <is>
+          <t>12:04</t>
+        </is>
+      </c>
+      <c r="AA75" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="AB75" t="inlineStr">
+        <is>
+          <t>12:04</t>
+        </is>
+      </c>
+      <c r="AC75" t="inlineStr">
+        <is>
+          <t>äldre ringhack</t>
+        </is>
+      </c>
+      <c r="AD75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT75" t="inlineStr"/>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX75" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY75" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>135192119</v>
+      </c>
+      <c r="B76" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E76" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr"/>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t>Höbrännflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q76" t="n">
+        <v>469139</v>
+      </c>
+      <c r="R76" t="n">
+        <v>7077825</v>
+      </c>
+      <c r="S76" t="n">
+        <v>10</v>
+      </c>
+      <c r="T76" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U76" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V76" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W76" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y76" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="Z76" t="inlineStr">
+        <is>
+          <t>12:07</t>
+        </is>
+      </c>
+      <c r="AA76" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="AB76" t="inlineStr">
+        <is>
+          <t>12:07</t>
+        </is>
+      </c>
+      <c r="AC76" t="inlineStr">
+        <is>
+          <t>äldre ringhack</t>
+        </is>
+      </c>
+      <c r="AD76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT76" t="inlineStr"/>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX76" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY76" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>135192123</v>
+      </c>
+      <c r="B77" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E77" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr"/>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P77" t="inlineStr">
+        <is>
+          <t>Höbrännflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q77" t="n">
+        <v>469108</v>
+      </c>
+      <c r="R77" t="n">
+        <v>7077950</v>
+      </c>
+      <c r="S77" t="n">
+        <v>10</v>
+      </c>
+      <c r="T77" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U77" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V77" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W77" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y77" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="Z77" t="inlineStr">
+        <is>
+          <t>12:11</t>
+        </is>
+      </c>
+      <c r="AA77" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="AB77" t="inlineStr">
+        <is>
+          <t>12:11</t>
+        </is>
+      </c>
+      <c r="AC77" t="inlineStr">
+        <is>
+          <t>färska ringhack</t>
+        </is>
+      </c>
+      <c r="AD77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT77" t="inlineStr"/>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX77" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY77" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>135192124</v>
+      </c>
+      <c r="B78" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E78" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr"/>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P78" t="inlineStr">
+        <is>
+          <t>Höbrännflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q78" t="n">
+        <v>469109</v>
+      </c>
+      <c r="R78" t="n">
+        <v>7077945</v>
+      </c>
+      <c r="S78" t="n">
+        <v>10</v>
+      </c>
+      <c r="T78" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U78" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V78" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W78" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y78" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="Z78" t="inlineStr">
+        <is>
+          <t>12:12</t>
+        </is>
+      </c>
+      <c r="AA78" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="AB78" t="inlineStr">
+        <is>
+          <t>12:12</t>
+        </is>
+      </c>
+      <c r="AC78" t="inlineStr">
+        <is>
+          <t>färska ringhack</t>
+        </is>
+      </c>
+      <c r="AD78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT78" t="inlineStr"/>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX78" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY78" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>135192125</v>
+      </c>
+      <c r="B79" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E79" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr"/>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P79" t="inlineStr">
+        <is>
+          <t>Höbrännflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q79" t="n">
+        <v>469118</v>
+      </c>
+      <c r="R79" t="n">
+        <v>7077938</v>
+      </c>
+      <c r="S79" t="n">
+        <v>10</v>
+      </c>
+      <c r="T79" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U79" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V79" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W79" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y79" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="Z79" t="inlineStr">
+        <is>
+          <t>12:12</t>
+        </is>
+      </c>
+      <c r="AA79" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="AB79" t="inlineStr">
+        <is>
+          <t>12:12</t>
+        </is>
+      </c>
+      <c r="AC79" t="inlineStr">
+        <is>
+          <t>färska ringhack</t>
+        </is>
+      </c>
+      <c r="AD79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT79" t="inlineStr"/>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX79" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY79" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>135192127</v>
+      </c>
+      <c r="B80" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E80" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr"/>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P80" t="inlineStr">
+        <is>
+          <t>Höbrännflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q80" t="n">
+        <v>469140</v>
+      </c>
+      <c r="R80" t="n">
+        <v>7077913</v>
+      </c>
+      <c r="S80" t="n">
+        <v>10</v>
+      </c>
+      <c r="T80" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U80" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V80" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W80" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y80" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="Z80" t="inlineStr">
+        <is>
+          <t>12:13</t>
+        </is>
+      </c>
+      <c r="AA80" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="AB80" t="inlineStr">
+        <is>
+          <t>12:13</t>
+        </is>
+      </c>
+      <c r="AC80" t="inlineStr">
+        <is>
+          <t>färska ringhack</t>
+        </is>
+      </c>
+      <c r="AD80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT80" t="inlineStr"/>
+      <c r="AW80" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX80" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY80" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>135192128</v>
+      </c>
+      <c r="B81" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E81" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr"/>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P81" t="inlineStr">
+        <is>
+          <t>Höbrännflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q81" t="n">
+        <v>469149</v>
+      </c>
+      <c r="R81" t="n">
+        <v>7077895</v>
+      </c>
+      <c r="S81" t="n">
+        <v>10</v>
+      </c>
+      <c r="T81" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U81" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V81" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W81" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y81" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="Z81" t="inlineStr">
+        <is>
+          <t>12:14</t>
+        </is>
+      </c>
+      <c r="AA81" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="AB81" t="inlineStr">
+        <is>
+          <t>12:14</t>
+        </is>
+      </c>
+      <c r="AC81" t="inlineStr">
+        <is>
+          <t>färska ringhack</t>
+        </is>
+      </c>
+      <c r="AD81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT81" t="inlineStr"/>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX81" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY81" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>135192130</v>
+      </c>
+      <c r="B82" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E82" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr"/>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P82" t="inlineStr">
+        <is>
+          <t>Höbrännflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q82" t="n">
+        <v>469158</v>
+      </c>
+      <c r="R82" t="n">
+        <v>7077852</v>
+      </c>
+      <c r="S82" t="n">
+        <v>10</v>
+      </c>
+      <c r="T82" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U82" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V82" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W82" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y82" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="Z82" t="inlineStr">
+        <is>
+          <t>12:15</t>
+        </is>
+      </c>
+      <c r="AA82" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="AB82" t="inlineStr">
+        <is>
+          <t>12:15</t>
+        </is>
+      </c>
+      <c r="AC82" t="inlineStr">
+        <is>
+          <t>färska ringhack</t>
+        </is>
+      </c>
+      <c r="AD82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT82" t="inlineStr"/>
+      <c r="AW82" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX82" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY82" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>135192131</v>
+      </c>
+      <c r="B83" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E83" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr"/>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P83" t="inlineStr">
+        <is>
+          <t>Höbrännflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q83" t="n">
+        <v>469166</v>
+      </c>
+      <c r="R83" t="n">
+        <v>7077841</v>
+      </c>
+      <c r="S83" t="n">
+        <v>10</v>
+      </c>
+      <c r="T83" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U83" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V83" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W83" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y83" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="Z83" t="inlineStr">
+        <is>
+          <t>12:16</t>
+        </is>
+      </c>
+      <c r="AA83" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="AB83" t="inlineStr">
+        <is>
+          <t>12:16</t>
+        </is>
+      </c>
+      <c r="AC83" t="inlineStr">
+        <is>
+          <t>färska ringhack</t>
+        </is>
+      </c>
+      <c r="AD83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT83" t="inlineStr"/>
+      <c r="AW83" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX83" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY83" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>135192132</v>
+      </c>
+      <c r="B84" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E84" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr"/>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P84" t="inlineStr">
+        <is>
+          <t>Höbrännflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q84" t="n">
+        <v>469163</v>
+      </c>
+      <c r="R84" t="n">
+        <v>7077822</v>
+      </c>
+      <c r="S84" t="n">
+        <v>10</v>
+      </c>
+      <c r="T84" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U84" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V84" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W84" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y84" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="Z84" t="inlineStr">
+        <is>
+          <t>12:17</t>
+        </is>
+      </c>
+      <c r="AA84" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="AB84" t="inlineStr">
+        <is>
+          <t>12:17</t>
+        </is>
+      </c>
+      <c r="AC84" t="inlineStr">
+        <is>
+          <t>färska ringhack</t>
+        </is>
+      </c>
+      <c r="AD84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT84" t="inlineStr"/>
+      <c r="AW84" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX84" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY84" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>135192134</v>
+      </c>
+      <c r="B85" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E85" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr"/>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P85" t="inlineStr">
+        <is>
+          <t>Höbrännflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q85" t="n">
+        <v>469172</v>
+      </c>
+      <c r="R85" t="n">
+        <v>7077811</v>
+      </c>
+      <c r="S85" t="n">
+        <v>10</v>
+      </c>
+      <c r="T85" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U85" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V85" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W85" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y85" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="Z85" t="inlineStr">
+        <is>
+          <t>12:17</t>
+        </is>
+      </c>
+      <c r="AA85" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="AB85" t="inlineStr">
+        <is>
+          <t>12:17</t>
+        </is>
+      </c>
+      <c r="AC85" t="inlineStr">
+        <is>
+          <t>färska ringhack</t>
+        </is>
+      </c>
+      <c r="AD85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT85" t="inlineStr"/>
+      <c r="AW85" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX85" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY85" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>135192135</v>
+      </c>
+      <c r="B86" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E86" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr"/>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P86" t="inlineStr">
+        <is>
+          <t>Höbrännflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q86" t="n">
+        <v>469180</v>
+      </c>
+      <c r="R86" t="n">
+        <v>7077818</v>
+      </c>
+      <c r="S86" t="n">
+        <v>10</v>
+      </c>
+      <c r="T86" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U86" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V86" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W86" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y86" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="Z86" t="inlineStr">
+        <is>
+          <t>12:18</t>
+        </is>
+      </c>
+      <c r="AA86" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="AB86" t="inlineStr">
+        <is>
+          <t>12:18</t>
+        </is>
+      </c>
+      <c r="AC86" t="inlineStr">
+        <is>
+          <t>äldre ringhack</t>
+        </is>
+      </c>
+      <c r="AD86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT86" t="inlineStr"/>
+      <c r="AW86" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX86" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY86" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>135192136</v>
+      </c>
+      <c r="B87" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E87" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr"/>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P87" t="inlineStr">
+        <is>
+          <t>Höbrännflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q87" t="n">
+        <v>469176</v>
+      </c>
+      <c r="R87" t="n">
+        <v>7077799</v>
+      </c>
+      <c r="S87" t="n">
+        <v>10</v>
+      </c>
+      <c r="T87" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U87" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V87" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W87" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y87" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="Z87" t="inlineStr">
+        <is>
+          <t>12:19</t>
+        </is>
+      </c>
+      <c r="AA87" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="AB87" t="inlineStr">
+        <is>
+          <t>12:19</t>
+        </is>
+      </c>
+      <c r="AC87" t="inlineStr">
+        <is>
+          <t>färska ringhack</t>
+        </is>
+      </c>
+      <c r="AD87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT87" t="inlineStr"/>
+      <c r="AW87" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX87" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY87" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>135192137</v>
+      </c>
+      <c r="B88" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E88" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr"/>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P88" t="inlineStr">
+        <is>
+          <t>Höbrännflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q88" t="n">
+        <v>469181</v>
+      </c>
+      <c r="R88" t="n">
+        <v>7077798</v>
+      </c>
+      <c r="S88" t="n">
+        <v>10</v>
+      </c>
+      <c r="T88" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U88" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V88" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W88" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y88" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="Z88" t="inlineStr">
+        <is>
+          <t>12:20</t>
+        </is>
+      </c>
+      <c r="AA88" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="AB88" t="inlineStr">
+        <is>
+          <t>12:20</t>
+        </is>
+      </c>
+      <c r="AC88" t="inlineStr">
+        <is>
+          <t>färska ringhack</t>
+        </is>
+      </c>
+      <c r="AD88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT88" t="inlineStr"/>
+      <c r="AW88" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX88" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY88" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>135192151</v>
+      </c>
+      <c r="B89" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E89" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr"/>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P89" t="inlineStr">
+        <is>
+          <t>Höbrännflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q89" t="n">
+        <v>469393</v>
+      </c>
+      <c r="R89" t="n">
+        <v>7077846</v>
+      </c>
+      <c r="S89" t="n">
+        <v>10</v>
+      </c>
+      <c r="T89" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U89" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V89" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W89" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y89" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="Z89" t="inlineStr">
+        <is>
+          <t>12:42</t>
+        </is>
+      </c>
+      <c r="AA89" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="AB89" t="inlineStr">
+        <is>
+          <t>12:42</t>
+        </is>
+      </c>
+      <c r="AC89" t="inlineStr">
+        <is>
+          <t>äldre ringhack</t>
+        </is>
+      </c>
+      <c r="AD89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT89" t="inlineStr"/>
+      <c r="AW89" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX89" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY89" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>135192152</v>
+      </c>
+      <c r="B90" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E90" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr"/>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P90" t="inlineStr">
+        <is>
+          <t>Höbrännflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q90" t="n">
+        <v>469356</v>
+      </c>
+      <c r="R90" t="n">
+        <v>7077867</v>
+      </c>
+      <c r="S90" t="n">
+        <v>10</v>
+      </c>
+      <c r="T90" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U90" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V90" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W90" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y90" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="Z90" t="inlineStr">
+        <is>
+          <t>12:45</t>
+        </is>
+      </c>
+      <c r="AA90" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="AB90" t="inlineStr">
+        <is>
+          <t>12:45</t>
+        </is>
+      </c>
+      <c r="AC90" t="inlineStr">
+        <is>
+          <t>äldre ringhack</t>
+        </is>
+      </c>
+      <c r="AD90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT90" t="inlineStr"/>
+      <c r="AW90" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX90" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY90" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>135192153</v>
+      </c>
+      <c r="B91" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E91" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr"/>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P91" t="inlineStr">
+        <is>
+          <t>Höbrännflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q91" t="n">
+        <v>469347</v>
+      </c>
+      <c r="R91" t="n">
+        <v>7077869</v>
+      </c>
+      <c r="S91" t="n">
+        <v>10</v>
+      </c>
+      <c r="T91" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U91" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V91" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W91" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y91" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="Z91" t="inlineStr">
+        <is>
+          <t>12:46</t>
+        </is>
+      </c>
+      <c r="AA91" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="AB91" t="inlineStr">
+        <is>
+          <t>12:46</t>
+        </is>
+      </c>
+      <c r="AC91" t="inlineStr">
+        <is>
+          <t>äldre ringhack</t>
+        </is>
+      </c>
+      <c r="AD91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT91" t="inlineStr"/>
+      <c r="AW91" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX91" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY91" t="inlineStr"/>
+    </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>135192157</v>
+      </c>
+      <c r="B92" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E92" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr"/>
+      <c r="M92" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P92" t="inlineStr">
+        <is>
+          <t>Höbrännflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q92" t="n">
+        <v>469381</v>
+      </c>
+      <c r="R92" t="n">
+        <v>7077873</v>
+      </c>
+      <c r="S92" t="n">
+        <v>10</v>
+      </c>
+      <c r="T92" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U92" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V92" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W92" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y92" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="Z92" t="inlineStr">
+        <is>
+          <t>12:52</t>
+        </is>
+      </c>
+      <c r="AA92" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="AB92" t="inlineStr">
+        <is>
+          <t>12:52</t>
+        </is>
+      </c>
+      <c r="AC92" t="inlineStr">
+        <is>
+          <t>äldre ringhack</t>
+        </is>
+      </c>
+      <c r="AD92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT92" t="inlineStr"/>
+      <c r="AW92" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX92" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY92" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>135192158</v>
+      </c>
+      <c r="B93" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E93" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr"/>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P93" t="inlineStr">
+        <is>
+          <t>Höbrännflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q93" t="n">
+        <v>469401</v>
+      </c>
+      <c r="R93" t="n">
+        <v>7077887</v>
+      </c>
+      <c r="S93" t="n">
+        <v>10</v>
+      </c>
+      <c r="T93" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U93" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V93" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W93" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y93" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="Z93" t="inlineStr">
+        <is>
+          <t>12:54</t>
+        </is>
+      </c>
+      <c r="AA93" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="AB93" t="inlineStr">
+        <is>
+          <t>12:54</t>
+        </is>
+      </c>
+      <c r="AC93" t="inlineStr">
+        <is>
+          <t>äldre ringhack</t>
+        </is>
+      </c>
+      <c r="AD93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT93" t="inlineStr"/>
+      <c r="AW93" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX93" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY93" t="inlineStr"/>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>135192161</v>
+      </c>
+      <c r="B94" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E94" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr"/>
+      <c r="M94" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P94" t="inlineStr">
+        <is>
+          <t>Höbrännflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q94" t="n">
+        <v>469388</v>
+      </c>
+      <c r="R94" t="n">
+        <v>7077920</v>
+      </c>
+      <c r="S94" t="n">
+        <v>10</v>
+      </c>
+      <c r="T94" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U94" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V94" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W94" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y94" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="Z94" t="inlineStr">
+        <is>
+          <t>12:56</t>
+        </is>
+      </c>
+      <c r="AA94" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="AB94" t="inlineStr">
+        <is>
+          <t>12:56</t>
+        </is>
+      </c>
+      <c r="AC94" t="inlineStr">
+        <is>
+          <t>äldre ringhack</t>
+        </is>
+      </c>
+      <c r="AD94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT94" t="inlineStr"/>
+      <c r="AW94" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX94" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY94" t="inlineStr"/>
+    </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>135192166</v>
+      </c>
+      <c r="B95" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E95" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr"/>
+      <c r="P95" t="inlineStr">
+        <is>
+          <t>Höbrännflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q95" t="n">
+        <v>469249</v>
+      </c>
+      <c r="R95" t="n">
+        <v>7077922</v>
+      </c>
+      <c r="S95" t="n">
+        <v>10</v>
+      </c>
+      <c r="T95" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U95" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V95" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W95" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y95" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="Z95" t="inlineStr">
+        <is>
+          <t>13:07</t>
+        </is>
+      </c>
+      <c r="AA95" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="AB95" t="inlineStr">
+        <is>
+          <t>13:07</t>
+        </is>
+      </c>
+      <c r="AC95" t="inlineStr">
+        <is>
+          <t>ringhack</t>
+        </is>
+      </c>
+      <c r="AD95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT95" t="inlineStr"/>
+      <c r="AW95" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX95" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY95" t="inlineStr"/>
+    </row>
+    <row r="96">
+      <c r="A96" t="n">
+        <v>128346628</v>
+      </c>
+      <c r="B96" t="n">
+        <v>97989</v>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E96" t="n">
+        <v>221941</v>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>Plattlummer</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>Lycopodium complanatum</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr"/>
+      <c r="P96" t="inlineStr">
+        <is>
+          <t>Höbrännflon sö, Jmt</t>
+        </is>
+      </c>
+      <c r="Q96" t="n">
+        <v>468931</v>
+      </c>
+      <c r="R96" t="n">
+        <v>7077743</v>
+      </c>
+      <c r="S96" t="n">
+        <v>10</v>
+      </c>
+      <c r="T96" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U96" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V96" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W96" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y96" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AA96" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AD96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT96" t="inlineStr"/>
+      <c r="AW96" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX96" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY96" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 28940-2026 artfynd.xlsx
+++ b/artfynd/A 28940-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY96"/>
+  <dimension ref="A1:AZ96"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128346636</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128346637</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128346641</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1070,6 +1090,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135192063</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1177,6 +1202,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135192175</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1284,6 +1314,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135192051</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1381,6 +1416,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128346578</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1478,6 +1518,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128346633</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1590,6 +1635,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135192023</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1702,6 +1752,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135192025</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1814,6 +1869,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135192028</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1926,6 +1986,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135192031</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2038,6 +2103,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135192033</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2150,6 +2220,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135192036</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2262,6 +2337,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135192038</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2374,6 +2454,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135192040</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2486,6 +2571,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135192041</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2598,6 +2688,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135192043</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2710,6 +2805,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135192053</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2822,6 +2922,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135192055</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2934,6 +3039,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135192059</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3046,6 +3156,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135192065</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3158,6 +3273,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135192069</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3270,6 +3390,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135192110</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3382,6 +3507,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135192141</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3494,6 +3624,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135192145</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3606,6 +3741,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135192148</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3718,6 +3858,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135192171</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3815,6 +3960,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128346632</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3938,6 +4088,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135192073</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4040,6 +4195,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128346579</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4142,6 +4302,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128346580</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4244,6 +4409,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128346581</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4346,6 +4516,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128346582</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4448,6 +4623,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128346583</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4550,6 +4730,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128346585</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4652,6 +4837,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128346586</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4754,6 +4944,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128346607</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4856,6 +5051,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128346608</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4958,6 +5158,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128346609</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5060,6 +5265,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128346610</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5162,6 +5372,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128346611</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5264,6 +5479,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128346612</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5366,6 +5586,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128346613</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5468,6 +5693,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128346614</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5570,6 +5800,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128346615</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5672,6 +5907,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128346616</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5774,6 +6014,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128346617</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5876,6 +6121,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128346618</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -5978,6 +6228,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128346619</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -6080,6 +6335,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128346620</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -6182,6 +6442,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128346621</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6284,6 +6549,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128346622</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6386,6 +6656,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128346623</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6488,6 +6763,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128346624</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6590,6 +6870,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128346625</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6707,6 +6992,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135192022</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6824,6 +7114,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135192026</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -6941,6 +7236,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135192030</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -7053,6 +7353,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135192045</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -7170,6 +7475,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135192047</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -7287,6 +7597,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135192048</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -7404,6 +7719,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135192050</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -7521,6 +7841,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135192056</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -7638,6 +7963,11 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135192074</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -7755,6 +8085,11 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135192077</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -7872,6 +8207,11 @@
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135192079</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -7989,6 +8329,11 @@
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135192085</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -8106,6 +8451,11 @@
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135192088</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -8223,6 +8573,11 @@
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135192093</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -8340,6 +8695,11 @@
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135192095</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -8457,6 +8817,11 @@
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135192112</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -8574,6 +8939,11 @@
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135192116</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -8691,6 +9061,11 @@
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135192118</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -8808,6 +9183,11 @@
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135192119</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -8925,6 +9305,11 @@
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135192123</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -9042,6 +9427,11 @@
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135192124</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -9159,6 +9549,11 @@
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135192125</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -9276,6 +9671,11 @@
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135192127</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -9393,6 +9793,11 @@
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135192128</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -9510,6 +9915,11 @@
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135192130</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -9627,6 +10037,11 @@
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135192131</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -9744,6 +10159,11 @@
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135192132</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -9861,6 +10281,11 @@
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135192134</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -9978,6 +10403,11 @@
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
+      <c r="AZ86" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135192135</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -10095,6 +10525,11 @@
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
+      <c r="AZ87" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135192136</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -10212,6 +10647,11 @@
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
+      <c r="AZ88" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135192137</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -10329,6 +10769,11 @@
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
+      <c r="AZ89" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135192151</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -10446,6 +10891,11 @@
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
+      <c r="AZ90" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135192152</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -10563,6 +11013,11 @@
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
+      <c r="AZ91" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135192153</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -10680,6 +11135,11 @@
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
+      <c r="AZ92" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135192157</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -10797,6 +11257,11 @@
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
+      <c r="AZ93" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135192158</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -10914,6 +11379,11 @@
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
+      <c r="AZ94" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135192161</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -11026,6 +11496,11 @@
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
+      <c r="AZ95" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135192166</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -11123,8 +11598,110 @@
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
+      <c r="AZ96" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128346628</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ91" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ92" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ93" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ94" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ95" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ96" r:id="rId95"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 28940-2026 artfynd.xlsx
+++ b/artfynd/A 28940-2026 artfynd.xlsx
@@ -989,7 +989,7 @@
         <v>135192063</v>
       </c>
       <c r="B5" t="n">
-        <v>89354</v>
+        <v>89396</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1101,7 +1101,7 @@
         <v>135192175</v>
       </c>
       <c r="B6" t="n">
-        <v>92546</v>
+        <v>92588</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         <v>135192051</v>
       </c>
       <c r="B7" t="n">
-        <v>91970</v>
+        <v>92012</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1529,7 +1529,7 @@
         <v>135192023</v>
       </c>
       <c r="B10" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1646,7 +1646,7 @@
         <v>135192025</v>
       </c>
       <c r="B11" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1763,7 +1763,7 @@
         <v>135192028</v>
       </c>
       <c r="B12" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1880,7 +1880,7 @@
         <v>135192031</v>
       </c>
       <c r="B13" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1997,7 +1997,7 @@
         <v>135192033</v>
       </c>
       <c r="B14" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2114,7 +2114,7 @@
         <v>135192036</v>
       </c>
       <c r="B15" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2231,7 +2231,7 @@
         <v>135192038</v>
       </c>
       <c r="B16" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2348,7 +2348,7 @@
         <v>135192040</v>
       </c>
       <c r="B17" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2465,7 +2465,7 @@
         <v>135192041</v>
       </c>
       <c r="B18" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2582,7 +2582,7 @@
         <v>135192043</v>
       </c>
       <c r="B19" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2699,7 +2699,7 @@
         <v>135192053</v>
       </c>
       <c r="B20" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2816,7 +2816,7 @@
         <v>135192055</v>
       </c>
       <c r="B21" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2933,7 +2933,7 @@
         <v>135192059</v>
       </c>
       <c r="B22" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3050,7 +3050,7 @@
         <v>135192065</v>
       </c>
       <c r="B23" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3167,7 +3167,7 @@
         <v>135192069</v>
       </c>
       <c r="B24" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3284,7 +3284,7 @@
         <v>135192110</v>
       </c>
       <c r="B25" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3401,7 +3401,7 @@
         <v>135192141</v>
       </c>
       <c r="B26" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3518,7 +3518,7 @@
         <v>135192145</v>
       </c>
       <c r="B27" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3635,7 +3635,7 @@
         <v>135192148</v>
       </c>
       <c r="B28" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3752,7 +3752,7 @@
         <v>135192171</v>
       </c>
       <c r="B29" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3971,7 +3971,7 @@
         <v>135192073</v>
       </c>
       <c r="B31" t="n">
-        <v>57972</v>
+        <v>57977</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -6881,7 +6881,7 @@
         <v>135192022</v>
       </c>
       <c r="B58" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7003,7 +7003,7 @@
         <v>135192026</v>
       </c>
       <c r="B59" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7125,7 +7125,7 @@
         <v>135192030</v>
       </c>
       <c r="B60" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7247,7 +7247,7 @@
         <v>135192045</v>
       </c>
       <c r="B61" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7364,7 +7364,7 @@
         <v>135192047</v>
       </c>
       <c r="B62" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7486,7 +7486,7 @@
         <v>135192048</v>
       </c>
       <c r="B63" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7608,7 +7608,7 @@
         <v>135192050</v>
       </c>
       <c r="B64" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7730,7 +7730,7 @@
         <v>135192056</v>
       </c>
       <c r="B65" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7852,7 +7852,7 @@
         <v>135192074</v>
       </c>
       <c r="B66" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7974,7 +7974,7 @@
         <v>135192077</v>
       </c>
       <c r="B67" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8096,7 +8096,7 @@
         <v>135192079</v>
       </c>
       <c r="B68" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8218,7 +8218,7 @@
         <v>135192085</v>
       </c>
       <c r="B69" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8340,7 +8340,7 @@
         <v>135192088</v>
       </c>
       <c r="B70" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8462,7 +8462,7 @@
         <v>135192093</v>
       </c>
       <c r="B71" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8584,7 +8584,7 @@
         <v>135192095</v>
       </c>
       <c r="B72" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8706,7 +8706,7 @@
         <v>135192112</v>
       </c>
       <c r="B73" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8828,7 +8828,7 @@
         <v>135192116</v>
       </c>
       <c r="B74" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8950,7 +8950,7 @@
         <v>135192118</v>
       </c>
       <c r="B75" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9072,7 +9072,7 @@
         <v>135192119</v>
       </c>
       <c r="B76" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9194,7 +9194,7 @@
         <v>135192123</v>
       </c>
       <c r="B77" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9316,7 +9316,7 @@
         <v>135192124</v>
       </c>
       <c r="B78" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9438,7 +9438,7 @@
         <v>135192125</v>
       </c>
       <c r="B79" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9560,7 +9560,7 @@
         <v>135192127</v>
       </c>
       <c r="B80" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9682,7 +9682,7 @@
         <v>135192128</v>
       </c>
       <c r="B81" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9804,7 +9804,7 @@
         <v>135192130</v>
       </c>
       <c r="B82" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9926,7 +9926,7 @@
         <v>135192131</v>
       </c>
       <c r="B83" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -10048,7 +10048,7 @@
         <v>135192132</v>
       </c>
       <c r="B84" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -10170,7 +10170,7 @@
         <v>135192134</v>
       </c>
       <c r="B85" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10292,7 +10292,7 @@
         <v>135192135</v>
       </c>
       <c r="B86" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10414,7 +10414,7 @@
         <v>135192136</v>
       </c>
       <c r="B87" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10536,7 +10536,7 @@
         <v>135192137</v>
       </c>
       <c r="B88" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10658,7 +10658,7 @@
         <v>135192151</v>
       </c>
       <c r="B89" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10780,7 +10780,7 @@
         <v>135192152</v>
       </c>
       <c r="B90" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10902,7 +10902,7 @@
         <v>135192153</v>
       </c>
       <c r="B91" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -11024,7 +11024,7 @@
         <v>135192157</v>
       </c>
       <c r="B92" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -11146,7 +11146,7 @@
         <v>135192158</v>
       </c>
       <c r="B93" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -11268,7 +11268,7 @@
         <v>135192161</v>
       </c>
       <c r="B94" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -11390,7 +11390,7 @@
         <v>135192166</v>
       </c>
       <c r="B95" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>

--- a/artfynd/A 28940-2026 artfynd.xlsx
+++ b/artfynd/A 28940-2026 artfynd.xlsx
@@ -989,7 +989,7 @@
         <v>135192063</v>
       </c>
       <c r="B5" t="n">
-        <v>89396</v>
+        <v>89423</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1101,7 +1101,7 @@
         <v>135192175</v>
       </c>
       <c r="B6" t="n">
-        <v>92588</v>
+        <v>92615</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         <v>135192051</v>
       </c>
       <c r="B7" t="n">
-        <v>92012</v>
+        <v>92039</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1529,7 +1529,7 @@
         <v>135192023</v>
       </c>
       <c r="B10" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1646,7 +1646,7 @@
         <v>135192025</v>
       </c>
       <c r="B11" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1763,7 +1763,7 @@
         <v>135192028</v>
       </c>
       <c r="B12" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1880,7 +1880,7 @@
         <v>135192031</v>
       </c>
       <c r="B13" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1997,7 +1997,7 @@
         <v>135192033</v>
       </c>
       <c r="B14" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2114,7 +2114,7 @@
         <v>135192036</v>
       </c>
       <c r="B15" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2231,7 +2231,7 @@
         <v>135192038</v>
       </c>
       <c r="B16" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2348,7 +2348,7 @@
         <v>135192040</v>
       </c>
       <c r="B17" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2465,7 +2465,7 @@
         <v>135192041</v>
       </c>
       <c r="B18" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2582,7 +2582,7 @@
         <v>135192043</v>
       </c>
       <c r="B19" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2699,7 +2699,7 @@
         <v>135192053</v>
       </c>
       <c r="B20" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2816,7 +2816,7 @@
         <v>135192055</v>
       </c>
       <c r="B21" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2933,7 +2933,7 @@
         <v>135192059</v>
       </c>
       <c r="B22" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3050,7 +3050,7 @@
         <v>135192065</v>
       </c>
       <c r="B23" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3167,7 +3167,7 @@
         <v>135192069</v>
       </c>
       <c r="B24" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3284,7 +3284,7 @@
         <v>135192110</v>
       </c>
       <c r="B25" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3401,7 +3401,7 @@
         <v>135192141</v>
       </c>
       <c r="B26" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3518,7 +3518,7 @@
         <v>135192145</v>
       </c>
       <c r="B27" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3635,7 +3635,7 @@
         <v>135192148</v>
       </c>
       <c r="B28" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3752,7 +3752,7 @@
         <v>135192171</v>
       </c>
       <c r="B29" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>

--- a/artfynd/A 28940-2026 artfynd.xlsx
+++ b/artfynd/A 28940-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ34"/>
+  <dimension ref="A1:AZ96"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -986,10 +986,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128346578</v>
+        <v>135192063</v>
       </c>
       <c r="B5" t="n">
-        <v>91909</v>
+        <v>89426</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -997,34 +997,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>510</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Höbrännflon sö, Jmt</t>
+          <t>Höbrännflon, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>469082</v>
+        <v>469031</v>
       </c>
       <c r="R5" t="n">
-        <v>7078001</v>
+        <v>7078166</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1051,12 +1051,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-09-09</t>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-09-09</t>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1082,16 +1092,16 @@
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128346578</t>
+          <t>https://artportalen.se/Sighting/135192063</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128346633</v>
+        <v>135192175</v>
       </c>
       <c r="B6" t="n">
-        <v>91923</v>
+        <v>92620</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1099,34 +1109,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1204</v>
+        <v>760</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Höbrännflon sö, Jmt</t>
+          <t>Höbrännflon, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>469137</v>
+        <v>469206</v>
       </c>
       <c r="R6" t="n">
-        <v>7078055</v>
+        <v>7078077</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1153,12 +1163,22 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-09-09</t>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-09-09</t>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1184,16 +1204,16 @@
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128346633</t>
+          <t>https://artportalen.se/Sighting/135192175</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128346632</v>
+        <v>135192051</v>
       </c>
       <c r="B7" t="n">
-        <v>80432</v>
+        <v>92044</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1201,34 +1221,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>1108</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Höbrännflon sö, Jmt</t>
+          <t>Höbrännflon, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>468909</v>
+        <v>468905</v>
       </c>
       <c r="R7" t="n">
-        <v>7077971</v>
+        <v>7078357</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1255,12 +1275,22 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-09-09</t>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-09-09</t>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1286,16 +1316,16 @@
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128346632</t>
+          <t>https://artportalen.se/Sighting/135192051</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128346579</v>
+        <v>128346578</v>
       </c>
       <c r="B8" t="n">
-        <v>57953</v>
+        <v>91909</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1303,21 +1333,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1327,10 +1357,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>469196</v>
+        <v>469082</v>
       </c>
       <c r="R8" t="n">
-        <v>7077970</v>
+        <v>7078001</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1365,11 +1395,6 @@
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
-        </is>
-      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
@@ -1393,38 +1418,38 @@
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128346579</t>
+          <t>https://artportalen.se/Sighting/128346578</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128346580</v>
+        <v>128346633</v>
       </c>
       <c r="B9" t="n">
-        <v>57953</v>
+        <v>91923</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>1204</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1434,10 +1459,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>469066</v>
+        <v>469137</v>
       </c>
       <c r="R9" t="n">
-        <v>7077948</v>
+        <v>7078055</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1472,11 +1497,6 @@
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
-        </is>
-      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
@@ -1500,51 +1520,51 @@
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128346580</t>
+          <t>https://artportalen.se/Sighting/128346633</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128346581</v>
+        <v>135192023</v>
       </c>
       <c r="B10" t="n">
-        <v>57953</v>
+        <v>79441</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Höbrännflon sö, Jmt</t>
+          <t>Höbrännflon, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>468873</v>
+        <v>469151</v>
       </c>
       <c r="R10" t="n">
-        <v>7077929</v>
+        <v>7078176</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1571,17 +1591,27 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-09-09</t>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>09:31</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2025-09-09</t>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>09:31</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1607,51 +1637,51 @@
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128346581</t>
+          <t>https://artportalen.se/Sighting/135192023</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128346582</v>
+        <v>135192025</v>
       </c>
       <c r="B11" t="n">
-        <v>57953</v>
+        <v>79441</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Höbrännflon sö, Jmt</t>
+          <t>Höbrännflon, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>468940</v>
+        <v>469160</v>
       </c>
       <c r="R11" t="n">
-        <v>7077734</v>
+        <v>7078154</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1678,17 +1708,27 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-09-09</t>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>09:36</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2025-09-09</t>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>09:36</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1714,51 +1754,51 @@
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128346582</t>
+          <t>https://artportalen.se/Sighting/135192025</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128346583</v>
+        <v>135192028</v>
       </c>
       <c r="B12" t="n">
-        <v>57953</v>
+        <v>79441</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Höbrännflon sö, Jmt</t>
+          <t>Höbrännflon, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>468969</v>
+        <v>469195</v>
       </c>
       <c r="R12" t="n">
-        <v>7077711</v>
+        <v>7078100</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1785,17 +1825,27 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-09-09</t>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2025-09-09</t>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1821,51 +1871,51 @@
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128346583</t>
+          <t>https://artportalen.se/Sighting/135192028</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128346585</v>
+        <v>135192031</v>
       </c>
       <c r="B13" t="n">
-        <v>57953</v>
+        <v>79441</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Höbrännflon sö, Jmt</t>
+          <t>Höbrännflon, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>468968</v>
+        <v>469158</v>
       </c>
       <c r="R13" t="n">
-        <v>7077679</v>
+        <v>7078106</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1892,17 +1942,27 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-09-09</t>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2025-09-09</t>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1928,51 +1988,51 @@
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128346585</t>
+          <t>https://artportalen.se/Sighting/135192031</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128346586</v>
+        <v>135192033</v>
       </c>
       <c r="B14" t="n">
-        <v>57953</v>
+        <v>79441</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Höbrännflon sö, Jmt</t>
+          <t>Höbrännflon, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>468984</v>
+        <v>469111</v>
       </c>
       <c r="R14" t="n">
-        <v>7077636</v>
+        <v>7078095</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1999,17 +2059,27 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-09-09</t>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>09:53</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2025-09-09</t>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>09:53</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2035,51 +2105,51 @@
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128346586</t>
+          <t>https://artportalen.se/Sighting/135192033</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128346607</v>
+        <v>135192036</v>
       </c>
       <c r="B15" t="n">
-        <v>57953</v>
+        <v>79441</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Höbrännflon sö, Jmt</t>
+          <t>Höbrännflon, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>468839</v>
+        <v>469089</v>
       </c>
       <c r="R15" t="n">
-        <v>7077932</v>
+        <v>7078197</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2106,17 +2176,27 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-09-09</t>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2025-09-09</t>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2142,51 +2222,51 @@
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128346607</t>
+          <t>https://artportalen.se/Sighting/135192036</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128346608</v>
+        <v>135192038</v>
       </c>
       <c r="B16" t="n">
-        <v>57953</v>
+        <v>79441</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Höbrännflon sö, Jmt</t>
+          <t>Höbrännflon, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>468870</v>
+        <v>469078</v>
       </c>
       <c r="R16" t="n">
-        <v>7077959</v>
+        <v>7078215</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2213,17 +2293,27 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-09-09</t>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2025-09-09</t>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2249,51 +2339,51 @@
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128346608</t>
+          <t>https://artportalen.se/Sighting/135192038</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128346609</v>
+        <v>135192040</v>
       </c>
       <c r="B17" t="n">
-        <v>57953</v>
+        <v>79441</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Höbrännflon sö, Jmt</t>
+          <t>Höbrännflon, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>468906</v>
+        <v>469055</v>
       </c>
       <c r="R17" t="n">
-        <v>7077980</v>
+        <v>7078251</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2320,17 +2410,27 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-09-09</t>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2025-09-09</t>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2356,51 +2456,51 @@
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128346609</t>
+          <t>https://artportalen.se/Sighting/135192040</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128346610</v>
+        <v>135192041</v>
       </c>
       <c r="B18" t="n">
-        <v>57953</v>
+        <v>79441</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Höbrännflon sö, Jmt</t>
+          <t>Höbrännflon, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>468891</v>
+        <v>469057</v>
       </c>
       <c r="R18" t="n">
-        <v>7077967</v>
+        <v>7078295</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2427,17 +2527,27 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-09-09</t>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2025-09-09</t>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Ringhack färska 2 träd</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2463,51 +2573,51 @@
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128346610</t>
+          <t>https://artportalen.se/Sighting/135192041</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128346611</v>
+        <v>135192043</v>
       </c>
       <c r="B19" t="n">
-        <v>57953</v>
+        <v>79441</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Höbrännflon sö, Jmt</t>
+          <t>Höbrännflon, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>468913</v>
+        <v>469004</v>
       </c>
       <c r="R19" t="n">
-        <v>7077967</v>
+        <v>7078286</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2534,17 +2644,27 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-09-09</t>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2025-09-09</t>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2570,51 +2690,51 @@
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128346611</t>
+          <t>https://artportalen.se/Sighting/135192043</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128346612</v>
+        <v>135192053</v>
       </c>
       <c r="B20" t="n">
-        <v>57953</v>
+        <v>79441</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Höbrännflon sö, Jmt</t>
+          <t>Höbrännflon, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>468917</v>
+        <v>468898</v>
       </c>
       <c r="R20" t="n">
-        <v>7077967</v>
+        <v>7078332</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2641,17 +2761,27 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-09-09</t>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2025-09-09</t>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2677,51 +2807,51 @@
       <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128346612</t>
+          <t>https://artportalen.se/Sighting/135192053</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128346613</v>
+        <v>135192055</v>
       </c>
       <c r="B21" t="n">
-        <v>57953</v>
+        <v>79441</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Höbrännflon sö, Jmt</t>
+          <t>Höbrännflon, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>468925</v>
+        <v>468928</v>
       </c>
       <c r="R21" t="n">
-        <v>7077966</v>
+        <v>7078320</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2748,17 +2878,27 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-09-09</t>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2025-09-09</t>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2784,51 +2924,51 @@
       <c r="AY21" t="inlineStr"/>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128346613</t>
+          <t>https://artportalen.se/Sighting/135192055</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128346614</v>
+        <v>135192059</v>
       </c>
       <c r="B22" t="n">
-        <v>57953</v>
+        <v>79441</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Höbrännflon sö, Jmt</t>
+          <t>Höbrännflon, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>468931</v>
+        <v>468977</v>
       </c>
       <c r="R22" t="n">
-        <v>7077965</v>
+        <v>7078269</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2855,17 +2995,27 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-09-09</t>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2025-09-09</t>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2891,51 +3041,51 @@
       <c r="AY22" t="inlineStr"/>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128346614</t>
+          <t>https://artportalen.se/Sighting/135192059</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128346615</v>
+        <v>135192065</v>
       </c>
       <c r="B23" t="n">
-        <v>57953</v>
+        <v>79441</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Höbrännflon sö, Jmt</t>
+          <t>Höbrännflon, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>468940</v>
+        <v>469039</v>
       </c>
       <c r="R23" t="n">
-        <v>7077960</v>
+        <v>7078146</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2962,17 +3112,27 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-09-09</t>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2025-09-09</t>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2998,51 +3158,51 @@
       <c r="AY23" t="inlineStr"/>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128346615</t>
+          <t>https://artportalen.se/Sighting/135192065</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128346616</v>
+        <v>135192069</v>
       </c>
       <c r="B24" t="n">
-        <v>57953</v>
+        <v>79441</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Höbrännflon sö, Jmt</t>
+          <t>Höbrännflon, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>468979</v>
+        <v>469072</v>
       </c>
       <c r="R24" t="n">
-        <v>7077962</v>
+        <v>7078093</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3069,17 +3229,27 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2025-09-09</t>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2025-09-09</t>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3105,51 +3275,51 @@
       <c r="AY24" t="inlineStr"/>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128346616</t>
+          <t>https://artportalen.se/Sighting/135192069</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128346617</v>
+        <v>135192110</v>
       </c>
       <c r="B25" t="n">
-        <v>57953</v>
+        <v>79441</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Höbrännflon sö, Jmt</t>
+          <t>Höbrännflon, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>468994</v>
+        <v>469052</v>
       </c>
       <c r="R25" t="n">
-        <v>7077960</v>
+        <v>7077724</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3176,17 +3346,27 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2025-09-09</t>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2025-09-09</t>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3212,51 +3392,51 @@
       <c r="AY25" t="inlineStr"/>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128346617</t>
+          <t>https://artportalen.se/Sighting/135192110</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128346618</v>
+        <v>135192141</v>
       </c>
       <c r="B26" t="n">
-        <v>57953</v>
+        <v>79441</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Höbrännflon sö, Jmt</t>
+          <t>Höbrännflon, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>469012</v>
+        <v>469190</v>
       </c>
       <c r="R26" t="n">
-        <v>7077965</v>
+        <v>7077923</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3283,17 +3463,27 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2025-09-09</t>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2025-09-09</t>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3319,51 +3509,51 @@
       <c r="AY26" t="inlineStr"/>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128346618</t>
+          <t>https://artportalen.se/Sighting/135192141</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128346619</v>
+        <v>135192145</v>
       </c>
       <c r="B27" t="n">
-        <v>57953</v>
+        <v>79441</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Höbrännflon sö, Jmt</t>
+          <t>Höbrännflon, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>469014</v>
+        <v>469302</v>
       </c>
       <c r="R27" t="n">
-        <v>7077963</v>
+        <v>7077879</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3390,17 +3580,27 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2025-09-09</t>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2025-09-09</t>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3426,51 +3626,51 @@
       <c r="AY27" t="inlineStr"/>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128346619</t>
+          <t>https://artportalen.se/Sighting/135192145</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128346620</v>
+        <v>135192148</v>
       </c>
       <c r="B28" t="n">
-        <v>57953</v>
+        <v>79441</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Höbrännflon sö, Jmt</t>
+          <t>Höbrännflon, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>469031</v>
+        <v>469354</v>
       </c>
       <c r="R28" t="n">
-        <v>7077964</v>
+        <v>7077833</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3497,17 +3697,27 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2025-09-09</t>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2025-09-09</t>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3533,51 +3743,51 @@
       <c r="AY28" t="inlineStr"/>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128346620</t>
+          <t>https://artportalen.se/Sighting/135192148</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128346621</v>
+        <v>135192171</v>
       </c>
       <c r="B29" t="n">
-        <v>57953</v>
+        <v>79441</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Höbrännflon sö, Jmt</t>
+          <t>Höbrännflon, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>469043</v>
+        <v>469197</v>
       </c>
       <c r="R29" t="n">
-        <v>7077965</v>
+        <v>7078034</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3604,17 +3814,27 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2025-09-09</t>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2025-09-09</t>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3640,16 +3860,16 @@
       <c r="AY29" t="inlineStr"/>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128346621</t>
+          <t>https://artportalen.se/Sighting/135192171</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128346622</v>
+        <v>128346632</v>
       </c>
       <c r="B30" t="n">
-        <v>57953</v>
+        <v>80432</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3657,21 +3877,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3681,10 +3901,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>469052</v>
+        <v>468909</v>
       </c>
       <c r="R30" t="n">
-        <v>7077969</v>
+        <v>7077971</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3719,11 +3939,6 @@
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Ringhack färska</t>
-        </is>
-      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
@@ -3747,33 +3962,33 @@
       <c r="AY30" t="inlineStr"/>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128346622</t>
+          <t>https://artportalen.se/Sighting/128346632</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128346623</v>
+        <v>135192073</v>
       </c>
       <c r="B31" t="n">
-        <v>57953</v>
+        <v>57977</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -3781,17 +3996,33 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I31" t="inlineStr"/>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Höbrännflon sö, Jmt</t>
+          <t>Höbrännflon, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>469057</v>
+        <v>469093</v>
       </c>
       <c r="R31" t="n">
-        <v>7077970</v>
+        <v>7078018</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3818,17 +4049,22 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2025-09-09</t>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2025-09-09</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Ringhack färska</t>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3854,13 +4090,13 @@
       <c r="AY31" t="inlineStr"/>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128346623</t>
+          <t>https://artportalen.se/Sighting/135192073</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128346624</v>
+        <v>128346579</v>
       </c>
       <c r="B32" t="n">
         <v>57953</v>
@@ -3895,10 +4131,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>469057</v>
+        <v>469196</v>
       </c>
       <c r="R32" t="n">
-        <v>7077968</v>
+        <v>7077970</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3935,7 +4171,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3961,13 +4197,13 @@
       <c r="AY32" t="inlineStr"/>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128346624</t>
+          <t>https://artportalen.se/Sighting/128346579</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128346625</v>
+        <v>128346580</v>
       </c>
       <c r="B33" t="n">
         <v>57953</v>
@@ -4002,10 +4238,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>469169</v>
+        <v>469066</v>
       </c>
       <c r="R33" t="n">
-        <v>7078067</v>
+        <v>7077948</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4068,38 +4304,38 @@
       <c r="AY33" t="inlineStr"/>
       <c r="AZ33" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128346625</t>
+          <t>https://artportalen.se/Sighting/128346580</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128346628</v>
+        <v>128346581</v>
       </c>
       <c r="B34" t="n">
-        <v>97989</v>
+        <v>57953</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>221941</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4109,10 +4345,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>468931</v>
+        <v>468873</v>
       </c>
       <c r="R34" t="n">
-        <v>7077743</v>
+        <v>7077929</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4147,6 +4383,11 @@
           <t>2025-09-09</t>
         </is>
       </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
+        </is>
+      </c>
       <c r="AD34" t="b">
         <v>0</v>
       </c>
@@ -4169,6 +4410,7195 @@
       </c>
       <c r="AY34" t="inlineStr"/>
       <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128346581</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>128346582</v>
+      </c>
+      <c r="B35" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Höbrännflon sö, Jmt</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>468940</v>
+      </c>
+      <c r="R35" t="n">
+        <v>7077734</v>
+      </c>
+      <c r="S35" t="n">
+        <v>10</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128346582</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>128346583</v>
+      </c>
+      <c r="B36" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Höbrännflon sö, Jmt</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>468969</v>
+      </c>
+      <c r="R36" t="n">
+        <v>7077711</v>
+      </c>
+      <c r="S36" t="n">
+        <v>10</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128346583</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>128346585</v>
+      </c>
+      <c r="B37" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Höbrännflon sö, Jmt</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>468968</v>
+      </c>
+      <c r="R37" t="n">
+        <v>7077679</v>
+      </c>
+      <c r="S37" t="n">
+        <v>10</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128346585</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>128346586</v>
+      </c>
+      <c r="B38" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Höbrännflon sö, Jmt</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>468984</v>
+      </c>
+      <c r="R38" t="n">
+        <v>7077636</v>
+      </c>
+      <c r="S38" t="n">
+        <v>10</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128346586</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>128346607</v>
+      </c>
+      <c r="B39" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Höbrännflon sö, Jmt</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>468839</v>
+      </c>
+      <c r="R39" t="n">
+        <v>7077932</v>
+      </c>
+      <c r="S39" t="n">
+        <v>10</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128346607</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>128346608</v>
+      </c>
+      <c r="B40" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Höbrännflon sö, Jmt</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>468870</v>
+      </c>
+      <c r="R40" t="n">
+        <v>7077959</v>
+      </c>
+      <c r="S40" t="n">
+        <v>10</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128346608</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>128346609</v>
+      </c>
+      <c r="B41" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Höbrännflon sö, Jmt</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>468906</v>
+      </c>
+      <c r="R41" t="n">
+        <v>7077980</v>
+      </c>
+      <c r="S41" t="n">
+        <v>10</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128346609</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>128346610</v>
+      </c>
+      <c r="B42" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Höbrännflon sö, Jmt</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>468891</v>
+      </c>
+      <c r="R42" t="n">
+        <v>7077967</v>
+      </c>
+      <c r="S42" t="n">
+        <v>10</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Ringhack färska 2 träd</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128346610</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>128346611</v>
+      </c>
+      <c r="B43" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Höbrännflon sö, Jmt</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>468913</v>
+      </c>
+      <c r="R43" t="n">
+        <v>7077967</v>
+      </c>
+      <c r="S43" t="n">
+        <v>10</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128346611</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>128346612</v>
+      </c>
+      <c r="B44" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Höbrännflon sö, Jmt</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>468917</v>
+      </c>
+      <c r="R44" t="n">
+        <v>7077967</v>
+      </c>
+      <c r="S44" t="n">
+        <v>10</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128346612</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>128346613</v>
+      </c>
+      <c r="B45" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Höbrännflon sö, Jmt</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>468925</v>
+      </c>
+      <c r="R45" t="n">
+        <v>7077966</v>
+      </c>
+      <c r="S45" t="n">
+        <v>10</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128346613</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>128346614</v>
+      </c>
+      <c r="B46" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Höbrännflon sö, Jmt</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>468931</v>
+      </c>
+      <c r="R46" t="n">
+        <v>7077965</v>
+      </c>
+      <c r="S46" t="n">
+        <v>10</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128346614</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>128346615</v>
+      </c>
+      <c r="B47" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Höbrännflon sö, Jmt</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>468940</v>
+      </c>
+      <c r="R47" t="n">
+        <v>7077960</v>
+      </c>
+      <c r="S47" t="n">
+        <v>10</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128346615</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>128346616</v>
+      </c>
+      <c r="B48" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Höbrännflon sö, Jmt</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>468979</v>
+      </c>
+      <c r="R48" t="n">
+        <v>7077962</v>
+      </c>
+      <c r="S48" t="n">
+        <v>10</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128346616</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>128346617</v>
+      </c>
+      <c r="B49" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Höbrännflon sö, Jmt</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>468994</v>
+      </c>
+      <c r="R49" t="n">
+        <v>7077960</v>
+      </c>
+      <c r="S49" t="n">
+        <v>10</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128346617</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>128346618</v>
+      </c>
+      <c r="B50" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Höbrännflon sö, Jmt</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>469012</v>
+      </c>
+      <c r="R50" t="n">
+        <v>7077965</v>
+      </c>
+      <c r="S50" t="n">
+        <v>10</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128346618</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>128346619</v>
+      </c>
+      <c r="B51" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Höbrännflon sö, Jmt</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>469014</v>
+      </c>
+      <c r="R51" t="n">
+        <v>7077963</v>
+      </c>
+      <c r="S51" t="n">
+        <v>10</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
+        </is>
+      </c>
+      <c r="AD51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128346619</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>128346620</v>
+      </c>
+      <c r="B52" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Höbrännflon sö, Jmt</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>469031</v>
+      </c>
+      <c r="R52" t="n">
+        <v>7077964</v>
+      </c>
+      <c r="S52" t="n">
+        <v>10</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
+        </is>
+      </c>
+      <c r="AD52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128346620</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>128346621</v>
+      </c>
+      <c r="B53" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>Höbrännflon sö, Jmt</t>
+        </is>
+      </c>
+      <c r="Q53" t="n">
+        <v>469043</v>
+      </c>
+      <c r="R53" t="n">
+        <v>7077965</v>
+      </c>
+      <c r="S53" t="n">
+        <v>10</v>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
+        </is>
+      </c>
+      <c r="AD53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT53" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128346621</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>128346622</v>
+      </c>
+      <c r="B54" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>Höbrännflon sö, Jmt</t>
+        </is>
+      </c>
+      <c r="Q54" t="n">
+        <v>469052</v>
+      </c>
+      <c r="R54" t="n">
+        <v>7077969</v>
+      </c>
+      <c r="S54" t="n">
+        <v>10</v>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
+        </is>
+      </c>
+      <c r="AD54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT54" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128346622</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>128346623</v>
+      </c>
+      <c r="B55" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>Höbrännflon sö, Jmt</t>
+        </is>
+      </c>
+      <c r="Q55" t="n">
+        <v>469057</v>
+      </c>
+      <c r="R55" t="n">
+        <v>7077970</v>
+      </c>
+      <c r="S55" t="n">
+        <v>10</v>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
+        </is>
+      </c>
+      <c r="AD55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT55" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX55" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128346623</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>128346624</v>
+      </c>
+      <c r="B56" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>Höbrännflon sö, Jmt</t>
+        </is>
+      </c>
+      <c r="Q56" t="n">
+        <v>469057</v>
+      </c>
+      <c r="R56" t="n">
+        <v>7077968</v>
+      </c>
+      <c r="S56" t="n">
+        <v>10</v>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
+        </is>
+      </c>
+      <c r="AD56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT56" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128346624</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>128346625</v>
+      </c>
+      <c r="B57" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>Höbrännflon sö, Jmt</t>
+        </is>
+      </c>
+      <c r="Q57" t="n">
+        <v>469169</v>
+      </c>
+      <c r="R57" t="n">
+        <v>7078067</v>
+      </c>
+      <c r="S57" t="n">
+        <v>10</v>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
+      <c r="AD57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT57" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX57" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128346625</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>135192022</v>
+      </c>
+      <c r="B58" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>Höbrännflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q58" t="n">
+        <v>469168</v>
+      </c>
+      <c r="R58" t="n">
+        <v>7078178</v>
+      </c>
+      <c r="S58" t="n">
+        <v>10</v>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="Z58" t="inlineStr">
+        <is>
+          <t>09:29</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="AB58" t="inlineStr">
+        <is>
+          <t>09:29</t>
+        </is>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>äldre ringhack</t>
+        </is>
+      </c>
+      <c r="AD58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT58" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX58" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135192022</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>135192026</v>
+      </c>
+      <c r="B59" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>Höbrännflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q59" t="n">
+        <v>469186</v>
+      </c>
+      <c r="R59" t="n">
+        <v>7078140</v>
+      </c>
+      <c r="S59" t="n">
+        <v>10</v>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="Z59" t="inlineStr">
+        <is>
+          <t>09:38</t>
+        </is>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="AB59" t="inlineStr">
+        <is>
+          <t>09:38</t>
+        </is>
+      </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>äldre ringhack</t>
+        </is>
+      </c>
+      <c r="AD59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT59" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX59" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135192026</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>135192030</v>
+      </c>
+      <c r="B60" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>Höbrännflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q60" t="n">
+        <v>469177</v>
+      </c>
+      <c r="R60" t="n">
+        <v>7078094</v>
+      </c>
+      <c r="S60" t="n">
+        <v>10</v>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="Z60" t="inlineStr">
+        <is>
+          <t>09:48</t>
+        </is>
+      </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="AB60" t="inlineStr">
+        <is>
+          <t>09:48</t>
+        </is>
+      </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>äldre ringhack</t>
+        </is>
+      </c>
+      <c r="AD60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT60" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX60" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135192030</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>135192045</v>
+      </c>
+      <c r="B61" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>Höbrännflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q61" t="n">
+        <v>468993</v>
+      </c>
+      <c r="R61" t="n">
+        <v>7078287</v>
+      </c>
+      <c r="S61" t="n">
+        <v>10</v>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y61" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="Z61" t="inlineStr">
+        <is>
+          <t>10:18</t>
+        </is>
+      </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="AB61" t="inlineStr">
+        <is>
+          <t>10:18</t>
+        </is>
+      </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>ringhack</t>
+        </is>
+      </c>
+      <c r="AD61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT61" t="inlineStr"/>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX61" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135192045</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>135192047</v>
+      </c>
+      <c r="B62" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>Höbrännflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q62" t="n">
+        <v>468901</v>
+      </c>
+      <c r="R62" t="n">
+        <v>7078371</v>
+      </c>
+      <c r="S62" t="n">
+        <v>10</v>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="Z62" t="inlineStr">
+        <is>
+          <t>10:25</t>
+        </is>
+      </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="AB62" t="inlineStr">
+        <is>
+          <t>10:25</t>
+        </is>
+      </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>äldre ringhack</t>
+        </is>
+      </c>
+      <c r="AD62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT62" t="inlineStr"/>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX62" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135192047</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>135192048</v>
+      </c>
+      <c r="B63" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>Höbrännflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q63" t="n">
+        <v>468891</v>
+      </c>
+      <c r="R63" t="n">
+        <v>7078390</v>
+      </c>
+      <c r="S63" t="n">
+        <v>10</v>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="Z63" t="inlineStr">
+        <is>
+          <t>10:28</t>
+        </is>
+      </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="AB63" t="inlineStr">
+        <is>
+          <t>10:28</t>
+        </is>
+      </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>färska o och äldre ringhack</t>
+        </is>
+      </c>
+      <c r="AD63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT63" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX63" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135192048</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>135192050</v>
+      </c>
+      <c r="B64" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>Höbrännflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q64" t="n">
+        <v>468864</v>
+      </c>
+      <c r="R64" t="n">
+        <v>7078369</v>
+      </c>
+      <c r="S64" t="n">
+        <v>10</v>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="Z64" t="inlineStr">
+        <is>
+          <t>10:31</t>
+        </is>
+      </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="AB64" t="inlineStr">
+        <is>
+          <t>10:31</t>
+        </is>
+      </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>färska och äldre ringhack</t>
+        </is>
+      </c>
+      <c r="AD64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT64" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX64" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135192050</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>135192056</v>
+      </c>
+      <c r="B65" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>Höbrännflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q65" t="n">
+        <v>468923</v>
+      </c>
+      <c r="R65" t="n">
+        <v>7078311</v>
+      </c>
+      <c r="S65" t="n">
+        <v>10</v>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y65" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="Z65" t="inlineStr">
+        <is>
+          <t>10:37</t>
+        </is>
+      </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="AB65" t="inlineStr">
+        <is>
+          <t>10:37</t>
+        </is>
+      </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>äldre ringhack</t>
+        </is>
+      </c>
+      <c r="AD65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT65" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX65" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135192056</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>135192074</v>
+      </c>
+      <c r="B66" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>Höbrännflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q66" t="n">
+        <v>469051</v>
+      </c>
+      <c r="R66" t="n">
+        <v>7077912</v>
+      </c>
+      <c r="S66" t="n">
+        <v>10</v>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W66" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y66" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="Z66" t="inlineStr">
+        <is>
+          <t>11:05</t>
+        </is>
+      </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="AB66" t="inlineStr">
+        <is>
+          <t>11:05</t>
+        </is>
+      </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>äldre ringhack</t>
+        </is>
+      </c>
+      <c r="AD66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT66" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX66" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135192074</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>135192077</v>
+      </c>
+      <c r="B67" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>Höbrännflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q67" t="n">
+        <v>469002</v>
+      </c>
+      <c r="R67" t="n">
+        <v>7077895</v>
+      </c>
+      <c r="S67" t="n">
+        <v>10</v>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W67" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y67" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="Z67" t="inlineStr">
+        <is>
+          <t>11:09</t>
+        </is>
+      </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="AB67" t="inlineStr">
+        <is>
+          <t>11:09</t>
+        </is>
+      </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>äldre ringhack</t>
+        </is>
+      </c>
+      <c r="AD67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT67" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX67" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135192077</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>135192079</v>
+      </c>
+      <c r="B68" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr"/>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>Höbrännflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q68" t="n">
+        <v>469028</v>
+      </c>
+      <c r="R68" t="n">
+        <v>7077856</v>
+      </c>
+      <c r="S68" t="n">
+        <v>10</v>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W68" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y68" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="Z68" t="inlineStr">
+        <is>
+          <t>11:12</t>
+        </is>
+      </c>
+      <c r="AA68" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="AB68" t="inlineStr">
+        <is>
+          <t>11:12</t>
+        </is>
+      </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>äldre ringhack</t>
+        </is>
+      </c>
+      <c r="AD68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT68" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX68" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135192079</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>135192085</v>
+      </c>
+      <c r="B69" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>Höbrännflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q69" t="n">
+        <v>468941</v>
+      </c>
+      <c r="R69" t="n">
+        <v>7077921</v>
+      </c>
+      <c r="S69" t="n">
+        <v>10</v>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W69" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y69" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="Z69" t="inlineStr">
+        <is>
+          <t>11:18</t>
+        </is>
+      </c>
+      <c r="AA69" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="AB69" t="inlineStr">
+        <is>
+          <t>11:18</t>
+        </is>
+      </c>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>äldre ringhack</t>
+        </is>
+      </c>
+      <c r="AD69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT69" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX69" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135192085</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>135192088</v>
+      </c>
+      <c r="B70" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>Höbrännflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q70" t="n">
+        <v>468900</v>
+      </c>
+      <c r="R70" t="n">
+        <v>7077908</v>
+      </c>
+      <c r="S70" t="n">
+        <v>10</v>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W70" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y70" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="Z70" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="AA70" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="AB70" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="AC70" t="inlineStr">
+        <is>
+          <t>färska och äldre ringhack</t>
+        </is>
+      </c>
+      <c r="AD70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT70" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX70" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135192088</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>135192093</v>
+      </c>
+      <c r="B71" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr"/>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>Höbrännflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q71" t="n">
+        <v>468841</v>
+      </c>
+      <c r="R71" t="n">
+        <v>7077895</v>
+      </c>
+      <c r="S71" t="n">
+        <v>10</v>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W71" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y71" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="Z71" t="inlineStr">
+        <is>
+          <t>11:28</t>
+        </is>
+      </c>
+      <c r="AA71" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="AB71" t="inlineStr">
+        <is>
+          <t>11:28</t>
+        </is>
+      </c>
+      <c r="AC71" t="inlineStr">
+        <is>
+          <t>äldre ringhack</t>
+        </is>
+      </c>
+      <c r="AD71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT71" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX71" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135192093</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>135192095</v>
+      </c>
+      <c r="B72" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr"/>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>Höbrännflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q72" t="n">
+        <v>468832</v>
+      </c>
+      <c r="R72" t="n">
+        <v>7077861</v>
+      </c>
+      <c r="S72" t="n">
+        <v>10</v>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V72" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W72" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y72" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="Z72" t="inlineStr">
+        <is>
+          <t>11:32</t>
+        </is>
+      </c>
+      <c r="AA72" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="AB72" t="inlineStr">
+        <is>
+          <t>11:32</t>
+        </is>
+      </c>
+      <c r="AC72" t="inlineStr">
+        <is>
+          <t>äldre ringhack</t>
+        </is>
+      </c>
+      <c r="AD72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT72" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX72" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135192095</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>135192112</v>
+      </c>
+      <c r="B73" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E73" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr"/>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>Höbrännflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q73" t="n">
+        <v>469029</v>
+      </c>
+      <c r="R73" t="n">
+        <v>7077764</v>
+      </c>
+      <c r="S73" t="n">
+        <v>10</v>
+      </c>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V73" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W73" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y73" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="Z73" t="inlineStr">
+        <is>
+          <t>11:55</t>
+        </is>
+      </c>
+      <c r="AA73" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="AB73" t="inlineStr">
+        <is>
+          <t>11:55</t>
+        </is>
+      </c>
+      <c r="AC73" t="inlineStr">
+        <is>
+          <t>äldre ringhack</t>
+        </is>
+      </c>
+      <c r="AD73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT73" t="inlineStr"/>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX73" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY73" t="inlineStr"/>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135192112</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>135192116</v>
+      </c>
+      <c r="B74" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E74" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr"/>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>Höbrännflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q74" t="n">
+        <v>469092</v>
+      </c>
+      <c r="R74" t="n">
+        <v>7077868</v>
+      </c>
+      <c r="S74" t="n">
+        <v>10</v>
+      </c>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V74" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W74" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y74" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="Z74" t="inlineStr">
+        <is>
+          <t>12:02</t>
+        </is>
+      </c>
+      <c r="AA74" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="AB74" t="inlineStr">
+        <is>
+          <t>12:02</t>
+        </is>
+      </c>
+      <c r="AC74" t="inlineStr">
+        <is>
+          <t>äldre ringhack</t>
+        </is>
+      </c>
+      <c r="AD74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT74" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX74" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY74" t="inlineStr"/>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135192116</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>135192118</v>
+      </c>
+      <c r="B75" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E75" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr"/>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t>Höbrännflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q75" t="n">
+        <v>469121</v>
+      </c>
+      <c r="R75" t="n">
+        <v>7077852</v>
+      </c>
+      <c r="S75" t="n">
+        <v>10</v>
+      </c>
+      <c r="T75" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U75" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V75" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W75" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y75" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="Z75" t="inlineStr">
+        <is>
+          <t>12:04</t>
+        </is>
+      </c>
+      <c r="AA75" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="AB75" t="inlineStr">
+        <is>
+          <t>12:04</t>
+        </is>
+      </c>
+      <c r="AC75" t="inlineStr">
+        <is>
+          <t>äldre ringhack</t>
+        </is>
+      </c>
+      <c r="AD75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT75" t="inlineStr"/>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX75" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY75" t="inlineStr"/>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135192118</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>135192119</v>
+      </c>
+      <c r="B76" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E76" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr"/>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t>Höbrännflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q76" t="n">
+        <v>469139</v>
+      </c>
+      <c r="R76" t="n">
+        <v>7077825</v>
+      </c>
+      <c r="S76" t="n">
+        <v>10</v>
+      </c>
+      <c r="T76" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U76" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V76" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W76" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y76" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="Z76" t="inlineStr">
+        <is>
+          <t>12:07</t>
+        </is>
+      </c>
+      <c r="AA76" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="AB76" t="inlineStr">
+        <is>
+          <t>12:07</t>
+        </is>
+      </c>
+      <c r="AC76" t="inlineStr">
+        <is>
+          <t>äldre ringhack</t>
+        </is>
+      </c>
+      <c r="AD76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT76" t="inlineStr"/>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX76" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY76" t="inlineStr"/>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135192119</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>135192123</v>
+      </c>
+      <c r="B77" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E77" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr"/>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P77" t="inlineStr">
+        <is>
+          <t>Höbrännflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q77" t="n">
+        <v>469108</v>
+      </c>
+      <c r="R77" t="n">
+        <v>7077950</v>
+      </c>
+      <c r="S77" t="n">
+        <v>10</v>
+      </c>
+      <c r="T77" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U77" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V77" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W77" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y77" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="Z77" t="inlineStr">
+        <is>
+          <t>12:11</t>
+        </is>
+      </c>
+      <c r="AA77" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="AB77" t="inlineStr">
+        <is>
+          <t>12:11</t>
+        </is>
+      </c>
+      <c r="AC77" t="inlineStr">
+        <is>
+          <t>färska ringhack</t>
+        </is>
+      </c>
+      <c r="AD77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT77" t="inlineStr"/>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX77" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY77" t="inlineStr"/>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135192123</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>135192124</v>
+      </c>
+      <c r="B78" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E78" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr"/>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P78" t="inlineStr">
+        <is>
+          <t>Höbrännflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q78" t="n">
+        <v>469109</v>
+      </c>
+      <c r="R78" t="n">
+        <v>7077945</v>
+      </c>
+      <c r="S78" t="n">
+        <v>10</v>
+      </c>
+      <c r="T78" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U78" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V78" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W78" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y78" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="Z78" t="inlineStr">
+        <is>
+          <t>12:12</t>
+        </is>
+      </c>
+      <c r="AA78" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="AB78" t="inlineStr">
+        <is>
+          <t>12:12</t>
+        </is>
+      </c>
+      <c r="AC78" t="inlineStr">
+        <is>
+          <t>färska ringhack</t>
+        </is>
+      </c>
+      <c r="AD78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT78" t="inlineStr"/>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX78" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY78" t="inlineStr"/>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135192124</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>135192125</v>
+      </c>
+      <c r="B79" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E79" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr"/>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P79" t="inlineStr">
+        <is>
+          <t>Höbrännflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q79" t="n">
+        <v>469118</v>
+      </c>
+      <c r="R79" t="n">
+        <v>7077938</v>
+      </c>
+      <c r="S79" t="n">
+        <v>10</v>
+      </c>
+      <c r="T79" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U79" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V79" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W79" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y79" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="Z79" t="inlineStr">
+        <is>
+          <t>12:12</t>
+        </is>
+      </c>
+      <c r="AA79" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="AB79" t="inlineStr">
+        <is>
+          <t>12:12</t>
+        </is>
+      </c>
+      <c r="AC79" t="inlineStr">
+        <is>
+          <t>färska ringhack</t>
+        </is>
+      </c>
+      <c r="AD79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT79" t="inlineStr"/>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX79" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY79" t="inlineStr"/>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135192125</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>135192127</v>
+      </c>
+      <c r="B80" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E80" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr"/>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P80" t="inlineStr">
+        <is>
+          <t>Höbrännflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q80" t="n">
+        <v>469140</v>
+      </c>
+      <c r="R80" t="n">
+        <v>7077913</v>
+      </c>
+      <c r="S80" t="n">
+        <v>10</v>
+      </c>
+      <c r="T80" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U80" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V80" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W80" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y80" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="Z80" t="inlineStr">
+        <is>
+          <t>12:13</t>
+        </is>
+      </c>
+      <c r="AA80" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="AB80" t="inlineStr">
+        <is>
+          <t>12:13</t>
+        </is>
+      </c>
+      <c r="AC80" t="inlineStr">
+        <is>
+          <t>färska ringhack</t>
+        </is>
+      </c>
+      <c r="AD80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT80" t="inlineStr"/>
+      <c r="AW80" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX80" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY80" t="inlineStr"/>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135192127</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>135192128</v>
+      </c>
+      <c r="B81" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E81" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr"/>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P81" t="inlineStr">
+        <is>
+          <t>Höbrännflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q81" t="n">
+        <v>469149</v>
+      </c>
+      <c r="R81" t="n">
+        <v>7077895</v>
+      </c>
+      <c r="S81" t="n">
+        <v>10</v>
+      </c>
+      <c r="T81" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U81" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V81" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W81" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y81" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="Z81" t="inlineStr">
+        <is>
+          <t>12:14</t>
+        </is>
+      </c>
+      <c r="AA81" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="AB81" t="inlineStr">
+        <is>
+          <t>12:14</t>
+        </is>
+      </c>
+      <c r="AC81" t="inlineStr">
+        <is>
+          <t>färska ringhack</t>
+        </is>
+      </c>
+      <c r="AD81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT81" t="inlineStr"/>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX81" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY81" t="inlineStr"/>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135192128</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>135192130</v>
+      </c>
+      <c r="B82" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E82" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr"/>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P82" t="inlineStr">
+        <is>
+          <t>Höbrännflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q82" t="n">
+        <v>469158</v>
+      </c>
+      <c r="R82" t="n">
+        <v>7077852</v>
+      </c>
+      <c r="S82" t="n">
+        <v>10</v>
+      </c>
+      <c r="T82" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U82" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V82" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W82" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y82" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="Z82" t="inlineStr">
+        <is>
+          <t>12:15</t>
+        </is>
+      </c>
+      <c r="AA82" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="AB82" t="inlineStr">
+        <is>
+          <t>12:15</t>
+        </is>
+      </c>
+      <c r="AC82" t="inlineStr">
+        <is>
+          <t>färska ringhack</t>
+        </is>
+      </c>
+      <c r="AD82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT82" t="inlineStr"/>
+      <c r="AW82" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX82" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY82" t="inlineStr"/>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135192130</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>135192131</v>
+      </c>
+      <c r="B83" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E83" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr"/>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P83" t="inlineStr">
+        <is>
+          <t>Höbrännflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q83" t="n">
+        <v>469166</v>
+      </c>
+      <c r="R83" t="n">
+        <v>7077841</v>
+      </c>
+      <c r="S83" t="n">
+        <v>10</v>
+      </c>
+      <c r="T83" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U83" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V83" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W83" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y83" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="Z83" t="inlineStr">
+        <is>
+          <t>12:16</t>
+        </is>
+      </c>
+      <c r="AA83" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="AB83" t="inlineStr">
+        <is>
+          <t>12:16</t>
+        </is>
+      </c>
+      <c r="AC83" t="inlineStr">
+        <is>
+          <t>färska ringhack</t>
+        </is>
+      </c>
+      <c r="AD83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT83" t="inlineStr"/>
+      <c r="AW83" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX83" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY83" t="inlineStr"/>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135192131</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>135192132</v>
+      </c>
+      <c r="B84" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E84" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr"/>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P84" t="inlineStr">
+        <is>
+          <t>Höbrännflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q84" t="n">
+        <v>469163</v>
+      </c>
+      <c r="R84" t="n">
+        <v>7077822</v>
+      </c>
+      <c r="S84" t="n">
+        <v>10</v>
+      </c>
+      <c r="T84" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U84" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V84" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W84" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y84" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="Z84" t="inlineStr">
+        <is>
+          <t>12:17</t>
+        </is>
+      </c>
+      <c r="AA84" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="AB84" t="inlineStr">
+        <is>
+          <t>12:17</t>
+        </is>
+      </c>
+      <c r="AC84" t="inlineStr">
+        <is>
+          <t>färska ringhack</t>
+        </is>
+      </c>
+      <c r="AD84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT84" t="inlineStr"/>
+      <c r="AW84" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX84" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY84" t="inlineStr"/>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135192132</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>135192134</v>
+      </c>
+      <c r="B85" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E85" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr"/>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P85" t="inlineStr">
+        <is>
+          <t>Höbrännflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q85" t="n">
+        <v>469172</v>
+      </c>
+      <c r="R85" t="n">
+        <v>7077811</v>
+      </c>
+      <c r="S85" t="n">
+        <v>10</v>
+      </c>
+      <c r="T85" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U85" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V85" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W85" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y85" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="Z85" t="inlineStr">
+        <is>
+          <t>12:17</t>
+        </is>
+      </c>
+      <c r="AA85" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="AB85" t="inlineStr">
+        <is>
+          <t>12:17</t>
+        </is>
+      </c>
+      <c r="AC85" t="inlineStr">
+        <is>
+          <t>färska ringhack</t>
+        </is>
+      </c>
+      <c r="AD85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT85" t="inlineStr"/>
+      <c r="AW85" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX85" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY85" t="inlineStr"/>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135192134</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>135192135</v>
+      </c>
+      <c r="B86" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E86" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr"/>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P86" t="inlineStr">
+        <is>
+          <t>Höbrännflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q86" t="n">
+        <v>469180</v>
+      </c>
+      <c r="R86" t="n">
+        <v>7077818</v>
+      </c>
+      <c r="S86" t="n">
+        <v>10</v>
+      </c>
+      <c r="T86" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U86" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V86" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W86" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y86" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="Z86" t="inlineStr">
+        <is>
+          <t>12:18</t>
+        </is>
+      </c>
+      <c r="AA86" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="AB86" t="inlineStr">
+        <is>
+          <t>12:18</t>
+        </is>
+      </c>
+      <c r="AC86" t="inlineStr">
+        <is>
+          <t>äldre ringhack</t>
+        </is>
+      </c>
+      <c r="AD86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT86" t="inlineStr"/>
+      <c r="AW86" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX86" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY86" t="inlineStr"/>
+      <c r="AZ86" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135192135</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>135192136</v>
+      </c>
+      <c r="B87" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E87" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr"/>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P87" t="inlineStr">
+        <is>
+          <t>Höbrännflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q87" t="n">
+        <v>469176</v>
+      </c>
+      <c r="R87" t="n">
+        <v>7077799</v>
+      </c>
+      <c r="S87" t="n">
+        <v>10</v>
+      </c>
+      <c r="T87" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U87" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V87" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W87" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y87" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="Z87" t="inlineStr">
+        <is>
+          <t>12:19</t>
+        </is>
+      </c>
+      <c r="AA87" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="AB87" t="inlineStr">
+        <is>
+          <t>12:19</t>
+        </is>
+      </c>
+      <c r="AC87" t="inlineStr">
+        <is>
+          <t>färska ringhack</t>
+        </is>
+      </c>
+      <c r="AD87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT87" t="inlineStr"/>
+      <c r="AW87" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX87" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY87" t="inlineStr"/>
+      <c r="AZ87" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135192136</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>135192137</v>
+      </c>
+      <c r="B88" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E88" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr"/>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P88" t="inlineStr">
+        <is>
+          <t>Höbrännflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q88" t="n">
+        <v>469181</v>
+      </c>
+      <c r="R88" t="n">
+        <v>7077798</v>
+      </c>
+      <c r="S88" t="n">
+        <v>10</v>
+      </c>
+      <c r="T88" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U88" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V88" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W88" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y88" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="Z88" t="inlineStr">
+        <is>
+          <t>12:20</t>
+        </is>
+      </c>
+      <c r="AA88" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="AB88" t="inlineStr">
+        <is>
+          <t>12:20</t>
+        </is>
+      </c>
+      <c r="AC88" t="inlineStr">
+        <is>
+          <t>färska ringhack</t>
+        </is>
+      </c>
+      <c r="AD88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT88" t="inlineStr"/>
+      <c r="AW88" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX88" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY88" t="inlineStr"/>
+      <c r="AZ88" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135192137</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>135192151</v>
+      </c>
+      <c r="B89" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E89" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr"/>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P89" t="inlineStr">
+        <is>
+          <t>Höbrännflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q89" t="n">
+        <v>469393</v>
+      </c>
+      <c r="R89" t="n">
+        <v>7077846</v>
+      </c>
+      <c r="S89" t="n">
+        <v>10</v>
+      </c>
+      <c r="T89" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U89" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V89" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W89" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y89" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="Z89" t="inlineStr">
+        <is>
+          <t>12:42</t>
+        </is>
+      </c>
+      <c r="AA89" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="AB89" t="inlineStr">
+        <is>
+          <t>12:42</t>
+        </is>
+      </c>
+      <c r="AC89" t="inlineStr">
+        <is>
+          <t>äldre ringhack</t>
+        </is>
+      </c>
+      <c r="AD89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT89" t="inlineStr"/>
+      <c r="AW89" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX89" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY89" t="inlineStr"/>
+      <c r="AZ89" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135192151</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>135192152</v>
+      </c>
+      <c r="B90" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E90" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr"/>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P90" t="inlineStr">
+        <is>
+          <t>Höbrännflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q90" t="n">
+        <v>469356</v>
+      </c>
+      <c r="R90" t="n">
+        <v>7077867</v>
+      </c>
+      <c r="S90" t="n">
+        <v>10</v>
+      </c>
+      <c r="T90" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U90" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V90" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W90" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y90" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="Z90" t="inlineStr">
+        <is>
+          <t>12:45</t>
+        </is>
+      </c>
+      <c r="AA90" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="AB90" t="inlineStr">
+        <is>
+          <t>12:45</t>
+        </is>
+      </c>
+      <c r="AC90" t="inlineStr">
+        <is>
+          <t>äldre ringhack</t>
+        </is>
+      </c>
+      <c r="AD90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT90" t="inlineStr"/>
+      <c r="AW90" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX90" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY90" t="inlineStr"/>
+      <c r="AZ90" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135192152</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>135192153</v>
+      </c>
+      <c r="B91" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E91" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr"/>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P91" t="inlineStr">
+        <is>
+          <t>Höbrännflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q91" t="n">
+        <v>469347</v>
+      </c>
+      <c r="R91" t="n">
+        <v>7077869</v>
+      </c>
+      <c r="S91" t="n">
+        <v>10</v>
+      </c>
+      <c r="T91" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U91" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V91" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W91" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y91" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="Z91" t="inlineStr">
+        <is>
+          <t>12:46</t>
+        </is>
+      </c>
+      <c r="AA91" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="AB91" t="inlineStr">
+        <is>
+          <t>12:46</t>
+        </is>
+      </c>
+      <c r="AC91" t="inlineStr">
+        <is>
+          <t>äldre ringhack</t>
+        </is>
+      </c>
+      <c r="AD91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT91" t="inlineStr"/>
+      <c r="AW91" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX91" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY91" t="inlineStr"/>
+      <c r="AZ91" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135192153</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>135192157</v>
+      </c>
+      <c r="B92" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E92" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr"/>
+      <c r="M92" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P92" t="inlineStr">
+        <is>
+          <t>Höbrännflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q92" t="n">
+        <v>469381</v>
+      </c>
+      <c r="R92" t="n">
+        <v>7077873</v>
+      </c>
+      <c r="S92" t="n">
+        <v>10</v>
+      </c>
+      <c r="T92" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U92" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V92" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W92" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y92" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="Z92" t="inlineStr">
+        <is>
+          <t>12:52</t>
+        </is>
+      </c>
+      <c r="AA92" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="AB92" t="inlineStr">
+        <is>
+          <t>12:52</t>
+        </is>
+      </c>
+      <c r="AC92" t="inlineStr">
+        <is>
+          <t>äldre ringhack</t>
+        </is>
+      </c>
+      <c r="AD92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT92" t="inlineStr"/>
+      <c r="AW92" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX92" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY92" t="inlineStr"/>
+      <c r="AZ92" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135192157</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>135192158</v>
+      </c>
+      <c r="B93" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E93" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr"/>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P93" t="inlineStr">
+        <is>
+          <t>Höbrännflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q93" t="n">
+        <v>469401</v>
+      </c>
+      <c r="R93" t="n">
+        <v>7077887</v>
+      </c>
+      <c r="S93" t="n">
+        <v>10</v>
+      </c>
+      <c r="T93" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U93" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V93" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W93" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y93" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="Z93" t="inlineStr">
+        <is>
+          <t>12:54</t>
+        </is>
+      </c>
+      <c r="AA93" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="AB93" t="inlineStr">
+        <is>
+          <t>12:54</t>
+        </is>
+      </c>
+      <c r="AC93" t="inlineStr">
+        <is>
+          <t>äldre ringhack</t>
+        </is>
+      </c>
+      <c r="AD93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT93" t="inlineStr"/>
+      <c r="AW93" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX93" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY93" t="inlineStr"/>
+      <c r="AZ93" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135192158</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>135192161</v>
+      </c>
+      <c r="B94" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E94" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr"/>
+      <c r="M94" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P94" t="inlineStr">
+        <is>
+          <t>Höbrännflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q94" t="n">
+        <v>469388</v>
+      </c>
+      <c r="R94" t="n">
+        <v>7077920</v>
+      </c>
+      <c r="S94" t="n">
+        <v>10</v>
+      </c>
+      <c r="T94" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U94" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V94" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W94" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y94" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="Z94" t="inlineStr">
+        <is>
+          <t>12:56</t>
+        </is>
+      </c>
+      <c r="AA94" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="AB94" t="inlineStr">
+        <is>
+          <t>12:56</t>
+        </is>
+      </c>
+      <c r="AC94" t="inlineStr">
+        <is>
+          <t>äldre ringhack</t>
+        </is>
+      </c>
+      <c r="AD94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT94" t="inlineStr"/>
+      <c r="AW94" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX94" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY94" t="inlineStr"/>
+      <c r="AZ94" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135192161</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>135192166</v>
+      </c>
+      <c r="B95" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E95" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr"/>
+      <c r="P95" t="inlineStr">
+        <is>
+          <t>Höbrännflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q95" t="n">
+        <v>469249</v>
+      </c>
+      <c r="R95" t="n">
+        <v>7077922</v>
+      </c>
+      <c r="S95" t="n">
+        <v>10</v>
+      </c>
+      <c r="T95" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U95" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V95" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W95" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y95" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="Z95" t="inlineStr">
+        <is>
+          <t>13:07</t>
+        </is>
+      </c>
+      <c r="AA95" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="AB95" t="inlineStr">
+        <is>
+          <t>13:07</t>
+        </is>
+      </c>
+      <c r="AC95" t="inlineStr">
+        <is>
+          <t>ringhack</t>
+        </is>
+      </c>
+      <c r="AD95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT95" t="inlineStr"/>
+      <c r="AW95" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX95" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY95" t="inlineStr"/>
+      <c r="AZ95" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135192166</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="n">
+        <v>128346628</v>
+      </c>
+      <c r="B96" t="n">
+        <v>97989</v>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E96" t="n">
+        <v>221941</v>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>Plattlummer</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>Lycopodium complanatum</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr"/>
+      <c r="P96" t="inlineStr">
+        <is>
+          <t>Höbrännflon sö, Jmt</t>
+        </is>
+      </c>
+      <c r="Q96" t="n">
+        <v>468931</v>
+      </c>
+      <c r="R96" t="n">
+        <v>7077743</v>
+      </c>
+      <c r="S96" t="n">
+        <v>10</v>
+      </c>
+      <c r="T96" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U96" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V96" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W96" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y96" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AA96" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AD96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT96" t="inlineStr"/>
+      <c r="AW96" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX96" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY96" t="inlineStr"/>
+      <c r="AZ96" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/128346628</t>
         </is>
@@ -4209,6 +11639,68 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ91" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ92" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ93" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ94" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ95" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ96" r:id="rId95"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 28940-2026 artfynd.xlsx
+++ b/artfynd/A 28940-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ96"/>
+  <dimension ref="A1:AZ58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6878,50 +6878,45 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>135192022</v>
+        <v>128346628</v>
       </c>
       <c r="B58" t="n">
-        <v>57980</v>
+        <v>97989</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>100109</v>
+        <v>221941</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
-      <c r="M58" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Höbrännflon, Jmt</t>
+          <t>Höbrännflon sö, Jmt</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>469168</v>
+        <v>468931</v>
       </c>
       <c r="R58" t="n">
-        <v>7078178</v>
+        <v>7077743</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6948,27 +6943,12 @@
       </c>
       <c r="Y58" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
-        </is>
-      </c>
-      <c r="Z58" t="inlineStr">
-        <is>
-          <t>09:29</t>
+          <t>2025-09-09</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
-        </is>
-      </c>
-      <c r="AB58" t="inlineStr">
-        <is>
-          <t>09:29</t>
-        </is>
-      </c>
-      <c r="AC58" t="inlineStr">
-        <is>
-          <t>äldre ringhack</t>
+          <t>2025-09-09</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6993,4612 +6973,6 @@
       </c>
       <c r="AY58" t="inlineStr"/>
       <c r="AZ58" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135192022</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="n">
-        <v>135192026</v>
-      </c>
-      <c r="B59" t="n">
-        <v>57980</v>
-      </c>
-      <c r="D59" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E59" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F59" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G59" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H59" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr"/>
-      <c r="M59" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="P59" t="inlineStr">
-        <is>
-          <t>Höbrännflon, Jmt</t>
-        </is>
-      </c>
-      <c r="Q59" t="n">
-        <v>469186</v>
-      </c>
-      <c r="R59" t="n">
-        <v>7078140</v>
-      </c>
-      <c r="S59" t="n">
-        <v>10</v>
-      </c>
-      <c r="T59" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U59" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V59" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W59" t="inlineStr">
-        <is>
-          <t>Föllinge</t>
-        </is>
-      </c>
-      <c r="Y59" t="inlineStr">
-        <is>
-          <t>2026-07-14</t>
-        </is>
-      </c>
-      <c r="Z59" t="inlineStr">
-        <is>
-          <t>09:38</t>
-        </is>
-      </c>
-      <c r="AA59" t="inlineStr">
-        <is>
-          <t>2026-07-14</t>
-        </is>
-      </c>
-      <c r="AB59" t="inlineStr">
-        <is>
-          <t>09:38</t>
-        </is>
-      </c>
-      <c r="AC59" t="inlineStr">
-        <is>
-          <t>äldre ringhack</t>
-        </is>
-      </c>
-      <c r="AD59" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE59" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG59" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT59" t="inlineStr"/>
-      <c r="AW59" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX59" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY59" t="inlineStr"/>
-      <c r="AZ59" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135192026</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="n">
-        <v>135192030</v>
-      </c>
-      <c r="B60" t="n">
-        <v>57980</v>
-      </c>
-      <c r="D60" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E60" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F60" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G60" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H60" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr"/>
-      <c r="M60" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="P60" t="inlineStr">
-        <is>
-          <t>Höbrännflon, Jmt</t>
-        </is>
-      </c>
-      <c r="Q60" t="n">
-        <v>469177</v>
-      </c>
-      <c r="R60" t="n">
-        <v>7078094</v>
-      </c>
-      <c r="S60" t="n">
-        <v>10</v>
-      </c>
-      <c r="T60" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U60" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V60" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W60" t="inlineStr">
-        <is>
-          <t>Föllinge</t>
-        </is>
-      </c>
-      <c r="Y60" t="inlineStr">
-        <is>
-          <t>2026-07-14</t>
-        </is>
-      </c>
-      <c r="Z60" t="inlineStr">
-        <is>
-          <t>09:48</t>
-        </is>
-      </c>
-      <c r="AA60" t="inlineStr">
-        <is>
-          <t>2026-07-14</t>
-        </is>
-      </c>
-      <c r="AB60" t="inlineStr">
-        <is>
-          <t>09:48</t>
-        </is>
-      </c>
-      <c r="AC60" t="inlineStr">
-        <is>
-          <t>äldre ringhack</t>
-        </is>
-      </c>
-      <c r="AD60" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE60" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG60" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT60" t="inlineStr"/>
-      <c r="AW60" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX60" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY60" t="inlineStr"/>
-      <c r="AZ60" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135192030</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="n">
-        <v>135192045</v>
-      </c>
-      <c r="B61" t="n">
-        <v>57980</v>
-      </c>
-      <c r="D61" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E61" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F61" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G61" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H61" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr"/>
-      <c r="P61" t="inlineStr">
-        <is>
-          <t>Höbrännflon, Jmt</t>
-        </is>
-      </c>
-      <c r="Q61" t="n">
-        <v>468993</v>
-      </c>
-      <c r="R61" t="n">
-        <v>7078287</v>
-      </c>
-      <c r="S61" t="n">
-        <v>10</v>
-      </c>
-      <c r="T61" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U61" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V61" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W61" t="inlineStr">
-        <is>
-          <t>Föllinge</t>
-        </is>
-      </c>
-      <c r="Y61" t="inlineStr">
-        <is>
-          <t>2026-07-14</t>
-        </is>
-      </c>
-      <c r="Z61" t="inlineStr">
-        <is>
-          <t>10:18</t>
-        </is>
-      </c>
-      <c r="AA61" t="inlineStr">
-        <is>
-          <t>2026-07-14</t>
-        </is>
-      </c>
-      <c r="AB61" t="inlineStr">
-        <is>
-          <t>10:18</t>
-        </is>
-      </c>
-      <c r="AC61" t="inlineStr">
-        <is>
-          <t>ringhack</t>
-        </is>
-      </c>
-      <c r="AD61" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE61" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG61" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT61" t="inlineStr"/>
-      <c r="AW61" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX61" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY61" t="inlineStr"/>
-      <c r="AZ61" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135192045</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="n">
-        <v>135192047</v>
-      </c>
-      <c r="B62" t="n">
-        <v>57980</v>
-      </c>
-      <c r="D62" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E62" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F62" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G62" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H62" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr"/>
-      <c r="M62" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="P62" t="inlineStr">
-        <is>
-          <t>Höbrännflon, Jmt</t>
-        </is>
-      </c>
-      <c r="Q62" t="n">
-        <v>468901</v>
-      </c>
-      <c r="R62" t="n">
-        <v>7078371</v>
-      </c>
-      <c r="S62" t="n">
-        <v>10</v>
-      </c>
-      <c r="T62" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U62" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V62" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W62" t="inlineStr">
-        <is>
-          <t>Föllinge</t>
-        </is>
-      </c>
-      <c r="Y62" t="inlineStr">
-        <is>
-          <t>2026-07-14</t>
-        </is>
-      </c>
-      <c r="Z62" t="inlineStr">
-        <is>
-          <t>10:25</t>
-        </is>
-      </c>
-      <c r="AA62" t="inlineStr">
-        <is>
-          <t>2026-07-14</t>
-        </is>
-      </c>
-      <c r="AB62" t="inlineStr">
-        <is>
-          <t>10:25</t>
-        </is>
-      </c>
-      <c r="AC62" t="inlineStr">
-        <is>
-          <t>äldre ringhack</t>
-        </is>
-      </c>
-      <c r="AD62" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE62" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG62" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT62" t="inlineStr"/>
-      <c r="AW62" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX62" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY62" t="inlineStr"/>
-      <c r="AZ62" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135192047</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="n">
-        <v>135192048</v>
-      </c>
-      <c r="B63" t="n">
-        <v>57980</v>
-      </c>
-      <c r="D63" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E63" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F63" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G63" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H63" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr"/>
-      <c r="M63" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="P63" t="inlineStr">
-        <is>
-          <t>Höbrännflon, Jmt</t>
-        </is>
-      </c>
-      <c r="Q63" t="n">
-        <v>468891</v>
-      </c>
-      <c r="R63" t="n">
-        <v>7078390</v>
-      </c>
-      <c r="S63" t="n">
-        <v>10</v>
-      </c>
-      <c r="T63" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U63" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V63" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W63" t="inlineStr">
-        <is>
-          <t>Föllinge</t>
-        </is>
-      </c>
-      <c r="Y63" t="inlineStr">
-        <is>
-          <t>2026-07-14</t>
-        </is>
-      </c>
-      <c r="Z63" t="inlineStr">
-        <is>
-          <t>10:28</t>
-        </is>
-      </c>
-      <c r="AA63" t="inlineStr">
-        <is>
-          <t>2026-07-14</t>
-        </is>
-      </c>
-      <c r="AB63" t="inlineStr">
-        <is>
-          <t>10:28</t>
-        </is>
-      </c>
-      <c r="AC63" t="inlineStr">
-        <is>
-          <t>färska o och äldre ringhack</t>
-        </is>
-      </c>
-      <c r="AD63" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE63" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG63" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT63" t="inlineStr"/>
-      <c r="AW63" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX63" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY63" t="inlineStr"/>
-      <c r="AZ63" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135192048</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="n">
-        <v>135192050</v>
-      </c>
-      <c r="B64" t="n">
-        <v>57980</v>
-      </c>
-      <c r="D64" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E64" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F64" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G64" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H64" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr"/>
-      <c r="M64" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="P64" t="inlineStr">
-        <is>
-          <t>Höbrännflon, Jmt</t>
-        </is>
-      </c>
-      <c r="Q64" t="n">
-        <v>468864</v>
-      </c>
-      <c r="R64" t="n">
-        <v>7078369</v>
-      </c>
-      <c r="S64" t="n">
-        <v>10</v>
-      </c>
-      <c r="T64" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U64" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V64" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W64" t="inlineStr">
-        <is>
-          <t>Föllinge</t>
-        </is>
-      </c>
-      <c r="Y64" t="inlineStr">
-        <is>
-          <t>2026-07-14</t>
-        </is>
-      </c>
-      <c r="Z64" t="inlineStr">
-        <is>
-          <t>10:31</t>
-        </is>
-      </c>
-      <c r="AA64" t="inlineStr">
-        <is>
-          <t>2026-07-14</t>
-        </is>
-      </c>
-      <c r="AB64" t="inlineStr">
-        <is>
-          <t>10:31</t>
-        </is>
-      </c>
-      <c r="AC64" t="inlineStr">
-        <is>
-          <t>färska och äldre ringhack</t>
-        </is>
-      </c>
-      <c r="AD64" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE64" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG64" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT64" t="inlineStr"/>
-      <c r="AW64" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX64" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY64" t="inlineStr"/>
-      <c r="AZ64" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135192050</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="n">
-        <v>135192056</v>
-      </c>
-      <c r="B65" t="n">
-        <v>57980</v>
-      </c>
-      <c r="D65" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E65" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F65" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G65" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H65" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr"/>
-      <c r="M65" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="P65" t="inlineStr">
-        <is>
-          <t>Höbrännflon, Jmt</t>
-        </is>
-      </c>
-      <c r="Q65" t="n">
-        <v>468923</v>
-      </c>
-      <c r="R65" t="n">
-        <v>7078311</v>
-      </c>
-      <c r="S65" t="n">
-        <v>10</v>
-      </c>
-      <c r="T65" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U65" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V65" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W65" t="inlineStr">
-        <is>
-          <t>Föllinge</t>
-        </is>
-      </c>
-      <c r="Y65" t="inlineStr">
-        <is>
-          <t>2026-07-14</t>
-        </is>
-      </c>
-      <c r="Z65" t="inlineStr">
-        <is>
-          <t>10:37</t>
-        </is>
-      </c>
-      <c r="AA65" t="inlineStr">
-        <is>
-          <t>2026-07-14</t>
-        </is>
-      </c>
-      <c r="AB65" t="inlineStr">
-        <is>
-          <t>10:37</t>
-        </is>
-      </c>
-      <c r="AC65" t="inlineStr">
-        <is>
-          <t>äldre ringhack</t>
-        </is>
-      </c>
-      <c r="AD65" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE65" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG65" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT65" t="inlineStr"/>
-      <c r="AW65" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX65" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY65" t="inlineStr"/>
-      <c r="AZ65" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135192056</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="n">
-        <v>135192074</v>
-      </c>
-      <c r="B66" t="n">
-        <v>57980</v>
-      </c>
-      <c r="D66" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E66" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F66" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G66" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H66" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr"/>
-      <c r="M66" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="P66" t="inlineStr">
-        <is>
-          <t>Höbrännflon, Jmt</t>
-        </is>
-      </c>
-      <c r="Q66" t="n">
-        <v>469051</v>
-      </c>
-      <c r="R66" t="n">
-        <v>7077912</v>
-      </c>
-      <c r="S66" t="n">
-        <v>10</v>
-      </c>
-      <c r="T66" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U66" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V66" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W66" t="inlineStr">
-        <is>
-          <t>Föllinge</t>
-        </is>
-      </c>
-      <c r="Y66" t="inlineStr">
-        <is>
-          <t>2026-07-14</t>
-        </is>
-      </c>
-      <c r="Z66" t="inlineStr">
-        <is>
-          <t>11:05</t>
-        </is>
-      </c>
-      <c r="AA66" t="inlineStr">
-        <is>
-          <t>2026-07-14</t>
-        </is>
-      </c>
-      <c r="AB66" t="inlineStr">
-        <is>
-          <t>11:05</t>
-        </is>
-      </c>
-      <c r="AC66" t="inlineStr">
-        <is>
-          <t>äldre ringhack</t>
-        </is>
-      </c>
-      <c r="AD66" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE66" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG66" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT66" t="inlineStr"/>
-      <c r="AW66" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX66" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY66" t="inlineStr"/>
-      <c r="AZ66" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135192074</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="n">
-        <v>135192077</v>
-      </c>
-      <c r="B67" t="n">
-        <v>57980</v>
-      </c>
-      <c r="D67" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E67" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F67" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G67" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H67" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr"/>
-      <c r="M67" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="P67" t="inlineStr">
-        <is>
-          <t>Höbrännflon, Jmt</t>
-        </is>
-      </c>
-      <c r="Q67" t="n">
-        <v>469002</v>
-      </c>
-      <c r="R67" t="n">
-        <v>7077895</v>
-      </c>
-      <c r="S67" t="n">
-        <v>10</v>
-      </c>
-      <c r="T67" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U67" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V67" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W67" t="inlineStr">
-        <is>
-          <t>Föllinge</t>
-        </is>
-      </c>
-      <c r="Y67" t="inlineStr">
-        <is>
-          <t>2026-07-14</t>
-        </is>
-      </c>
-      <c r="Z67" t="inlineStr">
-        <is>
-          <t>11:09</t>
-        </is>
-      </c>
-      <c r="AA67" t="inlineStr">
-        <is>
-          <t>2026-07-14</t>
-        </is>
-      </c>
-      <c r="AB67" t="inlineStr">
-        <is>
-          <t>11:09</t>
-        </is>
-      </c>
-      <c r="AC67" t="inlineStr">
-        <is>
-          <t>äldre ringhack</t>
-        </is>
-      </c>
-      <c r="AD67" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE67" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG67" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT67" t="inlineStr"/>
-      <c r="AW67" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX67" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY67" t="inlineStr"/>
-      <c r="AZ67" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135192077</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="n">
-        <v>135192079</v>
-      </c>
-      <c r="B68" t="n">
-        <v>57980</v>
-      </c>
-      <c r="D68" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E68" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F68" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G68" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H68" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr"/>
-      <c r="M68" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="P68" t="inlineStr">
-        <is>
-          <t>Höbrännflon, Jmt</t>
-        </is>
-      </c>
-      <c r="Q68" t="n">
-        <v>469028</v>
-      </c>
-      <c r="R68" t="n">
-        <v>7077856</v>
-      </c>
-      <c r="S68" t="n">
-        <v>10</v>
-      </c>
-      <c r="T68" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U68" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V68" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W68" t="inlineStr">
-        <is>
-          <t>Föllinge</t>
-        </is>
-      </c>
-      <c r="Y68" t="inlineStr">
-        <is>
-          <t>2026-07-14</t>
-        </is>
-      </c>
-      <c r="Z68" t="inlineStr">
-        <is>
-          <t>11:12</t>
-        </is>
-      </c>
-      <c r="AA68" t="inlineStr">
-        <is>
-          <t>2026-07-14</t>
-        </is>
-      </c>
-      <c r="AB68" t="inlineStr">
-        <is>
-          <t>11:12</t>
-        </is>
-      </c>
-      <c r="AC68" t="inlineStr">
-        <is>
-          <t>äldre ringhack</t>
-        </is>
-      </c>
-      <c r="AD68" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE68" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG68" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT68" t="inlineStr"/>
-      <c r="AW68" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX68" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY68" t="inlineStr"/>
-      <c r="AZ68" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135192079</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="n">
-        <v>135192085</v>
-      </c>
-      <c r="B69" t="n">
-        <v>57980</v>
-      </c>
-      <c r="D69" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E69" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F69" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G69" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H69" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr"/>
-      <c r="M69" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="P69" t="inlineStr">
-        <is>
-          <t>Höbrännflon, Jmt</t>
-        </is>
-      </c>
-      <c r="Q69" t="n">
-        <v>468941</v>
-      </c>
-      <c r="R69" t="n">
-        <v>7077921</v>
-      </c>
-      <c r="S69" t="n">
-        <v>10</v>
-      </c>
-      <c r="T69" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U69" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V69" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W69" t="inlineStr">
-        <is>
-          <t>Föllinge</t>
-        </is>
-      </c>
-      <c r="Y69" t="inlineStr">
-        <is>
-          <t>2026-07-14</t>
-        </is>
-      </c>
-      <c r="Z69" t="inlineStr">
-        <is>
-          <t>11:18</t>
-        </is>
-      </c>
-      <c r="AA69" t="inlineStr">
-        <is>
-          <t>2026-07-14</t>
-        </is>
-      </c>
-      <c r="AB69" t="inlineStr">
-        <is>
-          <t>11:18</t>
-        </is>
-      </c>
-      <c r="AC69" t="inlineStr">
-        <is>
-          <t>äldre ringhack</t>
-        </is>
-      </c>
-      <c r="AD69" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE69" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG69" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT69" t="inlineStr"/>
-      <c r="AW69" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX69" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY69" t="inlineStr"/>
-      <c r="AZ69" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135192085</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="n">
-        <v>135192088</v>
-      </c>
-      <c r="B70" t="n">
-        <v>57980</v>
-      </c>
-      <c r="D70" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E70" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F70" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G70" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H70" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr"/>
-      <c r="M70" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="P70" t="inlineStr">
-        <is>
-          <t>Höbrännflon, Jmt</t>
-        </is>
-      </c>
-      <c r="Q70" t="n">
-        <v>468900</v>
-      </c>
-      <c r="R70" t="n">
-        <v>7077908</v>
-      </c>
-      <c r="S70" t="n">
-        <v>10</v>
-      </c>
-      <c r="T70" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U70" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V70" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W70" t="inlineStr">
-        <is>
-          <t>Föllinge</t>
-        </is>
-      </c>
-      <c r="Y70" t="inlineStr">
-        <is>
-          <t>2026-07-14</t>
-        </is>
-      </c>
-      <c r="Z70" t="inlineStr">
-        <is>
-          <t>11:20</t>
-        </is>
-      </c>
-      <c r="AA70" t="inlineStr">
-        <is>
-          <t>2026-07-14</t>
-        </is>
-      </c>
-      <c r="AB70" t="inlineStr">
-        <is>
-          <t>11:20</t>
-        </is>
-      </c>
-      <c r="AC70" t="inlineStr">
-        <is>
-          <t>färska och äldre ringhack</t>
-        </is>
-      </c>
-      <c r="AD70" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE70" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG70" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT70" t="inlineStr"/>
-      <c r="AW70" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX70" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY70" t="inlineStr"/>
-      <c r="AZ70" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135192088</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="n">
-        <v>135192093</v>
-      </c>
-      <c r="B71" t="n">
-        <v>57980</v>
-      </c>
-      <c r="D71" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E71" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F71" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G71" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H71" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I71" t="inlineStr"/>
-      <c r="M71" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="P71" t="inlineStr">
-        <is>
-          <t>Höbrännflon, Jmt</t>
-        </is>
-      </c>
-      <c r="Q71" t="n">
-        <v>468841</v>
-      </c>
-      <c r="R71" t="n">
-        <v>7077895</v>
-      </c>
-      <c r="S71" t="n">
-        <v>10</v>
-      </c>
-      <c r="T71" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U71" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V71" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W71" t="inlineStr">
-        <is>
-          <t>Föllinge</t>
-        </is>
-      </c>
-      <c r="Y71" t="inlineStr">
-        <is>
-          <t>2026-07-14</t>
-        </is>
-      </c>
-      <c r="Z71" t="inlineStr">
-        <is>
-          <t>11:28</t>
-        </is>
-      </c>
-      <c r="AA71" t="inlineStr">
-        <is>
-          <t>2026-07-14</t>
-        </is>
-      </c>
-      <c r="AB71" t="inlineStr">
-        <is>
-          <t>11:28</t>
-        </is>
-      </c>
-      <c r="AC71" t="inlineStr">
-        <is>
-          <t>äldre ringhack</t>
-        </is>
-      </c>
-      <c r="AD71" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE71" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG71" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT71" t="inlineStr"/>
-      <c r="AW71" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX71" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY71" t="inlineStr"/>
-      <c r="AZ71" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135192093</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="n">
-        <v>135192095</v>
-      </c>
-      <c r="B72" t="n">
-        <v>57980</v>
-      </c>
-      <c r="D72" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E72" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F72" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G72" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H72" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I72" t="inlineStr"/>
-      <c r="M72" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="P72" t="inlineStr">
-        <is>
-          <t>Höbrännflon, Jmt</t>
-        </is>
-      </c>
-      <c r="Q72" t="n">
-        <v>468832</v>
-      </c>
-      <c r="R72" t="n">
-        <v>7077861</v>
-      </c>
-      <c r="S72" t="n">
-        <v>10</v>
-      </c>
-      <c r="T72" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U72" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V72" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W72" t="inlineStr">
-        <is>
-          <t>Föllinge</t>
-        </is>
-      </c>
-      <c r="Y72" t="inlineStr">
-        <is>
-          <t>2026-07-14</t>
-        </is>
-      </c>
-      <c r="Z72" t="inlineStr">
-        <is>
-          <t>11:32</t>
-        </is>
-      </c>
-      <c r="AA72" t="inlineStr">
-        <is>
-          <t>2026-07-14</t>
-        </is>
-      </c>
-      <c r="AB72" t="inlineStr">
-        <is>
-          <t>11:32</t>
-        </is>
-      </c>
-      <c r="AC72" t="inlineStr">
-        <is>
-          <t>äldre ringhack</t>
-        </is>
-      </c>
-      <c r="AD72" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE72" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG72" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT72" t="inlineStr"/>
-      <c r="AW72" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX72" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY72" t="inlineStr"/>
-      <c r="AZ72" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135192095</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="n">
-        <v>135192112</v>
-      </c>
-      <c r="B73" t="n">
-        <v>57980</v>
-      </c>
-      <c r="D73" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E73" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F73" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G73" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H73" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I73" t="inlineStr"/>
-      <c r="M73" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="P73" t="inlineStr">
-        <is>
-          <t>Höbrännflon, Jmt</t>
-        </is>
-      </c>
-      <c r="Q73" t="n">
-        <v>469029</v>
-      </c>
-      <c r="R73" t="n">
-        <v>7077764</v>
-      </c>
-      <c r="S73" t="n">
-        <v>10</v>
-      </c>
-      <c r="T73" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U73" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V73" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W73" t="inlineStr">
-        <is>
-          <t>Föllinge</t>
-        </is>
-      </c>
-      <c r="Y73" t="inlineStr">
-        <is>
-          <t>2026-07-14</t>
-        </is>
-      </c>
-      <c r="Z73" t="inlineStr">
-        <is>
-          <t>11:55</t>
-        </is>
-      </c>
-      <c r="AA73" t="inlineStr">
-        <is>
-          <t>2026-07-14</t>
-        </is>
-      </c>
-      <c r="AB73" t="inlineStr">
-        <is>
-          <t>11:55</t>
-        </is>
-      </c>
-      <c r="AC73" t="inlineStr">
-        <is>
-          <t>äldre ringhack</t>
-        </is>
-      </c>
-      <c r="AD73" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE73" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG73" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT73" t="inlineStr"/>
-      <c r="AW73" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX73" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY73" t="inlineStr"/>
-      <c r="AZ73" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135192112</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="n">
-        <v>135192116</v>
-      </c>
-      <c r="B74" t="n">
-        <v>57980</v>
-      </c>
-      <c r="D74" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E74" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F74" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G74" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H74" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I74" t="inlineStr"/>
-      <c r="M74" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="P74" t="inlineStr">
-        <is>
-          <t>Höbrännflon, Jmt</t>
-        </is>
-      </c>
-      <c r="Q74" t="n">
-        <v>469092</v>
-      </c>
-      <c r="R74" t="n">
-        <v>7077868</v>
-      </c>
-      <c r="S74" t="n">
-        <v>10</v>
-      </c>
-      <c r="T74" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U74" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V74" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W74" t="inlineStr">
-        <is>
-          <t>Föllinge</t>
-        </is>
-      </c>
-      <c r="Y74" t="inlineStr">
-        <is>
-          <t>2026-07-14</t>
-        </is>
-      </c>
-      <c r="Z74" t="inlineStr">
-        <is>
-          <t>12:02</t>
-        </is>
-      </c>
-      <c r="AA74" t="inlineStr">
-        <is>
-          <t>2026-07-14</t>
-        </is>
-      </c>
-      <c r="AB74" t="inlineStr">
-        <is>
-          <t>12:02</t>
-        </is>
-      </c>
-      <c r="AC74" t="inlineStr">
-        <is>
-          <t>äldre ringhack</t>
-        </is>
-      </c>
-      <c r="AD74" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE74" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG74" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT74" t="inlineStr"/>
-      <c r="AW74" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX74" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY74" t="inlineStr"/>
-      <c r="AZ74" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135192116</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="n">
-        <v>135192118</v>
-      </c>
-      <c r="B75" t="n">
-        <v>57980</v>
-      </c>
-      <c r="D75" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E75" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F75" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G75" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H75" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I75" t="inlineStr"/>
-      <c r="M75" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="P75" t="inlineStr">
-        <is>
-          <t>Höbrännflon, Jmt</t>
-        </is>
-      </c>
-      <c r="Q75" t="n">
-        <v>469121</v>
-      </c>
-      <c r="R75" t="n">
-        <v>7077852</v>
-      </c>
-      <c r="S75" t="n">
-        <v>10</v>
-      </c>
-      <c r="T75" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U75" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V75" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W75" t="inlineStr">
-        <is>
-          <t>Föllinge</t>
-        </is>
-      </c>
-      <c r="Y75" t="inlineStr">
-        <is>
-          <t>2026-07-14</t>
-        </is>
-      </c>
-      <c r="Z75" t="inlineStr">
-        <is>
-          <t>12:04</t>
-        </is>
-      </c>
-      <c r="AA75" t="inlineStr">
-        <is>
-          <t>2026-07-14</t>
-        </is>
-      </c>
-      <c r="AB75" t="inlineStr">
-        <is>
-          <t>12:04</t>
-        </is>
-      </c>
-      <c r="AC75" t="inlineStr">
-        <is>
-          <t>äldre ringhack</t>
-        </is>
-      </c>
-      <c r="AD75" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE75" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG75" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT75" t="inlineStr"/>
-      <c r="AW75" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX75" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY75" t="inlineStr"/>
-      <c r="AZ75" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135192118</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="n">
-        <v>135192119</v>
-      </c>
-      <c r="B76" t="n">
-        <v>57980</v>
-      </c>
-      <c r="D76" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E76" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F76" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G76" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H76" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I76" t="inlineStr"/>
-      <c r="M76" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="P76" t="inlineStr">
-        <is>
-          <t>Höbrännflon, Jmt</t>
-        </is>
-      </c>
-      <c r="Q76" t="n">
-        <v>469139</v>
-      </c>
-      <c r="R76" t="n">
-        <v>7077825</v>
-      </c>
-      <c r="S76" t="n">
-        <v>10</v>
-      </c>
-      <c r="T76" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U76" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V76" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W76" t="inlineStr">
-        <is>
-          <t>Föllinge</t>
-        </is>
-      </c>
-      <c r="Y76" t="inlineStr">
-        <is>
-          <t>2026-07-14</t>
-        </is>
-      </c>
-      <c r="Z76" t="inlineStr">
-        <is>
-          <t>12:07</t>
-        </is>
-      </c>
-      <c r="AA76" t="inlineStr">
-        <is>
-          <t>2026-07-14</t>
-        </is>
-      </c>
-      <c r="AB76" t="inlineStr">
-        <is>
-          <t>12:07</t>
-        </is>
-      </c>
-      <c r="AC76" t="inlineStr">
-        <is>
-          <t>äldre ringhack</t>
-        </is>
-      </c>
-      <c r="AD76" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE76" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG76" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT76" t="inlineStr"/>
-      <c r="AW76" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX76" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY76" t="inlineStr"/>
-      <c r="AZ76" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135192119</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="n">
-        <v>135192123</v>
-      </c>
-      <c r="B77" t="n">
-        <v>57980</v>
-      </c>
-      <c r="D77" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E77" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F77" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G77" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H77" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I77" t="inlineStr"/>
-      <c r="M77" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="P77" t="inlineStr">
-        <is>
-          <t>Höbrännflon, Jmt</t>
-        </is>
-      </c>
-      <c r="Q77" t="n">
-        <v>469108</v>
-      </c>
-      <c r="R77" t="n">
-        <v>7077950</v>
-      </c>
-      <c r="S77" t="n">
-        <v>10</v>
-      </c>
-      <c r="T77" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U77" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V77" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W77" t="inlineStr">
-        <is>
-          <t>Föllinge</t>
-        </is>
-      </c>
-      <c r="Y77" t="inlineStr">
-        <is>
-          <t>2026-07-14</t>
-        </is>
-      </c>
-      <c r="Z77" t="inlineStr">
-        <is>
-          <t>12:11</t>
-        </is>
-      </c>
-      <c r="AA77" t="inlineStr">
-        <is>
-          <t>2026-07-14</t>
-        </is>
-      </c>
-      <c r="AB77" t="inlineStr">
-        <is>
-          <t>12:11</t>
-        </is>
-      </c>
-      <c r="AC77" t="inlineStr">
-        <is>
-          <t>färska ringhack</t>
-        </is>
-      </c>
-      <c r="AD77" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE77" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG77" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT77" t="inlineStr"/>
-      <c r="AW77" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX77" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY77" t="inlineStr"/>
-      <c r="AZ77" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135192123</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="n">
-        <v>135192124</v>
-      </c>
-      <c r="B78" t="n">
-        <v>57980</v>
-      </c>
-      <c r="D78" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E78" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F78" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G78" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H78" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I78" t="inlineStr"/>
-      <c r="M78" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="P78" t="inlineStr">
-        <is>
-          <t>Höbrännflon, Jmt</t>
-        </is>
-      </c>
-      <c r="Q78" t="n">
-        <v>469109</v>
-      </c>
-      <c r="R78" t="n">
-        <v>7077945</v>
-      </c>
-      <c r="S78" t="n">
-        <v>10</v>
-      </c>
-      <c r="T78" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U78" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V78" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W78" t="inlineStr">
-        <is>
-          <t>Föllinge</t>
-        </is>
-      </c>
-      <c r="Y78" t="inlineStr">
-        <is>
-          <t>2026-07-14</t>
-        </is>
-      </c>
-      <c r="Z78" t="inlineStr">
-        <is>
-          <t>12:12</t>
-        </is>
-      </c>
-      <c r="AA78" t="inlineStr">
-        <is>
-          <t>2026-07-14</t>
-        </is>
-      </c>
-      <c r="AB78" t="inlineStr">
-        <is>
-          <t>12:12</t>
-        </is>
-      </c>
-      <c r="AC78" t="inlineStr">
-        <is>
-          <t>färska ringhack</t>
-        </is>
-      </c>
-      <c r="AD78" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE78" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG78" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT78" t="inlineStr"/>
-      <c r="AW78" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX78" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY78" t="inlineStr"/>
-      <c r="AZ78" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135192124</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="n">
-        <v>135192125</v>
-      </c>
-      <c r="B79" t="n">
-        <v>57980</v>
-      </c>
-      <c r="D79" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E79" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F79" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G79" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H79" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I79" t="inlineStr"/>
-      <c r="M79" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="P79" t="inlineStr">
-        <is>
-          <t>Höbrännflon, Jmt</t>
-        </is>
-      </c>
-      <c r="Q79" t="n">
-        <v>469118</v>
-      </c>
-      <c r="R79" t="n">
-        <v>7077938</v>
-      </c>
-      <c r="S79" t="n">
-        <v>10</v>
-      </c>
-      <c r="T79" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U79" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V79" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W79" t="inlineStr">
-        <is>
-          <t>Föllinge</t>
-        </is>
-      </c>
-      <c r="Y79" t="inlineStr">
-        <is>
-          <t>2026-07-14</t>
-        </is>
-      </c>
-      <c r="Z79" t="inlineStr">
-        <is>
-          <t>12:12</t>
-        </is>
-      </c>
-      <c r="AA79" t="inlineStr">
-        <is>
-          <t>2026-07-14</t>
-        </is>
-      </c>
-      <c r="AB79" t="inlineStr">
-        <is>
-          <t>12:12</t>
-        </is>
-      </c>
-      <c r="AC79" t="inlineStr">
-        <is>
-          <t>färska ringhack</t>
-        </is>
-      </c>
-      <c r="AD79" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE79" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG79" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT79" t="inlineStr"/>
-      <c r="AW79" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX79" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY79" t="inlineStr"/>
-      <c r="AZ79" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135192125</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="n">
-        <v>135192127</v>
-      </c>
-      <c r="B80" t="n">
-        <v>57980</v>
-      </c>
-      <c r="D80" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E80" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F80" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G80" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H80" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I80" t="inlineStr"/>
-      <c r="M80" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="P80" t="inlineStr">
-        <is>
-          <t>Höbrännflon, Jmt</t>
-        </is>
-      </c>
-      <c r="Q80" t="n">
-        <v>469140</v>
-      </c>
-      <c r="R80" t="n">
-        <v>7077913</v>
-      </c>
-      <c r="S80" t="n">
-        <v>10</v>
-      </c>
-      <c r="T80" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U80" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V80" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W80" t="inlineStr">
-        <is>
-          <t>Föllinge</t>
-        </is>
-      </c>
-      <c r="Y80" t="inlineStr">
-        <is>
-          <t>2026-07-14</t>
-        </is>
-      </c>
-      <c r="Z80" t="inlineStr">
-        <is>
-          <t>12:13</t>
-        </is>
-      </c>
-      <c r="AA80" t="inlineStr">
-        <is>
-          <t>2026-07-14</t>
-        </is>
-      </c>
-      <c r="AB80" t="inlineStr">
-        <is>
-          <t>12:13</t>
-        </is>
-      </c>
-      <c r="AC80" t="inlineStr">
-        <is>
-          <t>färska ringhack</t>
-        </is>
-      </c>
-      <c r="AD80" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE80" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG80" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT80" t="inlineStr"/>
-      <c r="AW80" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX80" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY80" t="inlineStr"/>
-      <c r="AZ80" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135192127</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="n">
-        <v>135192128</v>
-      </c>
-      <c r="B81" t="n">
-        <v>57980</v>
-      </c>
-      <c r="D81" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E81" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F81" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G81" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H81" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I81" t="inlineStr"/>
-      <c r="M81" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="P81" t="inlineStr">
-        <is>
-          <t>Höbrännflon, Jmt</t>
-        </is>
-      </c>
-      <c r="Q81" t="n">
-        <v>469149</v>
-      </c>
-      <c r="R81" t="n">
-        <v>7077895</v>
-      </c>
-      <c r="S81" t="n">
-        <v>10</v>
-      </c>
-      <c r="T81" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U81" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V81" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W81" t="inlineStr">
-        <is>
-          <t>Föllinge</t>
-        </is>
-      </c>
-      <c r="Y81" t="inlineStr">
-        <is>
-          <t>2026-07-14</t>
-        </is>
-      </c>
-      <c r="Z81" t="inlineStr">
-        <is>
-          <t>12:14</t>
-        </is>
-      </c>
-      <c r="AA81" t="inlineStr">
-        <is>
-          <t>2026-07-14</t>
-        </is>
-      </c>
-      <c r="AB81" t="inlineStr">
-        <is>
-          <t>12:14</t>
-        </is>
-      </c>
-      <c r="AC81" t="inlineStr">
-        <is>
-          <t>färska ringhack</t>
-        </is>
-      </c>
-      <c r="AD81" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE81" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG81" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT81" t="inlineStr"/>
-      <c r="AW81" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX81" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY81" t="inlineStr"/>
-      <c r="AZ81" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135192128</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="n">
-        <v>135192130</v>
-      </c>
-      <c r="B82" t="n">
-        <v>57980</v>
-      </c>
-      <c r="D82" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E82" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F82" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G82" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H82" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I82" t="inlineStr"/>
-      <c r="M82" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="P82" t="inlineStr">
-        <is>
-          <t>Höbrännflon, Jmt</t>
-        </is>
-      </c>
-      <c r="Q82" t="n">
-        <v>469158</v>
-      </c>
-      <c r="R82" t="n">
-        <v>7077852</v>
-      </c>
-      <c r="S82" t="n">
-        <v>10</v>
-      </c>
-      <c r="T82" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U82" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V82" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W82" t="inlineStr">
-        <is>
-          <t>Föllinge</t>
-        </is>
-      </c>
-      <c r="Y82" t="inlineStr">
-        <is>
-          <t>2026-07-14</t>
-        </is>
-      </c>
-      <c r="Z82" t="inlineStr">
-        <is>
-          <t>12:15</t>
-        </is>
-      </c>
-      <c r="AA82" t="inlineStr">
-        <is>
-          <t>2026-07-14</t>
-        </is>
-      </c>
-      <c r="AB82" t="inlineStr">
-        <is>
-          <t>12:15</t>
-        </is>
-      </c>
-      <c r="AC82" t="inlineStr">
-        <is>
-          <t>färska ringhack</t>
-        </is>
-      </c>
-      <c r="AD82" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE82" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG82" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT82" t="inlineStr"/>
-      <c r="AW82" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX82" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY82" t="inlineStr"/>
-      <c r="AZ82" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135192130</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="n">
-        <v>135192131</v>
-      </c>
-      <c r="B83" t="n">
-        <v>57980</v>
-      </c>
-      <c r="D83" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E83" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F83" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G83" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H83" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I83" t="inlineStr"/>
-      <c r="M83" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="P83" t="inlineStr">
-        <is>
-          <t>Höbrännflon, Jmt</t>
-        </is>
-      </c>
-      <c r="Q83" t="n">
-        <v>469166</v>
-      </c>
-      <c r="R83" t="n">
-        <v>7077841</v>
-      </c>
-      <c r="S83" t="n">
-        <v>10</v>
-      </c>
-      <c r="T83" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U83" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V83" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W83" t="inlineStr">
-        <is>
-          <t>Föllinge</t>
-        </is>
-      </c>
-      <c r="Y83" t="inlineStr">
-        <is>
-          <t>2026-07-14</t>
-        </is>
-      </c>
-      <c r="Z83" t="inlineStr">
-        <is>
-          <t>12:16</t>
-        </is>
-      </c>
-      <c r="AA83" t="inlineStr">
-        <is>
-          <t>2026-07-14</t>
-        </is>
-      </c>
-      <c r="AB83" t="inlineStr">
-        <is>
-          <t>12:16</t>
-        </is>
-      </c>
-      <c r="AC83" t="inlineStr">
-        <is>
-          <t>färska ringhack</t>
-        </is>
-      </c>
-      <c r="AD83" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE83" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG83" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT83" t="inlineStr"/>
-      <c r="AW83" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX83" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY83" t="inlineStr"/>
-      <c r="AZ83" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135192131</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="n">
-        <v>135192132</v>
-      </c>
-      <c r="B84" t="n">
-        <v>57980</v>
-      </c>
-      <c r="D84" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E84" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F84" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G84" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H84" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I84" t="inlineStr"/>
-      <c r="M84" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="P84" t="inlineStr">
-        <is>
-          <t>Höbrännflon, Jmt</t>
-        </is>
-      </c>
-      <c r="Q84" t="n">
-        <v>469163</v>
-      </c>
-      <c r="R84" t="n">
-        <v>7077822</v>
-      </c>
-      <c r="S84" t="n">
-        <v>10</v>
-      </c>
-      <c r="T84" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U84" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V84" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W84" t="inlineStr">
-        <is>
-          <t>Föllinge</t>
-        </is>
-      </c>
-      <c r="Y84" t="inlineStr">
-        <is>
-          <t>2026-07-14</t>
-        </is>
-      </c>
-      <c r="Z84" t="inlineStr">
-        <is>
-          <t>12:17</t>
-        </is>
-      </c>
-      <c r="AA84" t="inlineStr">
-        <is>
-          <t>2026-07-14</t>
-        </is>
-      </c>
-      <c r="AB84" t="inlineStr">
-        <is>
-          <t>12:17</t>
-        </is>
-      </c>
-      <c r="AC84" t="inlineStr">
-        <is>
-          <t>färska ringhack</t>
-        </is>
-      </c>
-      <c r="AD84" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE84" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG84" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT84" t="inlineStr"/>
-      <c r="AW84" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX84" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY84" t="inlineStr"/>
-      <c r="AZ84" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135192132</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="n">
-        <v>135192134</v>
-      </c>
-      <c r="B85" t="n">
-        <v>57980</v>
-      </c>
-      <c r="D85" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E85" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F85" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G85" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H85" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I85" t="inlineStr"/>
-      <c r="M85" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="P85" t="inlineStr">
-        <is>
-          <t>Höbrännflon, Jmt</t>
-        </is>
-      </c>
-      <c r="Q85" t="n">
-        <v>469172</v>
-      </c>
-      <c r="R85" t="n">
-        <v>7077811</v>
-      </c>
-      <c r="S85" t="n">
-        <v>10</v>
-      </c>
-      <c r="T85" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U85" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V85" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W85" t="inlineStr">
-        <is>
-          <t>Föllinge</t>
-        </is>
-      </c>
-      <c r="Y85" t="inlineStr">
-        <is>
-          <t>2026-07-14</t>
-        </is>
-      </c>
-      <c r="Z85" t="inlineStr">
-        <is>
-          <t>12:17</t>
-        </is>
-      </c>
-      <c r="AA85" t="inlineStr">
-        <is>
-          <t>2026-07-14</t>
-        </is>
-      </c>
-      <c r="AB85" t="inlineStr">
-        <is>
-          <t>12:17</t>
-        </is>
-      </c>
-      <c r="AC85" t="inlineStr">
-        <is>
-          <t>färska ringhack</t>
-        </is>
-      </c>
-      <c r="AD85" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE85" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG85" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT85" t="inlineStr"/>
-      <c r="AW85" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX85" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY85" t="inlineStr"/>
-      <c r="AZ85" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135192134</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="n">
-        <v>135192135</v>
-      </c>
-      <c r="B86" t="n">
-        <v>57980</v>
-      </c>
-      <c r="D86" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E86" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F86" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G86" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H86" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I86" t="inlineStr"/>
-      <c r="M86" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="P86" t="inlineStr">
-        <is>
-          <t>Höbrännflon, Jmt</t>
-        </is>
-      </c>
-      <c r="Q86" t="n">
-        <v>469180</v>
-      </c>
-      <c r="R86" t="n">
-        <v>7077818</v>
-      </c>
-      <c r="S86" t="n">
-        <v>10</v>
-      </c>
-      <c r="T86" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U86" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V86" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W86" t="inlineStr">
-        <is>
-          <t>Föllinge</t>
-        </is>
-      </c>
-      <c r="Y86" t="inlineStr">
-        <is>
-          <t>2026-07-14</t>
-        </is>
-      </c>
-      <c r="Z86" t="inlineStr">
-        <is>
-          <t>12:18</t>
-        </is>
-      </c>
-      <c r="AA86" t="inlineStr">
-        <is>
-          <t>2026-07-14</t>
-        </is>
-      </c>
-      <c r="AB86" t="inlineStr">
-        <is>
-          <t>12:18</t>
-        </is>
-      </c>
-      <c r="AC86" t="inlineStr">
-        <is>
-          <t>äldre ringhack</t>
-        </is>
-      </c>
-      <c r="AD86" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE86" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG86" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT86" t="inlineStr"/>
-      <c r="AW86" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX86" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY86" t="inlineStr"/>
-      <c r="AZ86" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135192135</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="n">
-        <v>135192136</v>
-      </c>
-      <c r="B87" t="n">
-        <v>57980</v>
-      </c>
-      <c r="D87" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E87" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F87" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G87" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H87" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I87" t="inlineStr"/>
-      <c r="M87" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="P87" t="inlineStr">
-        <is>
-          <t>Höbrännflon, Jmt</t>
-        </is>
-      </c>
-      <c r="Q87" t="n">
-        <v>469176</v>
-      </c>
-      <c r="R87" t="n">
-        <v>7077799</v>
-      </c>
-      <c r="S87" t="n">
-        <v>10</v>
-      </c>
-      <c r="T87" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U87" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V87" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W87" t="inlineStr">
-        <is>
-          <t>Föllinge</t>
-        </is>
-      </c>
-      <c r="Y87" t="inlineStr">
-        <is>
-          <t>2026-07-14</t>
-        </is>
-      </c>
-      <c r="Z87" t="inlineStr">
-        <is>
-          <t>12:19</t>
-        </is>
-      </c>
-      <c r="AA87" t="inlineStr">
-        <is>
-          <t>2026-07-14</t>
-        </is>
-      </c>
-      <c r="AB87" t="inlineStr">
-        <is>
-          <t>12:19</t>
-        </is>
-      </c>
-      <c r="AC87" t="inlineStr">
-        <is>
-          <t>färska ringhack</t>
-        </is>
-      </c>
-      <c r="AD87" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE87" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG87" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT87" t="inlineStr"/>
-      <c r="AW87" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX87" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY87" t="inlineStr"/>
-      <c r="AZ87" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135192136</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="n">
-        <v>135192137</v>
-      </c>
-      <c r="B88" t="n">
-        <v>57980</v>
-      </c>
-      <c r="D88" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E88" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F88" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G88" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H88" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I88" t="inlineStr"/>
-      <c r="M88" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="P88" t="inlineStr">
-        <is>
-          <t>Höbrännflon, Jmt</t>
-        </is>
-      </c>
-      <c r="Q88" t="n">
-        <v>469181</v>
-      </c>
-      <c r="R88" t="n">
-        <v>7077798</v>
-      </c>
-      <c r="S88" t="n">
-        <v>10</v>
-      </c>
-      <c r="T88" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U88" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V88" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W88" t="inlineStr">
-        <is>
-          <t>Föllinge</t>
-        </is>
-      </c>
-      <c r="Y88" t="inlineStr">
-        <is>
-          <t>2026-07-14</t>
-        </is>
-      </c>
-      <c r="Z88" t="inlineStr">
-        <is>
-          <t>12:20</t>
-        </is>
-      </c>
-      <c r="AA88" t="inlineStr">
-        <is>
-          <t>2026-07-14</t>
-        </is>
-      </c>
-      <c r="AB88" t="inlineStr">
-        <is>
-          <t>12:20</t>
-        </is>
-      </c>
-      <c r="AC88" t="inlineStr">
-        <is>
-          <t>färska ringhack</t>
-        </is>
-      </c>
-      <c r="AD88" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE88" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG88" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT88" t="inlineStr"/>
-      <c r="AW88" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX88" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY88" t="inlineStr"/>
-      <c r="AZ88" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135192137</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="n">
-        <v>135192151</v>
-      </c>
-      <c r="B89" t="n">
-        <v>57980</v>
-      </c>
-      <c r="D89" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E89" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F89" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G89" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H89" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I89" t="inlineStr"/>
-      <c r="M89" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="P89" t="inlineStr">
-        <is>
-          <t>Höbrännflon, Jmt</t>
-        </is>
-      </c>
-      <c r="Q89" t="n">
-        <v>469393</v>
-      </c>
-      <c r="R89" t="n">
-        <v>7077846</v>
-      </c>
-      <c r="S89" t="n">
-        <v>10</v>
-      </c>
-      <c r="T89" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U89" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V89" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W89" t="inlineStr">
-        <is>
-          <t>Föllinge</t>
-        </is>
-      </c>
-      <c r="Y89" t="inlineStr">
-        <is>
-          <t>2026-07-14</t>
-        </is>
-      </c>
-      <c r="Z89" t="inlineStr">
-        <is>
-          <t>12:42</t>
-        </is>
-      </c>
-      <c r="AA89" t="inlineStr">
-        <is>
-          <t>2026-07-14</t>
-        </is>
-      </c>
-      <c r="AB89" t="inlineStr">
-        <is>
-          <t>12:42</t>
-        </is>
-      </c>
-      <c r="AC89" t="inlineStr">
-        <is>
-          <t>äldre ringhack</t>
-        </is>
-      </c>
-      <c r="AD89" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE89" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG89" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT89" t="inlineStr"/>
-      <c r="AW89" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX89" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY89" t="inlineStr"/>
-      <c r="AZ89" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135192151</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="n">
-        <v>135192152</v>
-      </c>
-      <c r="B90" t="n">
-        <v>57980</v>
-      </c>
-      <c r="D90" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E90" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F90" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G90" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H90" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I90" t="inlineStr"/>
-      <c r="M90" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="P90" t="inlineStr">
-        <is>
-          <t>Höbrännflon, Jmt</t>
-        </is>
-      </c>
-      <c r="Q90" t="n">
-        <v>469356</v>
-      </c>
-      <c r="R90" t="n">
-        <v>7077867</v>
-      </c>
-      <c r="S90" t="n">
-        <v>10</v>
-      </c>
-      <c r="T90" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U90" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V90" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W90" t="inlineStr">
-        <is>
-          <t>Föllinge</t>
-        </is>
-      </c>
-      <c r="Y90" t="inlineStr">
-        <is>
-          <t>2026-07-14</t>
-        </is>
-      </c>
-      <c r="Z90" t="inlineStr">
-        <is>
-          <t>12:45</t>
-        </is>
-      </c>
-      <c r="AA90" t="inlineStr">
-        <is>
-          <t>2026-07-14</t>
-        </is>
-      </c>
-      <c r="AB90" t="inlineStr">
-        <is>
-          <t>12:45</t>
-        </is>
-      </c>
-      <c r="AC90" t="inlineStr">
-        <is>
-          <t>äldre ringhack</t>
-        </is>
-      </c>
-      <c r="AD90" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE90" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG90" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT90" t="inlineStr"/>
-      <c r="AW90" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX90" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY90" t="inlineStr"/>
-      <c r="AZ90" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135192152</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="n">
-        <v>135192153</v>
-      </c>
-      <c r="B91" t="n">
-        <v>57980</v>
-      </c>
-      <c r="D91" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E91" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F91" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G91" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H91" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I91" t="inlineStr"/>
-      <c r="M91" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="P91" t="inlineStr">
-        <is>
-          <t>Höbrännflon, Jmt</t>
-        </is>
-      </c>
-      <c r="Q91" t="n">
-        <v>469347</v>
-      </c>
-      <c r="R91" t="n">
-        <v>7077869</v>
-      </c>
-      <c r="S91" t="n">
-        <v>10</v>
-      </c>
-      <c r="T91" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U91" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V91" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W91" t="inlineStr">
-        <is>
-          <t>Föllinge</t>
-        </is>
-      </c>
-      <c r="Y91" t="inlineStr">
-        <is>
-          <t>2026-07-14</t>
-        </is>
-      </c>
-      <c r="Z91" t="inlineStr">
-        <is>
-          <t>12:46</t>
-        </is>
-      </c>
-      <c r="AA91" t="inlineStr">
-        <is>
-          <t>2026-07-14</t>
-        </is>
-      </c>
-      <c r="AB91" t="inlineStr">
-        <is>
-          <t>12:46</t>
-        </is>
-      </c>
-      <c r="AC91" t="inlineStr">
-        <is>
-          <t>äldre ringhack</t>
-        </is>
-      </c>
-      <c r="AD91" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE91" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG91" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT91" t="inlineStr"/>
-      <c r="AW91" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX91" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY91" t="inlineStr"/>
-      <c r="AZ91" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135192153</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="n">
-        <v>135192157</v>
-      </c>
-      <c r="B92" t="n">
-        <v>57980</v>
-      </c>
-      <c r="D92" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E92" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F92" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G92" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H92" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I92" t="inlineStr"/>
-      <c r="M92" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="P92" t="inlineStr">
-        <is>
-          <t>Höbrännflon, Jmt</t>
-        </is>
-      </c>
-      <c r="Q92" t="n">
-        <v>469381</v>
-      </c>
-      <c r="R92" t="n">
-        <v>7077873</v>
-      </c>
-      <c r="S92" t="n">
-        <v>10</v>
-      </c>
-      <c r="T92" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U92" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V92" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W92" t="inlineStr">
-        <is>
-          <t>Föllinge</t>
-        </is>
-      </c>
-      <c r="Y92" t="inlineStr">
-        <is>
-          <t>2026-07-14</t>
-        </is>
-      </c>
-      <c r="Z92" t="inlineStr">
-        <is>
-          <t>12:52</t>
-        </is>
-      </c>
-      <c r="AA92" t="inlineStr">
-        <is>
-          <t>2026-07-14</t>
-        </is>
-      </c>
-      <c r="AB92" t="inlineStr">
-        <is>
-          <t>12:52</t>
-        </is>
-      </c>
-      <c r="AC92" t="inlineStr">
-        <is>
-          <t>äldre ringhack</t>
-        </is>
-      </c>
-      <c r="AD92" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE92" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG92" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT92" t="inlineStr"/>
-      <c r="AW92" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX92" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY92" t="inlineStr"/>
-      <c r="AZ92" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135192157</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="n">
-        <v>135192158</v>
-      </c>
-      <c r="B93" t="n">
-        <v>57980</v>
-      </c>
-      <c r="D93" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E93" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F93" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G93" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H93" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I93" t="inlineStr"/>
-      <c r="M93" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="P93" t="inlineStr">
-        <is>
-          <t>Höbrännflon, Jmt</t>
-        </is>
-      </c>
-      <c r="Q93" t="n">
-        <v>469401</v>
-      </c>
-      <c r="R93" t="n">
-        <v>7077887</v>
-      </c>
-      <c r="S93" t="n">
-        <v>10</v>
-      </c>
-      <c r="T93" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U93" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V93" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W93" t="inlineStr">
-        <is>
-          <t>Föllinge</t>
-        </is>
-      </c>
-      <c r="Y93" t="inlineStr">
-        <is>
-          <t>2026-07-14</t>
-        </is>
-      </c>
-      <c r="Z93" t="inlineStr">
-        <is>
-          <t>12:54</t>
-        </is>
-      </c>
-      <c r="AA93" t="inlineStr">
-        <is>
-          <t>2026-07-14</t>
-        </is>
-      </c>
-      <c r="AB93" t="inlineStr">
-        <is>
-          <t>12:54</t>
-        </is>
-      </c>
-      <c r="AC93" t="inlineStr">
-        <is>
-          <t>äldre ringhack</t>
-        </is>
-      </c>
-      <c r="AD93" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE93" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG93" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT93" t="inlineStr"/>
-      <c r="AW93" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX93" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY93" t="inlineStr"/>
-      <c r="AZ93" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135192158</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="n">
-        <v>135192161</v>
-      </c>
-      <c r="B94" t="n">
-        <v>57980</v>
-      </c>
-      <c r="D94" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E94" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F94" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G94" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H94" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I94" t="inlineStr"/>
-      <c r="M94" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="P94" t="inlineStr">
-        <is>
-          <t>Höbrännflon, Jmt</t>
-        </is>
-      </c>
-      <c r="Q94" t="n">
-        <v>469388</v>
-      </c>
-      <c r="R94" t="n">
-        <v>7077920</v>
-      </c>
-      <c r="S94" t="n">
-        <v>10</v>
-      </c>
-      <c r="T94" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U94" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V94" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W94" t="inlineStr">
-        <is>
-          <t>Föllinge</t>
-        </is>
-      </c>
-      <c r="Y94" t="inlineStr">
-        <is>
-          <t>2026-07-14</t>
-        </is>
-      </c>
-      <c r="Z94" t="inlineStr">
-        <is>
-          <t>12:56</t>
-        </is>
-      </c>
-      <c r="AA94" t="inlineStr">
-        <is>
-          <t>2026-07-14</t>
-        </is>
-      </c>
-      <c r="AB94" t="inlineStr">
-        <is>
-          <t>12:56</t>
-        </is>
-      </c>
-      <c r="AC94" t="inlineStr">
-        <is>
-          <t>äldre ringhack</t>
-        </is>
-      </c>
-      <c r="AD94" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE94" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG94" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT94" t="inlineStr"/>
-      <c r="AW94" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX94" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY94" t="inlineStr"/>
-      <c r="AZ94" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135192161</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="n">
-        <v>135192166</v>
-      </c>
-      <c r="B95" t="n">
-        <v>57980</v>
-      </c>
-      <c r="D95" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E95" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F95" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G95" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H95" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I95" t="inlineStr"/>
-      <c r="P95" t="inlineStr">
-        <is>
-          <t>Höbrännflon, Jmt</t>
-        </is>
-      </c>
-      <c r="Q95" t="n">
-        <v>469249</v>
-      </c>
-      <c r="R95" t="n">
-        <v>7077922</v>
-      </c>
-      <c r="S95" t="n">
-        <v>10</v>
-      </c>
-      <c r="T95" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U95" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V95" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W95" t="inlineStr">
-        <is>
-          <t>Föllinge</t>
-        </is>
-      </c>
-      <c r="Y95" t="inlineStr">
-        <is>
-          <t>2026-07-14</t>
-        </is>
-      </c>
-      <c r="Z95" t="inlineStr">
-        <is>
-          <t>13:07</t>
-        </is>
-      </c>
-      <c r="AA95" t="inlineStr">
-        <is>
-          <t>2026-07-14</t>
-        </is>
-      </c>
-      <c r="AB95" t="inlineStr">
-        <is>
-          <t>13:07</t>
-        </is>
-      </c>
-      <c r="AC95" t="inlineStr">
-        <is>
-          <t>ringhack</t>
-        </is>
-      </c>
-      <c r="AD95" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE95" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG95" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT95" t="inlineStr"/>
-      <c r="AW95" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX95" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY95" t="inlineStr"/>
-      <c r="AZ95" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135192166</t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="n">
-        <v>128346628</v>
-      </c>
-      <c r="B96" t="n">
-        <v>97989</v>
-      </c>
-      <c r="D96" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E96" t="n">
-        <v>221941</v>
-      </c>
-      <c r="F96" t="inlineStr">
-        <is>
-          <t>Plattlummer</t>
-        </is>
-      </c>
-      <c r="G96" t="inlineStr">
-        <is>
-          <t>Lycopodium complanatum</t>
-        </is>
-      </c>
-      <c r="H96" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I96" t="inlineStr"/>
-      <c r="P96" t="inlineStr">
-        <is>
-          <t>Höbrännflon sö, Jmt</t>
-        </is>
-      </c>
-      <c r="Q96" t="n">
-        <v>468931</v>
-      </c>
-      <c r="R96" t="n">
-        <v>7077743</v>
-      </c>
-      <c r="S96" t="n">
-        <v>10</v>
-      </c>
-      <c r="T96" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U96" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V96" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W96" t="inlineStr">
-        <is>
-          <t>Föllinge</t>
-        </is>
-      </c>
-      <c r="Y96" t="inlineStr">
-        <is>
-          <t>2025-09-09</t>
-        </is>
-      </c>
-      <c r="AA96" t="inlineStr">
-        <is>
-          <t>2025-09-09</t>
-        </is>
-      </c>
-      <c r="AD96" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE96" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG96" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT96" t="inlineStr"/>
-      <c r="AW96" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX96" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY96" t="inlineStr"/>
-      <c r="AZ96" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/128346628</t>
         </is>
@@ -11663,44 +7037,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ87" r:id="rId86"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ88" r:id="rId87"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ89" r:id="rId88"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ90" r:id="rId89"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ91" r:id="rId90"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ92" r:id="rId91"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ93" r:id="rId92"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ94" r:id="rId93"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ95" r:id="rId94"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ96" r:id="rId95"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 28940-2026 artfynd.xlsx
+++ b/artfynd/A 28940-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ58"/>
+  <dimension ref="A1:AZ96"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6878,45 +6878,50 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128346628</v>
+        <v>135192022</v>
       </c>
       <c r="B58" t="n">
-        <v>97989</v>
+        <v>57980</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>221941</v>
+        <v>100109</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Höbrännflon sö, Jmt</t>
+          <t>Höbrännflon, Jmt</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>468931</v>
+        <v>469168</v>
       </c>
       <c r="R58" t="n">
-        <v>7077743</v>
+        <v>7078178</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6943,12 +6948,27 @@
       </c>
       <c r="Y58" t="inlineStr">
         <is>
-          <t>2025-09-09</t>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="Z58" t="inlineStr">
+        <is>
+          <t>09:29</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>2025-09-09</t>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="AB58" t="inlineStr">
+        <is>
+          <t>09:29</t>
+        </is>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>äldre ringhack</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6973,6 +6993,4612 @@
       </c>
       <c r="AY58" t="inlineStr"/>
       <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135192022</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>135192026</v>
+      </c>
+      <c r="B59" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>Höbrännflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q59" t="n">
+        <v>469186</v>
+      </c>
+      <c r="R59" t="n">
+        <v>7078140</v>
+      </c>
+      <c r="S59" t="n">
+        <v>10</v>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="Z59" t="inlineStr">
+        <is>
+          <t>09:38</t>
+        </is>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="AB59" t="inlineStr">
+        <is>
+          <t>09:38</t>
+        </is>
+      </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>äldre ringhack</t>
+        </is>
+      </c>
+      <c r="AD59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT59" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX59" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135192026</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>135192030</v>
+      </c>
+      <c r="B60" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>Höbrännflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q60" t="n">
+        <v>469177</v>
+      </c>
+      <c r="R60" t="n">
+        <v>7078094</v>
+      </c>
+      <c r="S60" t="n">
+        <v>10</v>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="Z60" t="inlineStr">
+        <is>
+          <t>09:48</t>
+        </is>
+      </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="AB60" t="inlineStr">
+        <is>
+          <t>09:48</t>
+        </is>
+      </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>äldre ringhack</t>
+        </is>
+      </c>
+      <c r="AD60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT60" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX60" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135192030</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>135192045</v>
+      </c>
+      <c r="B61" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>Höbrännflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q61" t="n">
+        <v>468993</v>
+      </c>
+      <c r="R61" t="n">
+        <v>7078287</v>
+      </c>
+      <c r="S61" t="n">
+        <v>10</v>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y61" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="Z61" t="inlineStr">
+        <is>
+          <t>10:18</t>
+        </is>
+      </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="AB61" t="inlineStr">
+        <is>
+          <t>10:18</t>
+        </is>
+      </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>ringhack</t>
+        </is>
+      </c>
+      <c r="AD61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT61" t="inlineStr"/>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX61" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135192045</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>135192047</v>
+      </c>
+      <c r="B62" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>Höbrännflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q62" t="n">
+        <v>468901</v>
+      </c>
+      <c r="R62" t="n">
+        <v>7078371</v>
+      </c>
+      <c r="S62" t="n">
+        <v>10</v>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="Z62" t="inlineStr">
+        <is>
+          <t>10:25</t>
+        </is>
+      </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="AB62" t="inlineStr">
+        <is>
+          <t>10:25</t>
+        </is>
+      </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>äldre ringhack</t>
+        </is>
+      </c>
+      <c r="AD62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT62" t="inlineStr"/>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX62" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135192047</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>135192048</v>
+      </c>
+      <c r="B63" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>Höbrännflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q63" t="n">
+        <v>468891</v>
+      </c>
+      <c r="R63" t="n">
+        <v>7078390</v>
+      </c>
+      <c r="S63" t="n">
+        <v>10</v>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="Z63" t="inlineStr">
+        <is>
+          <t>10:28</t>
+        </is>
+      </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="AB63" t="inlineStr">
+        <is>
+          <t>10:28</t>
+        </is>
+      </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>färska o och äldre ringhack</t>
+        </is>
+      </c>
+      <c r="AD63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT63" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX63" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135192048</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>135192050</v>
+      </c>
+      <c r="B64" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>Höbrännflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q64" t="n">
+        <v>468864</v>
+      </c>
+      <c r="R64" t="n">
+        <v>7078369</v>
+      </c>
+      <c r="S64" t="n">
+        <v>10</v>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="Z64" t="inlineStr">
+        <is>
+          <t>10:31</t>
+        </is>
+      </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="AB64" t="inlineStr">
+        <is>
+          <t>10:31</t>
+        </is>
+      </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>färska och äldre ringhack</t>
+        </is>
+      </c>
+      <c r="AD64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT64" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX64" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135192050</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>135192056</v>
+      </c>
+      <c r="B65" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>Höbrännflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q65" t="n">
+        <v>468923</v>
+      </c>
+      <c r="R65" t="n">
+        <v>7078311</v>
+      </c>
+      <c r="S65" t="n">
+        <v>10</v>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y65" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="Z65" t="inlineStr">
+        <is>
+          <t>10:37</t>
+        </is>
+      </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="AB65" t="inlineStr">
+        <is>
+          <t>10:37</t>
+        </is>
+      </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>äldre ringhack</t>
+        </is>
+      </c>
+      <c r="AD65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT65" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX65" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135192056</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>135192074</v>
+      </c>
+      <c r="B66" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>Höbrännflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q66" t="n">
+        <v>469051</v>
+      </c>
+      <c r="R66" t="n">
+        <v>7077912</v>
+      </c>
+      <c r="S66" t="n">
+        <v>10</v>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W66" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y66" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="Z66" t="inlineStr">
+        <is>
+          <t>11:05</t>
+        </is>
+      </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="AB66" t="inlineStr">
+        <is>
+          <t>11:05</t>
+        </is>
+      </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>äldre ringhack</t>
+        </is>
+      </c>
+      <c r="AD66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT66" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX66" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135192074</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>135192077</v>
+      </c>
+      <c r="B67" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>Höbrännflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q67" t="n">
+        <v>469002</v>
+      </c>
+      <c r="R67" t="n">
+        <v>7077895</v>
+      </c>
+      <c r="S67" t="n">
+        <v>10</v>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W67" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y67" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="Z67" t="inlineStr">
+        <is>
+          <t>11:09</t>
+        </is>
+      </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="AB67" t="inlineStr">
+        <is>
+          <t>11:09</t>
+        </is>
+      </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>äldre ringhack</t>
+        </is>
+      </c>
+      <c r="AD67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT67" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX67" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135192077</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>135192079</v>
+      </c>
+      <c r="B68" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr"/>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>Höbrännflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q68" t="n">
+        <v>469028</v>
+      </c>
+      <c r="R68" t="n">
+        <v>7077856</v>
+      </c>
+      <c r="S68" t="n">
+        <v>10</v>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W68" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y68" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="Z68" t="inlineStr">
+        <is>
+          <t>11:12</t>
+        </is>
+      </c>
+      <c r="AA68" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="AB68" t="inlineStr">
+        <is>
+          <t>11:12</t>
+        </is>
+      </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>äldre ringhack</t>
+        </is>
+      </c>
+      <c r="AD68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT68" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX68" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135192079</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>135192085</v>
+      </c>
+      <c r="B69" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>Höbrännflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q69" t="n">
+        <v>468941</v>
+      </c>
+      <c r="R69" t="n">
+        <v>7077921</v>
+      </c>
+      <c r="S69" t="n">
+        <v>10</v>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W69" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y69" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="Z69" t="inlineStr">
+        <is>
+          <t>11:18</t>
+        </is>
+      </c>
+      <c r="AA69" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="AB69" t="inlineStr">
+        <is>
+          <t>11:18</t>
+        </is>
+      </c>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>äldre ringhack</t>
+        </is>
+      </c>
+      <c r="AD69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT69" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX69" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135192085</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>135192088</v>
+      </c>
+      <c r="B70" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>Höbrännflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q70" t="n">
+        <v>468900</v>
+      </c>
+      <c r="R70" t="n">
+        <v>7077908</v>
+      </c>
+      <c r="S70" t="n">
+        <v>10</v>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W70" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y70" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="Z70" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="AA70" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="AB70" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="AC70" t="inlineStr">
+        <is>
+          <t>färska och äldre ringhack</t>
+        </is>
+      </c>
+      <c r="AD70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT70" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX70" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135192088</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>135192093</v>
+      </c>
+      <c r="B71" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr"/>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>Höbrännflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q71" t="n">
+        <v>468841</v>
+      </c>
+      <c r="R71" t="n">
+        <v>7077895</v>
+      </c>
+      <c r="S71" t="n">
+        <v>10</v>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W71" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y71" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="Z71" t="inlineStr">
+        <is>
+          <t>11:28</t>
+        </is>
+      </c>
+      <c r="AA71" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="AB71" t="inlineStr">
+        <is>
+          <t>11:28</t>
+        </is>
+      </c>
+      <c r="AC71" t="inlineStr">
+        <is>
+          <t>äldre ringhack</t>
+        </is>
+      </c>
+      <c r="AD71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT71" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX71" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135192093</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>135192095</v>
+      </c>
+      <c r="B72" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr"/>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>Höbrännflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q72" t="n">
+        <v>468832</v>
+      </c>
+      <c r="R72" t="n">
+        <v>7077861</v>
+      </c>
+      <c r="S72" t="n">
+        <v>10</v>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V72" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W72" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y72" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="Z72" t="inlineStr">
+        <is>
+          <t>11:32</t>
+        </is>
+      </c>
+      <c r="AA72" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="AB72" t="inlineStr">
+        <is>
+          <t>11:32</t>
+        </is>
+      </c>
+      <c r="AC72" t="inlineStr">
+        <is>
+          <t>äldre ringhack</t>
+        </is>
+      </c>
+      <c r="AD72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT72" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX72" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135192095</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>135192112</v>
+      </c>
+      <c r="B73" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E73" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr"/>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>Höbrännflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q73" t="n">
+        <v>469029</v>
+      </c>
+      <c r="R73" t="n">
+        <v>7077764</v>
+      </c>
+      <c r="S73" t="n">
+        <v>10</v>
+      </c>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V73" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W73" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y73" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="Z73" t="inlineStr">
+        <is>
+          <t>11:55</t>
+        </is>
+      </c>
+      <c r="AA73" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="AB73" t="inlineStr">
+        <is>
+          <t>11:55</t>
+        </is>
+      </c>
+      <c r="AC73" t="inlineStr">
+        <is>
+          <t>äldre ringhack</t>
+        </is>
+      </c>
+      <c r="AD73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT73" t="inlineStr"/>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX73" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY73" t="inlineStr"/>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135192112</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>135192116</v>
+      </c>
+      <c r="B74" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E74" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr"/>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>Höbrännflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q74" t="n">
+        <v>469092</v>
+      </c>
+      <c r="R74" t="n">
+        <v>7077868</v>
+      </c>
+      <c r="S74" t="n">
+        <v>10</v>
+      </c>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V74" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W74" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y74" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="Z74" t="inlineStr">
+        <is>
+          <t>12:02</t>
+        </is>
+      </c>
+      <c r="AA74" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="AB74" t="inlineStr">
+        <is>
+          <t>12:02</t>
+        </is>
+      </c>
+      <c r="AC74" t="inlineStr">
+        <is>
+          <t>äldre ringhack</t>
+        </is>
+      </c>
+      <c r="AD74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT74" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX74" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY74" t="inlineStr"/>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135192116</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>135192118</v>
+      </c>
+      <c r="B75" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E75" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr"/>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t>Höbrännflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q75" t="n">
+        <v>469121</v>
+      </c>
+      <c r="R75" t="n">
+        <v>7077852</v>
+      </c>
+      <c r="S75" t="n">
+        <v>10</v>
+      </c>
+      <c r="T75" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U75" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V75" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W75" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y75" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="Z75" t="inlineStr">
+        <is>
+          <t>12:04</t>
+        </is>
+      </c>
+      <c r="AA75" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="AB75" t="inlineStr">
+        <is>
+          <t>12:04</t>
+        </is>
+      </c>
+      <c r="AC75" t="inlineStr">
+        <is>
+          <t>äldre ringhack</t>
+        </is>
+      </c>
+      <c r="AD75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT75" t="inlineStr"/>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX75" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY75" t="inlineStr"/>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135192118</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>135192119</v>
+      </c>
+      <c r="B76" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E76" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr"/>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t>Höbrännflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q76" t="n">
+        <v>469139</v>
+      </c>
+      <c r="R76" t="n">
+        <v>7077825</v>
+      </c>
+      <c r="S76" t="n">
+        <v>10</v>
+      </c>
+      <c r="T76" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U76" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V76" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W76" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y76" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="Z76" t="inlineStr">
+        <is>
+          <t>12:07</t>
+        </is>
+      </c>
+      <c r="AA76" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="AB76" t="inlineStr">
+        <is>
+          <t>12:07</t>
+        </is>
+      </c>
+      <c r="AC76" t="inlineStr">
+        <is>
+          <t>äldre ringhack</t>
+        </is>
+      </c>
+      <c r="AD76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT76" t="inlineStr"/>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX76" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY76" t="inlineStr"/>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135192119</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>135192123</v>
+      </c>
+      <c r="B77" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E77" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr"/>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P77" t="inlineStr">
+        <is>
+          <t>Höbrännflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q77" t="n">
+        <v>469108</v>
+      </c>
+      <c r="R77" t="n">
+        <v>7077950</v>
+      </c>
+      <c r="S77" t="n">
+        <v>10</v>
+      </c>
+      <c r="T77" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U77" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V77" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W77" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y77" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="Z77" t="inlineStr">
+        <is>
+          <t>12:11</t>
+        </is>
+      </c>
+      <c r="AA77" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="AB77" t="inlineStr">
+        <is>
+          <t>12:11</t>
+        </is>
+      </c>
+      <c r="AC77" t="inlineStr">
+        <is>
+          <t>färska ringhack</t>
+        </is>
+      </c>
+      <c r="AD77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT77" t="inlineStr"/>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX77" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY77" t="inlineStr"/>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135192123</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>135192124</v>
+      </c>
+      <c r="B78" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E78" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr"/>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P78" t="inlineStr">
+        <is>
+          <t>Höbrännflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q78" t="n">
+        <v>469109</v>
+      </c>
+      <c r="R78" t="n">
+        <v>7077945</v>
+      </c>
+      <c r="S78" t="n">
+        <v>10</v>
+      </c>
+      <c r="T78" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U78" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V78" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W78" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y78" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="Z78" t="inlineStr">
+        <is>
+          <t>12:12</t>
+        </is>
+      </c>
+      <c r="AA78" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="AB78" t="inlineStr">
+        <is>
+          <t>12:12</t>
+        </is>
+      </c>
+      <c r="AC78" t="inlineStr">
+        <is>
+          <t>färska ringhack</t>
+        </is>
+      </c>
+      <c r="AD78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT78" t="inlineStr"/>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX78" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY78" t="inlineStr"/>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135192124</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>135192125</v>
+      </c>
+      <c r="B79" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E79" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr"/>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P79" t="inlineStr">
+        <is>
+          <t>Höbrännflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q79" t="n">
+        <v>469118</v>
+      </c>
+      <c r="R79" t="n">
+        <v>7077938</v>
+      </c>
+      <c r="S79" t="n">
+        <v>10</v>
+      </c>
+      <c r="T79" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U79" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V79" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W79" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y79" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="Z79" t="inlineStr">
+        <is>
+          <t>12:12</t>
+        </is>
+      </c>
+      <c r="AA79" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="AB79" t="inlineStr">
+        <is>
+          <t>12:12</t>
+        </is>
+      </c>
+      <c r="AC79" t="inlineStr">
+        <is>
+          <t>färska ringhack</t>
+        </is>
+      </c>
+      <c r="AD79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT79" t="inlineStr"/>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX79" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY79" t="inlineStr"/>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135192125</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>135192127</v>
+      </c>
+      <c r="B80" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E80" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr"/>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P80" t="inlineStr">
+        <is>
+          <t>Höbrännflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q80" t="n">
+        <v>469140</v>
+      </c>
+      <c r="R80" t="n">
+        <v>7077913</v>
+      </c>
+      <c r="S80" t="n">
+        <v>10</v>
+      </c>
+      <c r="T80" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U80" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V80" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W80" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y80" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="Z80" t="inlineStr">
+        <is>
+          <t>12:13</t>
+        </is>
+      </c>
+      <c r="AA80" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="AB80" t="inlineStr">
+        <is>
+          <t>12:13</t>
+        </is>
+      </c>
+      <c r="AC80" t="inlineStr">
+        <is>
+          <t>färska ringhack</t>
+        </is>
+      </c>
+      <c r="AD80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT80" t="inlineStr"/>
+      <c r="AW80" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX80" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY80" t="inlineStr"/>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135192127</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>135192128</v>
+      </c>
+      <c r="B81" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E81" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr"/>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P81" t="inlineStr">
+        <is>
+          <t>Höbrännflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q81" t="n">
+        <v>469149</v>
+      </c>
+      <c r="R81" t="n">
+        <v>7077895</v>
+      </c>
+      <c r="S81" t="n">
+        <v>10</v>
+      </c>
+      <c r="T81" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U81" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V81" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W81" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y81" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="Z81" t="inlineStr">
+        <is>
+          <t>12:14</t>
+        </is>
+      </c>
+      <c r="AA81" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="AB81" t="inlineStr">
+        <is>
+          <t>12:14</t>
+        </is>
+      </c>
+      <c r="AC81" t="inlineStr">
+        <is>
+          <t>färska ringhack</t>
+        </is>
+      </c>
+      <c r="AD81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT81" t="inlineStr"/>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX81" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY81" t="inlineStr"/>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135192128</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>135192130</v>
+      </c>
+      <c r="B82" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E82" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr"/>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P82" t="inlineStr">
+        <is>
+          <t>Höbrännflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q82" t="n">
+        <v>469158</v>
+      </c>
+      <c r="R82" t="n">
+        <v>7077852</v>
+      </c>
+      <c r="S82" t="n">
+        <v>10</v>
+      </c>
+      <c r="T82" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U82" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V82" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W82" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y82" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="Z82" t="inlineStr">
+        <is>
+          <t>12:15</t>
+        </is>
+      </c>
+      <c r="AA82" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="AB82" t="inlineStr">
+        <is>
+          <t>12:15</t>
+        </is>
+      </c>
+      <c r="AC82" t="inlineStr">
+        <is>
+          <t>färska ringhack</t>
+        </is>
+      </c>
+      <c r="AD82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT82" t="inlineStr"/>
+      <c r="AW82" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX82" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY82" t="inlineStr"/>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135192130</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>135192131</v>
+      </c>
+      <c r="B83" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E83" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr"/>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P83" t="inlineStr">
+        <is>
+          <t>Höbrännflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q83" t="n">
+        <v>469166</v>
+      </c>
+      <c r="R83" t="n">
+        <v>7077841</v>
+      </c>
+      <c r="S83" t="n">
+        <v>10</v>
+      </c>
+      <c r="T83" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U83" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V83" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W83" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y83" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="Z83" t="inlineStr">
+        <is>
+          <t>12:16</t>
+        </is>
+      </c>
+      <c r="AA83" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="AB83" t="inlineStr">
+        <is>
+          <t>12:16</t>
+        </is>
+      </c>
+      <c r="AC83" t="inlineStr">
+        <is>
+          <t>färska ringhack</t>
+        </is>
+      </c>
+      <c r="AD83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT83" t="inlineStr"/>
+      <c r="AW83" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX83" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY83" t="inlineStr"/>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135192131</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>135192132</v>
+      </c>
+      <c r="B84" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E84" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr"/>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P84" t="inlineStr">
+        <is>
+          <t>Höbrännflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q84" t="n">
+        <v>469163</v>
+      </c>
+      <c r="R84" t="n">
+        <v>7077822</v>
+      </c>
+      <c r="S84" t="n">
+        <v>10</v>
+      </c>
+      <c r="T84" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U84" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V84" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W84" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y84" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="Z84" t="inlineStr">
+        <is>
+          <t>12:17</t>
+        </is>
+      </c>
+      <c r="AA84" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="AB84" t="inlineStr">
+        <is>
+          <t>12:17</t>
+        </is>
+      </c>
+      <c r="AC84" t="inlineStr">
+        <is>
+          <t>färska ringhack</t>
+        </is>
+      </c>
+      <c r="AD84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT84" t="inlineStr"/>
+      <c r="AW84" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX84" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY84" t="inlineStr"/>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135192132</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>135192134</v>
+      </c>
+      <c r="B85" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E85" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr"/>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P85" t="inlineStr">
+        <is>
+          <t>Höbrännflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q85" t="n">
+        <v>469172</v>
+      </c>
+      <c r="R85" t="n">
+        <v>7077811</v>
+      </c>
+      <c r="S85" t="n">
+        <v>10</v>
+      </c>
+      <c r="T85" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U85" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V85" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W85" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y85" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="Z85" t="inlineStr">
+        <is>
+          <t>12:17</t>
+        </is>
+      </c>
+      <c r="AA85" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="AB85" t="inlineStr">
+        <is>
+          <t>12:17</t>
+        </is>
+      </c>
+      <c r="AC85" t="inlineStr">
+        <is>
+          <t>färska ringhack</t>
+        </is>
+      </c>
+      <c r="AD85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT85" t="inlineStr"/>
+      <c r="AW85" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX85" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY85" t="inlineStr"/>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135192134</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>135192135</v>
+      </c>
+      <c r="B86" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E86" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr"/>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P86" t="inlineStr">
+        <is>
+          <t>Höbrännflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q86" t="n">
+        <v>469180</v>
+      </c>
+      <c r="R86" t="n">
+        <v>7077818</v>
+      </c>
+      <c r="S86" t="n">
+        <v>10</v>
+      </c>
+      <c r="T86" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U86" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V86" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W86" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y86" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="Z86" t="inlineStr">
+        <is>
+          <t>12:18</t>
+        </is>
+      </c>
+      <c r="AA86" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="AB86" t="inlineStr">
+        <is>
+          <t>12:18</t>
+        </is>
+      </c>
+      <c r="AC86" t="inlineStr">
+        <is>
+          <t>äldre ringhack</t>
+        </is>
+      </c>
+      <c r="AD86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT86" t="inlineStr"/>
+      <c r="AW86" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX86" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY86" t="inlineStr"/>
+      <c r="AZ86" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135192135</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>135192136</v>
+      </c>
+      <c r="B87" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E87" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr"/>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P87" t="inlineStr">
+        <is>
+          <t>Höbrännflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q87" t="n">
+        <v>469176</v>
+      </c>
+      <c r="R87" t="n">
+        <v>7077799</v>
+      </c>
+      <c r="S87" t="n">
+        <v>10</v>
+      </c>
+      <c r="T87" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U87" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V87" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W87" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y87" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="Z87" t="inlineStr">
+        <is>
+          <t>12:19</t>
+        </is>
+      </c>
+      <c r="AA87" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="AB87" t="inlineStr">
+        <is>
+          <t>12:19</t>
+        </is>
+      </c>
+      <c r="AC87" t="inlineStr">
+        <is>
+          <t>färska ringhack</t>
+        </is>
+      </c>
+      <c r="AD87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT87" t="inlineStr"/>
+      <c r="AW87" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX87" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY87" t="inlineStr"/>
+      <c r="AZ87" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135192136</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>135192137</v>
+      </c>
+      <c r="B88" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E88" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr"/>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P88" t="inlineStr">
+        <is>
+          <t>Höbrännflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q88" t="n">
+        <v>469181</v>
+      </c>
+      <c r="R88" t="n">
+        <v>7077798</v>
+      </c>
+      <c r="S88" t="n">
+        <v>10</v>
+      </c>
+      <c r="T88" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U88" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V88" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W88" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y88" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="Z88" t="inlineStr">
+        <is>
+          <t>12:20</t>
+        </is>
+      </c>
+      <c r="AA88" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="AB88" t="inlineStr">
+        <is>
+          <t>12:20</t>
+        </is>
+      </c>
+      <c r="AC88" t="inlineStr">
+        <is>
+          <t>färska ringhack</t>
+        </is>
+      </c>
+      <c r="AD88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT88" t="inlineStr"/>
+      <c r="AW88" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX88" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY88" t="inlineStr"/>
+      <c r="AZ88" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135192137</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>135192151</v>
+      </c>
+      <c r="B89" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E89" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr"/>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P89" t="inlineStr">
+        <is>
+          <t>Höbrännflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q89" t="n">
+        <v>469393</v>
+      </c>
+      <c r="R89" t="n">
+        <v>7077846</v>
+      </c>
+      <c r="S89" t="n">
+        <v>10</v>
+      </c>
+      <c r="T89" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U89" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V89" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W89" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y89" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="Z89" t="inlineStr">
+        <is>
+          <t>12:42</t>
+        </is>
+      </c>
+      <c r="AA89" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="AB89" t="inlineStr">
+        <is>
+          <t>12:42</t>
+        </is>
+      </c>
+      <c r="AC89" t="inlineStr">
+        <is>
+          <t>äldre ringhack</t>
+        </is>
+      </c>
+      <c r="AD89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT89" t="inlineStr"/>
+      <c r="AW89" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX89" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY89" t="inlineStr"/>
+      <c r="AZ89" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135192151</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>135192152</v>
+      </c>
+      <c r="B90" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E90" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr"/>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P90" t="inlineStr">
+        <is>
+          <t>Höbrännflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q90" t="n">
+        <v>469356</v>
+      </c>
+      <c r="R90" t="n">
+        <v>7077867</v>
+      </c>
+      <c r="S90" t="n">
+        <v>10</v>
+      </c>
+      <c r="T90" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U90" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V90" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W90" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y90" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="Z90" t="inlineStr">
+        <is>
+          <t>12:45</t>
+        </is>
+      </c>
+      <c r="AA90" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="AB90" t="inlineStr">
+        <is>
+          <t>12:45</t>
+        </is>
+      </c>
+      <c r="AC90" t="inlineStr">
+        <is>
+          <t>äldre ringhack</t>
+        </is>
+      </c>
+      <c r="AD90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT90" t="inlineStr"/>
+      <c r="AW90" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX90" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY90" t="inlineStr"/>
+      <c r="AZ90" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135192152</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>135192153</v>
+      </c>
+      <c r="B91" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E91" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr"/>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P91" t="inlineStr">
+        <is>
+          <t>Höbrännflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q91" t="n">
+        <v>469347</v>
+      </c>
+      <c r="R91" t="n">
+        <v>7077869</v>
+      </c>
+      <c r="S91" t="n">
+        <v>10</v>
+      </c>
+      <c r="T91" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U91" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V91" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W91" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y91" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="Z91" t="inlineStr">
+        <is>
+          <t>12:46</t>
+        </is>
+      </c>
+      <c r="AA91" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="AB91" t="inlineStr">
+        <is>
+          <t>12:46</t>
+        </is>
+      </c>
+      <c r="AC91" t="inlineStr">
+        <is>
+          <t>äldre ringhack</t>
+        </is>
+      </c>
+      <c r="AD91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT91" t="inlineStr"/>
+      <c r="AW91" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX91" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY91" t="inlineStr"/>
+      <c r="AZ91" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135192153</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>135192157</v>
+      </c>
+      <c r="B92" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E92" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr"/>
+      <c r="M92" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P92" t="inlineStr">
+        <is>
+          <t>Höbrännflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q92" t="n">
+        <v>469381</v>
+      </c>
+      <c r="R92" t="n">
+        <v>7077873</v>
+      </c>
+      <c r="S92" t="n">
+        <v>10</v>
+      </c>
+      <c r="T92" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U92" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V92" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W92" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y92" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="Z92" t="inlineStr">
+        <is>
+          <t>12:52</t>
+        </is>
+      </c>
+      <c r="AA92" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="AB92" t="inlineStr">
+        <is>
+          <t>12:52</t>
+        </is>
+      </c>
+      <c r="AC92" t="inlineStr">
+        <is>
+          <t>äldre ringhack</t>
+        </is>
+      </c>
+      <c r="AD92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT92" t="inlineStr"/>
+      <c r="AW92" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX92" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY92" t="inlineStr"/>
+      <c r="AZ92" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135192157</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>135192158</v>
+      </c>
+      <c r="B93" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E93" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr"/>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P93" t="inlineStr">
+        <is>
+          <t>Höbrännflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q93" t="n">
+        <v>469401</v>
+      </c>
+      <c r="R93" t="n">
+        <v>7077887</v>
+      </c>
+      <c r="S93" t="n">
+        <v>10</v>
+      </c>
+      <c r="T93" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U93" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V93" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W93" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y93" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="Z93" t="inlineStr">
+        <is>
+          <t>12:54</t>
+        </is>
+      </c>
+      <c r="AA93" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="AB93" t="inlineStr">
+        <is>
+          <t>12:54</t>
+        </is>
+      </c>
+      <c r="AC93" t="inlineStr">
+        <is>
+          <t>äldre ringhack</t>
+        </is>
+      </c>
+      <c r="AD93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT93" t="inlineStr"/>
+      <c r="AW93" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX93" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY93" t="inlineStr"/>
+      <c r="AZ93" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135192158</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>135192161</v>
+      </c>
+      <c r="B94" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E94" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr"/>
+      <c r="M94" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P94" t="inlineStr">
+        <is>
+          <t>Höbrännflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q94" t="n">
+        <v>469388</v>
+      </c>
+      <c r="R94" t="n">
+        <v>7077920</v>
+      </c>
+      <c r="S94" t="n">
+        <v>10</v>
+      </c>
+      <c r="T94" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U94" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V94" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W94" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y94" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="Z94" t="inlineStr">
+        <is>
+          <t>12:56</t>
+        </is>
+      </c>
+      <c r="AA94" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="AB94" t="inlineStr">
+        <is>
+          <t>12:56</t>
+        </is>
+      </c>
+      <c r="AC94" t="inlineStr">
+        <is>
+          <t>äldre ringhack</t>
+        </is>
+      </c>
+      <c r="AD94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT94" t="inlineStr"/>
+      <c r="AW94" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX94" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY94" t="inlineStr"/>
+      <c r="AZ94" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135192161</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>135192166</v>
+      </c>
+      <c r="B95" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E95" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr"/>
+      <c r="P95" t="inlineStr">
+        <is>
+          <t>Höbrännflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q95" t="n">
+        <v>469249</v>
+      </c>
+      <c r="R95" t="n">
+        <v>7077922</v>
+      </c>
+      <c r="S95" t="n">
+        <v>10</v>
+      </c>
+      <c r="T95" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U95" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V95" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W95" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y95" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="Z95" t="inlineStr">
+        <is>
+          <t>13:07</t>
+        </is>
+      </c>
+      <c r="AA95" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="AB95" t="inlineStr">
+        <is>
+          <t>13:07</t>
+        </is>
+      </c>
+      <c r="AC95" t="inlineStr">
+        <is>
+          <t>ringhack</t>
+        </is>
+      </c>
+      <c r="AD95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT95" t="inlineStr"/>
+      <c r="AW95" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX95" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY95" t="inlineStr"/>
+      <c r="AZ95" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135192166</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="n">
+        <v>128346628</v>
+      </c>
+      <c r="B96" t="n">
+        <v>97989</v>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E96" t="n">
+        <v>221941</v>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>Plattlummer</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>Lycopodium complanatum</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr"/>
+      <c r="P96" t="inlineStr">
+        <is>
+          <t>Höbrännflon sö, Jmt</t>
+        </is>
+      </c>
+      <c r="Q96" t="n">
+        <v>468931</v>
+      </c>
+      <c r="R96" t="n">
+        <v>7077743</v>
+      </c>
+      <c r="S96" t="n">
+        <v>10</v>
+      </c>
+      <c r="T96" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U96" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V96" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W96" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y96" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AA96" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AD96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT96" t="inlineStr"/>
+      <c r="AW96" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX96" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY96" t="inlineStr"/>
+      <c r="AZ96" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/128346628</t>
         </is>
@@ -7037,6 +11663,44 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ91" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ92" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ93" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ94" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ95" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ96" r:id="rId95"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 28940-2026 artfynd.xlsx
+++ b/artfynd/A 28940-2026 artfynd.xlsx
@@ -6881,7 +6881,7 @@
         <v>135192022</v>
       </c>
       <c r="B58" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7003,7 +7003,7 @@
         <v>135192026</v>
       </c>
       <c r="B59" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7125,7 +7125,7 @@
         <v>135192030</v>
       </c>
       <c r="B60" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7247,7 +7247,7 @@
         <v>135192045</v>
       </c>
       <c r="B61" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7364,7 +7364,7 @@
         <v>135192047</v>
       </c>
       <c r="B62" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7486,7 +7486,7 @@
         <v>135192048</v>
       </c>
       <c r="B63" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7608,7 +7608,7 @@
         <v>135192050</v>
       </c>
       <c r="B64" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7730,7 +7730,7 @@
         <v>135192056</v>
       </c>
       <c r="B65" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7852,7 +7852,7 @@
         <v>135192074</v>
       </c>
       <c r="B66" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7974,7 +7974,7 @@
         <v>135192077</v>
       </c>
       <c r="B67" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8096,7 +8096,7 @@
         <v>135192079</v>
       </c>
       <c r="B68" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8218,7 +8218,7 @@
         <v>135192085</v>
       </c>
       <c r="B69" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8340,7 +8340,7 @@
         <v>135192088</v>
       </c>
       <c r="B70" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8462,7 +8462,7 @@
         <v>135192093</v>
       </c>
       <c r="B71" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8584,7 +8584,7 @@
         <v>135192095</v>
       </c>
       <c r="B72" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8706,7 +8706,7 @@
         <v>135192112</v>
       </c>
       <c r="B73" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8828,7 +8828,7 @@
         <v>135192116</v>
       </c>
       <c r="B74" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8950,7 +8950,7 @@
         <v>135192118</v>
       </c>
       <c r="B75" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9072,7 +9072,7 @@
         <v>135192119</v>
       </c>
       <c r="B76" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9194,7 +9194,7 @@
         <v>135192123</v>
       </c>
       <c r="B77" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9316,7 +9316,7 @@
         <v>135192124</v>
       </c>
       <c r="B78" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9438,7 +9438,7 @@
         <v>135192125</v>
       </c>
       <c r="B79" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9560,7 +9560,7 @@
         <v>135192127</v>
       </c>
       <c r="B80" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9682,7 +9682,7 @@
         <v>135192128</v>
       </c>
       <c r="B81" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9804,7 +9804,7 @@
         <v>135192130</v>
       </c>
       <c r="B82" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9926,7 +9926,7 @@
         <v>135192131</v>
       </c>
       <c r="B83" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -10048,7 +10048,7 @@
         <v>135192132</v>
       </c>
       <c r="B84" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -10170,7 +10170,7 @@
         <v>135192134</v>
       </c>
       <c r="B85" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10292,7 +10292,7 @@
         <v>135192135</v>
       </c>
       <c r="B86" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10414,7 +10414,7 @@
         <v>135192136</v>
       </c>
       <c r="B87" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10536,7 +10536,7 @@
         <v>135192137</v>
       </c>
       <c r="B88" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10658,7 +10658,7 @@
         <v>135192151</v>
       </c>
       <c r="B89" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10780,7 +10780,7 @@
         <v>135192152</v>
       </c>
       <c r="B90" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10902,7 +10902,7 @@
         <v>135192153</v>
       </c>
       <c r="B91" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -11024,7 +11024,7 @@
         <v>135192157</v>
       </c>
       <c r="B92" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -11146,7 +11146,7 @@
         <v>135192158</v>
       </c>
       <c r="B93" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -11268,7 +11268,7 @@
         <v>135192161</v>
       </c>
       <c r="B94" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -11390,7 +11390,7 @@
         <v>135192166</v>
       </c>
       <c r="B95" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>

--- a/artfynd/A 28940-2026 artfynd.xlsx
+++ b/artfynd/A 28940-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ96"/>
+  <dimension ref="A1:AZ58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6878,50 +6878,45 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>135192022</v>
+        <v>128346628</v>
       </c>
       <c r="B58" t="n">
-        <v>57982</v>
+        <v>97989</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>100109</v>
+        <v>221941</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
-      <c r="M58" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Höbrännflon, Jmt</t>
+          <t>Höbrännflon sö, Jmt</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>469168</v>
+        <v>468931</v>
       </c>
       <c r="R58" t="n">
-        <v>7078178</v>
+        <v>7077743</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6948,27 +6943,12 @@
       </c>
       <c r="Y58" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
-        </is>
-      </c>
-      <c r="Z58" t="inlineStr">
-        <is>
-          <t>09:29</t>
+          <t>2025-09-09</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
-        </is>
-      </c>
-      <c r="AB58" t="inlineStr">
-        <is>
-          <t>09:29</t>
-        </is>
-      </c>
-      <c r="AC58" t="inlineStr">
-        <is>
-          <t>äldre ringhack</t>
+          <t>2025-09-09</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6993,4612 +6973,6 @@
       </c>
       <c r="AY58" t="inlineStr"/>
       <c r="AZ58" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135192022</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="n">
-        <v>135192026</v>
-      </c>
-      <c r="B59" t="n">
-        <v>57982</v>
-      </c>
-      <c r="D59" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E59" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F59" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G59" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H59" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr"/>
-      <c r="M59" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="P59" t="inlineStr">
-        <is>
-          <t>Höbrännflon, Jmt</t>
-        </is>
-      </c>
-      <c r="Q59" t="n">
-        <v>469186</v>
-      </c>
-      <c r="R59" t="n">
-        <v>7078140</v>
-      </c>
-      <c r="S59" t="n">
-        <v>10</v>
-      </c>
-      <c r="T59" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U59" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V59" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W59" t="inlineStr">
-        <is>
-          <t>Föllinge</t>
-        </is>
-      </c>
-      <c r="Y59" t="inlineStr">
-        <is>
-          <t>2026-07-14</t>
-        </is>
-      </c>
-      <c r="Z59" t="inlineStr">
-        <is>
-          <t>09:38</t>
-        </is>
-      </c>
-      <c r="AA59" t="inlineStr">
-        <is>
-          <t>2026-07-14</t>
-        </is>
-      </c>
-      <c r="AB59" t="inlineStr">
-        <is>
-          <t>09:38</t>
-        </is>
-      </c>
-      <c r="AC59" t="inlineStr">
-        <is>
-          <t>äldre ringhack</t>
-        </is>
-      </c>
-      <c r="AD59" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE59" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG59" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT59" t="inlineStr"/>
-      <c r="AW59" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX59" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY59" t="inlineStr"/>
-      <c r="AZ59" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135192026</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="n">
-        <v>135192030</v>
-      </c>
-      <c r="B60" t="n">
-        <v>57982</v>
-      </c>
-      <c r="D60" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E60" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F60" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G60" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H60" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr"/>
-      <c r="M60" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="P60" t="inlineStr">
-        <is>
-          <t>Höbrännflon, Jmt</t>
-        </is>
-      </c>
-      <c r="Q60" t="n">
-        <v>469177</v>
-      </c>
-      <c r="R60" t="n">
-        <v>7078094</v>
-      </c>
-      <c r="S60" t="n">
-        <v>10</v>
-      </c>
-      <c r="T60" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U60" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V60" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W60" t="inlineStr">
-        <is>
-          <t>Föllinge</t>
-        </is>
-      </c>
-      <c r="Y60" t="inlineStr">
-        <is>
-          <t>2026-07-14</t>
-        </is>
-      </c>
-      <c r="Z60" t="inlineStr">
-        <is>
-          <t>09:48</t>
-        </is>
-      </c>
-      <c r="AA60" t="inlineStr">
-        <is>
-          <t>2026-07-14</t>
-        </is>
-      </c>
-      <c r="AB60" t="inlineStr">
-        <is>
-          <t>09:48</t>
-        </is>
-      </c>
-      <c r="AC60" t="inlineStr">
-        <is>
-          <t>äldre ringhack</t>
-        </is>
-      </c>
-      <c r="AD60" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE60" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG60" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT60" t="inlineStr"/>
-      <c r="AW60" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX60" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY60" t="inlineStr"/>
-      <c r="AZ60" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135192030</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="n">
-        <v>135192045</v>
-      </c>
-      <c r="B61" t="n">
-        <v>57982</v>
-      </c>
-      <c r="D61" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E61" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F61" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G61" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H61" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr"/>
-      <c r="P61" t="inlineStr">
-        <is>
-          <t>Höbrännflon, Jmt</t>
-        </is>
-      </c>
-      <c r="Q61" t="n">
-        <v>468993</v>
-      </c>
-      <c r="R61" t="n">
-        <v>7078287</v>
-      </c>
-      <c r="S61" t="n">
-        <v>10</v>
-      </c>
-      <c r="T61" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U61" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V61" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W61" t="inlineStr">
-        <is>
-          <t>Föllinge</t>
-        </is>
-      </c>
-      <c r="Y61" t="inlineStr">
-        <is>
-          <t>2026-07-14</t>
-        </is>
-      </c>
-      <c r="Z61" t="inlineStr">
-        <is>
-          <t>10:18</t>
-        </is>
-      </c>
-      <c r="AA61" t="inlineStr">
-        <is>
-          <t>2026-07-14</t>
-        </is>
-      </c>
-      <c r="AB61" t="inlineStr">
-        <is>
-          <t>10:18</t>
-        </is>
-      </c>
-      <c r="AC61" t="inlineStr">
-        <is>
-          <t>ringhack</t>
-        </is>
-      </c>
-      <c r="AD61" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE61" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG61" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT61" t="inlineStr"/>
-      <c r="AW61" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX61" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY61" t="inlineStr"/>
-      <c r="AZ61" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135192045</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="n">
-        <v>135192047</v>
-      </c>
-      <c r="B62" t="n">
-        <v>57982</v>
-      </c>
-      <c r="D62" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E62" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F62" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G62" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H62" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr"/>
-      <c r="M62" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="P62" t="inlineStr">
-        <is>
-          <t>Höbrännflon, Jmt</t>
-        </is>
-      </c>
-      <c r="Q62" t="n">
-        <v>468901</v>
-      </c>
-      <c r="R62" t="n">
-        <v>7078371</v>
-      </c>
-      <c r="S62" t="n">
-        <v>10</v>
-      </c>
-      <c r="T62" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U62" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V62" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W62" t="inlineStr">
-        <is>
-          <t>Föllinge</t>
-        </is>
-      </c>
-      <c r="Y62" t="inlineStr">
-        <is>
-          <t>2026-07-14</t>
-        </is>
-      </c>
-      <c r="Z62" t="inlineStr">
-        <is>
-          <t>10:25</t>
-        </is>
-      </c>
-      <c r="AA62" t="inlineStr">
-        <is>
-          <t>2026-07-14</t>
-        </is>
-      </c>
-      <c r="AB62" t="inlineStr">
-        <is>
-          <t>10:25</t>
-        </is>
-      </c>
-      <c r="AC62" t="inlineStr">
-        <is>
-          <t>äldre ringhack</t>
-        </is>
-      </c>
-      <c r="AD62" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE62" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG62" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT62" t="inlineStr"/>
-      <c r="AW62" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX62" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY62" t="inlineStr"/>
-      <c r="AZ62" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135192047</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="n">
-        <v>135192048</v>
-      </c>
-      <c r="B63" t="n">
-        <v>57982</v>
-      </c>
-      <c r="D63" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E63" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F63" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G63" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H63" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr"/>
-      <c r="M63" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="P63" t="inlineStr">
-        <is>
-          <t>Höbrännflon, Jmt</t>
-        </is>
-      </c>
-      <c r="Q63" t="n">
-        <v>468891</v>
-      </c>
-      <c r="R63" t="n">
-        <v>7078390</v>
-      </c>
-      <c r="S63" t="n">
-        <v>10</v>
-      </c>
-      <c r="T63" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U63" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V63" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W63" t="inlineStr">
-        <is>
-          <t>Föllinge</t>
-        </is>
-      </c>
-      <c r="Y63" t="inlineStr">
-        <is>
-          <t>2026-07-14</t>
-        </is>
-      </c>
-      <c r="Z63" t="inlineStr">
-        <is>
-          <t>10:28</t>
-        </is>
-      </c>
-      <c r="AA63" t="inlineStr">
-        <is>
-          <t>2026-07-14</t>
-        </is>
-      </c>
-      <c r="AB63" t="inlineStr">
-        <is>
-          <t>10:28</t>
-        </is>
-      </c>
-      <c r="AC63" t="inlineStr">
-        <is>
-          <t>färska o och äldre ringhack</t>
-        </is>
-      </c>
-      <c r="AD63" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE63" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG63" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT63" t="inlineStr"/>
-      <c r="AW63" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX63" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY63" t="inlineStr"/>
-      <c r="AZ63" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135192048</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="n">
-        <v>135192050</v>
-      </c>
-      <c r="B64" t="n">
-        <v>57982</v>
-      </c>
-      <c r="D64" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E64" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F64" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G64" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H64" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr"/>
-      <c r="M64" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="P64" t="inlineStr">
-        <is>
-          <t>Höbrännflon, Jmt</t>
-        </is>
-      </c>
-      <c r="Q64" t="n">
-        <v>468864</v>
-      </c>
-      <c r="R64" t="n">
-        <v>7078369</v>
-      </c>
-      <c r="S64" t="n">
-        <v>10</v>
-      </c>
-      <c r="T64" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U64" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V64" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W64" t="inlineStr">
-        <is>
-          <t>Föllinge</t>
-        </is>
-      </c>
-      <c r="Y64" t="inlineStr">
-        <is>
-          <t>2026-07-14</t>
-        </is>
-      </c>
-      <c r="Z64" t="inlineStr">
-        <is>
-          <t>10:31</t>
-        </is>
-      </c>
-      <c r="AA64" t="inlineStr">
-        <is>
-          <t>2026-07-14</t>
-        </is>
-      </c>
-      <c r="AB64" t="inlineStr">
-        <is>
-          <t>10:31</t>
-        </is>
-      </c>
-      <c r="AC64" t="inlineStr">
-        <is>
-          <t>färska och äldre ringhack</t>
-        </is>
-      </c>
-      <c r="AD64" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE64" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG64" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT64" t="inlineStr"/>
-      <c r="AW64" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX64" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY64" t="inlineStr"/>
-      <c r="AZ64" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135192050</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="n">
-        <v>135192056</v>
-      </c>
-      <c r="B65" t="n">
-        <v>57982</v>
-      </c>
-      <c r="D65" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E65" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F65" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G65" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H65" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr"/>
-      <c r="M65" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="P65" t="inlineStr">
-        <is>
-          <t>Höbrännflon, Jmt</t>
-        </is>
-      </c>
-      <c r="Q65" t="n">
-        <v>468923</v>
-      </c>
-      <c r="R65" t="n">
-        <v>7078311</v>
-      </c>
-      <c r="S65" t="n">
-        <v>10</v>
-      </c>
-      <c r="T65" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U65" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V65" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W65" t="inlineStr">
-        <is>
-          <t>Föllinge</t>
-        </is>
-      </c>
-      <c r="Y65" t="inlineStr">
-        <is>
-          <t>2026-07-14</t>
-        </is>
-      </c>
-      <c r="Z65" t="inlineStr">
-        <is>
-          <t>10:37</t>
-        </is>
-      </c>
-      <c r="AA65" t="inlineStr">
-        <is>
-          <t>2026-07-14</t>
-        </is>
-      </c>
-      <c r="AB65" t="inlineStr">
-        <is>
-          <t>10:37</t>
-        </is>
-      </c>
-      <c r="AC65" t="inlineStr">
-        <is>
-          <t>äldre ringhack</t>
-        </is>
-      </c>
-      <c r="AD65" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE65" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG65" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT65" t="inlineStr"/>
-      <c r="AW65" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX65" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY65" t="inlineStr"/>
-      <c r="AZ65" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135192056</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="n">
-        <v>135192074</v>
-      </c>
-      <c r="B66" t="n">
-        <v>57982</v>
-      </c>
-      <c r="D66" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E66" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F66" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G66" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H66" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr"/>
-      <c r="M66" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="P66" t="inlineStr">
-        <is>
-          <t>Höbrännflon, Jmt</t>
-        </is>
-      </c>
-      <c r="Q66" t="n">
-        <v>469051</v>
-      </c>
-      <c r="R66" t="n">
-        <v>7077912</v>
-      </c>
-      <c r="S66" t="n">
-        <v>10</v>
-      </c>
-      <c r="T66" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U66" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V66" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W66" t="inlineStr">
-        <is>
-          <t>Föllinge</t>
-        </is>
-      </c>
-      <c r="Y66" t="inlineStr">
-        <is>
-          <t>2026-07-14</t>
-        </is>
-      </c>
-      <c r="Z66" t="inlineStr">
-        <is>
-          <t>11:05</t>
-        </is>
-      </c>
-      <c r="AA66" t="inlineStr">
-        <is>
-          <t>2026-07-14</t>
-        </is>
-      </c>
-      <c r="AB66" t="inlineStr">
-        <is>
-          <t>11:05</t>
-        </is>
-      </c>
-      <c r="AC66" t="inlineStr">
-        <is>
-          <t>äldre ringhack</t>
-        </is>
-      </c>
-      <c r="AD66" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE66" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG66" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT66" t="inlineStr"/>
-      <c r="AW66" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX66" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY66" t="inlineStr"/>
-      <c r="AZ66" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135192074</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="n">
-        <v>135192077</v>
-      </c>
-      <c r="B67" t="n">
-        <v>57982</v>
-      </c>
-      <c r="D67" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E67" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F67" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G67" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H67" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr"/>
-      <c r="M67" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="P67" t="inlineStr">
-        <is>
-          <t>Höbrännflon, Jmt</t>
-        </is>
-      </c>
-      <c r="Q67" t="n">
-        <v>469002</v>
-      </c>
-      <c r="R67" t="n">
-        <v>7077895</v>
-      </c>
-      <c r="S67" t="n">
-        <v>10</v>
-      </c>
-      <c r="T67" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U67" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V67" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W67" t="inlineStr">
-        <is>
-          <t>Föllinge</t>
-        </is>
-      </c>
-      <c r="Y67" t="inlineStr">
-        <is>
-          <t>2026-07-14</t>
-        </is>
-      </c>
-      <c r="Z67" t="inlineStr">
-        <is>
-          <t>11:09</t>
-        </is>
-      </c>
-      <c r="AA67" t="inlineStr">
-        <is>
-          <t>2026-07-14</t>
-        </is>
-      </c>
-      <c r="AB67" t="inlineStr">
-        <is>
-          <t>11:09</t>
-        </is>
-      </c>
-      <c r="AC67" t="inlineStr">
-        <is>
-          <t>äldre ringhack</t>
-        </is>
-      </c>
-      <c r="AD67" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE67" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG67" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT67" t="inlineStr"/>
-      <c r="AW67" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX67" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY67" t="inlineStr"/>
-      <c r="AZ67" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135192077</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="n">
-        <v>135192079</v>
-      </c>
-      <c r="B68" t="n">
-        <v>57982</v>
-      </c>
-      <c r="D68" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E68" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F68" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G68" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H68" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr"/>
-      <c r="M68" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="P68" t="inlineStr">
-        <is>
-          <t>Höbrännflon, Jmt</t>
-        </is>
-      </c>
-      <c r="Q68" t="n">
-        <v>469028</v>
-      </c>
-      <c r="R68" t="n">
-        <v>7077856</v>
-      </c>
-      <c r="S68" t="n">
-        <v>10</v>
-      </c>
-      <c r="T68" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U68" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V68" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W68" t="inlineStr">
-        <is>
-          <t>Föllinge</t>
-        </is>
-      </c>
-      <c r="Y68" t="inlineStr">
-        <is>
-          <t>2026-07-14</t>
-        </is>
-      </c>
-      <c r="Z68" t="inlineStr">
-        <is>
-          <t>11:12</t>
-        </is>
-      </c>
-      <c r="AA68" t="inlineStr">
-        <is>
-          <t>2026-07-14</t>
-        </is>
-      </c>
-      <c r="AB68" t="inlineStr">
-        <is>
-          <t>11:12</t>
-        </is>
-      </c>
-      <c r="AC68" t="inlineStr">
-        <is>
-          <t>äldre ringhack</t>
-        </is>
-      </c>
-      <c r="AD68" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE68" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG68" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT68" t="inlineStr"/>
-      <c r="AW68" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX68" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY68" t="inlineStr"/>
-      <c r="AZ68" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135192079</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="n">
-        <v>135192085</v>
-      </c>
-      <c r="B69" t="n">
-        <v>57982</v>
-      </c>
-      <c r="D69" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E69" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F69" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G69" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H69" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr"/>
-      <c r="M69" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="P69" t="inlineStr">
-        <is>
-          <t>Höbrännflon, Jmt</t>
-        </is>
-      </c>
-      <c r="Q69" t="n">
-        <v>468941</v>
-      </c>
-      <c r="R69" t="n">
-        <v>7077921</v>
-      </c>
-      <c r="S69" t="n">
-        <v>10</v>
-      </c>
-      <c r="T69" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U69" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V69" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W69" t="inlineStr">
-        <is>
-          <t>Föllinge</t>
-        </is>
-      </c>
-      <c r="Y69" t="inlineStr">
-        <is>
-          <t>2026-07-14</t>
-        </is>
-      </c>
-      <c r="Z69" t="inlineStr">
-        <is>
-          <t>11:18</t>
-        </is>
-      </c>
-      <c r="AA69" t="inlineStr">
-        <is>
-          <t>2026-07-14</t>
-        </is>
-      </c>
-      <c r="AB69" t="inlineStr">
-        <is>
-          <t>11:18</t>
-        </is>
-      </c>
-      <c r="AC69" t="inlineStr">
-        <is>
-          <t>äldre ringhack</t>
-        </is>
-      </c>
-      <c r="AD69" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE69" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG69" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT69" t="inlineStr"/>
-      <c r="AW69" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX69" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY69" t="inlineStr"/>
-      <c r="AZ69" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135192085</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="n">
-        <v>135192088</v>
-      </c>
-      <c r="B70" t="n">
-        <v>57982</v>
-      </c>
-      <c r="D70" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E70" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F70" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G70" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H70" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr"/>
-      <c r="M70" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="P70" t="inlineStr">
-        <is>
-          <t>Höbrännflon, Jmt</t>
-        </is>
-      </c>
-      <c r="Q70" t="n">
-        <v>468900</v>
-      </c>
-      <c r="R70" t="n">
-        <v>7077908</v>
-      </c>
-      <c r="S70" t="n">
-        <v>10</v>
-      </c>
-      <c r="T70" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U70" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V70" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W70" t="inlineStr">
-        <is>
-          <t>Föllinge</t>
-        </is>
-      </c>
-      <c r="Y70" t="inlineStr">
-        <is>
-          <t>2026-07-14</t>
-        </is>
-      </c>
-      <c r="Z70" t="inlineStr">
-        <is>
-          <t>11:20</t>
-        </is>
-      </c>
-      <c r="AA70" t="inlineStr">
-        <is>
-          <t>2026-07-14</t>
-        </is>
-      </c>
-      <c r="AB70" t="inlineStr">
-        <is>
-          <t>11:20</t>
-        </is>
-      </c>
-      <c r="AC70" t="inlineStr">
-        <is>
-          <t>färska och äldre ringhack</t>
-        </is>
-      </c>
-      <c r="AD70" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE70" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG70" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT70" t="inlineStr"/>
-      <c r="AW70" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX70" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY70" t="inlineStr"/>
-      <c r="AZ70" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135192088</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="n">
-        <v>135192093</v>
-      </c>
-      <c r="B71" t="n">
-        <v>57982</v>
-      </c>
-      <c r="D71" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E71" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F71" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G71" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H71" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I71" t="inlineStr"/>
-      <c r="M71" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="P71" t="inlineStr">
-        <is>
-          <t>Höbrännflon, Jmt</t>
-        </is>
-      </c>
-      <c r="Q71" t="n">
-        <v>468841</v>
-      </c>
-      <c r="R71" t="n">
-        <v>7077895</v>
-      </c>
-      <c r="S71" t="n">
-        <v>10</v>
-      </c>
-      <c r="T71" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U71" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V71" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W71" t="inlineStr">
-        <is>
-          <t>Föllinge</t>
-        </is>
-      </c>
-      <c r="Y71" t="inlineStr">
-        <is>
-          <t>2026-07-14</t>
-        </is>
-      </c>
-      <c r="Z71" t="inlineStr">
-        <is>
-          <t>11:28</t>
-        </is>
-      </c>
-      <c r="AA71" t="inlineStr">
-        <is>
-          <t>2026-07-14</t>
-        </is>
-      </c>
-      <c r="AB71" t="inlineStr">
-        <is>
-          <t>11:28</t>
-        </is>
-      </c>
-      <c r="AC71" t="inlineStr">
-        <is>
-          <t>äldre ringhack</t>
-        </is>
-      </c>
-      <c r="AD71" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE71" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG71" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT71" t="inlineStr"/>
-      <c r="AW71" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX71" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY71" t="inlineStr"/>
-      <c r="AZ71" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135192093</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="n">
-        <v>135192095</v>
-      </c>
-      <c r="B72" t="n">
-        <v>57982</v>
-      </c>
-      <c r="D72" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E72" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F72" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G72" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H72" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I72" t="inlineStr"/>
-      <c r="M72" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="P72" t="inlineStr">
-        <is>
-          <t>Höbrännflon, Jmt</t>
-        </is>
-      </c>
-      <c r="Q72" t="n">
-        <v>468832</v>
-      </c>
-      <c r="R72" t="n">
-        <v>7077861</v>
-      </c>
-      <c r="S72" t="n">
-        <v>10</v>
-      </c>
-      <c r="T72" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U72" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V72" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W72" t="inlineStr">
-        <is>
-          <t>Föllinge</t>
-        </is>
-      </c>
-      <c r="Y72" t="inlineStr">
-        <is>
-          <t>2026-07-14</t>
-        </is>
-      </c>
-      <c r="Z72" t="inlineStr">
-        <is>
-          <t>11:32</t>
-        </is>
-      </c>
-      <c r="AA72" t="inlineStr">
-        <is>
-          <t>2026-07-14</t>
-        </is>
-      </c>
-      <c r="AB72" t="inlineStr">
-        <is>
-          <t>11:32</t>
-        </is>
-      </c>
-      <c r="AC72" t="inlineStr">
-        <is>
-          <t>äldre ringhack</t>
-        </is>
-      </c>
-      <c r="AD72" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE72" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG72" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT72" t="inlineStr"/>
-      <c r="AW72" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX72" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY72" t="inlineStr"/>
-      <c r="AZ72" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135192095</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="n">
-        <v>135192112</v>
-      </c>
-      <c r="B73" t="n">
-        <v>57982</v>
-      </c>
-      <c r="D73" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E73" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F73" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G73" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H73" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I73" t="inlineStr"/>
-      <c r="M73" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="P73" t="inlineStr">
-        <is>
-          <t>Höbrännflon, Jmt</t>
-        </is>
-      </c>
-      <c r="Q73" t="n">
-        <v>469029</v>
-      </c>
-      <c r="R73" t="n">
-        <v>7077764</v>
-      </c>
-      <c r="S73" t="n">
-        <v>10</v>
-      </c>
-      <c r="T73" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U73" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V73" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W73" t="inlineStr">
-        <is>
-          <t>Föllinge</t>
-        </is>
-      </c>
-      <c r="Y73" t="inlineStr">
-        <is>
-          <t>2026-07-14</t>
-        </is>
-      </c>
-      <c r="Z73" t="inlineStr">
-        <is>
-          <t>11:55</t>
-        </is>
-      </c>
-      <c r="AA73" t="inlineStr">
-        <is>
-          <t>2026-07-14</t>
-        </is>
-      </c>
-      <c r="AB73" t="inlineStr">
-        <is>
-          <t>11:55</t>
-        </is>
-      </c>
-      <c r="AC73" t="inlineStr">
-        <is>
-          <t>äldre ringhack</t>
-        </is>
-      </c>
-      <c r="AD73" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE73" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG73" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT73" t="inlineStr"/>
-      <c r="AW73" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX73" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY73" t="inlineStr"/>
-      <c r="AZ73" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135192112</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="n">
-        <v>135192116</v>
-      </c>
-      <c r="B74" t="n">
-        <v>57982</v>
-      </c>
-      <c r="D74" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E74" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F74" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G74" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H74" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I74" t="inlineStr"/>
-      <c r="M74" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="P74" t="inlineStr">
-        <is>
-          <t>Höbrännflon, Jmt</t>
-        </is>
-      </c>
-      <c r="Q74" t="n">
-        <v>469092</v>
-      </c>
-      <c r="R74" t="n">
-        <v>7077868</v>
-      </c>
-      <c r="S74" t="n">
-        <v>10</v>
-      </c>
-      <c r="T74" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U74" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V74" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W74" t="inlineStr">
-        <is>
-          <t>Föllinge</t>
-        </is>
-      </c>
-      <c r="Y74" t="inlineStr">
-        <is>
-          <t>2026-07-14</t>
-        </is>
-      </c>
-      <c r="Z74" t="inlineStr">
-        <is>
-          <t>12:02</t>
-        </is>
-      </c>
-      <c r="AA74" t="inlineStr">
-        <is>
-          <t>2026-07-14</t>
-        </is>
-      </c>
-      <c r="AB74" t="inlineStr">
-        <is>
-          <t>12:02</t>
-        </is>
-      </c>
-      <c r="AC74" t="inlineStr">
-        <is>
-          <t>äldre ringhack</t>
-        </is>
-      </c>
-      <c r="AD74" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE74" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG74" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT74" t="inlineStr"/>
-      <c r="AW74" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX74" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY74" t="inlineStr"/>
-      <c r="AZ74" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135192116</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="n">
-        <v>135192118</v>
-      </c>
-      <c r="B75" t="n">
-        <v>57982</v>
-      </c>
-      <c r="D75" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E75" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F75" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G75" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H75" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I75" t="inlineStr"/>
-      <c r="M75" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="P75" t="inlineStr">
-        <is>
-          <t>Höbrännflon, Jmt</t>
-        </is>
-      </c>
-      <c r="Q75" t="n">
-        <v>469121</v>
-      </c>
-      <c r="R75" t="n">
-        <v>7077852</v>
-      </c>
-      <c r="S75" t="n">
-        <v>10</v>
-      </c>
-      <c r="T75" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U75" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V75" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W75" t="inlineStr">
-        <is>
-          <t>Föllinge</t>
-        </is>
-      </c>
-      <c r="Y75" t="inlineStr">
-        <is>
-          <t>2026-07-14</t>
-        </is>
-      </c>
-      <c r="Z75" t="inlineStr">
-        <is>
-          <t>12:04</t>
-        </is>
-      </c>
-      <c r="AA75" t="inlineStr">
-        <is>
-          <t>2026-07-14</t>
-        </is>
-      </c>
-      <c r="AB75" t="inlineStr">
-        <is>
-          <t>12:04</t>
-        </is>
-      </c>
-      <c r="AC75" t="inlineStr">
-        <is>
-          <t>äldre ringhack</t>
-        </is>
-      </c>
-      <c r="AD75" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE75" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG75" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT75" t="inlineStr"/>
-      <c r="AW75" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX75" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY75" t="inlineStr"/>
-      <c r="AZ75" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135192118</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="n">
-        <v>135192119</v>
-      </c>
-      <c r="B76" t="n">
-        <v>57982</v>
-      </c>
-      <c r="D76" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E76" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F76" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G76" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H76" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I76" t="inlineStr"/>
-      <c r="M76" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="P76" t="inlineStr">
-        <is>
-          <t>Höbrännflon, Jmt</t>
-        </is>
-      </c>
-      <c r="Q76" t="n">
-        <v>469139</v>
-      </c>
-      <c r="R76" t="n">
-        <v>7077825</v>
-      </c>
-      <c r="S76" t="n">
-        <v>10</v>
-      </c>
-      <c r="T76" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U76" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V76" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W76" t="inlineStr">
-        <is>
-          <t>Föllinge</t>
-        </is>
-      </c>
-      <c r="Y76" t="inlineStr">
-        <is>
-          <t>2026-07-14</t>
-        </is>
-      </c>
-      <c r="Z76" t="inlineStr">
-        <is>
-          <t>12:07</t>
-        </is>
-      </c>
-      <c r="AA76" t="inlineStr">
-        <is>
-          <t>2026-07-14</t>
-        </is>
-      </c>
-      <c r="AB76" t="inlineStr">
-        <is>
-          <t>12:07</t>
-        </is>
-      </c>
-      <c r="AC76" t="inlineStr">
-        <is>
-          <t>äldre ringhack</t>
-        </is>
-      </c>
-      <c r="AD76" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE76" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG76" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT76" t="inlineStr"/>
-      <c r="AW76" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX76" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY76" t="inlineStr"/>
-      <c r="AZ76" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135192119</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="n">
-        <v>135192123</v>
-      </c>
-      <c r="B77" t="n">
-        <v>57982</v>
-      </c>
-      <c r="D77" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E77" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F77" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G77" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H77" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I77" t="inlineStr"/>
-      <c r="M77" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="P77" t="inlineStr">
-        <is>
-          <t>Höbrännflon, Jmt</t>
-        </is>
-      </c>
-      <c r="Q77" t="n">
-        <v>469108</v>
-      </c>
-      <c r="R77" t="n">
-        <v>7077950</v>
-      </c>
-      <c r="S77" t="n">
-        <v>10</v>
-      </c>
-      <c r="T77" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U77" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V77" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W77" t="inlineStr">
-        <is>
-          <t>Föllinge</t>
-        </is>
-      </c>
-      <c r="Y77" t="inlineStr">
-        <is>
-          <t>2026-07-14</t>
-        </is>
-      </c>
-      <c r="Z77" t="inlineStr">
-        <is>
-          <t>12:11</t>
-        </is>
-      </c>
-      <c r="AA77" t="inlineStr">
-        <is>
-          <t>2026-07-14</t>
-        </is>
-      </c>
-      <c r="AB77" t="inlineStr">
-        <is>
-          <t>12:11</t>
-        </is>
-      </c>
-      <c r="AC77" t="inlineStr">
-        <is>
-          <t>färska ringhack</t>
-        </is>
-      </c>
-      <c r="AD77" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE77" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG77" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT77" t="inlineStr"/>
-      <c r="AW77" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX77" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY77" t="inlineStr"/>
-      <c r="AZ77" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135192123</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="n">
-        <v>135192124</v>
-      </c>
-      <c r="B78" t="n">
-        <v>57982</v>
-      </c>
-      <c r="D78" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E78" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F78" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G78" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H78" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I78" t="inlineStr"/>
-      <c r="M78" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="P78" t="inlineStr">
-        <is>
-          <t>Höbrännflon, Jmt</t>
-        </is>
-      </c>
-      <c r="Q78" t="n">
-        <v>469109</v>
-      </c>
-      <c r="R78" t="n">
-        <v>7077945</v>
-      </c>
-      <c r="S78" t="n">
-        <v>10</v>
-      </c>
-      <c r="T78" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U78" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V78" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W78" t="inlineStr">
-        <is>
-          <t>Föllinge</t>
-        </is>
-      </c>
-      <c r="Y78" t="inlineStr">
-        <is>
-          <t>2026-07-14</t>
-        </is>
-      </c>
-      <c r="Z78" t="inlineStr">
-        <is>
-          <t>12:12</t>
-        </is>
-      </c>
-      <c r="AA78" t="inlineStr">
-        <is>
-          <t>2026-07-14</t>
-        </is>
-      </c>
-      <c r="AB78" t="inlineStr">
-        <is>
-          <t>12:12</t>
-        </is>
-      </c>
-      <c r="AC78" t="inlineStr">
-        <is>
-          <t>färska ringhack</t>
-        </is>
-      </c>
-      <c r="AD78" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE78" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG78" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT78" t="inlineStr"/>
-      <c r="AW78" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX78" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY78" t="inlineStr"/>
-      <c r="AZ78" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135192124</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="n">
-        <v>135192125</v>
-      </c>
-      <c r="B79" t="n">
-        <v>57982</v>
-      </c>
-      <c r="D79" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E79" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F79" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G79" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H79" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I79" t="inlineStr"/>
-      <c r="M79" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="P79" t="inlineStr">
-        <is>
-          <t>Höbrännflon, Jmt</t>
-        </is>
-      </c>
-      <c r="Q79" t="n">
-        <v>469118</v>
-      </c>
-      <c r="R79" t="n">
-        <v>7077938</v>
-      </c>
-      <c r="S79" t="n">
-        <v>10</v>
-      </c>
-      <c r="T79" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U79" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V79" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W79" t="inlineStr">
-        <is>
-          <t>Föllinge</t>
-        </is>
-      </c>
-      <c r="Y79" t="inlineStr">
-        <is>
-          <t>2026-07-14</t>
-        </is>
-      </c>
-      <c r="Z79" t="inlineStr">
-        <is>
-          <t>12:12</t>
-        </is>
-      </c>
-      <c r="AA79" t="inlineStr">
-        <is>
-          <t>2026-07-14</t>
-        </is>
-      </c>
-      <c r="AB79" t="inlineStr">
-        <is>
-          <t>12:12</t>
-        </is>
-      </c>
-      <c r="AC79" t="inlineStr">
-        <is>
-          <t>färska ringhack</t>
-        </is>
-      </c>
-      <c r="AD79" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE79" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG79" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT79" t="inlineStr"/>
-      <c r="AW79" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX79" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY79" t="inlineStr"/>
-      <c r="AZ79" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135192125</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="n">
-        <v>135192127</v>
-      </c>
-      <c r="B80" t="n">
-        <v>57982</v>
-      </c>
-      <c r="D80" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E80" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F80" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G80" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H80" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I80" t="inlineStr"/>
-      <c r="M80" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="P80" t="inlineStr">
-        <is>
-          <t>Höbrännflon, Jmt</t>
-        </is>
-      </c>
-      <c r="Q80" t="n">
-        <v>469140</v>
-      </c>
-      <c r="R80" t="n">
-        <v>7077913</v>
-      </c>
-      <c r="S80" t="n">
-        <v>10</v>
-      </c>
-      <c r="T80" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U80" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V80" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W80" t="inlineStr">
-        <is>
-          <t>Föllinge</t>
-        </is>
-      </c>
-      <c r="Y80" t="inlineStr">
-        <is>
-          <t>2026-07-14</t>
-        </is>
-      </c>
-      <c r="Z80" t="inlineStr">
-        <is>
-          <t>12:13</t>
-        </is>
-      </c>
-      <c r="AA80" t="inlineStr">
-        <is>
-          <t>2026-07-14</t>
-        </is>
-      </c>
-      <c r="AB80" t="inlineStr">
-        <is>
-          <t>12:13</t>
-        </is>
-      </c>
-      <c r="AC80" t="inlineStr">
-        <is>
-          <t>färska ringhack</t>
-        </is>
-      </c>
-      <c r="AD80" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE80" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG80" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT80" t="inlineStr"/>
-      <c r="AW80" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX80" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY80" t="inlineStr"/>
-      <c r="AZ80" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135192127</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="n">
-        <v>135192128</v>
-      </c>
-      <c r="B81" t="n">
-        <v>57982</v>
-      </c>
-      <c r="D81" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E81" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F81" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G81" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H81" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I81" t="inlineStr"/>
-      <c r="M81" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="P81" t="inlineStr">
-        <is>
-          <t>Höbrännflon, Jmt</t>
-        </is>
-      </c>
-      <c r="Q81" t="n">
-        <v>469149</v>
-      </c>
-      <c r="R81" t="n">
-        <v>7077895</v>
-      </c>
-      <c r="S81" t="n">
-        <v>10</v>
-      </c>
-      <c r="T81" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U81" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V81" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W81" t="inlineStr">
-        <is>
-          <t>Föllinge</t>
-        </is>
-      </c>
-      <c r="Y81" t="inlineStr">
-        <is>
-          <t>2026-07-14</t>
-        </is>
-      </c>
-      <c r="Z81" t="inlineStr">
-        <is>
-          <t>12:14</t>
-        </is>
-      </c>
-      <c r="AA81" t="inlineStr">
-        <is>
-          <t>2026-07-14</t>
-        </is>
-      </c>
-      <c r="AB81" t="inlineStr">
-        <is>
-          <t>12:14</t>
-        </is>
-      </c>
-      <c r="AC81" t="inlineStr">
-        <is>
-          <t>färska ringhack</t>
-        </is>
-      </c>
-      <c r="AD81" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE81" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG81" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT81" t="inlineStr"/>
-      <c r="AW81" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX81" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY81" t="inlineStr"/>
-      <c r="AZ81" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135192128</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="n">
-        <v>135192130</v>
-      </c>
-      <c r="B82" t="n">
-        <v>57982</v>
-      </c>
-      <c r="D82" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E82" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F82" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G82" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H82" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I82" t="inlineStr"/>
-      <c r="M82" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="P82" t="inlineStr">
-        <is>
-          <t>Höbrännflon, Jmt</t>
-        </is>
-      </c>
-      <c r="Q82" t="n">
-        <v>469158</v>
-      </c>
-      <c r="R82" t="n">
-        <v>7077852</v>
-      </c>
-      <c r="S82" t="n">
-        <v>10</v>
-      </c>
-      <c r="T82" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U82" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V82" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W82" t="inlineStr">
-        <is>
-          <t>Föllinge</t>
-        </is>
-      </c>
-      <c r="Y82" t="inlineStr">
-        <is>
-          <t>2026-07-14</t>
-        </is>
-      </c>
-      <c r="Z82" t="inlineStr">
-        <is>
-          <t>12:15</t>
-        </is>
-      </c>
-      <c r="AA82" t="inlineStr">
-        <is>
-          <t>2026-07-14</t>
-        </is>
-      </c>
-      <c r="AB82" t="inlineStr">
-        <is>
-          <t>12:15</t>
-        </is>
-      </c>
-      <c r="AC82" t="inlineStr">
-        <is>
-          <t>färska ringhack</t>
-        </is>
-      </c>
-      <c r="AD82" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE82" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG82" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT82" t="inlineStr"/>
-      <c r="AW82" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX82" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY82" t="inlineStr"/>
-      <c r="AZ82" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135192130</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="n">
-        <v>135192131</v>
-      </c>
-      <c r="B83" t="n">
-        <v>57982</v>
-      </c>
-      <c r="D83" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E83" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F83" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G83" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H83" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I83" t="inlineStr"/>
-      <c r="M83" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="P83" t="inlineStr">
-        <is>
-          <t>Höbrännflon, Jmt</t>
-        </is>
-      </c>
-      <c r="Q83" t="n">
-        <v>469166</v>
-      </c>
-      <c r="R83" t="n">
-        <v>7077841</v>
-      </c>
-      <c r="S83" t="n">
-        <v>10</v>
-      </c>
-      <c r="T83" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U83" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V83" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W83" t="inlineStr">
-        <is>
-          <t>Föllinge</t>
-        </is>
-      </c>
-      <c r="Y83" t="inlineStr">
-        <is>
-          <t>2026-07-14</t>
-        </is>
-      </c>
-      <c r="Z83" t="inlineStr">
-        <is>
-          <t>12:16</t>
-        </is>
-      </c>
-      <c r="AA83" t="inlineStr">
-        <is>
-          <t>2026-07-14</t>
-        </is>
-      </c>
-      <c r="AB83" t="inlineStr">
-        <is>
-          <t>12:16</t>
-        </is>
-      </c>
-      <c r="AC83" t="inlineStr">
-        <is>
-          <t>färska ringhack</t>
-        </is>
-      </c>
-      <c r="AD83" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE83" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG83" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT83" t="inlineStr"/>
-      <c r="AW83" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX83" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY83" t="inlineStr"/>
-      <c r="AZ83" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135192131</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="n">
-        <v>135192132</v>
-      </c>
-      <c r="B84" t="n">
-        <v>57982</v>
-      </c>
-      <c r="D84" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E84" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F84" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G84" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H84" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I84" t="inlineStr"/>
-      <c r="M84" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="P84" t="inlineStr">
-        <is>
-          <t>Höbrännflon, Jmt</t>
-        </is>
-      </c>
-      <c r="Q84" t="n">
-        <v>469163</v>
-      </c>
-      <c r="R84" t="n">
-        <v>7077822</v>
-      </c>
-      <c r="S84" t="n">
-        <v>10</v>
-      </c>
-      <c r="T84" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U84" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V84" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W84" t="inlineStr">
-        <is>
-          <t>Föllinge</t>
-        </is>
-      </c>
-      <c r="Y84" t="inlineStr">
-        <is>
-          <t>2026-07-14</t>
-        </is>
-      </c>
-      <c r="Z84" t="inlineStr">
-        <is>
-          <t>12:17</t>
-        </is>
-      </c>
-      <c r="AA84" t="inlineStr">
-        <is>
-          <t>2026-07-14</t>
-        </is>
-      </c>
-      <c r="AB84" t="inlineStr">
-        <is>
-          <t>12:17</t>
-        </is>
-      </c>
-      <c r="AC84" t="inlineStr">
-        <is>
-          <t>färska ringhack</t>
-        </is>
-      </c>
-      <c r="AD84" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE84" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG84" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT84" t="inlineStr"/>
-      <c r="AW84" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX84" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY84" t="inlineStr"/>
-      <c r="AZ84" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135192132</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="n">
-        <v>135192134</v>
-      </c>
-      <c r="B85" t="n">
-        <v>57982</v>
-      </c>
-      <c r="D85" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E85" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F85" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G85" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H85" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I85" t="inlineStr"/>
-      <c r="M85" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="P85" t="inlineStr">
-        <is>
-          <t>Höbrännflon, Jmt</t>
-        </is>
-      </c>
-      <c r="Q85" t="n">
-        <v>469172</v>
-      </c>
-      <c r="R85" t="n">
-        <v>7077811</v>
-      </c>
-      <c r="S85" t="n">
-        <v>10</v>
-      </c>
-      <c r="T85" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U85" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V85" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W85" t="inlineStr">
-        <is>
-          <t>Föllinge</t>
-        </is>
-      </c>
-      <c r="Y85" t="inlineStr">
-        <is>
-          <t>2026-07-14</t>
-        </is>
-      </c>
-      <c r="Z85" t="inlineStr">
-        <is>
-          <t>12:17</t>
-        </is>
-      </c>
-      <c r="AA85" t="inlineStr">
-        <is>
-          <t>2026-07-14</t>
-        </is>
-      </c>
-      <c r="AB85" t="inlineStr">
-        <is>
-          <t>12:17</t>
-        </is>
-      </c>
-      <c r="AC85" t="inlineStr">
-        <is>
-          <t>färska ringhack</t>
-        </is>
-      </c>
-      <c r="AD85" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE85" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG85" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT85" t="inlineStr"/>
-      <c r="AW85" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX85" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY85" t="inlineStr"/>
-      <c r="AZ85" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135192134</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="n">
-        <v>135192135</v>
-      </c>
-      <c r="B86" t="n">
-        <v>57982</v>
-      </c>
-      <c r="D86" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E86" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F86" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G86" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H86" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I86" t="inlineStr"/>
-      <c r="M86" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="P86" t="inlineStr">
-        <is>
-          <t>Höbrännflon, Jmt</t>
-        </is>
-      </c>
-      <c r="Q86" t="n">
-        <v>469180</v>
-      </c>
-      <c r="R86" t="n">
-        <v>7077818</v>
-      </c>
-      <c r="S86" t="n">
-        <v>10</v>
-      </c>
-      <c r="T86" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U86" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V86" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W86" t="inlineStr">
-        <is>
-          <t>Föllinge</t>
-        </is>
-      </c>
-      <c r="Y86" t="inlineStr">
-        <is>
-          <t>2026-07-14</t>
-        </is>
-      </c>
-      <c r="Z86" t="inlineStr">
-        <is>
-          <t>12:18</t>
-        </is>
-      </c>
-      <c r="AA86" t="inlineStr">
-        <is>
-          <t>2026-07-14</t>
-        </is>
-      </c>
-      <c r="AB86" t="inlineStr">
-        <is>
-          <t>12:18</t>
-        </is>
-      </c>
-      <c r="AC86" t="inlineStr">
-        <is>
-          <t>äldre ringhack</t>
-        </is>
-      </c>
-      <c r="AD86" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE86" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG86" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT86" t="inlineStr"/>
-      <c r="AW86" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX86" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY86" t="inlineStr"/>
-      <c r="AZ86" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135192135</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="n">
-        <v>135192136</v>
-      </c>
-      <c r="B87" t="n">
-        <v>57982</v>
-      </c>
-      <c r="D87" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E87" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F87" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G87" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H87" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I87" t="inlineStr"/>
-      <c r="M87" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="P87" t="inlineStr">
-        <is>
-          <t>Höbrännflon, Jmt</t>
-        </is>
-      </c>
-      <c r="Q87" t="n">
-        <v>469176</v>
-      </c>
-      <c r="R87" t="n">
-        <v>7077799</v>
-      </c>
-      <c r="S87" t="n">
-        <v>10</v>
-      </c>
-      <c r="T87" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U87" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V87" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W87" t="inlineStr">
-        <is>
-          <t>Föllinge</t>
-        </is>
-      </c>
-      <c r="Y87" t="inlineStr">
-        <is>
-          <t>2026-07-14</t>
-        </is>
-      </c>
-      <c r="Z87" t="inlineStr">
-        <is>
-          <t>12:19</t>
-        </is>
-      </c>
-      <c r="AA87" t="inlineStr">
-        <is>
-          <t>2026-07-14</t>
-        </is>
-      </c>
-      <c r="AB87" t="inlineStr">
-        <is>
-          <t>12:19</t>
-        </is>
-      </c>
-      <c r="AC87" t="inlineStr">
-        <is>
-          <t>färska ringhack</t>
-        </is>
-      </c>
-      <c r="AD87" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE87" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG87" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT87" t="inlineStr"/>
-      <c r="AW87" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX87" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY87" t="inlineStr"/>
-      <c r="AZ87" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135192136</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="n">
-        <v>135192137</v>
-      </c>
-      <c r="B88" t="n">
-        <v>57982</v>
-      </c>
-      <c r="D88" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E88" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F88" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G88" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H88" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I88" t="inlineStr"/>
-      <c r="M88" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="P88" t="inlineStr">
-        <is>
-          <t>Höbrännflon, Jmt</t>
-        </is>
-      </c>
-      <c r="Q88" t="n">
-        <v>469181</v>
-      </c>
-      <c r="R88" t="n">
-        <v>7077798</v>
-      </c>
-      <c r="S88" t="n">
-        <v>10</v>
-      </c>
-      <c r="T88" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U88" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V88" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W88" t="inlineStr">
-        <is>
-          <t>Föllinge</t>
-        </is>
-      </c>
-      <c r="Y88" t="inlineStr">
-        <is>
-          <t>2026-07-14</t>
-        </is>
-      </c>
-      <c r="Z88" t="inlineStr">
-        <is>
-          <t>12:20</t>
-        </is>
-      </c>
-      <c r="AA88" t="inlineStr">
-        <is>
-          <t>2026-07-14</t>
-        </is>
-      </c>
-      <c r="AB88" t="inlineStr">
-        <is>
-          <t>12:20</t>
-        </is>
-      </c>
-      <c r="AC88" t="inlineStr">
-        <is>
-          <t>färska ringhack</t>
-        </is>
-      </c>
-      <c r="AD88" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE88" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG88" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT88" t="inlineStr"/>
-      <c r="AW88" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX88" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY88" t="inlineStr"/>
-      <c r="AZ88" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135192137</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="n">
-        <v>135192151</v>
-      </c>
-      <c r="B89" t="n">
-        <v>57982</v>
-      </c>
-      <c r="D89" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E89" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F89" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G89" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H89" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I89" t="inlineStr"/>
-      <c r="M89" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="P89" t="inlineStr">
-        <is>
-          <t>Höbrännflon, Jmt</t>
-        </is>
-      </c>
-      <c r="Q89" t="n">
-        <v>469393</v>
-      </c>
-      <c r="R89" t="n">
-        <v>7077846</v>
-      </c>
-      <c r="S89" t="n">
-        <v>10</v>
-      </c>
-      <c r="T89" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U89" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V89" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W89" t="inlineStr">
-        <is>
-          <t>Föllinge</t>
-        </is>
-      </c>
-      <c r="Y89" t="inlineStr">
-        <is>
-          <t>2026-07-14</t>
-        </is>
-      </c>
-      <c r="Z89" t="inlineStr">
-        <is>
-          <t>12:42</t>
-        </is>
-      </c>
-      <c r="AA89" t="inlineStr">
-        <is>
-          <t>2026-07-14</t>
-        </is>
-      </c>
-      <c r="AB89" t="inlineStr">
-        <is>
-          <t>12:42</t>
-        </is>
-      </c>
-      <c r="AC89" t="inlineStr">
-        <is>
-          <t>äldre ringhack</t>
-        </is>
-      </c>
-      <c r="AD89" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE89" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG89" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT89" t="inlineStr"/>
-      <c r="AW89" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX89" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY89" t="inlineStr"/>
-      <c r="AZ89" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135192151</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="n">
-        <v>135192152</v>
-      </c>
-      <c r="B90" t="n">
-        <v>57982</v>
-      </c>
-      <c r="D90" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E90" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F90" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G90" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H90" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I90" t="inlineStr"/>
-      <c r="M90" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="P90" t="inlineStr">
-        <is>
-          <t>Höbrännflon, Jmt</t>
-        </is>
-      </c>
-      <c r="Q90" t="n">
-        <v>469356</v>
-      </c>
-      <c r="R90" t="n">
-        <v>7077867</v>
-      </c>
-      <c r="S90" t="n">
-        <v>10</v>
-      </c>
-      <c r="T90" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U90" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V90" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W90" t="inlineStr">
-        <is>
-          <t>Föllinge</t>
-        </is>
-      </c>
-      <c r="Y90" t="inlineStr">
-        <is>
-          <t>2026-07-14</t>
-        </is>
-      </c>
-      <c r="Z90" t="inlineStr">
-        <is>
-          <t>12:45</t>
-        </is>
-      </c>
-      <c r="AA90" t="inlineStr">
-        <is>
-          <t>2026-07-14</t>
-        </is>
-      </c>
-      <c r="AB90" t="inlineStr">
-        <is>
-          <t>12:45</t>
-        </is>
-      </c>
-      <c r="AC90" t="inlineStr">
-        <is>
-          <t>äldre ringhack</t>
-        </is>
-      </c>
-      <c r="AD90" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE90" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG90" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT90" t="inlineStr"/>
-      <c r="AW90" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX90" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY90" t="inlineStr"/>
-      <c r="AZ90" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135192152</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="n">
-        <v>135192153</v>
-      </c>
-      <c r="B91" t="n">
-        <v>57982</v>
-      </c>
-      <c r="D91" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E91" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F91" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G91" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H91" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I91" t="inlineStr"/>
-      <c r="M91" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="P91" t="inlineStr">
-        <is>
-          <t>Höbrännflon, Jmt</t>
-        </is>
-      </c>
-      <c r="Q91" t="n">
-        <v>469347</v>
-      </c>
-      <c r="R91" t="n">
-        <v>7077869</v>
-      </c>
-      <c r="S91" t="n">
-        <v>10</v>
-      </c>
-      <c r="T91" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U91" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V91" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W91" t="inlineStr">
-        <is>
-          <t>Föllinge</t>
-        </is>
-      </c>
-      <c r="Y91" t="inlineStr">
-        <is>
-          <t>2026-07-14</t>
-        </is>
-      </c>
-      <c r="Z91" t="inlineStr">
-        <is>
-          <t>12:46</t>
-        </is>
-      </c>
-      <c r="AA91" t="inlineStr">
-        <is>
-          <t>2026-07-14</t>
-        </is>
-      </c>
-      <c r="AB91" t="inlineStr">
-        <is>
-          <t>12:46</t>
-        </is>
-      </c>
-      <c r="AC91" t="inlineStr">
-        <is>
-          <t>äldre ringhack</t>
-        </is>
-      </c>
-      <c r="AD91" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE91" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG91" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT91" t="inlineStr"/>
-      <c r="AW91" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX91" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY91" t="inlineStr"/>
-      <c r="AZ91" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135192153</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="n">
-        <v>135192157</v>
-      </c>
-      <c r="B92" t="n">
-        <v>57982</v>
-      </c>
-      <c r="D92" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E92" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F92" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G92" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H92" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I92" t="inlineStr"/>
-      <c r="M92" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="P92" t="inlineStr">
-        <is>
-          <t>Höbrännflon, Jmt</t>
-        </is>
-      </c>
-      <c r="Q92" t="n">
-        <v>469381</v>
-      </c>
-      <c r="R92" t="n">
-        <v>7077873</v>
-      </c>
-      <c r="S92" t="n">
-        <v>10</v>
-      </c>
-      <c r="T92" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U92" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V92" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W92" t="inlineStr">
-        <is>
-          <t>Föllinge</t>
-        </is>
-      </c>
-      <c r="Y92" t="inlineStr">
-        <is>
-          <t>2026-07-14</t>
-        </is>
-      </c>
-      <c r="Z92" t="inlineStr">
-        <is>
-          <t>12:52</t>
-        </is>
-      </c>
-      <c r="AA92" t="inlineStr">
-        <is>
-          <t>2026-07-14</t>
-        </is>
-      </c>
-      <c r="AB92" t="inlineStr">
-        <is>
-          <t>12:52</t>
-        </is>
-      </c>
-      <c r="AC92" t="inlineStr">
-        <is>
-          <t>äldre ringhack</t>
-        </is>
-      </c>
-      <c r="AD92" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE92" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG92" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT92" t="inlineStr"/>
-      <c r="AW92" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX92" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY92" t="inlineStr"/>
-      <c r="AZ92" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135192157</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="n">
-        <v>135192158</v>
-      </c>
-      <c r="B93" t="n">
-        <v>57982</v>
-      </c>
-      <c r="D93" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E93" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F93" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G93" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H93" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I93" t="inlineStr"/>
-      <c r="M93" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="P93" t="inlineStr">
-        <is>
-          <t>Höbrännflon, Jmt</t>
-        </is>
-      </c>
-      <c r="Q93" t="n">
-        <v>469401</v>
-      </c>
-      <c r="R93" t="n">
-        <v>7077887</v>
-      </c>
-      <c r="S93" t="n">
-        <v>10</v>
-      </c>
-      <c r="T93" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U93" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V93" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W93" t="inlineStr">
-        <is>
-          <t>Föllinge</t>
-        </is>
-      </c>
-      <c r="Y93" t="inlineStr">
-        <is>
-          <t>2026-07-14</t>
-        </is>
-      </c>
-      <c r="Z93" t="inlineStr">
-        <is>
-          <t>12:54</t>
-        </is>
-      </c>
-      <c r="AA93" t="inlineStr">
-        <is>
-          <t>2026-07-14</t>
-        </is>
-      </c>
-      <c r="AB93" t="inlineStr">
-        <is>
-          <t>12:54</t>
-        </is>
-      </c>
-      <c r="AC93" t="inlineStr">
-        <is>
-          <t>äldre ringhack</t>
-        </is>
-      </c>
-      <c r="AD93" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE93" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG93" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT93" t="inlineStr"/>
-      <c r="AW93" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX93" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY93" t="inlineStr"/>
-      <c r="AZ93" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135192158</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="n">
-        <v>135192161</v>
-      </c>
-      <c r="B94" t="n">
-        <v>57982</v>
-      </c>
-      <c r="D94" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E94" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F94" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G94" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H94" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I94" t="inlineStr"/>
-      <c r="M94" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="P94" t="inlineStr">
-        <is>
-          <t>Höbrännflon, Jmt</t>
-        </is>
-      </c>
-      <c r="Q94" t="n">
-        <v>469388</v>
-      </c>
-      <c r="R94" t="n">
-        <v>7077920</v>
-      </c>
-      <c r="S94" t="n">
-        <v>10</v>
-      </c>
-      <c r="T94" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U94" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V94" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W94" t="inlineStr">
-        <is>
-          <t>Föllinge</t>
-        </is>
-      </c>
-      <c r="Y94" t="inlineStr">
-        <is>
-          <t>2026-07-14</t>
-        </is>
-      </c>
-      <c r="Z94" t="inlineStr">
-        <is>
-          <t>12:56</t>
-        </is>
-      </c>
-      <c r="AA94" t="inlineStr">
-        <is>
-          <t>2026-07-14</t>
-        </is>
-      </c>
-      <c r="AB94" t="inlineStr">
-        <is>
-          <t>12:56</t>
-        </is>
-      </c>
-      <c r="AC94" t="inlineStr">
-        <is>
-          <t>äldre ringhack</t>
-        </is>
-      </c>
-      <c r="AD94" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE94" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG94" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT94" t="inlineStr"/>
-      <c r="AW94" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX94" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY94" t="inlineStr"/>
-      <c r="AZ94" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135192161</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="n">
-        <v>135192166</v>
-      </c>
-      <c r="B95" t="n">
-        <v>57982</v>
-      </c>
-      <c r="D95" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E95" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F95" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G95" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H95" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I95" t="inlineStr"/>
-      <c r="P95" t="inlineStr">
-        <is>
-          <t>Höbrännflon, Jmt</t>
-        </is>
-      </c>
-      <c r="Q95" t="n">
-        <v>469249</v>
-      </c>
-      <c r="R95" t="n">
-        <v>7077922</v>
-      </c>
-      <c r="S95" t="n">
-        <v>10</v>
-      </c>
-      <c r="T95" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U95" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V95" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W95" t="inlineStr">
-        <is>
-          <t>Föllinge</t>
-        </is>
-      </c>
-      <c r="Y95" t="inlineStr">
-        <is>
-          <t>2026-07-14</t>
-        </is>
-      </c>
-      <c r="Z95" t="inlineStr">
-        <is>
-          <t>13:07</t>
-        </is>
-      </c>
-      <c r="AA95" t="inlineStr">
-        <is>
-          <t>2026-07-14</t>
-        </is>
-      </c>
-      <c r="AB95" t="inlineStr">
-        <is>
-          <t>13:07</t>
-        </is>
-      </c>
-      <c r="AC95" t="inlineStr">
-        <is>
-          <t>ringhack</t>
-        </is>
-      </c>
-      <c r="AD95" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE95" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG95" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT95" t="inlineStr"/>
-      <c r="AW95" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX95" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY95" t="inlineStr"/>
-      <c r="AZ95" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135192166</t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="n">
-        <v>128346628</v>
-      </c>
-      <c r="B96" t="n">
-        <v>97989</v>
-      </c>
-      <c r="D96" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E96" t="n">
-        <v>221941</v>
-      </c>
-      <c r="F96" t="inlineStr">
-        <is>
-          <t>Plattlummer</t>
-        </is>
-      </c>
-      <c r="G96" t="inlineStr">
-        <is>
-          <t>Lycopodium complanatum</t>
-        </is>
-      </c>
-      <c r="H96" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I96" t="inlineStr"/>
-      <c r="P96" t="inlineStr">
-        <is>
-          <t>Höbrännflon sö, Jmt</t>
-        </is>
-      </c>
-      <c r="Q96" t="n">
-        <v>468931</v>
-      </c>
-      <c r="R96" t="n">
-        <v>7077743</v>
-      </c>
-      <c r="S96" t="n">
-        <v>10</v>
-      </c>
-      <c r="T96" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U96" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V96" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W96" t="inlineStr">
-        <is>
-          <t>Föllinge</t>
-        </is>
-      </c>
-      <c r="Y96" t="inlineStr">
-        <is>
-          <t>2025-09-09</t>
-        </is>
-      </c>
-      <c r="AA96" t="inlineStr">
-        <is>
-          <t>2025-09-09</t>
-        </is>
-      </c>
-      <c r="AD96" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE96" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG96" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT96" t="inlineStr"/>
-      <c r="AW96" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX96" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY96" t="inlineStr"/>
-      <c r="AZ96" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/128346628</t>
         </is>
@@ -11663,44 +7037,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ87" r:id="rId86"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ88" r:id="rId87"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ89" r:id="rId88"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ90" r:id="rId89"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ91" r:id="rId90"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ92" r:id="rId91"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ93" r:id="rId92"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ94" r:id="rId93"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ95" r:id="rId94"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ96" r:id="rId95"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 28940-2026 artfynd.xlsx
+++ b/artfynd/A 28940-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ58"/>
+  <dimension ref="A1:AZ96"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6878,45 +6878,50 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128346628</v>
+        <v>135192022</v>
       </c>
       <c r="B58" t="n">
-        <v>97989</v>
+        <v>57982</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>221941</v>
+        <v>100109</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Höbrännflon sö, Jmt</t>
+          <t>Höbrännflon, Jmt</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>468931</v>
+        <v>469168</v>
       </c>
       <c r="R58" t="n">
-        <v>7077743</v>
+        <v>7078178</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6943,12 +6948,27 @@
       </c>
       <c r="Y58" t="inlineStr">
         <is>
-          <t>2025-09-09</t>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="Z58" t="inlineStr">
+        <is>
+          <t>09:29</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>2025-09-09</t>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="AB58" t="inlineStr">
+        <is>
+          <t>09:29</t>
+        </is>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>äldre ringhack</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6973,6 +6993,4612 @@
       </c>
       <c r="AY58" t="inlineStr"/>
       <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135192022</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>135192026</v>
+      </c>
+      <c r="B59" t="n">
+        <v>57982</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>Höbrännflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q59" t="n">
+        <v>469186</v>
+      </c>
+      <c r="R59" t="n">
+        <v>7078140</v>
+      </c>
+      <c r="S59" t="n">
+        <v>10</v>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="Z59" t="inlineStr">
+        <is>
+          <t>09:38</t>
+        </is>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="AB59" t="inlineStr">
+        <is>
+          <t>09:38</t>
+        </is>
+      </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>äldre ringhack</t>
+        </is>
+      </c>
+      <c r="AD59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT59" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX59" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135192026</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>135192030</v>
+      </c>
+      <c r="B60" t="n">
+        <v>57982</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>Höbrännflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q60" t="n">
+        <v>469177</v>
+      </c>
+      <c r="R60" t="n">
+        <v>7078094</v>
+      </c>
+      <c r="S60" t="n">
+        <v>10</v>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="Z60" t="inlineStr">
+        <is>
+          <t>09:48</t>
+        </is>
+      </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="AB60" t="inlineStr">
+        <is>
+          <t>09:48</t>
+        </is>
+      </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>äldre ringhack</t>
+        </is>
+      </c>
+      <c r="AD60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT60" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX60" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135192030</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>135192045</v>
+      </c>
+      <c r="B61" t="n">
+        <v>57982</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>Höbrännflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q61" t="n">
+        <v>468993</v>
+      </c>
+      <c r="R61" t="n">
+        <v>7078287</v>
+      </c>
+      <c r="S61" t="n">
+        <v>10</v>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y61" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="Z61" t="inlineStr">
+        <is>
+          <t>10:18</t>
+        </is>
+      </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="AB61" t="inlineStr">
+        <is>
+          <t>10:18</t>
+        </is>
+      </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>ringhack</t>
+        </is>
+      </c>
+      <c r="AD61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT61" t="inlineStr"/>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX61" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135192045</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>135192047</v>
+      </c>
+      <c r="B62" t="n">
+        <v>57982</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>Höbrännflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q62" t="n">
+        <v>468901</v>
+      </c>
+      <c r="R62" t="n">
+        <v>7078371</v>
+      </c>
+      <c r="S62" t="n">
+        <v>10</v>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="Z62" t="inlineStr">
+        <is>
+          <t>10:25</t>
+        </is>
+      </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="AB62" t="inlineStr">
+        <is>
+          <t>10:25</t>
+        </is>
+      </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>äldre ringhack</t>
+        </is>
+      </c>
+      <c r="AD62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT62" t="inlineStr"/>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX62" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135192047</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>135192048</v>
+      </c>
+      <c r="B63" t="n">
+        <v>57982</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>Höbrännflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q63" t="n">
+        <v>468891</v>
+      </c>
+      <c r="R63" t="n">
+        <v>7078390</v>
+      </c>
+      <c r="S63" t="n">
+        <v>10</v>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="Z63" t="inlineStr">
+        <is>
+          <t>10:28</t>
+        </is>
+      </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="AB63" t="inlineStr">
+        <is>
+          <t>10:28</t>
+        </is>
+      </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>färska o och äldre ringhack</t>
+        </is>
+      </c>
+      <c r="AD63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT63" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX63" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135192048</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>135192050</v>
+      </c>
+      <c r="B64" t="n">
+        <v>57982</v>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>Höbrännflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q64" t="n">
+        <v>468864</v>
+      </c>
+      <c r="R64" t="n">
+        <v>7078369</v>
+      </c>
+      <c r="S64" t="n">
+        <v>10</v>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="Z64" t="inlineStr">
+        <is>
+          <t>10:31</t>
+        </is>
+      </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="AB64" t="inlineStr">
+        <is>
+          <t>10:31</t>
+        </is>
+      </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>färska och äldre ringhack</t>
+        </is>
+      </c>
+      <c r="AD64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT64" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX64" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135192050</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>135192056</v>
+      </c>
+      <c r="B65" t="n">
+        <v>57982</v>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>Höbrännflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q65" t="n">
+        <v>468923</v>
+      </c>
+      <c r="R65" t="n">
+        <v>7078311</v>
+      </c>
+      <c r="S65" t="n">
+        <v>10</v>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y65" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="Z65" t="inlineStr">
+        <is>
+          <t>10:37</t>
+        </is>
+      </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="AB65" t="inlineStr">
+        <is>
+          <t>10:37</t>
+        </is>
+      </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>äldre ringhack</t>
+        </is>
+      </c>
+      <c r="AD65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT65" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX65" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135192056</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>135192074</v>
+      </c>
+      <c r="B66" t="n">
+        <v>57982</v>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>Höbrännflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q66" t="n">
+        <v>469051</v>
+      </c>
+      <c r="R66" t="n">
+        <v>7077912</v>
+      </c>
+      <c r="S66" t="n">
+        <v>10</v>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W66" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y66" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="Z66" t="inlineStr">
+        <is>
+          <t>11:05</t>
+        </is>
+      </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="AB66" t="inlineStr">
+        <is>
+          <t>11:05</t>
+        </is>
+      </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>äldre ringhack</t>
+        </is>
+      </c>
+      <c r="AD66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT66" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX66" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135192074</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>135192077</v>
+      </c>
+      <c r="B67" t="n">
+        <v>57982</v>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>Höbrännflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q67" t="n">
+        <v>469002</v>
+      </c>
+      <c r="R67" t="n">
+        <v>7077895</v>
+      </c>
+      <c r="S67" t="n">
+        <v>10</v>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W67" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y67" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="Z67" t="inlineStr">
+        <is>
+          <t>11:09</t>
+        </is>
+      </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="AB67" t="inlineStr">
+        <is>
+          <t>11:09</t>
+        </is>
+      </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>äldre ringhack</t>
+        </is>
+      </c>
+      <c r="AD67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT67" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX67" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135192077</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>135192079</v>
+      </c>
+      <c r="B68" t="n">
+        <v>57982</v>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr"/>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>Höbrännflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q68" t="n">
+        <v>469028</v>
+      </c>
+      <c r="R68" t="n">
+        <v>7077856</v>
+      </c>
+      <c r="S68" t="n">
+        <v>10</v>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W68" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y68" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="Z68" t="inlineStr">
+        <is>
+          <t>11:12</t>
+        </is>
+      </c>
+      <c r="AA68" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="AB68" t="inlineStr">
+        <is>
+          <t>11:12</t>
+        </is>
+      </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>äldre ringhack</t>
+        </is>
+      </c>
+      <c r="AD68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT68" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX68" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135192079</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>135192085</v>
+      </c>
+      <c r="B69" t="n">
+        <v>57982</v>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>Höbrännflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q69" t="n">
+        <v>468941</v>
+      </c>
+      <c r="R69" t="n">
+        <v>7077921</v>
+      </c>
+      <c r="S69" t="n">
+        <v>10</v>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W69" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y69" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="Z69" t="inlineStr">
+        <is>
+          <t>11:18</t>
+        </is>
+      </c>
+      <c r="AA69" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="AB69" t="inlineStr">
+        <is>
+          <t>11:18</t>
+        </is>
+      </c>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>äldre ringhack</t>
+        </is>
+      </c>
+      <c r="AD69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT69" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX69" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135192085</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>135192088</v>
+      </c>
+      <c r="B70" t="n">
+        <v>57982</v>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>Höbrännflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q70" t="n">
+        <v>468900</v>
+      </c>
+      <c r="R70" t="n">
+        <v>7077908</v>
+      </c>
+      <c r="S70" t="n">
+        <v>10</v>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W70" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y70" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="Z70" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="AA70" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="AB70" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="AC70" t="inlineStr">
+        <is>
+          <t>färska och äldre ringhack</t>
+        </is>
+      </c>
+      <c r="AD70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT70" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX70" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135192088</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>135192093</v>
+      </c>
+      <c r="B71" t="n">
+        <v>57982</v>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr"/>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>Höbrännflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q71" t="n">
+        <v>468841</v>
+      </c>
+      <c r="R71" t="n">
+        <v>7077895</v>
+      </c>
+      <c r="S71" t="n">
+        <v>10</v>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W71" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y71" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="Z71" t="inlineStr">
+        <is>
+          <t>11:28</t>
+        </is>
+      </c>
+      <c r="AA71" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="AB71" t="inlineStr">
+        <is>
+          <t>11:28</t>
+        </is>
+      </c>
+      <c r="AC71" t="inlineStr">
+        <is>
+          <t>äldre ringhack</t>
+        </is>
+      </c>
+      <c r="AD71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT71" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX71" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135192093</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>135192095</v>
+      </c>
+      <c r="B72" t="n">
+        <v>57982</v>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr"/>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>Höbrännflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q72" t="n">
+        <v>468832</v>
+      </c>
+      <c r="R72" t="n">
+        <v>7077861</v>
+      </c>
+      <c r="S72" t="n">
+        <v>10</v>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V72" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W72" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y72" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="Z72" t="inlineStr">
+        <is>
+          <t>11:32</t>
+        </is>
+      </c>
+      <c r="AA72" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="AB72" t="inlineStr">
+        <is>
+          <t>11:32</t>
+        </is>
+      </c>
+      <c r="AC72" t="inlineStr">
+        <is>
+          <t>äldre ringhack</t>
+        </is>
+      </c>
+      <c r="AD72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT72" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX72" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135192095</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>135192112</v>
+      </c>
+      <c r="B73" t="n">
+        <v>57982</v>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E73" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr"/>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>Höbrännflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q73" t="n">
+        <v>469029</v>
+      </c>
+      <c r="R73" t="n">
+        <v>7077764</v>
+      </c>
+      <c r="S73" t="n">
+        <v>10</v>
+      </c>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V73" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W73" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y73" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="Z73" t="inlineStr">
+        <is>
+          <t>11:55</t>
+        </is>
+      </c>
+      <c r="AA73" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="AB73" t="inlineStr">
+        <is>
+          <t>11:55</t>
+        </is>
+      </c>
+      <c r="AC73" t="inlineStr">
+        <is>
+          <t>äldre ringhack</t>
+        </is>
+      </c>
+      <c r="AD73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT73" t="inlineStr"/>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX73" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY73" t="inlineStr"/>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135192112</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>135192116</v>
+      </c>
+      <c r="B74" t="n">
+        <v>57982</v>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E74" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr"/>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>Höbrännflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q74" t="n">
+        <v>469092</v>
+      </c>
+      <c r="R74" t="n">
+        <v>7077868</v>
+      </c>
+      <c r="S74" t="n">
+        <v>10</v>
+      </c>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V74" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W74" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y74" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="Z74" t="inlineStr">
+        <is>
+          <t>12:02</t>
+        </is>
+      </c>
+      <c r="AA74" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="AB74" t="inlineStr">
+        <is>
+          <t>12:02</t>
+        </is>
+      </c>
+      <c r="AC74" t="inlineStr">
+        <is>
+          <t>äldre ringhack</t>
+        </is>
+      </c>
+      <c r="AD74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT74" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX74" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY74" t="inlineStr"/>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135192116</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>135192118</v>
+      </c>
+      <c r="B75" t="n">
+        <v>57982</v>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E75" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr"/>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t>Höbrännflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q75" t="n">
+        <v>469121</v>
+      </c>
+      <c r="R75" t="n">
+        <v>7077852</v>
+      </c>
+      <c r="S75" t="n">
+        <v>10</v>
+      </c>
+      <c r="T75" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U75" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V75" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W75" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y75" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="Z75" t="inlineStr">
+        <is>
+          <t>12:04</t>
+        </is>
+      </c>
+      <c r="AA75" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="AB75" t="inlineStr">
+        <is>
+          <t>12:04</t>
+        </is>
+      </c>
+      <c r="AC75" t="inlineStr">
+        <is>
+          <t>äldre ringhack</t>
+        </is>
+      </c>
+      <c r="AD75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT75" t="inlineStr"/>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX75" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY75" t="inlineStr"/>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135192118</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>135192119</v>
+      </c>
+      <c r="B76" t="n">
+        <v>57982</v>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E76" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr"/>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t>Höbrännflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q76" t="n">
+        <v>469139</v>
+      </c>
+      <c r="R76" t="n">
+        <v>7077825</v>
+      </c>
+      <c r="S76" t="n">
+        <v>10</v>
+      </c>
+      <c r="T76" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U76" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V76" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W76" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y76" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="Z76" t="inlineStr">
+        <is>
+          <t>12:07</t>
+        </is>
+      </c>
+      <c r="AA76" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="AB76" t="inlineStr">
+        <is>
+          <t>12:07</t>
+        </is>
+      </c>
+      <c r="AC76" t="inlineStr">
+        <is>
+          <t>äldre ringhack</t>
+        </is>
+      </c>
+      <c r="AD76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT76" t="inlineStr"/>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX76" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY76" t="inlineStr"/>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135192119</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>135192123</v>
+      </c>
+      <c r="B77" t="n">
+        <v>57982</v>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E77" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr"/>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P77" t="inlineStr">
+        <is>
+          <t>Höbrännflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q77" t="n">
+        <v>469108</v>
+      </c>
+      <c r="R77" t="n">
+        <v>7077950</v>
+      </c>
+      <c r="S77" t="n">
+        <v>10</v>
+      </c>
+      <c r="T77" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U77" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V77" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W77" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y77" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="Z77" t="inlineStr">
+        <is>
+          <t>12:11</t>
+        </is>
+      </c>
+      <c r="AA77" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="AB77" t="inlineStr">
+        <is>
+          <t>12:11</t>
+        </is>
+      </c>
+      <c r="AC77" t="inlineStr">
+        <is>
+          <t>färska ringhack</t>
+        </is>
+      </c>
+      <c r="AD77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT77" t="inlineStr"/>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX77" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY77" t="inlineStr"/>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135192123</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>135192124</v>
+      </c>
+      <c r="B78" t="n">
+        <v>57982</v>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E78" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr"/>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P78" t="inlineStr">
+        <is>
+          <t>Höbrännflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q78" t="n">
+        <v>469109</v>
+      </c>
+      <c r="R78" t="n">
+        <v>7077945</v>
+      </c>
+      <c r="S78" t="n">
+        <v>10</v>
+      </c>
+      <c r="T78" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U78" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V78" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W78" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y78" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="Z78" t="inlineStr">
+        <is>
+          <t>12:12</t>
+        </is>
+      </c>
+      <c r="AA78" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="AB78" t="inlineStr">
+        <is>
+          <t>12:12</t>
+        </is>
+      </c>
+      <c r="AC78" t="inlineStr">
+        <is>
+          <t>färska ringhack</t>
+        </is>
+      </c>
+      <c r="AD78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT78" t="inlineStr"/>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX78" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY78" t="inlineStr"/>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135192124</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>135192125</v>
+      </c>
+      <c r="B79" t="n">
+        <v>57982</v>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E79" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr"/>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P79" t="inlineStr">
+        <is>
+          <t>Höbrännflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q79" t="n">
+        <v>469118</v>
+      </c>
+      <c r="R79" t="n">
+        <v>7077938</v>
+      </c>
+      <c r="S79" t="n">
+        <v>10</v>
+      </c>
+      <c r="T79" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U79" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V79" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W79" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y79" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="Z79" t="inlineStr">
+        <is>
+          <t>12:12</t>
+        </is>
+      </c>
+      <c r="AA79" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="AB79" t="inlineStr">
+        <is>
+          <t>12:12</t>
+        </is>
+      </c>
+      <c r="AC79" t="inlineStr">
+        <is>
+          <t>färska ringhack</t>
+        </is>
+      </c>
+      <c r="AD79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT79" t="inlineStr"/>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX79" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY79" t="inlineStr"/>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135192125</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>135192127</v>
+      </c>
+      <c r="B80" t="n">
+        <v>57982</v>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E80" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr"/>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P80" t="inlineStr">
+        <is>
+          <t>Höbrännflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q80" t="n">
+        <v>469140</v>
+      </c>
+      <c r="R80" t="n">
+        <v>7077913</v>
+      </c>
+      <c r="S80" t="n">
+        <v>10</v>
+      </c>
+      <c r="T80" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U80" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V80" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W80" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y80" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="Z80" t="inlineStr">
+        <is>
+          <t>12:13</t>
+        </is>
+      </c>
+      <c r="AA80" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="AB80" t="inlineStr">
+        <is>
+          <t>12:13</t>
+        </is>
+      </c>
+      <c r="AC80" t="inlineStr">
+        <is>
+          <t>färska ringhack</t>
+        </is>
+      </c>
+      <c r="AD80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT80" t="inlineStr"/>
+      <c r="AW80" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX80" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY80" t="inlineStr"/>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135192127</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>135192128</v>
+      </c>
+      <c r="B81" t="n">
+        <v>57982</v>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E81" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr"/>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P81" t="inlineStr">
+        <is>
+          <t>Höbrännflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q81" t="n">
+        <v>469149</v>
+      </c>
+      <c r="R81" t="n">
+        <v>7077895</v>
+      </c>
+      <c r="S81" t="n">
+        <v>10</v>
+      </c>
+      <c r="T81" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U81" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V81" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W81" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y81" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="Z81" t="inlineStr">
+        <is>
+          <t>12:14</t>
+        </is>
+      </c>
+      <c r="AA81" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="AB81" t="inlineStr">
+        <is>
+          <t>12:14</t>
+        </is>
+      </c>
+      <c r="AC81" t="inlineStr">
+        <is>
+          <t>färska ringhack</t>
+        </is>
+      </c>
+      <c r="AD81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT81" t="inlineStr"/>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX81" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY81" t="inlineStr"/>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135192128</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>135192130</v>
+      </c>
+      <c r="B82" t="n">
+        <v>57982</v>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E82" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr"/>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P82" t="inlineStr">
+        <is>
+          <t>Höbrännflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q82" t="n">
+        <v>469158</v>
+      </c>
+      <c r="R82" t="n">
+        <v>7077852</v>
+      </c>
+      <c r="S82" t="n">
+        <v>10</v>
+      </c>
+      <c r="T82" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U82" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V82" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W82" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y82" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="Z82" t="inlineStr">
+        <is>
+          <t>12:15</t>
+        </is>
+      </c>
+      <c r="AA82" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="AB82" t="inlineStr">
+        <is>
+          <t>12:15</t>
+        </is>
+      </c>
+      <c r="AC82" t="inlineStr">
+        <is>
+          <t>färska ringhack</t>
+        </is>
+      </c>
+      <c r="AD82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT82" t="inlineStr"/>
+      <c r="AW82" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX82" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY82" t="inlineStr"/>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135192130</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>135192131</v>
+      </c>
+      <c r="B83" t="n">
+        <v>57982</v>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E83" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr"/>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P83" t="inlineStr">
+        <is>
+          <t>Höbrännflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q83" t="n">
+        <v>469166</v>
+      </c>
+      <c r="R83" t="n">
+        <v>7077841</v>
+      </c>
+      <c r="S83" t="n">
+        <v>10</v>
+      </c>
+      <c r="T83" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U83" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V83" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W83" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y83" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="Z83" t="inlineStr">
+        <is>
+          <t>12:16</t>
+        </is>
+      </c>
+      <c r="AA83" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="AB83" t="inlineStr">
+        <is>
+          <t>12:16</t>
+        </is>
+      </c>
+      <c r="AC83" t="inlineStr">
+        <is>
+          <t>färska ringhack</t>
+        </is>
+      </c>
+      <c r="AD83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT83" t="inlineStr"/>
+      <c r="AW83" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX83" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY83" t="inlineStr"/>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135192131</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>135192132</v>
+      </c>
+      <c r="B84" t="n">
+        <v>57982</v>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E84" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr"/>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P84" t="inlineStr">
+        <is>
+          <t>Höbrännflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q84" t="n">
+        <v>469163</v>
+      </c>
+      <c r="R84" t="n">
+        <v>7077822</v>
+      </c>
+      <c r="S84" t="n">
+        <v>10</v>
+      </c>
+      <c r="T84" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U84" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V84" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W84" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y84" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="Z84" t="inlineStr">
+        <is>
+          <t>12:17</t>
+        </is>
+      </c>
+      <c r="AA84" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="AB84" t="inlineStr">
+        <is>
+          <t>12:17</t>
+        </is>
+      </c>
+      <c r="AC84" t="inlineStr">
+        <is>
+          <t>färska ringhack</t>
+        </is>
+      </c>
+      <c r="AD84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT84" t="inlineStr"/>
+      <c r="AW84" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX84" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY84" t="inlineStr"/>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135192132</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>135192134</v>
+      </c>
+      <c r="B85" t="n">
+        <v>57982</v>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E85" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr"/>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P85" t="inlineStr">
+        <is>
+          <t>Höbrännflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q85" t="n">
+        <v>469172</v>
+      </c>
+      <c r="R85" t="n">
+        <v>7077811</v>
+      </c>
+      <c r="S85" t="n">
+        <v>10</v>
+      </c>
+      <c r="T85" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U85" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V85" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W85" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y85" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="Z85" t="inlineStr">
+        <is>
+          <t>12:17</t>
+        </is>
+      </c>
+      <c r="AA85" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="AB85" t="inlineStr">
+        <is>
+          <t>12:17</t>
+        </is>
+      </c>
+      <c r="AC85" t="inlineStr">
+        <is>
+          <t>färska ringhack</t>
+        </is>
+      </c>
+      <c r="AD85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT85" t="inlineStr"/>
+      <c r="AW85" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX85" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY85" t="inlineStr"/>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135192134</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>135192135</v>
+      </c>
+      <c r="B86" t="n">
+        <v>57982</v>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E86" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr"/>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P86" t="inlineStr">
+        <is>
+          <t>Höbrännflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q86" t="n">
+        <v>469180</v>
+      </c>
+      <c r="R86" t="n">
+        <v>7077818</v>
+      </c>
+      <c r="S86" t="n">
+        <v>10</v>
+      </c>
+      <c r="T86" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U86" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V86" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W86" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y86" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="Z86" t="inlineStr">
+        <is>
+          <t>12:18</t>
+        </is>
+      </c>
+      <c r="AA86" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="AB86" t="inlineStr">
+        <is>
+          <t>12:18</t>
+        </is>
+      </c>
+      <c r="AC86" t="inlineStr">
+        <is>
+          <t>äldre ringhack</t>
+        </is>
+      </c>
+      <c r="AD86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT86" t="inlineStr"/>
+      <c r="AW86" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX86" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY86" t="inlineStr"/>
+      <c r="AZ86" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135192135</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>135192136</v>
+      </c>
+      <c r="B87" t="n">
+        <v>57982</v>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E87" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr"/>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P87" t="inlineStr">
+        <is>
+          <t>Höbrännflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q87" t="n">
+        <v>469176</v>
+      </c>
+      <c r="R87" t="n">
+        <v>7077799</v>
+      </c>
+      <c r="S87" t="n">
+        <v>10</v>
+      </c>
+      <c r="T87" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U87" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V87" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W87" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y87" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="Z87" t="inlineStr">
+        <is>
+          <t>12:19</t>
+        </is>
+      </c>
+      <c r="AA87" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="AB87" t="inlineStr">
+        <is>
+          <t>12:19</t>
+        </is>
+      </c>
+      <c r="AC87" t="inlineStr">
+        <is>
+          <t>färska ringhack</t>
+        </is>
+      </c>
+      <c r="AD87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT87" t="inlineStr"/>
+      <c r="AW87" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX87" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY87" t="inlineStr"/>
+      <c r="AZ87" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135192136</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>135192137</v>
+      </c>
+      <c r="B88" t="n">
+        <v>57982</v>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E88" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr"/>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P88" t="inlineStr">
+        <is>
+          <t>Höbrännflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q88" t="n">
+        <v>469181</v>
+      </c>
+      <c r="R88" t="n">
+        <v>7077798</v>
+      </c>
+      <c r="S88" t="n">
+        <v>10</v>
+      </c>
+      <c r="T88" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U88" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V88" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W88" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y88" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="Z88" t="inlineStr">
+        <is>
+          <t>12:20</t>
+        </is>
+      </c>
+      <c r="AA88" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="AB88" t="inlineStr">
+        <is>
+          <t>12:20</t>
+        </is>
+      </c>
+      <c r="AC88" t="inlineStr">
+        <is>
+          <t>färska ringhack</t>
+        </is>
+      </c>
+      <c r="AD88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT88" t="inlineStr"/>
+      <c r="AW88" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX88" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY88" t="inlineStr"/>
+      <c r="AZ88" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135192137</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>135192151</v>
+      </c>
+      <c r="B89" t="n">
+        <v>57982</v>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E89" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr"/>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P89" t="inlineStr">
+        <is>
+          <t>Höbrännflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q89" t="n">
+        <v>469393</v>
+      </c>
+      <c r="R89" t="n">
+        <v>7077846</v>
+      </c>
+      <c r="S89" t="n">
+        <v>10</v>
+      </c>
+      <c r="T89" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U89" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V89" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W89" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y89" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="Z89" t="inlineStr">
+        <is>
+          <t>12:42</t>
+        </is>
+      </c>
+      <c r="AA89" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="AB89" t="inlineStr">
+        <is>
+          <t>12:42</t>
+        </is>
+      </c>
+      <c r="AC89" t="inlineStr">
+        <is>
+          <t>äldre ringhack</t>
+        </is>
+      </c>
+      <c r="AD89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT89" t="inlineStr"/>
+      <c r="AW89" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX89" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY89" t="inlineStr"/>
+      <c r="AZ89" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135192151</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>135192152</v>
+      </c>
+      <c r="B90" t="n">
+        <v>57982</v>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E90" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr"/>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P90" t="inlineStr">
+        <is>
+          <t>Höbrännflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q90" t="n">
+        <v>469356</v>
+      </c>
+      <c r="R90" t="n">
+        <v>7077867</v>
+      </c>
+      <c r="S90" t="n">
+        <v>10</v>
+      </c>
+      <c r="T90" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U90" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V90" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W90" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y90" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="Z90" t="inlineStr">
+        <is>
+          <t>12:45</t>
+        </is>
+      </c>
+      <c r="AA90" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="AB90" t="inlineStr">
+        <is>
+          <t>12:45</t>
+        </is>
+      </c>
+      <c r="AC90" t="inlineStr">
+        <is>
+          <t>äldre ringhack</t>
+        </is>
+      </c>
+      <c r="AD90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT90" t="inlineStr"/>
+      <c r="AW90" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX90" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY90" t="inlineStr"/>
+      <c r="AZ90" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135192152</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>135192153</v>
+      </c>
+      <c r="B91" t="n">
+        <v>57982</v>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E91" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr"/>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P91" t="inlineStr">
+        <is>
+          <t>Höbrännflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q91" t="n">
+        <v>469347</v>
+      </c>
+      <c r="R91" t="n">
+        <v>7077869</v>
+      </c>
+      <c r="S91" t="n">
+        <v>10</v>
+      </c>
+      <c r="T91" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U91" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V91" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W91" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y91" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="Z91" t="inlineStr">
+        <is>
+          <t>12:46</t>
+        </is>
+      </c>
+      <c r="AA91" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="AB91" t="inlineStr">
+        <is>
+          <t>12:46</t>
+        </is>
+      </c>
+      <c r="AC91" t="inlineStr">
+        <is>
+          <t>äldre ringhack</t>
+        </is>
+      </c>
+      <c r="AD91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT91" t="inlineStr"/>
+      <c r="AW91" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX91" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY91" t="inlineStr"/>
+      <c r="AZ91" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135192153</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>135192157</v>
+      </c>
+      <c r="B92" t="n">
+        <v>57982</v>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E92" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr"/>
+      <c r="M92" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P92" t="inlineStr">
+        <is>
+          <t>Höbrännflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q92" t="n">
+        <v>469381</v>
+      </c>
+      <c r="R92" t="n">
+        <v>7077873</v>
+      </c>
+      <c r="S92" t="n">
+        <v>10</v>
+      </c>
+      <c r="T92" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U92" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V92" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W92" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y92" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="Z92" t="inlineStr">
+        <is>
+          <t>12:52</t>
+        </is>
+      </c>
+      <c r="AA92" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="AB92" t="inlineStr">
+        <is>
+          <t>12:52</t>
+        </is>
+      </c>
+      <c r="AC92" t="inlineStr">
+        <is>
+          <t>äldre ringhack</t>
+        </is>
+      </c>
+      <c r="AD92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT92" t="inlineStr"/>
+      <c r="AW92" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX92" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY92" t="inlineStr"/>
+      <c r="AZ92" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135192157</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>135192158</v>
+      </c>
+      <c r="B93" t="n">
+        <v>57982</v>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E93" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr"/>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P93" t="inlineStr">
+        <is>
+          <t>Höbrännflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q93" t="n">
+        <v>469401</v>
+      </c>
+      <c r="R93" t="n">
+        <v>7077887</v>
+      </c>
+      <c r="S93" t="n">
+        <v>10</v>
+      </c>
+      <c r="T93" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U93" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V93" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W93" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y93" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="Z93" t="inlineStr">
+        <is>
+          <t>12:54</t>
+        </is>
+      </c>
+      <c r="AA93" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="AB93" t="inlineStr">
+        <is>
+          <t>12:54</t>
+        </is>
+      </c>
+      <c r="AC93" t="inlineStr">
+        <is>
+          <t>äldre ringhack</t>
+        </is>
+      </c>
+      <c r="AD93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT93" t="inlineStr"/>
+      <c r="AW93" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX93" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY93" t="inlineStr"/>
+      <c r="AZ93" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135192158</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>135192161</v>
+      </c>
+      <c r="B94" t="n">
+        <v>57982</v>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E94" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr"/>
+      <c r="M94" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P94" t="inlineStr">
+        <is>
+          <t>Höbrännflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q94" t="n">
+        <v>469388</v>
+      </c>
+      <c r="R94" t="n">
+        <v>7077920</v>
+      </c>
+      <c r="S94" t="n">
+        <v>10</v>
+      </c>
+      <c r="T94" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U94" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V94" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W94" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y94" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="Z94" t="inlineStr">
+        <is>
+          <t>12:56</t>
+        </is>
+      </c>
+      <c r="AA94" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="AB94" t="inlineStr">
+        <is>
+          <t>12:56</t>
+        </is>
+      </c>
+      <c r="AC94" t="inlineStr">
+        <is>
+          <t>äldre ringhack</t>
+        </is>
+      </c>
+      <c r="AD94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT94" t="inlineStr"/>
+      <c r="AW94" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX94" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY94" t="inlineStr"/>
+      <c r="AZ94" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135192161</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>135192166</v>
+      </c>
+      <c r="B95" t="n">
+        <v>57982</v>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E95" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr"/>
+      <c r="P95" t="inlineStr">
+        <is>
+          <t>Höbrännflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q95" t="n">
+        <v>469249</v>
+      </c>
+      <c r="R95" t="n">
+        <v>7077922</v>
+      </c>
+      <c r="S95" t="n">
+        <v>10</v>
+      </c>
+      <c r="T95" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U95" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V95" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W95" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y95" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="Z95" t="inlineStr">
+        <is>
+          <t>13:07</t>
+        </is>
+      </c>
+      <c r="AA95" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="AB95" t="inlineStr">
+        <is>
+          <t>13:07</t>
+        </is>
+      </c>
+      <c r="AC95" t="inlineStr">
+        <is>
+          <t>ringhack</t>
+        </is>
+      </c>
+      <c r="AD95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT95" t="inlineStr"/>
+      <c r="AW95" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX95" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY95" t="inlineStr"/>
+      <c r="AZ95" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135192166</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="n">
+        <v>128346628</v>
+      </c>
+      <c r="B96" t="n">
+        <v>97989</v>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E96" t="n">
+        <v>221941</v>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>Plattlummer</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>Lycopodium complanatum</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr"/>
+      <c r="P96" t="inlineStr">
+        <is>
+          <t>Höbrännflon sö, Jmt</t>
+        </is>
+      </c>
+      <c r="Q96" t="n">
+        <v>468931</v>
+      </c>
+      <c r="R96" t="n">
+        <v>7077743</v>
+      </c>
+      <c r="S96" t="n">
+        <v>10</v>
+      </c>
+      <c r="T96" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U96" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V96" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W96" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y96" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AA96" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AD96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT96" t="inlineStr"/>
+      <c r="AW96" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX96" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY96" t="inlineStr"/>
+      <c r="AZ96" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/128346628</t>
         </is>
@@ -7037,6 +11663,44 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ91" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ92" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ93" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ94" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ95" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ96" r:id="rId95"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 28940-2026 artfynd.xlsx
+++ b/artfynd/A 28940-2026 artfynd.xlsx
@@ -6881,7 +6881,7 @@
         <v>135192022</v>
       </c>
       <c r="B58" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7003,7 +7003,7 @@
         <v>135192026</v>
       </c>
       <c r="B59" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7125,7 +7125,7 @@
         <v>135192030</v>
       </c>
       <c r="B60" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7247,7 +7247,7 @@
         <v>135192045</v>
       </c>
       <c r="B61" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7364,7 +7364,7 @@
         <v>135192047</v>
       </c>
       <c r="B62" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7486,7 +7486,7 @@
         <v>135192048</v>
       </c>
       <c r="B63" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7608,7 +7608,7 @@
         <v>135192050</v>
       </c>
       <c r="B64" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7730,7 +7730,7 @@
         <v>135192056</v>
       </c>
       <c r="B65" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7852,7 +7852,7 @@
         <v>135192074</v>
       </c>
       <c r="B66" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7974,7 +7974,7 @@
         <v>135192077</v>
       </c>
       <c r="B67" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8096,7 +8096,7 @@
         <v>135192079</v>
       </c>
       <c r="B68" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8218,7 +8218,7 @@
         <v>135192085</v>
       </c>
       <c r="B69" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8340,7 +8340,7 @@
         <v>135192088</v>
       </c>
       <c r="B70" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8462,7 +8462,7 @@
         <v>135192093</v>
       </c>
       <c r="B71" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8584,7 +8584,7 @@
         <v>135192095</v>
       </c>
       <c r="B72" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8706,7 +8706,7 @@
         <v>135192112</v>
       </c>
       <c r="B73" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8828,7 +8828,7 @@
         <v>135192116</v>
       </c>
       <c r="B74" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8950,7 +8950,7 @@
         <v>135192118</v>
       </c>
       <c r="B75" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9072,7 +9072,7 @@
         <v>135192119</v>
       </c>
       <c r="B76" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9194,7 +9194,7 @@
         <v>135192123</v>
       </c>
       <c r="B77" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9316,7 +9316,7 @@
         <v>135192124</v>
       </c>
       <c r="B78" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9438,7 +9438,7 @@
         <v>135192125</v>
       </c>
       <c r="B79" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9560,7 +9560,7 @@
         <v>135192127</v>
       </c>
       <c r="B80" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9682,7 +9682,7 @@
         <v>135192128</v>
       </c>
       <c r="B81" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9804,7 +9804,7 @@
         <v>135192130</v>
       </c>
       <c r="B82" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9926,7 +9926,7 @@
         <v>135192131</v>
       </c>
       <c r="B83" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -10048,7 +10048,7 @@
         <v>135192132</v>
       </c>
       <c r="B84" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -10170,7 +10170,7 @@
         <v>135192134</v>
       </c>
       <c r="B85" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10292,7 +10292,7 @@
         <v>135192135</v>
       </c>
       <c r="B86" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10414,7 +10414,7 @@
         <v>135192136</v>
       </c>
       <c r="B87" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10536,7 +10536,7 @@
         <v>135192137</v>
       </c>
       <c r="B88" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10658,7 +10658,7 @@
         <v>135192151</v>
       </c>
       <c r="B89" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10780,7 +10780,7 @@
         <v>135192152</v>
       </c>
       <c r="B90" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10902,7 +10902,7 @@
         <v>135192153</v>
       </c>
       <c r="B91" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -11024,7 +11024,7 @@
         <v>135192157</v>
       </c>
       <c r="B92" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -11146,7 +11146,7 @@
         <v>135192158</v>
       </c>
       <c r="B93" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -11268,7 +11268,7 @@
         <v>135192161</v>
       </c>
       <c r="B94" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -11390,7 +11390,7 @@
         <v>135192166</v>
       </c>
       <c r="B95" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>

--- a/artfynd/A 28940-2026 artfynd.xlsx
+++ b/artfynd/A 28940-2026 artfynd.xlsx
@@ -6881,7 +6881,7 @@
         <v>135192022</v>
       </c>
       <c r="B58" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7003,7 +7003,7 @@
         <v>135192026</v>
       </c>
       <c r="B59" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7125,7 +7125,7 @@
         <v>135192030</v>
       </c>
       <c r="B60" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7247,7 +7247,7 @@
         <v>135192045</v>
       </c>
       <c r="B61" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7364,7 +7364,7 @@
         <v>135192047</v>
       </c>
       <c r="B62" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7486,7 +7486,7 @@
         <v>135192048</v>
       </c>
       <c r="B63" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7608,7 +7608,7 @@
         <v>135192050</v>
       </c>
       <c r="B64" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7730,7 +7730,7 @@
         <v>135192056</v>
       </c>
       <c r="B65" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7852,7 +7852,7 @@
         <v>135192074</v>
       </c>
       <c r="B66" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7974,7 +7974,7 @@
         <v>135192077</v>
       </c>
       <c r="B67" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8096,7 +8096,7 @@
         <v>135192079</v>
       </c>
       <c r="B68" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8218,7 +8218,7 @@
         <v>135192085</v>
       </c>
       <c r="B69" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8340,7 +8340,7 @@
         <v>135192088</v>
       </c>
       <c r="B70" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8462,7 +8462,7 @@
         <v>135192093</v>
       </c>
       <c r="B71" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8584,7 +8584,7 @@
         <v>135192095</v>
       </c>
       <c r="B72" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8706,7 +8706,7 @@
         <v>135192112</v>
       </c>
       <c r="B73" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8828,7 +8828,7 @@
         <v>135192116</v>
       </c>
       <c r="B74" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8950,7 +8950,7 @@
         <v>135192118</v>
       </c>
       <c r="B75" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9072,7 +9072,7 @@
         <v>135192119</v>
       </c>
       <c r="B76" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9194,7 +9194,7 @@
         <v>135192123</v>
       </c>
       <c r="B77" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9316,7 +9316,7 @@
         <v>135192124</v>
       </c>
       <c r="B78" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9438,7 +9438,7 @@
         <v>135192125</v>
       </c>
       <c r="B79" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9560,7 +9560,7 @@
         <v>135192127</v>
       </c>
       <c r="B80" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9682,7 +9682,7 @@
         <v>135192128</v>
       </c>
       <c r="B81" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9804,7 +9804,7 @@
         <v>135192130</v>
       </c>
       <c r="B82" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9926,7 +9926,7 @@
         <v>135192131</v>
       </c>
       <c r="B83" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -10048,7 +10048,7 @@
         <v>135192132</v>
       </c>
       <c r="B84" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -10170,7 +10170,7 @@
         <v>135192134</v>
       </c>
       <c r="B85" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10292,7 +10292,7 @@
         <v>135192135</v>
       </c>
       <c r="B86" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10414,7 +10414,7 @@
         <v>135192136</v>
       </c>
       <c r="B87" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10536,7 +10536,7 @@
         <v>135192137</v>
       </c>
       <c r="B88" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10658,7 +10658,7 @@
         <v>135192151</v>
       </c>
       <c r="B89" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10780,7 +10780,7 @@
         <v>135192152</v>
       </c>
       <c r="B90" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10902,7 +10902,7 @@
         <v>135192153</v>
       </c>
       <c r="B91" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -11024,7 +11024,7 @@
         <v>135192157</v>
       </c>
       <c r="B92" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -11146,7 +11146,7 @@
         <v>135192158</v>
       </c>
       <c r="B93" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -11268,7 +11268,7 @@
         <v>135192161</v>
       </c>
       <c r="B94" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -11390,7 +11390,7 @@
         <v>135192166</v>
       </c>
       <c r="B95" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>

--- a/artfynd/A 28940-2026 artfynd.xlsx
+++ b/artfynd/A 28940-2026 artfynd.xlsx
@@ -6881,7 +6881,7 @@
         <v>135192022</v>
       </c>
       <c r="B58" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7003,7 +7003,7 @@
         <v>135192026</v>
       </c>
       <c r="B59" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7125,7 +7125,7 @@
         <v>135192030</v>
       </c>
       <c r="B60" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7247,7 +7247,7 @@
         <v>135192045</v>
       </c>
       <c r="B61" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7364,7 +7364,7 @@
         <v>135192047</v>
       </c>
       <c r="B62" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7486,7 +7486,7 @@
         <v>135192048</v>
       </c>
       <c r="B63" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7608,7 +7608,7 @@
         <v>135192050</v>
       </c>
       <c r="B64" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7730,7 +7730,7 @@
         <v>135192056</v>
       </c>
       <c r="B65" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7852,7 +7852,7 @@
         <v>135192074</v>
       </c>
       <c r="B66" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7974,7 +7974,7 @@
         <v>135192077</v>
       </c>
       <c r="B67" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8096,7 +8096,7 @@
         <v>135192079</v>
       </c>
       <c r="B68" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8218,7 +8218,7 @@
         <v>135192085</v>
       </c>
       <c r="B69" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8340,7 +8340,7 @@
         <v>135192088</v>
       </c>
       <c r="B70" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8462,7 +8462,7 @@
         <v>135192093</v>
       </c>
       <c r="B71" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8584,7 +8584,7 @@
         <v>135192095</v>
       </c>
       <c r="B72" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8706,7 +8706,7 @@
         <v>135192112</v>
       </c>
       <c r="B73" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8828,7 +8828,7 @@
         <v>135192116</v>
       </c>
       <c r="B74" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8950,7 +8950,7 @@
         <v>135192118</v>
       </c>
       <c r="B75" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9072,7 +9072,7 @@
         <v>135192119</v>
       </c>
       <c r="B76" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9194,7 +9194,7 @@
         <v>135192123</v>
       </c>
       <c r="B77" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9316,7 +9316,7 @@
         <v>135192124</v>
       </c>
       <c r="B78" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9438,7 +9438,7 @@
         <v>135192125</v>
       </c>
       <c r="B79" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9560,7 +9560,7 @@
         <v>135192127</v>
       </c>
       <c r="B80" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9682,7 +9682,7 @@
         <v>135192128</v>
       </c>
       <c r="B81" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9804,7 +9804,7 @@
         <v>135192130</v>
       </c>
       <c r="B82" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9926,7 +9926,7 @@
         <v>135192131</v>
       </c>
       <c r="B83" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -10048,7 +10048,7 @@
         <v>135192132</v>
       </c>
       <c r="B84" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -10170,7 +10170,7 @@
         <v>135192134</v>
       </c>
       <c r="B85" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10292,7 +10292,7 @@
         <v>135192135</v>
       </c>
       <c r="B86" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10414,7 +10414,7 @@
         <v>135192136</v>
       </c>
       <c r="B87" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10536,7 +10536,7 @@
         <v>135192137</v>
       </c>
       <c r="B88" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10658,7 +10658,7 @@
         <v>135192151</v>
       </c>
       <c r="B89" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10780,7 +10780,7 @@
         <v>135192152</v>
       </c>
       <c r="B90" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10902,7 +10902,7 @@
         <v>135192153</v>
       </c>
       <c r="B91" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -11024,7 +11024,7 @@
         <v>135192157</v>
       </c>
       <c r="B92" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -11146,7 +11146,7 @@
         <v>135192158</v>
       </c>
       <c r="B93" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -11268,7 +11268,7 @@
         <v>135192161</v>
       </c>
       <c r="B94" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -11390,7 +11390,7 @@
         <v>135192166</v>
       </c>
       <c r="B95" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>

--- a/artfynd/A 28940-2026 artfynd.xlsx
+++ b/artfynd/A 28940-2026 artfynd.xlsx
@@ -6881,7 +6881,7 @@
         <v>135192022</v>
       </c>
       <c r="B58" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7003,7 +7003,7 @@
         <v>135192026</v>
       </c>
       <c r="B59" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7125,7 +7125,7 @@
         <v>135192030</v>
       </c>
       <c r="B60" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7247,7 +7247,7 @@
         <v>135192045</v>
       </c>
       <c r="B61" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7364,7 +7364,7 @@
         <v>135192047</v>
       </c>
       <c r="B62" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7486,7 +7486,7 @@
         <v>135192048</v>
       </c>
       <c r="B63" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7608,7 +7608,7 @@
         <v>135192050</v>
       </c>
       <c r="B64" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7730,7 +7730,7 @@
         <v>135192056</v>
       </c>
       <c r="B65" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7852,7 +7852,7 @@
         <v>135192074</v>
       </c>
       <c r="B66" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7974,7 +7974,7 @@
         <v>135192077</v>
       </c>
       <c r="B67" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8096,7 +8096,7 @@
         <v>135192079</v>
       </c>
       <c r="B68" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8218,7 +8218,7 @@
         <v>135192085</v>
       </c>
       <c r="B69" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8340,7 +8340,7 @@
         <v>135192088</v>
       </c>
       <c r="B70" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8462,7 +8462,7 @@
         <v>135192093</v>
       </c>
       <c r="B71" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8584,7 +8584,7 @@
         <v>135192095</v>
       </c>
       <c r="B72" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8706,7 +8706,7 @@
         <v>135192112</v>
       </c>
       <c r="B73" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8828,7 +8828,7 @@
         <v>135192116</v>
       </c>
       <c r="B74" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8950,7 +8950,7 @@
         <v>135192118</v>
       </c>
       <c r="B75" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9072,7 +9072,7 @@
         <v>135192119</v>
       </c>
       <c r="B76" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9194,7 +9194,7 @@
         <v>135192123</v>
       </c>
       <c r="B77" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9316,7 +9316,7 @@
         <v>135192124</v>
       </c>
       <c r="B78" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9438,7 +9438,7 @@
         <v>135192125</v>
       </c>
       <c r="B79" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9560,7 +9560,7 @@
         <v>135192127</v>
       </c>
       <c r="B80" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9682,7 +9682,7 @@
         <v>135192128</v>
       </c>
       <c r="B81" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9804,7 +9804,7 @@
         <v>135192130</v>
       </c>
       <c r="B82" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9926,7 +9926,7 @@
         <v>135192131</v>
       </c>
       <c r="B83" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -10048,7 +10048,7 @@
         <v>135192132</v>
       </c>
       <c r="B84" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -10170,7 +10170,7 @@
         <v>135192134</v>
       </c>
       <c r="B85" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10292,7 +10292,7 @@
         <v>135192135</v>
       </c>
       <c r="B86" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10414,7 +10414,7 @@
         <v>135192136</v>
       </c>
       <c r="B87" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10536,7 +10536,7 @@
         <v>135192137</v>
       </c>
       <c r="B88" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10658,7 +10658,7 @@
         <v>135192151</v>
       </c>
       <c r="B89" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10780,7 +10780,7 @@
         <v>135192152</v>
       </c>
       <c r="B90" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10902,7 +10902,7 @@
         <v>135192153</v>
       </c>
       <c r="B91" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -11024,7 +11024,7 @@
         <v>135192157</v>
       </c>
       <c r="B92" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -11146,7 +11146,7 @@
         <v>135192158</v>
       </c>
       <c r="B93" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -11268,7 +11268,7 @@
         <v>135192161</v>
       </c>
       <c r="B94" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -11390,7 +11390,7 @@
         <v>135192166</v>
       </c>
       <c r="B95" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>

--- a/artfynd/A 28940-2026 artfynd.xlsx
+++ b/artfynd/A 28940-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ96"/>
+  <dimension ref="A1:AZ58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6878,50 +6878,45 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>135192022</v>
+        <v>128346628</v>
       </c>
       <c r="B58" t="n">
-        <v>57993</v>
+        <v>97989</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>100109</v>
+        <v>221941</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
-      <c r="M58" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Höbrännflon, Jmt</t>
+          <t>Höbrännflon sö, Jmt</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>469168</v>
+        <v>468931</v>
       </c>
       <c r="R58" t="n">
-        <v>7078178</v>
+        <v>7077743</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6948,27 +6943,12 @@
       </c>
       <c r="Y58" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
-        </is>
-      </c>
-      <c r="Z58" t="inlineStr">
-        <is>
-          <t>09:29</t>
+          <t>2025-09-09</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
-        </is>
-      </c>
-      <c r="AB58" t="inlineStr">
-        <is>
-          <t>09:29</t>
-        </is>
-      </c>
-      <c r="AC58" t="inlineStr">
-        <is>
-          <t>äldre ringhack</t>
+          <t>2025-09-09</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6993,4612 +6973,6 @@
       </c>
       <c r="AY58" t="inlineStr"/>
       <c r="AZ58" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135192022</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="n">
-        <v>135192026</v>
-      </c>
-      <c r="B59" t="n">
-        <v>57993</v>
-      </c>
-      <c r="D59" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E59" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F59" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G59" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H59" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr"/>
-      <c r="M59" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="P59" t="inlineStr">
-        <is>
-          <t>Höbrännflon, Jmt</t>
-        </is>
-      </c>
-      <c r="Q59" t="n">
-        <v>469186</v>
-      </c>
-      <c r="R59" t="n">
-        <v>7078140</v>
-      </c>
-      <c r="S59" t="n">
-        <v>10</v>
-      </c>
-      <c r="T59" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U59" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V59" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W59" t="inlineStr">
-        <is>
-          <t>Föllinge</t>
-        </is>
-      </c>
-      <c r="Y59" t="inlineStr">
-        <is>
-          <t>2026-07-14</t>
-        </is>
-      </c>
-      <c r="Z59" t="inlineStr">
-        <is>
-          <t>09:38</t>
-        </is>
-      </c>
-      <c r="AA59" t="inlineStr">
-        <is>
-          <t>2026-07-14</t>
-        </is>
-      </c>
-      <c r="AB59" t="inlineStr">
-        <is>
-          <t>09:38</t>
-        </is>
-      </c>
-      <c r="AC59" t="inlineStr">
-        <is>
-          <t>äldre ringhack</t>
-        </is>
-      </c>
-      <c r="AD59" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE59" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG59" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT59" t="inlineStr"/>
-      <c r="AW59" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX59" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY59" t="inlineStr"/>
-      <c r="AZ59" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135192026</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="n">
-        <v>135192030</v>
-      </c>
-      <c r="B60" t="n">
-        <v>57993</v>
-      </c>
-      <c r="D60" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E60" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F60" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G60" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H60" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr"/>
-      <c r="M60" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="P60" t="inlineStr">
-        <is>
-          <t>Höbrännflon, Jmt</t>
-        </is>
-      </c>
-      <c r="Q60" t="n">
-        <v>469177</v>
-      </c>
-      <c r="R60" t="n">
-        <v>7078094</v>
-      </c>
-      <c r="S60" t="n">
-        <v>10</v>
-      </c>
-      <c r="T60" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U60" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V60" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W60" t="inlineStr">
-        <is>
-          <t>Föllinge</t>
-        </is>
-      </c>
-      <c r="Y60" t="inlineStr">
-        <is>
-          <t>2026-07-14</t>
-        </is>
-      </c>
-      <c r="Z60" t="inlineStr">
-        <is>
-          <t>09:48</t>
-        </is>
-      </c>
-      <c r="AA60" t="inlineStr">
-        <is>
-          <t>2026-07-14</t>
-        </is>
-      </c>
-      <c r="AB60" t="inlineStr">
-        <is>
-          <t>09:48</t>
-        </is>
-      </c>
-      <c r="AC60" t="inlineStr">
-        <is>
-          <t>äldre ringhack</t>
-        </is>
-      </c>
-      <c r="AD60" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE60" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG60" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT60" t="inlineStr"/>
-      <c r="AW60" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX60" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY60" t="inlineStr"/>
-      <c r="AZ60" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135192030</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="n">
-        <v>135192045</v>
-      </c>
-      <c r="B61" t="n">
-        <v>57993</v>
-      </c>
-      <c r="D61" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E61" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F61" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G61" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H61" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr"/>
-      <c r="P61" t="inlineStr">
-        <is>
-          <t>Höbrännflon, Jmt</t>
-        </is>
-      </c>
-      <c r="Q61" t="n">
-        <v>468993</v>
-      </c>
-      <c r="R61" t="n">
-        <v>7078287</v>
-      </c>
-      <c r="S61" t="n">
-        <v>10</v>
-      </c>
-      <c r="T61" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U61" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V61" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W61" t="inlineStr">
-        <is>
-          <t>Föllinge</t>
-        </is>
-      </c>
-      <c r="Y61" t="inlineStr">
-        <is>
-          <t>2026-07-14</t>
-        </is>
-      </c>
-      <c r="Z61" t="inlineStr">
-        <is>
-          <t>10:18</t>
-        </is>
-      </c>
-      <c r="AA61" t="inlineStr">
-        <is>
-          <t>2026-07-14</t>
-        </is>
-      </c>
-      <c r="AB61" t="inlineStr">
-        <is>
-          <t>10:18</t>
-        </is>
-      </c>
-      <c r="AC61" t="inlineStr">
-        <is>
-          <t>ringhack</t>
-        </is>
-      </c>
-      <c r="AD61" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE61" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG61" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT61" t="inlineStr"/>
-      <c r="AW61" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX61" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY61" t="inlineStr"/>
-      <c r="AZ61" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135192045</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="n">
-        <v>135192047</v>
-      </c>
-      <c r="B62" t="n">
-        <v>57993</v>
-      </c>
-      <c r="D62" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E62" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F62" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G62" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H62" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr"/>
-      <c r="M62" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="P62" t="inlineStr">
-        <is>
-          <t>Höbrännflon, Jmt</t>
-        </is>
-      </c>
-      <c r="Q62" t="n">
-        <v>468901</v>
-      </c>
-      <c r="R62" t="n">
-        <v>7078371</v>
-      </c>
-      <c r="S62" t="n">
-        <v>10</v>
-      </c>
-      <c r="T62" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U62" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V62" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W62" t="inlineStr">
-        <is>
-          <t>Föllinge</t>
-        </is>
-      </c>
-      <c r="Y62" t="inlineStr">
-        <is>
-          <t>2026-07-14</t>
-        </is>
-      </c>
-      <c r="Z62" t="inlineStr">
-        <is>
-          <t>10:25</t>
-        </is>
-      </c>
-      <c r="AA62" t="inlineStr">
-        <is>
-          <t>2026-07-14</t>
-        </is>
-      </c>
-      <c r="AB62" t="inlineStr">
-        <is>
-          <t>10:25</t>
-        </is>
-      </c>
-      <c r="AC62" t="inlineStr">
-        <is>
-          <t>äldre ringhack</t>
-        </is>
-      </c>
-      <c r="AD62" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE62" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG62" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT62" t="inlineStr"/>
-      <c r="AW62" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX62" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY62" t="inlineStr"/>
-      <c r="AZ62" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135192047</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="n">
-        <v>135192048</v>
-      </c>
-      <c r="B63" t="n">
-        <v>57993</v>
-      </c>
-      <c r="D63" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E63" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F63" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G63" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H63" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr"/>
-      <c r="M63" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="P63" t="inlineStr">
-        <is>
-          <t>Höbrännflon, Jmt</t>
-        </is>
-      </c>
-      <c r="Q63" t="n">
-        <v>468891</v>
-      </c>
-      <c r="R63" t="n">
-        <v>7078390</v>
-      </c>
-      <c r="S63" t="n">
-        <v>10</v>
-      </c>
-      <c r="T63" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U63" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V63" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W63" t="inlineStr">
-        <is>
-          <t>Föllinge</t>
-        </is>
-      </c>
-      <c r="Y63" t="inlineStr">
-        <is>
-          <t>2026-07-14</t>
-        </is>
-      </c>
-      <c r="Z63" t="inlineStr">
-        <is>
-          <t>10:28</t>
-        </is>
-      </c>
-      <c r="AA63" t="inlineStr">
-        <is>
-          <t>2026-07-14</t>
-        </is>
-      </c>
-      <c r="AB63" t="inlineStr">
-        <is>
-          <t>10:28</t>
-        </is>
-      </c>
-      <c r="AC63" t="inlineStr">
-        <is>
-          <t>färska o och äldre ringhack</t>
-        </is>
-      </c>
-      <c r="AD63" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE63" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG63" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT63" t="inlineStr"/>
-      <c r="AW63" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX63" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY63" t="inlineStr"/>
-      <c r="AZ63" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135192048</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="n">
-        <v>135192050</v>
-      </c>
-      <c r="B64" t="n">
-        <v>57993</v>
-      </c>
-      <c r="D64" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E64" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F64" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G64" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H64" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr"/>
-      <c r="M64" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="P64" t="inlineStr">
-        <is>
-          <t>Höbrännflon, Jmt</t>
-        </is>
-      </c>
-      <c r="Q64" t="n">
-        <v>468864</v>
-      </c>
-      <c r="R64" t="n">
-        <v>7078369</v>
-      </c>
-      <c r="S64" t="n">
-        <v>10</v>
-      </c>
-      <c r="T64" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U64" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V64" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W64" t="inlineStr">
-        <is>
-          <t>Föllinge</t>
-        </is>
-      </c>
-      <c r="Y64" t="inlineStr">
-        <is>
-          <t>2026-07-14</t>
-        </is>
-      </c>
-      <c r="Z64" t="inlineStr">
-        <is>
-          <t>10:31</t>
-        </is>
-      </c>
-      <c r="AA64" t="inlineStr">
-        <is>
-          <t>2026-07-14</t>
-        </is>
-      </c>
-      <c r="AB64" t="inlineStr">
-        <is>
-          <t>10:31</t>
-        </is>
-      </c>
-      <c r="AC64" t="inlineStr">
-        <is>
-          <t>färska och äldre ringhack</t>
-        </is>
-      </c>
-      <c r="AD64" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE64" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG64" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT64" t="inlineStr"/>
-      <c r="AW64" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX64" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY64" t="inlineStr"/>
-      <c r="AZ64" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135192050</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="n">
-        <v>135192056</v>
-      </c>
-      <c r="B65" t="n">
-        <v>57993</v>
-      </c>
-      <c r="D65" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E65" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F65" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G65" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H65" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr"/>
-      <c r="M65" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="P65" t="inlineStr">
-        <is>
-          <t>Höbrännflon, Jmt</t>
-        </is>
-      </c>
-      <c r="Q65" t="n">
-        <v>468923</v>
-      </c>
-      <c r="R65" t="n">
-        <v>7078311</v>
-      </c>
-      <c r="S65" t="n">
-        <v>10</v>
-      </c>
-      <c r="T65" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U65" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V65" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W65" t="inlineStr">
-        <is>
-          <t>Föllinge</t>
-        </is>
-      </c>
-      <c r="Y65" t="inlineStr">
-        <is>
-          <t>2026-07-14</t>
-        </is>
-      </c>
-      <c r="Z65" t="inlineStr">
-        <is>
-          <t>10:37</t>
-        </is>
-      </c>
-      <c r="AA65" t="inlineStr">
-        <is>
-          <t>2026-07-14</t>
-        </is>
-      </c>
-      <c r="AB65" t="inlineStr">
-        <is>
-          <t>10:37</t>
-        </is>
-      </c>
-      <c r="AC65" t="inlineStr">
-        <is>
-          <t>äldre ringhack</t>
-        </is>
-      </c>
-      <c r="AD65" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE65" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG65" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT65" t="inlineStr"/>
-      <c r="AW65" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX65" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY65" t="inlineStr"/>
-      <c r="AZ65" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135192056</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="n">
-        <v>135192074</v>
-      </c>
-      <c r="B66" t="n">
-        <v>57993</v>
-      </c>
-      <c r="D66" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E66" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F66" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G66" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H66" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr"/>
-      <c r="M66" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="P66" t="inlineStr">
-        <is>
-          <t>Höbrännflon, Jmt</t>
-        </is>
-      </c>
-      <c r="Q66" t="n">
-        <v>469051</v>
-      </c>
-      <c r="R66" t="n">
-        <v>7077912</v>
-      </c>
-      <c r="S66" t="n">
-        <v>10</v>
-      </c>
-      <c r="T66" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U66" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V66" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W66" t="inlineStr">
-        <is>
-          <t>Föllinge</t>
-        </is>
-      </c>
-      <c r="Y66" t="inlineStr">
-        <is>
-          <t>2026-07-14</t>
-        </is>
-      </c>
-      <c r="Z66" t="inlineStr">
-        <is>
-          <t>11:05</t>
-        </is>
-      </c>
-      <c r="AA66" t="inlineStr">
-        <is>
-          <t>2026-07-14</t>
-        </is>
-      </c>
-      <c r="AB66" t="inlineStr">
-        <is>
-          <t>11:05</t>
-        </is>
-      </c>
-      <c r="AC66" t="inlineStr">
-        <is>
-          <t>äldre ringhack</t>
-        </is>
-      </c>
-      <c r="AD66" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE66" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG66" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT66" t="inlineStr"/>
-      <c r="AW66" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX66" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY66" t="inlineStr"/>
-      <c r="AZ66" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135192074</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="n">
-        <v>135192077</v>
-      </c>
-      <c r="B67" t="n">
-        <v>57993</v>
-      </c>
-      <c r="D67" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E67" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F67" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G67" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H67" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr"/>
-      <c r="M67" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="P67" t="inlineStr">
-        <is>
-          <t>Höbrännflon, Jmt</t>
-        </is>
-      </c>
-      <c r="Q67" t="n">
-        <v>469002</v>
-      </c>
-      <c r="R67" t="n">
-        <v>7077895</v>
-      </c>
-      <c r="S67" t="n">
-        <v>10</v>
-      </c>
-      <c r="T67" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U67" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V67" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W67" t="inlineStr">
-        <is>
-          <t>Föllinge</t>
-        </is>
-      </c>
-      <c r="Y67" t="inlineStr">
-        <is>
-          <t>2026-07-14</t>
-        </is>
-      </c>
-      <c r="Z67" t="inlineStr">
-        <is>
-          <t>11:09</t>
-        </is>
-      </c>
-      <c r="AA67" t="inlineStr">
-        <is>
-          <t>2026-07-14</t>
-        </is>
-      </c>
-      <c r="AB67" t="inlineStr">
-        <is>
-          <t>11:09</t>
-        </is>
-      </c>
-      <c r="AC67" t="inlineStr">
-        <is>
-          <t>äldre ringhack</t>
-        </is>
-      </c>
-      <c r="AD67" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE67" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG67" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT67" t="inlineStr"/>
-      <c r="AW67" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX67" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY67" t="inlineStr"/>
-      <c r="AZ67" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135192077</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="n">
-        <v>135192079</v>
-      </c>
-      <c r="B68" t="n">
-        <v>57993</v>
-      </c>
-      <c r="D68" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E68" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F68" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G68" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H68" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr"/>
-      <c r="M68" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="P68" t="inlineStr">
-        <is>
-          <t>Höbrännflon, Jmt</t>
-        </is>
-      </c>
-      <c r="Q68" t="n">
-        <v>469028</v>
-      </c>
-      <c r="R68" t="n">
-        <v>7077856</v>
-      </c>
-      <c r="S68" t="n">
-        <v>10</v>
-      </c>
-      <c r="T68" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U68" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V68" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W68" t="inlineStr">
-        <is>
-          <t>Föllinge</t>
-        </is>
-      </c>
-      <c r="Y68" t="inlineStr">
-        <is>
-          <t>2026-07-14</t>
-        </is>
-      </c>
-      <c r="Z68" t="inlineStr">
-        <is>
-          <t>11:12</t>
-        </is>
-      </c>
-      <c r="AA68" t="inlineStr">
-        <is>
-          <t>2026-07-14</t>
-        </is>
-      </c>
-      <c r="AB68" t="inlineStr">
-        <is>
-          <t>11:12</t>
-        </is>
-      </c>
-      <c r="AC68" t="inlineStr">
-        <is>
-          <t>äldre ringhack</t>
-        </is>
-      </c>
-      <c r="AD68" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE68" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG68" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT68" t="inlineStr"/>
-      <c r="AW68" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX68" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY68" t="inlineStr"/>
-      <c r="AZ68" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135192079</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="n">
-        <v>135192085</v>
-      </c>
-      <c r="B69" t="n">
-        <v>57993</v>
-      </c>
-      <c r="D69" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E69" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F69" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G69" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H69" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr"/>
-      <c r="M69" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="P69" t="inlineStr">
-        <is>
-          <t>Höbrännflon, Jmt</t>
-        </is>
-      </c>
-      <c r="Q69" t="n">
-        <v>468941</v>
-      </c>
-      <c r="R69" t="n">
-        <v>7077921</v>
-      </c>
-      <c r="S69" t="n">
-        <v>10</v>
-      </c>
-      <c r="T69" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U69" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V69" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W69" t="inlineStr">
-        <is>
-          <t>Föllinge</t>
-        </is>
-      </c>
-      <c r="Y69" t="inlineStr">
-        <is>
-          <t>2026-07-14</t>
-        </is>
-      </c>
-      <c r="Z69" t="inlineStr">
-        <is>
-          <t>11:18</t>
-        </is>
-      </c>
-      <c r="AA69" t="inlineStr">
-        <is>
-          <t>2026-07-14</t>
-        </is>
-      </c>
-      <c r="AB69" t="inlineStr">
-        <is>
-          <t>11:18</t>
-        </is>
-      </c>
-      <c r="AC69" t="inlineStr">
-        <is>
-          <t>äldre ringhack</t>
-        </is>
-      </c>
-      <c r="AD69" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE69" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG69" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT69" t="inlineStr"/>
-      <c r="AW69" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX69" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY69" t="inlineStr"/>
-      <c r="AZ69" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135192085</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="n">
-        <v>135192088</v>
-      </c>
-      <c r="B70" t="n">
-        <v>57993</v>
-      </c>
-      <c r="D70" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E70" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F70" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G70" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H70" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr"/>
-      <c r="M70" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="P70" t="inlineStr">
-        <is>
-          <t>Höbrännflon, Jmt</t>
-        </is>
-      </c>
-      <c r="Q70" t="n">
-        <v>468900</v>
-      </c>
-      <c r="R70" t="n">
-        <v>7077908</v>
-      </c>
-      <c r="S70" t="n">
-        <v>10</v>
-      </c>
-      <c r="T70" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U70" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V70" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W70" t="inlineStr">
-        <is>
-          <t>Föllinge</t>
-        </is>
-      </c>
-      <c r="Y70" t="inlineStr">
-        <is>
-          <t>2026-07-14</t>
-        </is>
-      </c>
-      <c r="Z70" t="inlineStr">
-        <is>
-          <t>11:20</t>
-        </is>
-      </c>
-      <c r="AA70" t="inlineStr">
-        <is>
-          <t>2026-07-14</t>
-        </is>
-      </c>
-      <c r="AB70" t="inlineStr">
-        <is>
-          <t>11:20</t>
-        </is>
-      </c>
-      <c r="AC70" t="inlineStr">
-        <is>
-          <t>färska och äldre ringhack</t>
-        </is>
-      </c>
-      <c r="AD70" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE70" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG70" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT70" t="inlineStr"/>
-      <c r="AW70" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX70" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY70" t="inlineStr"/>
-      <c r="AZ70" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135192088</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="n">
-        <v>135192093</v>
-      </c>
-      <c r="B71" t="n">
-        <v>57993</v>
-      </c>
-      <c r="D71" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E71" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F71" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G71" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H71" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I71" t="inlineStr"/>
-      <c r="M71" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="P71" t="inlineStr">
-        <is>
-          <t>Höbrännflon, Jmt</t>
-        </is>
-      </c>
-      <c r="Q71" t="n">
-        <v>468841</v>
-      </c>
-      <c r="R71" t="n">
-        <v>7077895</v>
-      </c>
-      <c r="S71" t="n">
-        <v>10</v>
-      </c>
-      <c r="T71" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U71" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V71" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W71" t="inlineStr">
-        <is>
-          <t>Föllinge</t>
-        </is>
-      </c>
-      <c r="Y71" t="inlineStr">
-        <is>
-          <t>2026-07-14</t>
-        </is>
-      </c>
-      <c r="Z71" t="inlineStr">
-        <is>
-          <t>11:28</t>
-        </is>
-      </c>
-      <c r="AA71" t="inlineStr">
-        <is>
-          <t>2026-07-14</t>
-        </is>
-      </c>
-      <c r="AB71" t="inlineStr">
-        <is>
-          <t>11:28</t>
-        </is>
-      </c>
-      <c r="AC71" t="inlineStr">
-        <is>
-          <t>äldre ringhack</t>
-        </is>
-      </c>
-      <c r="AD71" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE71" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG71" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT71" t="inlineStr"/>
-      <c r="AW71" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX71" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY71" t="inlineStr"/>
-      <c r="AZ71" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135192093</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="n">
-        <v>135192095</v>
-      </c>
-      <c r="B72" t="n">
-        <v>57993</v>
-      </c>
-      <c r="D72" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E72" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F72" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G72" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H72" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I72" t="inlineStr"/>
-      <c r="M72" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="P72" t="inlineStr">
-        <is>
-          <t>Höbrännflon, Jmt</t>
-        </is>
-      </c>
-      <c r="Q72" t="n">
-        <v>468832</v>
-      </c>
-      <c r="R72" t="n">
-        <v>7077861</v>
-      </c>
-      <c r="S72" t="n">
-        <v>10</v>
-      </c>
-      <c r="T72" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U72" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V72" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W72" t="inlineStr">
-        <is>
-          <t>Föllinge</t>
-        </is>
-      </c>
-      <c r="Y72" t="inlineStr">
-        <is>
-          <t>2026-07-14</t>
-        </is>
-      </c>
-      <c r="Z72" t="inlineStr">
-        <is>
-          <t>11:32</t>
-        </is>
-      </c>
-      <c r="AA72" t="inlineStr">
-        <is>
-          <t>2026-07-14</t>
-        </is>
-      </c>
-      <c r="AB72" t="inlineStr">
-        <is>
-          <t>11:32</t>
-        </is>
-      </c>
-      <c r="AC72" t="inlineStr">
-        <is>
-          <t>äldre ringhack</t>
-        </is>
-      </c>
-      <c r="AD72" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE72" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG72" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT72" t="inlineStr"/>
-      <c r="AW72" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX72" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY72" t="inlineStr"/>
-      <c r="AZ72" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135192095</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="n">
-        <v>135192112</v>
-      </c>
-      <c r="B73" t="n">
-        <v>57993</v>
-      </c>
-      <c r="D73" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E73" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F73" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G73" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H73" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I73" t="inlineStr"/>
-      <c r="M73" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="P73" t="inlineStr">
-        <is>
-          <t>Höbrännflon, Jmt</t>
-        </is>
-      </c>
-      <c r="Q73" t="n">
-        <v>469029</v>
-      </c>
-      <c r="R73" t="n">
-        <v>7077764</v>
-      </c>
-      <c r="S73" t="n">
-        <v>10</v>
-      </c>
-      <c r="T73" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U73" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V73" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W73" t="inlineStr">
-        <is>
-          <t>Föllinge</t>
-        </is>
-      </c>
-      <c r="Y73" t="inlineStr">
-        <is>
-          <t>2026-07-14</t>
-        </is>
-      </c>
-      <c r="Z73" t="inlineStr">
-        <is>
-          <t>11:55</t>
-        </is>
-      </c>
-      <c r="AA73" t="inlineStr">
-        <is>
-          <t>2026-07-14</t>
-        </is>
-      </c>
-      <c r="AB73" t="inlineStr">
-        <is>
-          <t>11:55</t>
-        </is>
-      </c>
-      <c r="AC73" t="inlineStr">
-        <is>
-          <t>äldre ringhack</t>
-        </is>
-      </c>
-      <c r="AD73" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE73" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG73" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT73" t="inlineStr"/>
-      <c r="AW73" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX73" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY73" t="inlineStr"/>
-      <c r="AZ73" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135192112</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="n">
-        <v>135192116</v>
-      </c>
-      <c r="B74" t="n">
-        <v>57993</v>
-      </c>
-      <c r="D74" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E74" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F74" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G74" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H74" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I74" t="inlineStr"/>
-      <c r="M74" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="P74" t="inlineStr">
-        <is>
-          <t>Höbrännflon, Jmt</t>
-        </is>
-      </c>
-      <c r="Q74" t="n">
-        <v>469092</v>
-      </c>
-      <c r="R74" t="n">
-        <v>7077868</v>
-      </c>
-      <c r="S74" t="n">
-        <v>10</v>
-      </c>
-      <c r="T74" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U74" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V74" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W74" t="inlineStr">
-        <is>
-          <t>Föllinge</t>
-        </is>
-      </c>
-      <c r="Y74" t="inlineStr">
-        <is>
-          <t>2026-07-14</t>
-        </is>
-      </c>
-      <c r="Z74" t="inlineStr">
-        <is>
-          <t>12:02</t>
-        </is>
-      </c>
-      <c r="AA74" t="inlineStr">
-        <is>
-          <t>2026-07-14</t>
-        </is>
-      </c>
-      <c r="AB74" t="inlineStr">
-        <is>
-          <t>12:02</t>
-        </is>
-      </c>
-      <c r="AC74" t="inlineStr">
-        <is>
-          <t>äldre ringhack</t>
-        </is>
-      </c>
-      <c r="AD74" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE74" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG74" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT74" t="inlineStr"/>
-      <c r="AW74" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX74" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY74" t="inlineStr"/>
-      <c r="AZ74" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135192116</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="n">
-        <v>135192118</v>
-      </c>
-      <c r="B75" t="n">
-        <v>57993</v>
-      </c>
-      <c r="D75" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E75" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F75" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G75" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H75" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I75" t="inlineStr"/>
-      <c r="M75" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="P75" t="inlineStr">
-        <is>
-          <t>Höbrännflon, Jmt</t>
-        </is>
-      </c>
-      <c r="Q75" t="n">
-        <v>469121</v>
-      </c>
-      <c r="R75" t="n">
-        <v>7077852</v>
-      </c>
-      <c r="S75" t="n">
-        <v>10</v>
-      </c>
-      <c r="T75" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U75" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V75" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W75" t="inlineStr">
-        <is>
-          <t>Föllinge</t>
-        </is>
-      </c>
-      <c r="Y75" t="inlineStr">
-        <is>
-          <t>2026-07-14</t>
-        </is>
-      </c>
-      <c r="Z75" t="inlineStr">
-        <is>
-          <t>12:04</t>
-        </is>
-      </c>
-      <c r="AA75" t="inlineStr">
-        <is>
-          <t>2026-07-14</t>
-        </is>
-      </c>
-      <c r="AB75" t="inlineStr">
-        <is>
-          <t>12:04</t>
-        </is>
-      </c>
-      <c r="AC75" t="inlineStr">
-        <is>
-          <t>äldre ringhack</t>
-        </is>
-      </c>
-      <c r="AD75" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE75" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG75" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT75" t="inlineStr"/>
-      <c r="AW75" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX75" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY75" t="inlineStr"/>
-      <c r="AZ75" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135192118</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="n">
-        <v>135192119</v>
-      </c>
-      <c r="B76" t="n">
-        <v>57993</v>
-      </c>
-      <c r="D76" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E76" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F76" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G76" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H76" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I76" t="inlineStr"/>
-      <c r="M76" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="P76" t="inlineStr">
-        <is>
-          <t>Höbrännflon, Jmt</t>
-        </is>
-      </c>
-      <c r="Q76" t="n">
-        <v>469139</v>
-      </c>
-      <c r="R76" t="n">
-        <v>7077825</v>
-      </c>
-      <c r="S76" t="n">
-        <v>10</v>
-      </c>
-      <c r="T76" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U76" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V76" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W76" t="inlineStr">
-        <is>
-          <t>Föllinge</t>
-        </is>
-      </c>
-      <c r="Y76" t="inlineStr">
-        <is>
-          <t>2026-07-14</t>
-        </is>
-      </c>
-      <c r="Z76" t="inlineStr">
-        <is>
-          <t>12:07</t>
-        </is>
-      </c>
-      <c r="AA76" t="inlineStr">
-        <is>
-          <t>2026-07-14</t>
-        </is>
-      </c>
-      <c r="AB76" t="inlineStr">
-        <is>
-          <t>12:07</t>
-        </is>
-      </c>
-      <c r="AC76" t="inlineStr">
-        <is>
-          <t>äldre ringhack</t>
-        </is>
-      </c>
-      <c r="AD76" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE76" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG76" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT76" t="inlineStr"/>
-      <c r="AW76" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX76" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY76" t="inlineStr"/>
-      <c r="AZ76" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135192119</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="n">
-        <v>135192123</v>
-      </c>
-      <c r="B77" t="n">
-        <v>57993</v>
-      </c>
-      <c r="D77" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E77" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F77" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G77" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H77" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I77" t="inlineStr"/>
-      <c r="M77" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="P77" t="inlineStr">
-        <is>
-          <t>Höbrännflon, Jmt</t>
-        </is>
-      </c>
-      <c r="Q77" t="n">
-        <v>469108</v>
-      </c>
-      <c r="R77" t="n">
-        <v>7077950</v>
-      </c>
-      <c r="S77" t="n">
-        <v>10</v>
-      </c>
-      <c r="T77" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U77" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V77" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W77" t="inlineStr">
-        <is>
-          <t>Föllinge</t>
-        </is>
-      </c>
-      <c r="Y77" t="inlineStr">
-        <is>
-          <t>2026-07-14</t>
-        </is>
-      </c>
-      <c r="Z77" t="inlineStr">
-        <is>
-          <t>12:11</t>
-        </is>
-      </c>
-      <c r="AA77" t="inlineStr">
-        <is>
-          <t>2026-07-14</t>
-        </is>
-      </c>
-      <c r="AB77" t="inlineStr">
-        <is>
-          <t>12:11</t>
-        </is>
-      </c>
-      <c r="AC77" t="inlineStr">
-        <is>
-          <t>färska ringhack</t>
-        </is>
-      </c>
-      <c r="AD77" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE77" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG77" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT77" t="inlineStr"/>
-      <c r="AW77" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX77" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY77" t="inlineStr"/>
-      <c r="AZ77" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135192123</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="n">
-        <v>135192124</v>
-      </c>
-      <c r="B78" t="n">
-        <v>57993</v>
-      </c>
-      <c r="D78" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E78" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F78" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G78" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H78" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I78" t="inlineStr"/>
-      <c r="M78" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="P78" t="inlineStr">
-        <is>
-          <t>Höbrännflon, Jmt</t>
-        </is>
-      </c>
-      <c r="Q78" t="n">
-        <v>469109</v>
-      </c>
-      <c r="R78" t="n">
-        <v>7077945</v>
-      </c>
-      <c r="S78" t="n">
-        <v>10</v>
-      </c>
-      <c r="T78" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U78" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V78" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W78" t="inlineStr">
-        <is>
-          <t>Föllinge</t>
-        </is>
-      </c>
-      <c r="Y78" t="inlineStr">
-        <is>
-          <t>2026-07-14</t>
-        </is>
-      </c>
-      <c r="Z78" t="inlineStr">
-        <is>
-          <t>12:12</t>
-        </is>
-      </c>
-      <c r="AA78" t="inlineStr">
-        <is>
-          <t>2026-07-14</t>
-        </is>
-      </c>
-      <c r="AB78" t="inlineStr">
-        <is>
-          <t>12:12</t>
-        </is>
-      </c>
-      <c r="AC78" t="inlineStr">
-        <is>
-          <t>färska ringhack</t>
-        </is>
-      </c>
-      <c r="AD78" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE78" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG78" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT78" t="inlineStr"/>
-      <c r="AW78" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX78" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY78" t="inlineStr"/>
-      <c r="AZ78" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135192124</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="n">
-        <v>135192125</v>
-      </c>
-      <c r="B79" t="n">
-        <v>57993</v>
-      </c>
-      <c r="D79" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E79" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F79" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G79" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H79" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I79" t="inlineStr"/>
-      <c r="M79" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="P79" t="inlineStr">
-        <is>
-          <t>Höbrännflon, Jmt</t>
-        </is>
-      </c>
-      <c r="Q79" t="n">
-        <v>469118</v>
-      </c>
-      <c r="R79" t="n">
-        <v>7077938</v>
-      </c>
-      <c r="S79" t="n">
-        <v>10</v>
-      </c>
-      <c r="T79" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U79" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V79" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W79" t="inlineStr">
-        <is>
-          <t>Föllinge</t>
-        </is>
-      </c>
-      <c r="Y79" t="inlineStr">
-        <is>
-          <t>2026-07-14</t>
-        </is>
-      </c>
-      <c r="Z79" t="inlineStr">
-        <is>
-          <t>12:12</t>
-        </is>
-      </c>
-      <c r="AA79" t="inlineStr">
-        <is>
-          <t>2026-07-14</t>
-        </is>
-      </c>
-      <c r="AB79" t="inlineStr">
-        <is>
-          <t>12:12</t>
-        </is>
-      </c>
-      <c r="AC79" t="inlineStr">
-        <is>
-          <t>färska ringhack</t>
-        </is>
-      </c>
-      <c r="AD79" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE79" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG79" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT79" t="inlineStr"/>
-      <c r="AW79" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX79" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY79" t="inlineStr"/>
-      <c r="AZ79" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135192125</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="n">
-        <v>135192127</v>
-      </c>
-      <c r="B80" t="n">
-        <v>57993</v>
-      </c>
-      <c r="D80" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E80" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F80" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G80" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H80" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I80" t="inlineStr"/>
-      <c r="M80" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="P80" t="inlineStr">
-        <is>
-          <t>Höbrännflon, Jmt</t>
-        </is>
-      </c>
-      <c r="Q80" t="n">
-        <v>469140</v>
-      </c>
-      <c r="R80" t="n">
-        <v>7077913</v>
-      </c>
-      <c r="S80" t="n">
-        <v>10</v>
-      </c>
-      <c r="T80" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U80" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V80" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W80" t="inlineStr">
-        <is>
-          <t>Föllinge</t>
-        </is>
-      </c>
-      <c r="Y80" t="inlineStr">
-        <is>
-          <t>2026-07-14</t>
-        </is>
-      </c>
-      <c r="Z80" t="inlineStr">
-        <is>
-          <t>12:13</t>
-        </is>
-      </c>
-      <c r="AA80" t="inlineStr">
-        <is>
-          <t>2026-07-14</t>
-        </is>
-      </c>
-      <c r="AB80" t="inlineStr">
-        <is>
-          <t>12:13</t>
-        </is>
-      </c>
-      <c r="AC80" t="inlineStr">
-        <is>
-          <t>färska ringhack</t>
-        </is>
-      </c>
-      <c r="AD80" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE80" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG80" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT80" t="inlineStr"/>
-      <c r="AW80" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX80" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY80" t="inlineStr"/>
-      <c r="AZ80" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135192127</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="n">
-        <v>135192128</v>
-      </c>
-      <c r="B81" t="n">
-        <v>57993</v>
-      </c>
-      <c r="D81" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E81" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F81" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G81" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H81" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I81" t="inlineStr"/>
-      <c r="M81" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="P81" t="inlineStr">
-        <is>
-          <t>Höbrännflon, Jmt</t>
-        </is>
-      </c>
-      <c r="Q81" t="n">
-        <v>469149</v>
-      </c>
-      <c r="R81" t="n">
-        <v>7077895</v>
-      </c>
-      <c r="S81" t="n">
-        <v>10</v>
-      </c>
-      <c r="T81" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U81" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V81" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W81" t="inlineStr">
-        <is>
-          <t>Föllinge</t>
-        </is>
-      </c>
-      <c r="Y81" t="inlineStr">
-        <is>
-          <t>2026-07-14</t>
-        </is>
-      </c>
-      <c r="Z81" t="inlineStr">
-        <is>
-          <t>12:14</t>
-        </is>
-      </c>
-      <c r="AA81" t="inlineStr">
-        <is>
-          <t>2026-07-14</t>
-        </is>
-      </c>
-      <c r="AB81" t="inlineStr">
-        <is>
-          <t>12:14</t>
-        </is>
-      </c>
-      <c r="AC81" t="inlineStr">
-        <is>
-          <t>färska ringhack</t>
-        </is>
-      </c>
-      <c r="AD81" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE81" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG81" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT81" t="inlineStr"/>
-      <c r="AW81" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX81" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY81" t="inlineStr"/>
-      <c r="AZ81" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135192128</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="n">
-        <v>135192130</v>
-      </c>
-      <c r="B82" t="n">
-        <v>57993</v>
-      </c>
-      <c r="D82" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E82" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F82" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G82" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H82" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I82" t="inlineStr"/>
-      <c r="M82" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="P82" t="inlineStr">
-        <is>
-          <t>Höbrännflon, Jmt</t>
-        </is>
-      </c>
-      <c r="Q82" t="n">
-        <v>469158</v>
-      </c>
-      <c r="R82" t="n">
-        <v>7077852</v>
-      </c>
-      <c r="S82" t="n">
-        <v>10</v>
-      </c>
-      <c r="T82" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U82" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V82" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W82" t="inlineStr">
-        <is>
-          <t>Föllinge</t>
-        </is>
-      </c>
-      <c r="Y82" t="inlineStr">
-        <is>
-          <t>2026-07-14</t>
-        </is>
-      </c>
-      <c r="Z82" t="inlineStr">
-        <is>
-          <t>12:15</t>
-        </is>
-      </c>
-      <c r="AA82" t="inlineStr">
-        <is>
-          <t>2026-07-14</t>
-        </is>
-      </c>
-      <c r="AB82" t="inlineStr">
-        <is>
-          <t>12:15</t>
-        </is>
-      </c>
-      <c r="AC82" t="inlineStr">
-        <is>
-          <t>färska ringhack</t>
-        </is>
-      </c>
-      <c r="AD82" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE82" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG82" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT82" t="inlineStr"/>
-      <c r="AW82" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX82" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY82" t="inlineStr"/>
-      <c r="AZ82" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135192130</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="n">
-        <v>135192131</v>
-      </c>
-      <c r="B83" t="n">
-        <v>57993</v>
-      </c>
-      <c r="D83" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E83" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F83" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G83" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H83" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I83" t="inlineStr"/>
-      <c r="M83" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="P83" t="inlineStr">
-        <is>
-          <t>Höbrännflon, Jmt</t>
-        </is>
-      </c>
-      <c r="Q83" t="n">
-        <v>469166</v>
-      </c>
-      <c r="R83" t="n">
-        <v>7077841</v>
-      </c>
-      <c r="S83" t="n">
-        <v>10</v>
-      </c>
-      <c r="T83" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U83" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V83" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W83" t="inlineStr">
-        <is>
-          <t>Föllinge</t>
-        </is>
-      </c>
-      <c r="Y83" t="inlineStr">
-        <is>
-          <t>2026-07-14</t>
-        </is>
-      </c>
-      <c r="Z83" t="inlineStr">
-        <is>
-          <t>12:16</t>
-        </is>
-      </c>
-      <c r="AA83" t="inlineStr">
-        <is>
-          <t>2026-07-14</t>
-        </is>
-      </c>
-      <c r="AB83" t="inlineStr">
-        <is>
-          <t>12:16</t>
-        </is>
-      </c>
-      <c r="AC83" t="inlineStr">
-        <is>
-          <t>färska ringhack</t>
-        </is>
-      </c>
-      <c r="AD83" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE83" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG83" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT83" t="inlineStr"/>
-      <c r="AW83" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX83" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY83" t="inlineStr"/>
-      <c r="AZ83" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135192131</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="n">
-        <v>135192132</v>
-      </c>
-      <c r="B84" t="n">
-        <v>57993</v>
-      </c>
-      <c r="D84" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E84" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F84" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G84" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H84" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I84" t="inlineStr"/>
-      <c r="M84" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="P84" t="inlineStr">
-        <is>
-          <t>Höbrännflon, Jmt</t>
-        </is>
-      </c>
-      <c r="Q84" t="n">
-        <v>469163</v>
-      </c>
-      <c r="R84" t="n">
-        <v>7077822</v>
-      </c>
-      <c r="S84" t="n">
-        <v>10</v>
-      </c>
-      <c r="T84" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U84" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V84" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W84" t="inlineStr">
-        <is>
-          <t>Föllinge</t>
-        </is>
-      </c>
-      <c r="Y84" t="inlineStr">
-        <is>
-          <t>2026-07-14</t>
-        </is>
-      </c>
-      <c r="Z84" t="inlineStr">
-        <is>
-          <t>12:17</t>
-        </is>
-      </c>
-      <c r="AA84" t="inlineStr">
-        <is>
-          <t>2026-07-14</t>
-        </is>
-      </c>
-      <c r="AB84" t="inlineStr">
-        <is>
-          <t>12:17</t>
-        </is>
-      </c>
-      <c r="AC84" t="inlineStr">
-        <is>
-          <t>färska ringhack</t>
-        </is>
-      </c>
-      <c r="AD84" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE84" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG84" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT84" t="inlineStr"/>
-      <c r="AW84" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX84" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY84" t="inlineStr"/>
-      <c r="AZ84" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135192132</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="n">
-        <v>135192134</v>
-      </c>
-      <c r="B85" t="n">
-        <v>57993</v>
-      </c>
-      <c r="D85" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E85" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F85" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G85" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H85" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I85" t="inlineStr"/>
-      <c r="M85" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="P85" t="inlineStr">
-        <is>
-          <t>Höbrännflon, Jmt</t>
-        </is>
-      </c>
-      <c r="Q85" t="n">
-        <v>469172</v>
-      </c>
-      <c r="R85" t="n">
-        <v>7077811</v>
-      </c>
-      <c r="S85" t="n">
-        <v>10</v>
-      </c>
-      <c r="T85" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U85" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V85" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W85" t="inlineStr">
-        <is>
-          <t>Föllinge</t>
-        </is>
-      </c>
-      <c r="Y85" t="inlineStr">
-        <is>
-          <t>2026-07-14</t>
-        </is>
-      </c>
-      <c r="Z85" t="inlineStr">
-        <is>
-          <t>12:17</t>
-        </is>
-      </c>
-      <c r="AA85" t="inlineStr">
-        <is>
-          <t>2026-07-14</t>
-        </is>
-      </c>
-      <c r="AB85" t="inlineStr">
-        <is>
-          <t>12:17</t>
-        </is>
-      </c>
-      <c r="AC85" t="inlineStr">
-        <is>
-          <t>färska ringhack</t>
-        </is>
-      </c>
-      <c r="AD85" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE85" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG85" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT85" t="inlineStr"/>
-      <c r="AW85" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX85" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY85" t="inlineStr"/>
-      <c r="AZ85" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135192134</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="n">
-        <v>135192135</v>
-      </c>
-      <c r="B86" t="n">
-        <v>57993</v>
-      </c>
-      <c r="D86" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E86" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F86" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G86" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H86" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I86" t="inlineStr"/>
-      <c r="M86" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="P86" t="inlineStr">
-        <is>
-          <t>Höbrännflon, Jmt</t>
-        </is>
-      </c>
-      <c r="Q86" t="n">
-        <v>469180</v>
-      </c>
-      <c r="R86" t="n">
-        <v>7077818</v>
-      </c>
-      <c r="S86" t="n">
-        <v>10</v>
-      </c>
-      <c r="T86" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U86" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V86" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W86" t="inlineStr">
-        <is>
-          <t>Föllinge</t>
-        </is>
-      </c>
-      <c r="Y86" t="inlineStr">
-        <is>
-          <t>2026-07-14</t>
-        </is>
-      </c>
-      <c r="Z86" t="inlineStr">
-        <is>
-          <t>12:18</t>
-        </is>
-      </c>
-      <c r="AA86" t="inlineStr">
-        <is>
-          <t>2026-07-14</t>
-        </is>
-      </c>
-      <c r="AB86" t="inlineStr">
-        <is>
-          <t>12:18</t>
-        </is>
-      </c>
-      <c r="AC86" t="inlineStr">
-        <is>
-          <t>äldre ringhack</t>
-        </is>
-      </c>
-      <c r="AD86" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE86" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG86" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT86" t="inlineStr"/>
-      <c r="AW86" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX86" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY86" t="inlineStr"/>
-      <c r="AZ86" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135192135</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="n">
-        <v>135192136</v>
-      </c>
-      <c r="B87" t="n">
-        <v>57993</v>
-      </c>
-      <c r="D87" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E87" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F87" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G87" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H87" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I87" t="inlineStr"/>
-      <c r="M87" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="P87" t="inlineStr">
-        <is>
-          <t>Höbrännflon, Jmt</t>
-        </is>
-      </c>
-      <c r="Q87" t="n">
-        <v>469176</v>
-      </c>
-      <c r="R87" t="n">
-        <v>7077799</v>
-      </c>
-      <c r="S87" t="n">
-        <v>10</v>
-      </c>
-      <c r="T87" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U87" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V87" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W87" t="inlineStr">
-        <is>
-          <t>Föllinge</t>
-        </is>
-      </c>
-      <c r="Y87" t="inlineStr">
-        <is>
-          <t>2026-07-14</t>
-        </is>
-      </c>
-      <c r="Z87" t="inlineStr">
-        <is>
-          <t>12:19</t>
-        </is>
-      </c>
-      <c r="AA87" t="inlineStr">
-        <is>
-          <t>2026-07-14</t>
-        </is>
-      </c>
-      <c r="AB87" t="inlineStr">
-        <is>
-          <t>12:19</t>
-        </is>
-      </c>
-      <c r="AC87" t="inlineStr">
-        <is>
-          <t>färska ringhack</t>
-        </is>
-      </c>
-      <c r="AD87" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE87" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG87" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT87" t="inlineStr"/>
-      <c r="AW87" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX87" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY87" t="inlineStr"/>
-      <c r="AZ87" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135192136</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="n">
-        <v>135192137</v>
-      </c>
-      <c r="B88" t="n">
-        <v>57993</v>
-      </c>
-      <c r="D88" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E88" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F88" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G88" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H88" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I88" t="inlineStr"/>
-      <c r="M88" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="P88" t="inlineStr">
-        <is>
-          <t>Höbrännflon, Jmt</t>
-        </is>
-      </c>
-      <c r="Q88" t="n">
-        <v>469181</v>
-      </c>
-      <c r="R88" t="n">
-        <v>7077798</v>
-      </c>
-      <c r="S88" t="n">
-        <v>10</v>
-      </c>
-      <c r="T88" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U88" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V88" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W88" t="inlineStr">
-        <is>
-          <t>Föllinge</t>
-        </is>
-      </c>
-      <c r="Y88" t="inlineStr">
-        <is>
-          <t>2026-07-14</t>
-        </is>
-      </c>
-      <c r="Z88" t="inlineStr">
-        <is>
-          <t>12:20</t>
-        </is>
-      </c>
-      <c r="AA88" t="inlineStr">
-        <is>
-          <t>2026-07-14</t>
-        </is>
-      </c>
-      <c r="AB88" t="inlineStr">
-        <is>
-          <t>12:20</t>
-        </is>
-      </c>
-      <c r="AC88" t="inlineStr">
-        <is>
-          <t>färska ringhack</t>
-        </is>
-      </c>
-      <c r="AD88" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE88" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG88" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT88" t="inlineStr"/>
-      <c r="AW88" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX88" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY88" t="inlineStr"/>
-      <c r="AZ88" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135192137</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="n">
-        <v>135192151</v>
-      </c>
-      <c r="B89" t="n">
-        <v>57993</v>
-      </c>
-      <c r="D89" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E89" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F89" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G89" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H89" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I89" t="inlineStr"/>
-      <c r="M89" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="P89" t="inlineStr">
-        <is>
-          <t>Höbrännflon, Jmt</t>
-        </is>
-      </c>
-      <c r="Q89" t="n">
-        <v>469393</v>
-      </c>
-      <c r="R89" t="n">
-        <v>7077846</v>
-      </c>
-      <c r="S89" t="n">
-        <v>10</v>
-      </c>
-      <c r="T89" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U89" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V89" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W89" t="inlineStr">
-        <is>
-          <t>Föllinge</t>
-        </is>
-      </c>
-      <c r="Y89" t="inlineStr">
-        <is>
-          <t>2026-07-14</t>
-        </is>
-      </c>
-      <c r="Z89" t="inlineStr">
-        <is>
-          <t>12:42</t>
-        </is>
-      </c>
-      <c r="AA89" t="inlineStr">
-        <is>
-          <t>2026-07-14</t>
-        </is>
-      </c>
-      <c r="AB89" t="inlineStr">
-        <is>
-          <t>12:42</t>
-        </is>
-      </c>
-      <c r="AC89" t="inlineStr">
-        <is>
-          <t>äldre ringhack</t>
-        </is>
-      </c>
-      <c r="AD89" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE89" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG89" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT89" t="inlineStr"/>
-      <c r="AW89" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX89" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY89" t="inlineStr"/>
-      <c r="AZ89" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135192151</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="n">
-        <v>135192152</v>
-      </c>
-      <c r="B90" t="n">
-        <v>57993</v>
-      </c>
-      <c r="D90" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E90" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F90" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G90" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H90" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I90" t="inlineStr"/>
-      <c r="M90" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="P90" t="inlineStr">
-        <is>
-          <t>Höbrännflon, Jmt</t>
-        </is>
-      </c>
-      <c r="Q90" t="n">
-        <v>469356</v>
-      </c>
-      <c r="R90" t="n">
-        <v>7077867</v>
-      </c>
-      <c r="S90" t="n">
-        <v>10</v>
-      </c>
-      <c r="T90" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U90" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V90" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W90" t="inlineStr">
-        <is>
-          <t>Föllinge</t>
-        </is>
-      </c>
-      <c r="Y90" t="inlineStr">
-        <is>
-          <t>2026-07-14</t>
-        </is>
-      </c>
-      <c r="Z90" t="inlineStr">
-        <is>
-          <t>12:45</t>
-        </is>
-      </c>
-      <c r="AA90" t="inlineStr">
-        <is>
-          <t>2026-07-14</t>
-        </is>
-      </c>
-      <c r="AB90" t="inlineStr">
-        <is>
-          <t>12:45</t>
-        </is>
-      </c>
-      <c r="AC90" t="inlineStr">
-        <is>
-          <t>äldre ringhack</t>
-        </is>
-      </c>
-      <c r="AD90" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE90" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG90" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT90" t="inlineStr"/>
-      <c r="AW90" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX90" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY90" t="inlineStr"/>
-      <c r="AZ90" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135192152</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="n">
-        <v>135192153</v>
-      </c>
-      <c r="B91" t="n">
-        <v>57993</v>
-      </c>
-      <c r="D91" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E91" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F91" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G91" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H91" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I91" t="inlineStr"/>
-      <c r="M91" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="P91" t="inlineStr">
-        <is>
-          <t>Höbrännflon, Jmt</t>
-        </is>
-      </c>
-      <c r="Q91" t="n">
-        <v>469347</v>
-      </c>
-      <c r="R91" t="n">
-        <v>7077869</v>
-      </c>
-      <c r="S91" t="n">
-        <v>10</v>
-      </c>
-      <c r="T91" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U91" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V91" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W91" t="inlineStr">
-        <is>
-          <t>Föllinge</t>
-        </is>
-      </c>
-      <c r="Y91" t="inlineStr">
-        <is>
-          <t>2026-07-14</t>
-        </is>
-      </c>
-      <c r="Z91" t="inlineStr">
-        <is>
-          <t>12:46</t>
-        </is>
-      </c>
-      <c r="AA91" t="inlineStr">
-        <is>
-          <t>2026-07-14</t>
-        </is>
-      </c>
-      <c r="AB91" t="inlineStr">
-        <is>
-          <t>12:46</t>
-        </is>
-      </c>
-      <c r="AC91" t="inlineStr">
-        <is>
-          <t>äldre ringhack</t>
-        </is>
-      </c>
-      <c r="AD91" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE91" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG91" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT91" t="inlineStr"/>
-      <c r="AW91" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX91" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY91" t="inlineStr"/>
-      <c r="AZ91" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135192153</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="n">
-        <v>135192157</v>
-      </c>
-      <c r="B92" t="n">
-        <v>57993</v>
-      </c>
-      <c r="D92" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E92" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F92" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G92" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H92" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I92" t="inlineStr"/>
-      <c r="M92" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="P92" t="inlineStr">
-        <is>
-          <t>Höbrännflon, Jmt</t>
-        </is>
-      </c>
-      <c r="Q92" t="n">
-        <v>469381</v>
-      </c>
-      <c r="R92" t="n">
-        <v>7077873</v>
-      </c>
-      <c r="S92" t="n">
-        <v>10</v>
-      </c>
-      <c r="T92" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U92" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V92" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W92" t="inlineStr">
-        <is>
-          <t>Föllinge</t>
-        </is>
-      </c>
-      <c r="Y92" t="inlineStr">
-        <is>
-          <t>2026-07-14</t>
-        </is>
-      </c>
-      <c r="Z92" t="inlineStr">
-        <is>
-          <t>12:52</t>
-        </is>
-      </c>
-      <c r="AA92" t="inlineStr">
-        <is>
-          <t>2026-07-14</t>
-        </is>
-      </c>
-      <c r="AB92" t="inlineStr">
-        <is>
-          <t>12:52</t>
-        </is>
-      </c>
-      <c r="AC92" t="inlineStr">
-        <is>
-          <t>äldre ringhack</t>
-        </is>
-      </c>
-      <c r="AD92" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE92" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG92" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT92" t="inlineStr"/>
-      <c r="AW92" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX92" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY92" t="inlineStr"/>
-      <c r="AZ92" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135192157</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="n">
-        <v>135192158</v>
-      </c>
-      <c r="B93" t="n">
-        <v>57993</v>
-      </c>
-      <c r="D93" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E93" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F93" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G93" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H93" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I93" t="inlineStr"/>
-      <c r="M93" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="P93" t="inlineStr">
-        <is>
-          <t>Höbrännflon, Jmt</t>
-        </is>
-      </c>
-      <c r="Q93" t="n">
-        <v>469401</v>
-      </c>
-      <c r="R93" t="n">
-        <v>7077887</v>
-      </c>
-      <c r="S93" t="n">
-        <v>10</v>
-      </c>
-      <c r="T93" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U93" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V93" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W93" t="inlineStr">
-        <is>
-          <t>Föllinge</t>
-        </is>
-      </c>
-      <c r="Y93" t="inlineStr">
-        <is>
-          <t>2026-07-14</t>
-        </is>
-      </c>
-      <c r="Z93" t="inlineStr">
-        <is>
-          <t>12:54</t>
-        </is>
-      </c>
-      <c r="AA93" t="inlineStr">
-        <is>
-          <t>2026-07-14</t>
-        </is>
-      </c>
-      <c r="AB93" t="inlineStr">
-        <is>
-          <t>12:54</t>
-        </is>
-      </c>
-      <c r="AC93" t="inlineStr">
-        <is>
-          <t>äldre ringhack</t>
-        </is>
-      </c>
-      <c r="AD93" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE93" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG93" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT93" t="inlineStr"/>
-      <c r="AW93" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX93" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY93" t="inlineStr"/>
-      <c r="AZ93" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135192158</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="n">
-        <v>135192161</v>
-      </c>
-      <c r="B94" t="n">
-        <v>57993</v>
-      </c>
-      <c r="D94" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E94" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F94" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G94" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H94" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I94" t="inlineStr"/>
-      <c r="M94" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="P94" t="inlineStr">
-        <is>
-          <t>Höbrännflon, Jmt</t>
-        </is>
-      </c>
-      <c r="Q94" t="n">
-        <v>469388</v>
-      </c>
-      <c r="R94" t="n">
-        <v>7077920</v>
-      </c>
-      <c r="S94" t="n">
-        <v>10</v>
-      </c>
-      <c r="T94" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U94" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V94" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W94" t="inlineStr">
-        <is>
-          <t>Föllinge</t>
-        </is>
-      </c>
-      <c r="Y94" t="inlineStr">
-        <is>
-          <t>2026-07-14</t>
-        </is>
-      </c>
-      <c r="Z94" t="inlineStr">
-        <is>
-          <t>12:56</t>
-        </is>
-      </c>
-      <c r="AA94" t="inlineStr">
-        <is>
-          <t>2026-07-14</t>
-        </is>
-      </c>
-      <c r="AB94" t="inlineStr">
-        <is>
-          <t>12:56</t>
-        </is>
-      </c>
-      <c r="AC94" t="inlineStr">
-        <is>
-          <t>äldre ringhack</t>
-        </is>
-      </c>
-      <c r="AD94" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE94" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG94" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT94" t="inlineStr"/>
-      <c r="AW94" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX94" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY94" t="inlineStr"/>
-      <c r="AZ94" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135192161</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="n">
-        <v>135192166</v>
-      </c>
-      <c r="B95" t="n">
-        <v>57993</v>
-      </c>
-      <c r="D95" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E95" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F95" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G95" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H95" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I95" t="inlineStr"/>
-      <c r="P95" t="inlineStr">
-        <is>
-          <t>Höbrännflon, Jmt</t>
-        </is>
-      </c>
-      <c r="Q95" t="n">
-        <v>469249</v>
-      </c>
-      <c r="R95" t="n">
-        <v>7077922</v>
-      </c>
-      <c r="S95" t="n">
-        <v>10</v>
-      </c>
-      <c r="T95" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U95" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V95" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W95" t="inlineStr">
-        <is>
-          <t>Föllinge</t>
-        </is>
-      </c>
-      <c r="Y95" t="inlineStr">
-        <is>
-          <t>2026-07-14</t>
-        </is>
-      </c>
-      <c r="Z95" t="inlineStr">
-        <is>
-          <t>13:07</t>
-        </is>
-      </c>
-      <c r="AA95" t="inlineStr">
-        <is>
-          <t>2026-07-14</t>
-        </is>
-      </c>
-      <c r="AB95" t="inlineStr">
-        <is>
-          <t>13:07</t>
-        </is>
-      </c>
-      <c r="AC95" t="inlineStr">
-        <is>
-          <t>ringhack</t>
-        </is>
-      </c>
-      <c r="AD95" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE95" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG95" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT95" t="inlineStr"/>
-      <c r="AW95" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX95" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY95" t="inlineStr"/>
-      <c r="AZ95" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135192166</t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="n">
-        <v>128346628</v>
-      </c>
-      <c r="B96" t="n">
-        <v>97989</v>
-      </c>
-      <c r="D96" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E96" t="n">
-        <v>221941</v>
-      </c>
-      <c r="F96" t="inlineStr">
-        <is>
-          <t>Plattlummer</t>
-        </is>
-      </c>
-      <c r="G96" t="inlineStr">
-        <is>
-          <t>Lycopodium complanatum</t>
-        </is>
-      </c>
-      <c r="H96" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I96" t="inlineStr"/>
-      <c r="P96" t="inlineStr">
-        <is>
-          <t>Höbrännflon sö, Jmt</t>
-        </is>
-      </c>
-      <c r="Q96" t="n">
-        <v>468931</v>
-      </c>
-      <c r="R96" t="n">
-        <v>7077743</v>
-      </c>
-      <c r="S96" t="n">
-        <v>10</v>
-      </c>
-      <c r="T96" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U96" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V96" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W96" t="inlineStr">
-        <is>
-          <t>Föllinge</t>
-        </is>
-      </c>
-      <c r="Y96" t="inlineStr">
-        <is>
-          <t>2025-09-09</t>
-        </is>
-      </c>
-      <c r="AA96" t="inlineStr">
-        <is>
-          <t>2025-09-09</t>
-        </is>
-      </c>
-      <c r="AD96" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE96" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG96" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT96" t="inlineStr"/>
-      <c r="AW96" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX96" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY96" t="inlineStr"/>
-      <c r="AZ96" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/128346628</t>
         </is>
@@ -11663,44 +7037,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ87" r:id="rId86"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ88" r:id="rId87"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ89" r:id="rId88"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ90" r:id="rId89"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ91" r:id="rId90"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ92" r:id="rId91"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ93" r:id="rId92"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ94" r:id="rId93"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ95" r:id="rId94"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ96" r:id="rId95"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 28940-2026 artfynd.xlsx
+++ b/artfynd/A 28940-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ58"/>
+  <dimension ref="A1:AZ96"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6878,45 +6878,50 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128346628</v>
+        <v>135192022</v>
       </c>
       <c r="B58" t="n">
-        <v>97989</v>
+        <v>58006</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>221941</v>
+        <v>100109</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Höbrännflon sö, Jmt</t>
+          <t>Höbrännflon, Jmt</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>468931</v>
+        <v>469168</v>
       </c>
       <c r="R58" t="n">
-        <v>7077743</v>
+        <v>7078178</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6943,12 +6948,27 @@
       </c>
       <c r="Y58" t="inlineStr">
         <is>
-          <t>2025-09-09</t>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="Z58" t="inlineStr">
+        <is>
+          <t>09:29</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>2025-09-09</t>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="AB58" t="inlineStr">
+        <is>
+          <t>09:29</t>
+        </is>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>äldre ringhack</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6973,6 +6993,4612 @@
       </c>
       <c r="AY58" t="inlineStr"/>
       <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135192022</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>135192026</v>
+      </c>
+      <c r="B59" t="n">
+        <v>58006</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>Höbrännflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q59" t="n">
+        <v>469186</v>
+      </c>
+      <c r="R59" t="n">
+        <v>7078140</v>
+      </c>
+      <c r="S59" t="n">
+        <v>10</v>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="Z59" t="inlineStr">
+        <is>
+          <t>09:38</t>
+        </is>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="AB59" t="inlineStr">
+        <is>
+          <t>09:38</t>
+        </is>
+      </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>äldre ringhack</t>
+        </is>
+      </c>
+      <c r="AD59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT59" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX59" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135192026</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>135192030</v>
+      </c>
+      <c r="B60" t="n">
+        <v>58006</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>Höbrännflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q60" t="n">
+        <v>469177</v>
+      </c>
+      <c r="R60" t="n">
+        <v>7078094</v>
+      </c>
+      <c r="S60" t="n">
+        <v>10</v>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="Z60" t="inlineStr">
+        <is>
+          <t>09:48</t>
+        </is>
+      </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="AB60" t="inlineStr">
+        <is>
+          <t>09:48</t>
+        </is>
+      </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>äldre ringhack</t>
+        </is>
+      </c>
+      <c r="AD60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT60" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX60" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135192030</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>135192045</v>
+      </c>
+      <c r="B61" t="n">
+        <v>58006</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>Höbrännflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q61" t="n">
+        <v>468993</v>
+      </c>
+      <c r="R61" t="n">
+        <v>7078287</v>
+      </c>
+      <c r="S61" t="n">
+        <v>10</v>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y61" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="Z61" t="inlineStr">
+        <is>
+          <t>10:18</t>
+        </is>
+      </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="AB61" t="inlineStr">
+        <is>
+          <t>10:18</t>
+        </is>
+      </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>ringhack</t>
+        </is>
+      </c>
+      <c r="AD61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT61" t="inlineStr"/>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX61" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135192045</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>135192047</v>
+      </c>
+      <c r="B62" t="n">
+        <v>58006</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>Höbrännflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q62" t="n">
+        <v>468901</v>
+      </c>
+      <c r="R62" t="n">
+        <v>7078371</v>
+      </c>
+      <c r="S62" t="n">
+        <v>10</v>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="Z62" t="inlineStr">
+        <is>
+          <t>10:25</t>
+        </is>
+      </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="AB62" t="inlineStr">
+        <is>
+          <t>10:25</t>
+        </is>
+      </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>äldre ringhack</t>
+        </is>
+      </c>
+      <c r="AD62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT62" t="inlineStr"/>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX62" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135192047</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>135192048</v>
+      </c>
+      <c r="B63" t="n">
+        <v>58006</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>Höbrännflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q63" t="n">
+        <v>468891</v>
+      </c>
+      <c r="R63" t="n">
+        <v>7078390</v>
+      </c>
+      <c r="S63" t="n">
+        <v>10</v>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="Z63" t="inlineStr">
+        <is>
+          <t>10:28</t>
+        </is>
+      </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="AB63" t="inlineStr">
+        <is>
+          <t>10:28</t>
+        </is>
+      </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>färska o och äldre ringhack</t>
+        </is>
+      </c>
+      <c r="AD63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT63" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX63" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135192048</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>135192050</v>
+      </c>
+      <c r="B64" t="n">
+        <v>58006</v>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>Höbrännflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q64" t="n">
+        <v>468864</v>
+      </c>
+      <c r="R64" t="n">
+        <v>7078369</v>
+      </c>
+      <c r="S64" t="n">
+        <v>10</v>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="Z64" t="inlineStr">
+        <is>
+          <t>10:31</t>
+        </is>
+      </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="AB64" t="inlineStr">
+        <is>
+          <t>10:31</t>
+        </is>
+      </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>färska och äldre ringhack</t>
+        </is>
+      </c>
+      <c r="AD64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT64" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX64" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135192050</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>135192056</v>
+      </c>
+      <c r="B65" t="n">
+        <v>58006</v>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>Höbrännflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q65" t="n">
+        <v>468923</v>
+      </c>
+      <c r="R65" t="n">
+        <v>7078311</v>
+      </c>
+      <c r="S65" t="n">
+        <v>10</v>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y65" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="Z65" t="inlineStr">
+        <is>
+          <t>10:37</t>
+        </is>
+      </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="AB65" t="inlineStr">
+        <is>
+          <t>10:37</t>
+        </is>
+      </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>äldre ringhack</t>
+        </is>
+      </c>
+      <c r="AD65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT65" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX65" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135192056</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>135192074</v>
+      </c>
+      <c r="B66" t="n">
+        <v>58006</v>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>Höbrännflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q66" t="n">
+        <v>469051</v>
+      </c>
+      <c r="R66" t="n">
+        <v>7077912</v>
+      </c>
+      <c r="S66" t="n">
+        <v>10</v>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W66" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y66" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="Z66" t="inlineStr">
+        <is>
+          <t>11:05</t>
+        </is>
+      </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="AB66" t="inlineStr">
+        <is>
+          <t>11:05</t>
+        </is>
+      </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>äldre ringhack</t>
+        </is>
+      </c>
+      <c r="AD66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT66" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX66" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135192074</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>135192077</v>
+      </c>
+      <c r="B67" t="n">
+        <v>58006</v>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>Höbrännflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q67" t="n">
+        <v>469002</v>
+      </c>
+      <c r="R67" t="n">
+        <v>7077895</v>
+      </c>
+      <c r="S67" t="n">
+        <v>10</v>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W67" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y67" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="Z67" t="inlineStr">
+        <is>
+          <t>11:09</t>
+        </is>
+      </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="AB67" t="inlineStr">
+        <is>
+          <t>11:09</t>
+        </is>
+      </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>äldre ringhack</t>
+        </is>
+      </c>
+      <c r="AD67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT67" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX67" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135192077</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>135192079</v>
+      </c>
+      <c r="B68" t="n">
+        <v>58006</v>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr"/>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>Höbrännflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q68" t="n">
+        <v>469028</v>
+      </c>
+      <c r="R68" t="n">
+        <v>7077856</v>
+      </c>
+      <c r="S68" t="n">
+        <v>10</v>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W68" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y68" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="Z68" t="inlineStr">
+        <is>
+          <t>11:12</t>
+        </is>
+      </c>
+      <c r="AA68" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="AB68" t="inlineStr">
+        <is>
+          <t>11:12</t>
+        </is>
+      </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>äldre ringhack</t>
+        </is>
+      </c>
+      <c r="AD68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT68" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX68" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135192079</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>135192085</v>
+      </c>
+      <c r="B69" t="n">
+        <v>58006</v>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>Höbrännflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q69" t="n">
+        <v>468941</v>
+      </c>
+      <c r="R69" t="n">
+        <v>7077921</v>
+      </c>
+      <c r="S69" t="n">
+        <v>10</v>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W69" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y69" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="Z69" t="inlineStr">
+        <is>
+          <t>11:18</t>
+        </is>
+      </c>
+      <c r="AA69" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="AB69" t="inlineStr">
+        <is>
+          <t>11:18</t>
+        </is>
+      </c>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>äldre ringhack</t>
+        </is>
+      </c>
+      <c r="AD69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT69" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX69" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135192085</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>135192088</v>
+      </c>
+      <c r="B70" t="n">
+        <v>58006</v>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>Höbrännflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q70" t="n">
+        <v>468900</v>
+      </c>
+      <c r="R70" t="n">
+        <v>7077908</v>
+      </c>
+      <c r="S70" t="n">
+        <v>10</v>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W70" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y70" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="Z70" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="AA70" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="AB70" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="AC70" t="inlineStr">
+        <is>
+          <t>färska och äldre ringhack</t>
+        </is>
+      </c>
+      <c r="AD70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT70" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX70" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135192088</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>135192093</v>
+      </c>
+      <c r="B71" t="n">
+        <v>58006</v>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr"/>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>Höbrännflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q71" t="n">
+        <v>468841</v>
+      </c>
+      <c r="R71" t="n">
+        <v>7077895</v>
+      </c>
+      <c r="S71" t="n">
+        <v>10</v>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W71" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y71" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="Z71" t="inlineStr">
+        <is>
+          <t>11:28</t>
+        </is>
+      </c>
+      <c r="AA71" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="AB71" t="inlineStr">
+        <is>
+          <t>11:28</t>
+        </is>
+      </c>
+      <c r="AC71" t="inlineStr">
+        <is>
+          <t>äldre ringhack</t>
+        </is>
+      </c>
+      <c r="AD71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT71" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX71" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135192093</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>135192095</v>
+      </c>
+      <c r="B72" t="n">
+        <v>58006</v>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr"/>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>Höbrännflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q72" t="n">
+        <v>468832</v>
+      </c>
+      <c r="R72" t="n">
+        <v>7077861</v>
+      </c>
+      <c r="S72" t="n">
+        <v>10</v>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V72" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W72" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y72" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="Z72" t="inlineStr">
+        <is>
+          <t>11:32</t>
+        </is>
+      </c>
+      <c r="AA72" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="AB72" t="inlineStr">
+        <is>
+          <t>11:32</t>
+        </is>
+      </c>
+      <c r="AC72" t="inlineStr">
+        <is>
+          <t>äldre ringhack</t>
+        </is>
+      </c>
+      <c r="AD72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT72" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX72" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135192095</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>135192112</v>
+      </c>
+      <c r="B73" t="n">
+        <v>58006</v>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E73" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr"/>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>Höbrännflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q73" t="n">
+        <v>469029</v>
+      </c>
+      <c r="R73" t="n">
+        <v>7077764</v>
+      </c>
+      <c r="S73" t="n">
+        <v>10</v>
+      </c>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V73" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W73" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y73" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="Z73" t="inlineStr">
+        <is>
+          <t>11:55</t>
+        </is>
+      </c>
+      <c r="AA73" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="AB73" t="inlineStr">
+        <is>
+          <t>11:55</t>
+        </is>
+      </c>
+      <c r="AC73" t="inlineStr">
+        <is>
+          <t>äldre ringhack</t>
+        </is>
+      </c>
+      <c r="AD73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT73" t="inlineStr"/>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX73" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY73" t="inlineStr"/>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135192112</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>135192116</v>
+      </c>
+      <c r="B74" t="n">
+        <v>58006</v>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E74" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr"/>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>Höbrännflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q74" t="n">
+        <v>469092</v>
+      </c>
+      <c r="R74" t="n">
+        <v>7077868</v>
+      </c>
+      <c r="S74" t="n">
+        <v>10</v>
+      </c>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V74" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W74" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y74" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="Z74" t="inlineStr">
+        <is>
+          <t>12:02</t>
+        </is>
+      </c>
+      <c r="AA74" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="AB74" t="inlineStr">
+        <is>
+          <t>12:02</t>
+        </is>
+      </c>
+      <c r="AC74" t="inlineStr">
+        <is>
+          <t>äldre ringhack</t>
+        </is>
+      </c>
+      <c r="AD74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT74" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX74" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY74" t="inlineStr"/>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135192116</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>135192118</v>
+      </c>
+      <c r="B75" t="n">
+        <v>58006</v>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E75" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr"/>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t>Höbrännflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q75" t="n">
+        <v>469121</v>
+      </c>
+      <c r="R75" t="n">
+        <v>7077852</v>
+      </c>
+      <c r="S75" t="n">
+        <v>10</v>
+      </c>
+      <c r="T75" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U75" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V75" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W75" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y75" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="Z75" t="inlineStr">
+        <is>
+          <t>12:04</t>
+        </is>
+      </c>
+      <c r="AA75" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="AB75" t="inlineStr">
+        <is>
+          <t>12:04</t>
+        </is>
+      </c>
+      <c r="AC75" t="inlineStr">
+        <is>
+          <t>äldre ringhack</t>
+        </is>
+      </c>
+      <c r="AD75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT75" t="inlineStr"/>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX75" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY75" t="inlineStr"/>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135192118</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>135192119</v>
+      </c>
+      <c r="B76" t="n">
+        <v>58006</v>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E76" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr"/>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t>Höbrännflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q76" t="n">
+        <v>469139</v>
+      </c>
+      <c r="R76" t="n">
+        <v>7077825</v>
+      </c>
+      <c r="S76" t="n">
+        <v>10</v>
+      </c>
+      <c r="T76" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U76" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V76" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W76" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y76" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="Z76" t="inlineStr">
+        <is>
+          <t>12:07</t>
+        </is>
+      </c>
+      <c r="AA76" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="AB76" t="inlineStr">
+        <is>
+          <t>12:07</t>
+        </is>
+      </c>
+      <c r="AC76" t="inlineStr">
+        <is>
+          <t>äldre ringhack</t>
+        </is>
+      </c>
+      <c r="AD76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT76" t="inlineStr"/>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX76" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY76" t="inlineStr"/>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135192119</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>135192123</v>
+      </c>
+      <c r="B77" t="n">
+        <v>58006</v>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E77" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr"/>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P77" t="inlineStr">
+        <is>
+          <t>Höbrännflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q77" t="n">
+        <v>469108</v>
+      </c>
+      <c r="R77" t="n">
+        <v>7077950</v>
+      </c>
+      <c r="S77" t="n">
+        <v>10</v>
+      </c>
+      <c r="T77" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U77" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V77" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W77" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y77" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="Z77" t="inlineStr">
+        <is>
+          <t>12:11</t>
+        </is>
+      </c>
+      <c r="AA77" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="AB77" t="inlineStr">
+        <is>
+          <t>12:11</t>
+        </is>
+      </c>
+      <c r="AC77" t="inlineStr">
+        <is>
+          <t>färska ringhack</t>
+        </is>
+      </c>
+      <c r="AD77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT77" t="inlineStr"/>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX77" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY77" t="inlineStr"/>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135192123</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>135192124</v>
+      </c>
+      <c r="B78" t="n">
+        <v>58006</v>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E78" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr"/>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P78" t="inlineStr">
+        <is>
+          <t>Höbrännflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q78" t="n">
+        <v>469109</v>
+      </c>
+      <c r="R78" t="n">
+        <v>7077945</v>
+      </c>
+      <c r="S78" t="n">
+        <v>10</v>
+      </c>
+      <c r="T78" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U78" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V78" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W78" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y78" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="Z78" t="inlineStr">
+        <is>
+          <t>12:12</t>
+        </is>
+      </c>
+      <c r="AA78" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="AB78" t="inlineStr">
+        <is>
+          <t>12:12</t>
+        </is>
+      </c>
+      <c r="AC78" t="inlineStr">
+        <is>
+          <t>färska ringhack</t>
+        </is>
+      </c>
+      <c r="AD78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT78" t="inlineStr"/>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX78" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY78" t="inlineStr"/>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135192124</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>135192125</v>
+      </c>
+      <c r="B79" t="n">
+        <v>58006</v>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E79" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr"/>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P79" t="inlineStr">
+        <is>
+          <t>Höbrännflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q79" t="n">
+        <v>469118</v>
+      </c>
+      <c r="R79" t="n">
+        <v>7077938</v>
+      </c>
+      <c r="S79" t="n">
+        <v>10</v>
+      </c>
+      <c r="T79" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U79" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V79" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W79" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y79" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="Z79" t="inlineStr">
+        <is>
+          <t>12:12</t>
+        </is>
+      </c>
+      <c r="AA79" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="AB79" t="inlineStr">
+        <is>
+          <t>12:12</t>
+        </is>
+      </c>
+      <c r="AC79" t="inlineStr">
+        <is>
+          <t>färska ringhack</t>
+        </is>
+      </c>
+      <c r="AD79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT79" t="inlineStr"/>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX79" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY79" t="inlineStr"/>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135192125</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>135192127</v>
+      </c>
+      <c r="B80" t="n">
+        <v>58006</v>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E80" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr"/>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P80" t="inlineStr">
+        <is>
+          <t>Höbrännflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q80" t="n">
+        <v>469140</v>
+      </c>
+      <c r="R80" t="n">
+        <v>7077913</v>
+      </c>
+      <c r="S80" t="n">
+        <v>10</v>
+      </c>
+      <c r="T80" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U80" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V80" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W80" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y80" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="Z80" t="inlineStr">
+        <is>
+          <t>12:13</t>
+        </is>
+      </c>
+      <c r="AA80" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="AB80" t="inlineStr">
+        <is>
+          <t>12:13</t>
+        </is>
+      </c>
+      <c r="AC80" t="inlineStr">
+        <is>
+          <t>färska ringhack</t>
+        </is>
+      </c>
+      <c r="AD80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT80" t="inlineStr"/>
+      <c r="AW80" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX80" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY80" t="inlineStr"/>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135192127</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>135192128</v>
+      </c>
+      <c r="B81" t="n">
+        <v>58006</v>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E81" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr"/>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P81" t="inlineStr">
+        <is>
+          <t>Höbrännflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q81" t="n">
+        <v>469149</v>
+      </c>
+      <c r="R81" t="n">
+        <v>7077895</v>
+      </c>
+      <c r="S81" t="n">
+        <v>10</v>
+      </c>
+      <c r="T81" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U81" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V81" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W81" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y81" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="Z81" t="inlineStr">
+        <is>
+          <t>12:14</t>
+        </is>
+      </c>
+      <c r="AA81" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="AB81" t="inlineStr">
+        <is>
+          <t>12:14</t>
+        </is>
+      </c>
+      <c r="AC81" t="inlineStr">
+        <is>
+          <t>färska ringhack</t>
+        </is>
+      </c>
+      <c r="AD81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT81" t="inlineStr"/>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX81" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY81" t="inlineStr"/>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135192128</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>135192130</v>
+      </c>
+      <c r="B82" t="n">
+        <v>58006</v>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E82" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr"/>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P82" t="inlineStr">
+        <is>
+          <t>Höbrännflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q82" t="n">
+        <v>469158</v>
+      </c>
+      <c r="R82" t="n">
+        <v>7077852</v>
+      </c>
+      <c r="S82" t="n">
+        <v>10</v>
+      </c>
+      <c r="T82" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U82" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V82" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W82" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y82" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="Z82" t="inlineStr">
+        <is>
+          <t>12:15</t>
+        </is>
+      </c>
+      <c r="AA82" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="AB82" t="inlineStr">
+        <is>
+          <t>12:15</t>
+        </is>
+      </c>
+      <c r="AC82" t="inlineStr">
+        <is>
+          <t>färska ringhack</t>
+        </is>
+      </c>
+      <c r="AD82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT82" t="inlineStr"/>
+      <c r="AW82" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX82" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY82" t="inlineStr"/>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135192130</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>135192131</v>
+      </c>
+      <c r="B83" t="n">
+        <v>58006</v>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E83" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr"/>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P83" t="inlineStr">
+        <is>
+          <t>Höbrännflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q83" t="n">
+        <v>469166</v>
+      </c>
+      <c r="R83" t="n">
+        <v>7077841</v>
+      </c>
+      <c r="S83" t="n">
+        <v>10</v>
+      </c>
+      <c r="T83" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U83" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V83" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W83" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y83" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="Z83" t="inlineStr">
+        <is>
+          <t>12:16</t>
+        </is>
+      </c>
+      <c r="AA83" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="AB83" t="inlineStr">
+        <is>
+          <t>12:16</t>
+        </is>
+      </c>
+      <c r="AC83" t="inlineStr">
+        <is>
+          <t>färska ringhack</t>
+        </is>
+      </c>
+      <c r="AD83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT83" t="inlineStr"/>
+      <c r="AW83" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX83" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY83" t="inlineStr"/>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135192131</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>135192132</v>
+      </c>
+      <c r="B84" t="n">
+        <v>58006</v>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E84" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr"/>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P84" t="inlineStr">
+        <is>
+          <t>Höbrännflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q84" t="n">
+        <v>469163</v>
+      </c>
+      <c r="R84" t="n">
+        <v>7077822</v>
+      </c>
+      <c r="S84" t="n">
+        <v>10</v>
+      </c>
+      <c r="T84" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U84" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V84" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W84" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y84" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="Z84" t="inlineStr">
+        <is>
+          <t>12:17</t>
+        </is>
+      </c>
+      <c r="AA84" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="AB84" t="inlineStr">
+        <is>
+          <t>12:17</t>
+        </is>
+      </c>
+      <c r="AC84" t="inlineStr">
+        <is>
+          <t>färska ringhack</t>
+        </is>
+      </c>
+      <c r="AD84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT84" t="inlineStr"/>
+      <c r="AW84" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX84" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY84" t="inlineStr"/>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135192132</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>135192134</v>
+      </c>
+      <c r="B85" t="n">
+        <v>58006</v>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E85" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr"/>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P85" t="inlineStr">
+        <is>
+          <t>Höbrännflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q85" t="n">
+        <v>469172</v>
+      </c>
+      <c r="R85" t="n">
+        <v>7077811</v>
+      </c>
+      <c r="S85" t="n">
+        <v>10</v>
+      </c>
+      <c r="T85" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U85" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V85" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W85" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y85" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="Z85" t="inlineStr">
+        <is>
+          <t>12:17</t>
+        </is>
+      </c>
+      <c r="AA85" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="AB85" t="inlineStr">
+        <is>
+          <t>12:17</t>
+        </is>
+      </c>
+      <c r="AC85" t="inlineStr">
+        <is>
+          <t>färska ringhack</t>
+        </is>
+      </c>
+      <c r="AD85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT85" t="inlineStr"/>
+      <c r="AW85" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX85" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY85" t="inlineStr"/>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135192134</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>135192135</v>
+      </c>
+      <c r="B86" t="n">
+        <v>58006</v>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E86" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr"/>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P86" t="inlineStr">
+        <is>
+          <t>Höbrännflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q86" t="n">
+        <v>469180</v>
+      </c>
+      <c r="R86" t="n">
+        <v>7077818</v>
+      </c>
+      <c r="S86" t="n">
+        <v>10</v>
+      </c>
+      <c r="T86" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U86" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V86" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W86" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y86" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="Z86" t="inlineStr">
+        <is>
+          <t>12:18</t>
+        </is>
+      </c>
+      <c r="AA86" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="AB86" t="inlineStr">
+        <is>
+          <t>12:18</t>
+        </is>
+      </c>
+      <c r="AC86" t="inlineStr">
+        <is>
+          <t>äldre ringhack</t>
+        </is>
+      </c>
+      <c r="AD86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT86" t="inlineStr"/>
+      <c r="AW86" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX86" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY86" t="inlineStr"/>
+      <c r="AZ86" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135192135</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>135192136</v>
+      </c>
+      <c r="B87" t="n">
+        <v>58006</v>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E87" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr"/>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P87" t="inlineStr">
+        <is>
+          <t>Höbrännflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q87" t="n">
+        <v>469176</v>
+      </c>
+      <c r="R87" t="n">
+        <v>7077799</v>
+      </c>
+      <c r="S87" t="n">
+        <v>10</v>
+      </c>
+      <c r="T87" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U87" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V87" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W87" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y87" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="Z87" t="inlineStr">
+        <is>
+          <t>12:19</t>
+        </is>
+      </c>
+      <c r="AA87" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="AB87" t="inlineStr">
+        <is>
+          <t>12:19</t>
+        </is>
+      </c>
+      <c r="AC87" t="inlineStr">
+        <is>
+          <t>färska ringhack</t>
+        </is>
+      </c>
+      <c r="AD87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT87" t="inlineStr"/>
+      <c r="AW87" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX87" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY87" t="inlineStr"/>
+      <c r="AZ87" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135192136</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>135192137</v>
+      </c>
+      <c r="B88" t="n">
+        <v>58006</v>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E88" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr"/>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P88" t="inlineStr">
+        <is>
+          <t>Höbrännflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q88" t="n">
+        <v>469181</v>
+      </c>
+      <c r="R88" t="n">
+        <v>7077798</v>
+      </c>
+      <c r="S88" t="n">
+        <v>10</v>
+      </c>
+      <c r="T88" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U88" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V88" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W88" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y88" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="Z88" t="inlineStr">
+        <is>
+          <t>12:20</t>
+        </is>
+      </c>
+      <c r="AA88" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="AB88" t="inlineStr">
+        <is>
+          <t>12:20</t>
+        </is>
+      </c>
+      <c r="AC88" t="inlineStr">
+        <is>
+          <t>färska ringhack</t>
+        </is>
+      </c>
+      <c r="AD88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT88" t="inlineStr"/>
+      <c r="AW88" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX88" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY88" t="inlineStr"/>
+      <c r="AZ88" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135192137</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>135192151</v>
+      </c>
+      <c r="B89" t="n">
+        <v>58006</v>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E89" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr"/>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P89" t="inlineStr">
+        <is>
+          <t>Höbrännflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q89" t="n">
+        <v>469393</v>
+      </c>
+      <c r="R89" t="n">
+        <v>7077846</v>
+      </c>
+      <c r="S89" t="n">
+        <v>10</v>
+      </c>
+      <c r="T89" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U89" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V89" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W89" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y89" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="Z89" t="inlineStr">
+        <is>
+          <t>12:42</t>
+        </is>
+      </c>
+      <c r="AA89" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="AB89" t="inlineStr">
+        <is>
+          <t>12:42</t>
+        </is>
+      </c>
+      <c r="AC89" t="inlineStr">
+        <is>
+          <t>äldre ringhack</t>
+        </is>
+      </c>
+      <c r="AD89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT89" t="inlineStr"/>
+      <c r="AW89" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX89" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY89" t="inlineStr"/>
+      <c r="AZ89" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135192151</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>135192152</v>
+      </c>
+      <c r="B90" t="n">
+        <v>58006</v>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E90" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr"/>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P90" t="inlineStr">
+        <is>
+          <t>Höbrännflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q90" t="n">
+        <v>469356</v>
+      </c>
+      <c r="R90" t="n">
+        <v>7077867</v>
+      </c>
+      <c r="S90" t="n">
+        <v>10</v>
+      </c>
+      <c r="T90" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U90" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V90" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W90" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y90" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="Z90" t="inlineStr">
+        <is>
+          <t>12:45</t>
+        </is>
+      </c>
+      <c r="AA90" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="AB90" t="inlineStr">
+        <is>
+          <t>12:45</t>
+        </is>
+      </c>
+      <c r="AC90" t="inlineStr">
+        <is>
+          <t>äldre ringhack</t>
+        </is>
+      </c>
+      <c r="AD90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT90" t="inlineStr"/>
+      <c r="AW90" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX90" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY90" t="inlineStr"/>
+      <c r="AZ90" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135192152</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>135192153</v>
+      </c>
+      <c r="B91" t="n">
+        <v>58006</v>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E91" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr"/>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P91" t="inlineStr">
+        <is>
+          <t>Höbrännflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q91" t="n">
+        <v>469347</v>
+      </c>
+      <c r="R91" t="n">
+        <v>7077869</v>
+      </c>
+      <c r="S91" t="n">
+        <v>10</v>
+      </c>
+      <c r="T91" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U91" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V91" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W91" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y91" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="Z91" t="inlineStr">
+        <is>
+          <t>12:46</t>
+        </is>
+      </c>
+      <c r="AA91" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="AB91" t="inlineStr">
+        <is>
+          <t>12:46</t>
+        </is>
+      </c>
+      <c r="AC91" t="inlineStr">
+        <is>
+          <t>äldre ringhack</t>
+        </is>
+      </c>
+      <c r="AD91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT91" t="inlineStr"/>
+      <c r="AW91" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX91" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY91" t="inlineStr"/>
+      <c r="AZ91" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135192153</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>135192157</v>
+      </c>
+      <c r="B92" t="n">
+        <v>58006</v>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E92" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr"/>
+      <c r="M92" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P92" t="inlineStr">
+        <is>
+          <t>Höbrännflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q92" t="n">
+        <v>469381</v>
+      </c>
+      <c r="R92" t="n">
+        <v>7077873</v>
+      </c>
+      <c r="S92" t="n">
+        <v>10</v>
+      </c>
+      <c r="T92" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U92" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V92" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W92" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y92" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="Z92" t="inlineStr">
+        <is>
+          <t>12:52</t>
+        </is>
+      </c>
+      <c r="AA92" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="AB92" t="inlineStr">
+        <is>
+          <t>12:52</t>
+        </is>
+      </c>
+      <c r="AC92" t="inlineStr">
+        <is>
+          <t>äldre ringhack</t>
+        </is>
+      </c>
+      <c r="AD92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT92" t="inlineStr"/>
+      <c r="AW92" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX92" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY92" t="inlineStr"/>
+      <c r="AZ92" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135192157</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>135192158</v>
+      </c>
+      <c r="B93" t="n">
+        <v>58006</v>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E93" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr"/>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P93" t="inlineStr">
+        <is>
+          <t>Höbrännflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q93" t="n">
+        <v>469401</v>
+      </c>
+      <c r="R93" t="n">
+        <v>7077887</v>
+      </c>
+      <c r="S93" t="n">
+        <v>10</v>
+      </c>
+      <c r="T93" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U93" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V93" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W93" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y93" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="Z93" t="inlineStr">
+        <is>
+          <t>12:54</t>
+        </is>
+      </c>
+      <c r="AA93" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="AB93" t="inlineStr">
+        <is>
+          <t>12:54</t>
+        </is>
+      </c>
+      <c r="AC93" t="inlineStr">
+        <is>
+          <t>äldre ringhack</t>
+        </is>
+      </c>
+      <c r="AD93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT93" t="inlineStr"/>
+      <c r="AW93" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX93" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY93" t="inlineStr"/>
+      <c r="AZ93" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135192158</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>135192161</v>
+      </c>
+      <c r="B94" t="n">
+        <v>58006</v>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E94" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr"/>
+      <c r="M94" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P94" t="inlineStr">
+        <is>
+          <t>Höbrännflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q94" t="n">
+        <v>469388</v>
+      </c>
+      <c r="R94" t="n">
+        <v>7077920</v>
+      </c>
+      <c r="S94" t="n">
+        <v>10</v>
+      </c>
+      <c r="T94" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U94" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V94" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W94" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y94" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="Z94" t="inlineStr">
+        <is>
+          <t>12:56</t>
+        </is>
+      </c>
+      <c r="AA94" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="AB94" t="inlineStr">
+        <is>
+          <t>12:56</t>
+        </is>
+      </c>
+      <c r="AC94" t="inlineStr">
+        <is>
+          <t>äldre ringhack</t>
+        </is>
+      </c>
+      <c r="AD94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT94" t="inlineStr"/>
+      <c r="AW94" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX94" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY94" t="inlineStr"/>
+      <c r="AZ94" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135192161</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>135192166</v>
+      </c>
+      <c r="B95" t="n">
+        <v>58006</v>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E95" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr"/>
+      <c r="P95" t="inlineStr">
+        <is>
+          <t>Höbrännflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q95" t="n">
+        <v>469249</v>
+      </c>
+      <c r="R95" t="n">
+        <v>7077922</v>
+      </c>
+      <c r="S95" t="n">
+        <v>10</v>
+      </c>
+      <c r="T95" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U95" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V95" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W95" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y95" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="Z95" t="inlineStr">
+        <is>
+          <t>13:07</t>
+        </is>
+      </c>
+      <c r="AA95" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="AB95" t="inlineStr">
+        <is>
+          <t>13:07</t>
+        </is>
+      </c>
+      <c r="AC95" t="inlineStr">
+        <is>
+          <t>ringhack</t>
+        </is>
+      </c>
+      <c r="AD95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT95" t="inlineStr"/>
+      <c r="AW95" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX95" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY95" t="inlineStr"/>
+      <c r="AZ95" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135192166</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="n">
+        <v>128346628</v>
+      </c>
+      <c r="B96" t="n">
+        <v>97989</v>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E96" t="n">
+        <v>221941</v>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>Plattlummer</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>Lycopodium complanatum</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr"/>
+      <c r="P96" t="inlineStr">
+        <is>
+          <t>Höbrännflon sö, Jmt</t>
+        </is>
+      </c>
+      <c r="Q96" t="n">
+        <v>468931</v>
+      </c>
+      <c r="R96" t="n">
+        <v>7077743</v>
+      </c>
+      <c r="S96" t="n">
+        <v>10</v>
+      </c>
+      <c r="T96" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U96" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V96" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W96" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y96" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AA96" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AD96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT96" t="inlineStr"/>
+      <c r="AW96" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX96" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY96" t="inlineStr"/>
+      <c r="AZ96" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/128346628</t>
         </is>
@@ -7037,6 +11663,44 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ91" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ92" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ93" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ94" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ95" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ96" r:id="rId95"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
